--- a/产品规格.xlsx
+++ b/产品规格.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1218" uniqueCount="883">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1301" uniqueCount="963">
   <si>
     <t>17.5*3*27</t>
   </si>
@@ -1987,12 +1987,6 @@
   </si>
   <si>
     <t>XC301</t>
-  </si>
-  <si>
-    <t>39梭多乐绵</t>
-  </si>
-  <si>
-    <t>16*4*39</t>
   </si>
   <si>
     <t>XC302</t>
@@ -2244,9 +2238,6 @@
     <t>100*150T8 4/2斜</t>
   </si>
   <si>
-    <t>17*4*225*44</t>
-  </si>
-  <si>
     <t>100D*150T800</t>
   </si>
   <si>
@@ -2289,9 +2280,6 @@
     <t>T400横条2*1</t>
   </si>
   <si>
-    <t>16*4+30</t>
-  </si>
-  <si>
     <t>T400横条1*4</t>
   </si>
   <si>
@@ -2337,9 +2325,6 @@
     <t>100D半光*35S-3/3斜</t>
   </si>
   <si>
-    <t>16*4*42</t>
-  </si>
-  <si>
     <t>100*35</t>
   </si>
   <si>
@@ -2397,9 +2382,6 @@
     <t>17*4*29</t>
   </si>
   <si>
-    <t>120*T800</t>
-  </si>
-  <si>
     <t>米克380</t>
   </si>
   <si>
@@ -2601,23 +2583,6 @@
     <t>100D*35S+150DT8</t>
   </si>
   <si>
-    <r>
-      <t>白坯3</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>00克</t>
-    </r>
-  </si>
-  <si>
     <t>天丝棉</t>
   </si>
   <si>
@@ -2651,9 +2616,6 @@
     <t>40S*35S</t>
   </si>
   <si>
-    <t>白坯370克</t>
-  </si>
-  <si>
     <t>210-钛金棉</t>
   </si>
   <si>
@@ -2685,6 +2647,270 @@
   </si>
   <si>
     <t>16*4*31</t>
+  </si>
+  <si>
+    <t>17*4*215*40</t>
+  </si>
+  <si>
+    <t>16*4+28</t>
+  </si>
+  <si>
+    <t>238克</t>
+  </si>
+  <si>
+    <t>16*4*40</t>
+  </si>
+  <si>
+    <t>120*150T800</t>
+  </si>
+  <si>
+    <t>120D扁平牛津</t>
+  </si>
+  <si>
+    <t>20*2*31</t>
+  </si>
+  <si>
+    <t>37梭多乐绵</t>
+  </si>
+  <si>
+    <t>16*4*37</t>
+  </si>
+  <si>
+    <t>白坯300克</t>
+  </si>
+  <si>
+    <t>16*4*44</t>
+  </si>
+  <si>
+    <t>白坯368克</t>
+  </si>
+  <si>
+    <t>XC325</t>
+  </si>
+  <si>
+    <t>XC326</t>
+  </si>
+  <si>
+    <t>XC327</t>
+  </si>
+  <si>
+    <t>XC328</t>
+  </si>
+  <si>
+    <t>XC329</t>
+  </si>
+  <si>
+    <t>XC330</t>
+  </si>
+  <si>
+    <t>XC331</t>
+  </si>
+  <si>
+    <t>XC332</t>
+  </si>
+  <si>
+    <t>XC333</t>
+  </si>
+  <si>
+    <t>XC334</t>
+  </si>
+  <si>
+    <t>XC335</t>
+  </si>
+  <si>
+    <t>XC336</t>
+  </si>
+  <si>
+    <t>XC337</t>
+  </si>
+  <si>
+    <t>XC338</t>
+  </si>
+  <si>
+    <t>XC339</t>
+  </si>
+  <si>
+    <t>XC340</t>
+  </si>
+  <si>
+    <t>XC341</t>
+  </si>
+  <si>
+    <t>XC342</t>
+  </si>
+  <si>
+    <t>XC343</t>
+  </si>
+  <si>
+    <t>XC344</t>
+  </si>
+  <si>
+    <t>XC345</t>
+  </si>
+  <si>
+    <t>XC346</t>
+  </si>
+  <si>
+    <t>XC347</t>
+  </si>
+  <si>
+    <t>XC348</t>
+  </si>
+  <si>
+    <t>XC349</t>
+  </si>
+  <si>
+    <t>XC350</t>
+  </si>
+  <si>
+    <t>XC351</t>
+  </si>
+  <si>
+    <t>XC352</t>
+  </si>
+  <si>
+    <t>XC353</t>
+  </si>
+  <si>
+    <t>XC354</t>
+  </si>
+  <si>
+    <t>XC355</t>
+  </si>
+  <si>
+    <t>XC356</t>
+  </si>
+  <si>
+    <t>XC357</t>
+  </si>
+  <si>
+    <t>XC358</t>
+  </si>
+  <si>
+    <t>XC359</t>
+  </si>
+  <si>
+    <t>XC360</t>
+  </si>
+  <si>
+    <t>XC361</t>
+  </si>
+  <si>
+    <t>XC362</t>
+  </si>
+  <si>
+    <t>XC363</t>
+  </si>
+  <si>
+    <t>XC364</t>
+  </si>
+  <si>
+    <t>XC365</t>
+  </si>
+  <si>
+    <t>XC366</t>
+  </si>
+  <si>
+    <t>XC367</t>
+  </si>
+  <si>
+    <t>XC368</t>
+  </si>
+  <si>
+    <t>XC369</t>
+  </si>
+  <si>
+    <t>XC370</t>
+  </si>
+  <si>
+    <t>XC371</t>
+  </si>
+  <si>
+    <t>XC372</t>
+  </si>
+  <si>
+    <t>XC373</t>
+  </si>
+  <si>
+    <t>XC374</t>
+  </si>
+  <si>
+    <t>XC375</t>
+  </si>
+  <si>
+    <t>XC376</t>
+  </si>
+  <si>
+    <t>XC377</t>
+  </si>
+  <si>
+    <t>XC378</t>
+  </si>
+  <si>
+    <t>XC379</t>
+  </si>
+  <si>
+    <t>XC380</t>
+  </si>
+  <si>
+    <t>XC381</t>
+  </si>
+  <si>
+    <t>XC382</t>
+  </si>
+  <si>
+    <t>XC383</t>
+  </si>
+  <si>
+    <t>XC384</t>
+  </si>
+  <si>
+    <t>XC385</t>
+  </si>
+  <si>
+    <t>XC386</t>
+  </si>
+  <si>
+    <t>XC387</t>
+  </si>
+  <si>
+    <t>XC388</t>
+  </si>
+  <si>
+    <t>XC389</t>
+  </si>
+  <si>
+    <t>XC390</t>
+  </si>
+  <si>
+    <t>XC391</t>
+  </si>
+  <si>
+    <t>XC392</t>
+  </si>
+  <si>
+    <t>XC393</t>
+  </si>
+  <si>
+    <t>XC394</t>
+  </si>
+  <si>
+    <t>XC395</t>
+  </si>
+  <si>
+    <t>XC396</t>
+  </si>
+  <si>
+    <t>XC397</t>
+  </si>
+  <si>
+    <t>XC398</t>
+  </si>
+  <si>
+    <t>XC399</t>
+  </si>
+  <si>
+    <t>XC400</t>
   </si>
 </sst>
 </file>
@@ -2942,7 +3168,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2973,221 +3199,230 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="11" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="11" fontId="4" fillId="6" borderId="1" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="11" fontId="4" fillId="6" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="12" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="13" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="12" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="11">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <alignment vertical="center"/>
+      <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="1" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="1" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="11" fontId="4" fillId="14" borderId="1" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="11" fontId="4" fillId="14" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="1" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="11" fontId="4" fillId="0" borderId="1" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="11" fontId="4" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="11" fontId="4" fillId="2" borderId="1" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="11" fontId="4" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="1" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="14" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="11" fontId="4" fillId="10" borderId="1" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="11" fontId="4" fillId="10" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -3501,7 +3736,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:M325"/>
+  <dimension ref="A1:M401"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="9" width="9" style="4"/>
@@ -3512,48 +3747,48 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
+        <v>693</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>694</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>695</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>696</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>697</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>698</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>699</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>700</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>701</v>
       </c>
-      <c r="H1" s="3" t="s">
-        <v>702</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>703</v>
-      </c>
       <c r="J1" s="5" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="9" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="C2" s="10" t="s">
         <v>0</v>
@@ -3573,13 +3808,13 @@
       </c>
       <c r="I2" s="11"/>
       <c r="J2" s="7" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="K2" s="7" t="s">
+        <v>702</v>
+      </c>
+      <c r="L2" s="8" t="s">
         <v>704</v>
-      </c>
-      <c r="L2" s="8" t="s">
-        <v>706</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -4246,7 +4481,7 @@
         <v>68</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="D29" s="10" t="s">
         <v>46</v>
@@ -4271,7 +4506,7 @@
         <v>70</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="D30" s="10" t="s">
         <v>46</v>
@@ -4859,7 +5094,7 @@
         <v>165</v>
       </c>
       <c r="H53" s="15">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="I53" s="11"/>
     </row>
@@ -4923,7 +5158,7 @@
         <v>137</v>
       </c>
       <c r="C56" s="13" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="D56" s="13" t="s">
         <v>135</v>
@@ -5638,7 +5873,7 @@
         <v>174</v>
       </c>
       <c r="H84" s="21">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="I84" s="11"/>
     </row>
@@ -6800,7 +7035,7 @@
         <v>330</v>
       </c>
       <c r="C131" s="24" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="D131" s="24" t="s">
         <v>148</v>
@@ -7419,7 +7654,7 @@
         <v>220</v>
       </c>
       <c r="H155" s="10">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="I155" s="11"/>
     </row>
@@ -7559,7 +7794,7 @@
         <v>412</v>
       </c>
       <c r="B161" s="22" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="C161" s="22" t="s">
         <v>413</v>
@@ -7640,7 +7875,7 @@
         <v>421</v>
       </c>
       <c r="B164" s="22" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="C164" s="22" t="s">
         <v>422</v>
@@ -7658,7 +7893,7 @@
         <v>208</v>
       </c>
       <c r="H164" s="22">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="I164" s="11"/>
     </row>
@@ -7667,10 +7902,10 @@
         <v>423</v>
       </c>
       <c r="B165" s="22" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="C165" s="22" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="D165" s="22" t="s">
         <v>414</v>
@@ -7707,13 +7942,13 @@
         <v>425</v>
       </c>
       <c r="B167" s="18" t="s">
+        <v>715</v>
+      </c>
+      <c r="C167" s="18" t="s">
+        <v>716</v>
+      </c>
+      <c r="D167" s="18" t="s">
         <v>717</v>
-      </c>
-      <c r="C167" s="18" t="s">
-        <v>718</v>
-      </c>
-      <c r="D167" s="18" t="s">
-        <v>719</v>
       </c>
       <c r="E167" s="18">
         <v>80</v>
@@ -7725,7 +7960,7 @@
         <v>220</v>
       </c>
       <c r="H167" s="18">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I167" s="11"/>
     </row>
@@ -7734,13 +7969,13 @@
         <v>426</v>
       </c>
       <c r="B168" s="18" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="C168" s="18" t="s">
         <v>417</v>
       </c>
       <c r="D168" s="18" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="E168" s="18">
         <v>110</v>
@@ -7752,7 +7987,7 @@
         <v>208</v>
       </c>
       <c r="H168" s="18">
-        <v>4.2</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="I168" s="11"/>
     </row>
@@ -7761,7 +7996,7 @@
         <v>427</v>
       </c>
       <c r="B169" s="18" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="C169" s="18" t="s">
         <v>428</v>
@@ -7779,7 +8014,7 @@
         <v>208</v>
       </c>
       <c r="H169" s="18">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="I169" s="32"/>
     </row>
@@ -7788,7 +8023,7 @@
         <v>430</v>
       </c>
       <c r="B170" s="18" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="C170" s="18" t="s">
         <v>431</v>
@@ -7815,7 +8050,7 @@
         <v>432</v>
       </c>
       <c r="B171" s="18" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="C171" s="18" t="s">
         <v>238</v>
@@ -7833,7 +8068,7 @@
         <v>215</v>
       </c>
       <c r="H171" s="32">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="I171" s="32"/>
     </row>
@@ -7869,7 +8104,7 @@
         <v>435</v>
       </c>
       <c r="B173" s="18" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="C173" s="18" t="s">
         <v>436</v>
@@ -7896,7 +8131,7 @@
         <v>438</v>
       </c>
       <c r="B174" s="18" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="C174" s="18" t="s">
         <v>439</v>
@@ -7923,7 +8158,7 @@
         <v>440</v>
       </c>
       <c r="B175" s="18" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="C175" s="18" t="s">
         <v>32</v>
@@ -7995,7 +8230,7 @@
         <v>215</v>
       </c>
       <c r="H177" s="18">
-        <v>4.7</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="I177" s="32"/>
     </row>
@@ -8004,7 +8239,7 @@
         <v>446</v>
       </c>
       <c r="B178" s="18" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="C178" s="18" t="s">
         <v>420</v>
@@ -8022,7 +8257,7 @@
         <v>208</v>
       </c>
       <c r="H178" s="18">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="I178" s="32"/>
     </row>
@@ -8049,7 +8284,7 @@
         <v>208</v>
       </c>
       <c r="H179" s="18">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="I179" s="32"/>
     </row>
@@ -8058,7 +8293,7 @@
         <v>450</v>
       </c>
       <c r="B180" s="18" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="C180" s="18" t="s">
         <v>451</v>
@@ -8076,7 +8311,7 @@
         <v>208</v>
       </c>
       <c r="H180" s="18">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="I180" s="32"/>
     </row>
@@ -8085,7 +8320,7 @@
         <v>452</v>
       </c>
       <c r="B181" s="18" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="C181" s="18" t="s">
         <v>445</v>
@@ -8112,7 +8347,7 @@
         <v>453</v>
       </c>
       <c r="B182" s="34" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="C182" s="34" t="s">
         <v>309</v>
@@ -8139,7 +8374,7 @@
         <v>455</v>
       </c>
       <c r="B183" s="34" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="C183" s="34" t="s">
         <v>309</v>
@@ -8193,7 +8428,7 @@
         <v>460</v>
       </c>
       <c r="B185" s="18" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="C185" s="18" t="s">
         <v>445</v>
@@ -8220,7 +8455,7 @@
         <v>461</v>
       </c>
       <c r="B186" s="34" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="C186" s="34" t="s">
         <v>309</v>
@@ -8244,7 +8479,7 @@
     </row>
     <row r="187" spans="1:9">
       <c r="A187" s="9" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="B187" s="18" t="s">
         <v>442</v>
@@ -8265,7 +8500,7 @@
         <v>215</v>
       </c>
       <c r="H187" s="18">
-        <v>4.5999999999999996</v>
+        <v>4.5</v>
       </c>
       <c r="I187" s="11"/>
     </row>
@@ -8274,13 +8509,13 @@
         <v>462</v>
       </c>
       <c r="B188" s="18" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="C188" s="18" t="s">
         <v>272</v>
       </c>
       <c r="D188" s="18" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="E188" s="18">
         <v>110</v>
@@ -8301,7 +8536,7 @@
         <v>463</v>
       </c>
       <c r="B189" s="18" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="C189" s="18" t="s">
         <v>445</v>
@@ -8319,7 +8554,7 @@
         <v>215</v>
       </c>
       <c r="H189" s="18">
-        <v>4.5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="I189" s="11"/>
     </row>
@@ -8328,25 +8563,25 @@
         <v>464</v>
       </c>
       <c r="B190" s="10" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="C190" s="10" t="s">
-        <v>740</v>
+        <v>875</v>
       </c>
       <c r="D190" s="10" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="E190" s="11">
-        <v>177</v>
+        <v>152</v>
       </c>
       <c r="F190" s="12">
-        <v>263</v>
+        <v>245</v>
       </c>
       <c r="G190" s="11">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="H190" s="10">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="I190" s="11"/>
     </row>
@@ -8355,7 +8590,7 @@
         <v>465</v>
       </c>
       <c r="B191" s="18" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="C191" s="18" t="s">
         <v>238</v>
@@ -8408,7 +8643,7 @@
         <v>468</v>
       </c>
       <c r="B194" s="41" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="C194" s="42" t="s">
         <v>385</v>
@@ -8435,7 +8670,7 @@
         <v>469</v>
       </c>
       <c r="B195" s="41" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="C195" s="42" t="s">
         <v>470</v>
@@ -8462,10 +8697,10 @@
         <v>471</v>
       </c>
       <c r="B196" s="45" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="C196" s="45" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="D196" s="45" t="s">
         <v>472</v>
@@ -8489,7 +8724,7 @@
         <v>473</v>
       </c>
       <c r="B197" s="45" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="C197" s="45" t="s">
         <v>389</v>
@@ -8507,7 +8742,7 @@
         <v>215</v>
       </c>
       <c r="H197" s="45">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="I197" s="37"/>
     </row>
@@ -8516,7 +8751,7 @@
         <v>474</v>
       </c>
       <c r="B198" s="45" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="C198" s="45" t="s">
         <v>475</v>
@@ -8534,7 +8769,7 @@
         <v>215</v>
       </c>
       <c r="H198" s="45">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I198" s="37"/>
     </row>
@@ -8543,13 +8778,13 @@
         <v>477</v>
       </c>
       <c r="B199" s="45" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="C199" s="45" t="s">
         <v>401</v>
       </c>
       <c r="D199" s="45" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="E199" s="45">
         <v>95</v>
@@ -8561,7 +8796,7 @@
         <v>215</v>
       </c>
       <c r="H199" s="45">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="I199" s="37"/>
     </row>
@@ -8727,7 +8962,7 @@
         <v>496</v>
       </c>
       <c r="C208" s="10" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="D208" s="10" t="s">
         <v>39</v>
@@ -8790,7 +9025,7 @@
         <v>501</v>
       </c>
       <c r="C211" s="10" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="D211" s="10" t="s">
         <v>39</v>
@@ -8812,10 +9047,10 @@
         <v>502</v>
       </c>
       <c r="B212" s="35" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="C212" s="35" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="D212" s="35" t="s">
         <v>144</v>
@@ -8855,7 +9090,7 @@
         <v>178</v>
       </c>
       <c r="H213" s="10">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="I213" s="37"/>
     </row>
@@ -8867,7 +9102,7 @@
         <v>507</v>
       </c>
       <c r="C214" s="35" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="D214" s="35" t="s">
         <v>144</v>
@@ -8980,19 +9215,19 @@
         <v>519</v>
       </c>
       <c r="B220" s="10" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="C220" s="10" t="s">
-        <v>755</v>
+        <v>876</v>
       </c>
       <c r="D220" s="49" t="s">
         <v>520</v>
       </c>
       <c r="E220" s="10">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="F220" s="9">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G220" s="11">
         <v>215</v>
@@ -9000,17 +9235,19 @@
       <c r="H220" s="10">
         <v>3.5</v>
       </c>
-      <c r="I220" s="11"/>
+      <c r="I220" s="11" t="s">
+        <v>877</v>
+      </c>
     </row>
     <row r="221" spans="1:9">
       <c r="A221" s="9" t="s">
         <v>521</v>
       </c>
       <c r="B221" s="10" t="s">
-        <v>756</v>
+        <v>752</v>
       </c>
       <c r="C221" s="10" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
       <c r="D221" s="49" t="s">
         <v>4</v>
@@ -9028,7 +9265,7 @@
         <v>3.3</v>
       </c>
       <c r="I221" s="37" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
     </row>
     <row r="222" spans="1:9">
@@ -9036,10 +9273,10 @@
         <v>522</v>
       </c>
       <c r="B222" s="10" t="s">
-        <v>759</v>
+        <v>755</v>
       </c>
       <c r="C222" s="10" t="s">
-        <v>760</v>
+        <v>756</v>
       </c>
       <c r="D222" s="49" t="s">
         <v>520</v>
@@ -9090,13 +9327,13 @@
         <v>526</v>
       </c>
       <c r="B224" s="35" t="s">
-        <v>761</v>
+        <v>757</v>
       </c>
       <c r="C224" s="35" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="D224" s="35" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="E224" s="35">
         <v>120</v>
@@ -9135,7 +9372,7 @@
         <v>215</v>
       </c>
       <c r="H225" s="35">
-        <v>4.9000000000000004</v>
+        <v>4.8</v>
       </c>
       <c r="I225" s="11"/>
     </row>
@@ -9144,7 +9381,7 @@
         <v>530</v>
       </c>
       <c r="B226" s="35" t="s">
-        <v>764</v>
+        <v>760</v>
       </c>
       <c r="C226" s="35" t="s">
         <v>238</v>
@@ -9162,7 +9399,7 @@
         <v>215</v>
       </c>
       <c r="H226" s="35">
-        <v>4.5999999999999996</v>
+        <v>4.5</v>
       </c>
       <c r="I226" s="37"/>
     </row>
@@ -9171,7 +9408,7 @@
         <v>531</v>
       </c>
       <c r="B227" s="35" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
       <c r="C227" s="35" t="s">
         <v>238</v>
@@ -9189,7 +9426,7 @@
         <v>215</v>
       </c>
       <c r="H227" s="35">
-        <v>4.5999999999999996</v>
+        <v>4.5</v>
       </c>
       <c r="I227" s="37"/>
     </row>
@@ -9216,7 +9453,7 @@
         <v>215</v>
       </c>
       <c r="H228" s="35">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="I228" s="11"/>
     </row>
@@ -9243,7 +9480,7 @@
         <v>215</v>
       </c>
       <c r="H229" s="35">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="I229" s="11"/>
     </row>
@@ -9270,7 +9507,7 @@
         <v>215</v>
       </c>
       <c r="H230" s="51">
-        <v>5</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="I230" s="11"/>
     </row>
@@ -9327,29 +9564,29 @@
       <c r="A234" s="9" t="s">
         <v>544</v>
       </c>
-      <c r="B234" s="36" t="s">
-        <v>766</v>
-      </c>
-      <c r="C234" s="36" t="s">
-        <v>767</v>
+      <c r="B234" s="52" t="s">
+        <v>762</v>
+      </c>
+      <c r="C234" s="52" t="s">
+        <v>763</v>
       </c>
       <c r="D234" s="50" t="s">
-        <v>768</v>
-      </c>
-      <c r="E234" s="36">
+        <v>764</v>
+      </c>
+      <c r="E234" s="52">
         <v>190</v>
       </c>
       <c r="F234" s="36">
         <v>275</v>
       </c>
-      <c r="G234" s="52">
+      <c r="G234" s="53">
         <v>215</v>
       </c>
-      <c r="H234" s="36">
-        <v>6</v>
-      </c>
-      <c r="I234" s="53" t="s">
-        <v>769</v>
+      <c r="H234" s="52">
+        <v>5.8</v>
+      </c>
+      <c r="I234" s="54" t="s">
+        <v>765</v>
       </c>
     </row>
     <row r="235" spans="1:9">
@@ -9357,13 +9594,13 @@
         <v>545</v>
       </c>
       <c r="B235" s="51" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
       <c r="C235" s="51" t="s">
-        <v>771</v>
+        <v>878</v>
       </c>
       <c r="D235" s="51" t="s">
-        <v>772</v>
+        <v>767</v>
       </c>
       <c r="E235" s="51">
         <v>155</v>
@@ -9371,13 +9608,13 @@
       <c r="F235" s="36">
         <v>230</v>
       </c>
-      <c r="G235" s="54">
-        <v>218</v>
+      <c r="G235" s="55">
+        <v>215</v>
       </c>
       <c r="H235" s="51">
-        <v>4.5</v>
-      </c>
-      <c r="I235" s="54" t="s">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="I235" s="55" t="s">
         <v>546</v>
       </c>
     </row>
@@ -9386,13 +9623,13 @@
         <v>547</v>
       </c>
       <c r="B236" s="51" t="s">
-        <v>773</v>
+        <v>768</v>
       </c>
       <c r="C236" s="51" t="s">
-        <v>774</v>
+        <v>769</v>
       </c>
       <c r="D236" s="51" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="E236" s="51">
         <v>170</v>
@@ -9400,13 +9637,13 @@
       <c r="F236" s="36">
         <v>250</v>
       </c>
-      <c r="G236" s="54">
+      <c r="G236" s="55">
         <v>220</v>
       </c>
       <c r="H236" s="51">
         <v>5</v>
       </c>
-      <c r="I236" s="53" t="s">
+      <c r="I236" s="54" t="s">
         <v>548</v>
       </c>
     </row>
@@ -9415,13 +9652,13 @@
         <v>549</v>
       </c>
       <c r="B237" s="51" t="s">
-        <v>776</v>
+        <v>771</v>
       </c>
       <c r="C237" s="51" t="s">
         <v>550</v>
       </c>
       <c r="D237" s="51" t="s">
-        <v>777</v>
+        <v>772</v>
       </c>
       <c r="E237" s="51">
         <v>155</v>
@@ -9429,13 +9666,13 @@
       <c r="F237" s="36">
         <v>230</v>
       </c>
-      <c r="G237" s="54">
+      <c r="G237" s="55">
         <v>218</v>
       </c>
       <c r="H237" s="51">
         <v>4.8</v>
       </c>
-      <c r="I237" s="54" t="s">
+      <c r="I237" s="55" t="s">
         <v>546</v>
       </c>
     </row>
@@ -9457,28 +9694,28 @@
         <v>552</v>
       </c>
       <c r="B239" s="51" t="s">
-        <v>778</v>
+        <v>773</v>
       </c>
       <c r="C239" s="51" t="s">
-        <v>779</v>
+        <v>774</v>
       </c>
       <c r="D239" s="51" t="s">
-        <v>775</v>
-      </c>
-      <c r="E239" s="36">
+        <v>770</v>
+      </c>
+      <c r="E239" s="52">
         <v>180</v>
       </c>
       <c r="F239" s="36">
         <v>270</v>
       </c>
-      <c r="G239" s="54">
+      <c r="G239" s="55">
         <v>220</v>
       </c>
       <c r="H239" s="51">
         <v>5.5</v>
       </c>
-      <c r="I239" s="53" t="s">
-        <v>780</v>
+      <c r="I239" s="54" t="s">
+        <v>775</v>
       </c>
     </row>
     <row r="240" spans="1:9">
@@ -9486,28 +9723,28 @@
         <v>553</v>
       </c>
       <c r="B240" s="51" t="s">
-        <v>781</v>
+        <v>776</v>
       </c>
       <c r="C240" s="51" t="s">
-        <v>782</v>
+        <v>777</v>
       </c>
       <c r="D240" s="51" t="s">
-        <v>775</v>
-      </c>
-      <c r="E240" s="36">
+        <v>770</v>
+      </c>
+      <c r="E240" s="52">
         <v>190</v>
       </c>
       <c r="F240" s="36">
         <v>270</v>
       </c>
-      <c r="G240" s="54">
+      <c r="G240" s="55">
         <v>225</v>
       </c>
       <c r="H240" s="35">
         <v>5.7</v>
       </c>
-      <c r="I240" s="53" t="s">
-        <v>783</v>
+      <c r="I240" s="54" t="s">
+        <v>778</v>
       </c>
     </row>
     <row r="241" spans="1:9">
@@ -9515,10 +9752,10 @@
         <v>554</v>
       </c>
       <c r="B241" s="51" t="s">
-        <v>784</v>
+        <v>779</v>
       </c>
       <c r="C241" s="51" t="s">
-        <v>785</v>
+        <v>780</v>
       </c>
       <c r="D241" s="11" t="s">
         <v>555</v>
@@ -9529,14 +9766,14 @@
       <c r="F241" s="36">
         <v>230</v>
       </c>
-      <c r="G241" s="54">
+      <c r="G241" s="55">
         <v>220</v>
       </c>
-      <c r="H241" s="36">
+      <c r="H241" s="52">
         <v>5.2</v>
       </c>
-      <c r="I241" s="54" t="s">
-        <v>786</v>
+      <c r="I241" s="55" t="s">
+        <v>781</v>
       </c>
     </row>
     <row r="242" spans="1:9">
@@ -9544,27 +9781,27 @@
         <v>556</v>
       </c>
       <c r="B242" s="51" t="s">
-        <v>787</v>
+        <v>782</v>
       </c>
       <c r="C242" s="51" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="D242" s="51" t="s">
-        <v>775</v>
-      </c>
-      <c r="E242" s="36">
+        <v>770</v>
+      </c>
+      <c r="E242" s="52">
         <v>160</v>
       </c>
       <c r="F242" s="36">
         <v>250</v>
       </c>
-      <c r="G242" s="54">
+      <c r="G242" s="55">
         <v>225</v>
       </c>
       <c r="H242" s="35">
         <v>4.9000000000000004</v>
       </c>
-      <c r="I242" s="53" t="s">
+      <c r="I242" s="54" t="s">
         <v>548</v>
       </c>
     </row>
@@ -9573,42 +9810,54 @@
         <v>557</v>
       </c>
       <c r="B243" s="51" t="s">
-        <v>789</v>
+        <v>784</v>
       </c>
       <c r="C243" s="51" t="s">
-        <v>790</v>
+        <v>785</v>
       </c>
       <c r="D243" s="51" t="s">
-        <v>791</v>
-      </c>
-      <c r="E243" s="36">
+        <v>879</v>
+      </c>
+      <c r="E243" s="52">
         <v>190</v>
       </c>
       <c r="F243" s="36">
         <v>280</v>
       </c>
-      <c r="G243" s="54">
+      <c r="G243" s="55">
         <v>220</v>
       </c>
       <c r="H243" s="35">
-        <v>5.2</v>
-      </c>
-      <c r="I243" s="53" t="s">
-        <v>792</v>
+        <v>5.6</v>
+      </c>
+      <c r="I243" s="54" t="s">
+        <v>786</v>
       </c>
     </row>
     <row r="244" spans="1:9">
       <c r="A244" s="9" t="s">
         <v>558</v>
       </c>
-      <c r="B244" s="38"/>
-      <c r="C244" s="38"/>
-      <c r="D244" s="38"/>
-      <c r="E244" s="38"/>
+      <c r="B244" s="51" t="s">
+        <v>880</v>
+      </c>
+      <c r="C244" s="51" t="s">
+        <v>881</v>
+      </c>
+      <c r="D244" s="51" t="s">
+        <v>879</v>
+      </c>
+      <c r="E244" s="51">
+        <v>150</v>
+      </c>
       <c r="F244" s="38"/>
-      <c r="G244" s="38"/>
-      <c r="H244" s="38"/>
-      <c r="I244" s="53"/>
+      <c r="G244" s="55">
+        <v>220</v>
+      </c>
+      <c r="H244" s="35">
+        <v>3.9</v>
+      </c>
+      <c r="I244" s="54"/>
     </row>
     <row r="245" spans="1:9">
       <c r="A245" s="9" t="s">
@@ -9628,10 +9877,10 @@
         <v>560</v>
       </c>
       <c r="B246" s="18" t="s">
-        <v>793</v>
+        <v>787</v>
       </c>
       <c r="C246" s="18" t="s">
-        <v>794</v>
+        <v>788</v>
       </c>
       <c r="D246" s="33" t="s">
         <v>429</v>
@@ -9655,7 +9904,7 @@
         <v>561</v>
       </c>
       <c r="B247" s="18" t="s">
-        <v>795</v>
+        <v>789</v>
       </c>
       <c r="C247" s="18" t="s">
         <v>529</v>
@@ -9675,14 +9924,14 @@
       <c r="H247" s="18">
         <v>4.3</v>
       </c>
-      <c r="I247" s="55"/>
+      <c r="I247" s="56"/>
     </row>
     <row r="248" spans="1:9">
       <c r="A248" s="31" t="s">
         <v>562</v>
       </c>
       <c r="B248" s="18" t="s">
-        <v>796</v>
+        <v>790</v>
       </c>
       <c r="C248" s="18" t="s">
         <v>563</v>
@@ -9702,14 +9951,14 @@
       <c r="H248" s="18">
         <v>5.2</v>
       </c>
-      <c r="I248" s="56"/>
+      <c r="I248" s="57"/>
     </row>
     <row r="249" spans="1:9">
       <c r="A249" s="31" t="s">
         <v>564</v>
       </c>
       <c r="B249" s="18" t="s">
-        <v>797</v>
+        <v>791</v>
       </c>
       <c r="C249" s="18" t="s">
         <v>439</v>
@@ -9720,7 +9969,7 @@
       <c r="E249" s="32">
         <v>105</v>
       </c>
-      <c r="F249" s="57">
+      <c r="F249" s="58">
         <v>150</v>
       </c>
       <c r="G249" s="32">
@@ -9729,14 +9978,14 @@
       <c r="H249" s="32">
         <v>3.4</v>
       </c>
-      <c r="I249" s="56"/>
+      <c r="I249" s="57"/>
     </row>
     <row r="250" spans="1:9">
       <c r="A250" s="31" t="s">
         <v>565</v>
       </c>
       <c r="B250" s="18" t="s">
-        <v>798</v>
+        <v>792</v>
       </c>
       <c r="C250" s="18" t="s">
         <v>153</v>
@@ -9747,11 +9996,11 @@
       <c r="E250" s="32">
         <v>108</v>
       </c>
-      <c r="F250" s="57">
+      <c r="F250" s="58">
         <v>150</v>
       </c>
       <c r="G250" s="32">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="H250" s="32">
         <v>3.4</v>
@@ -9763,7 +10012,7 @@
         <v>566</v>
       </c>
       <c r="B251" s="18" t="s">
-        <v>799</v>
+        <v>793</v>
       </c>
       <c r="C251" s="18" t="s">
         <v>567</v>
@@ -9774,14 +10023,14 @@
       <c r="E251" s="18">
         <v>116</v>
       </c>
-      <c r="F251" s="57">
+      <c r="F251" s="58">
         <v>180</v>
       </c>
       <c r="G251" s="32">
         <v>215</v>
       </c>
       <c r="H251" s="18">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I251" s="32"/>
     </row>
@@ -9790,7 +10039,7 @@
         <v>568</v>
       </c>
       <c r="B252" s="18" t="s">
-        <v>800</v>
+        <v>794</v>
       </c>
       <c r="C252" s="18" t="s">
         <v>439</v>
@@ -9801,7 +10050,7 @@
       <c r="E252" s="18">
         <v>105</v>
       </c>
-      <c r="F252" s="57">
+      <c r="F252" s="58">
         <v>155</v>
       </c>
       <c r="G252" s="32">
@@ -9817,7 +10066,7 @@
         <v>569</v>
       </c>
       <c r="B253" s="18" t="s">
-        <v>801</v>
+        <v>795</v>
       </c>
       <c r="C253" s="18" t="s">
         <v>567</v>
@@ -9828,14 +10077,14 @@
       <c r="E253" s="18">
         <v>116</v>
       </c>
-      <c r="F253" s="57">
+      <c r="F253" s="58">
         <v>180</v>
       </c>
       <c r="G253" s="32">
         <v>215</v>
       </c>
       <c r="H253" s="18">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I253" s="32"/>
     </row>
@@ -9844,19 +10093,19 @@
         <v>570</v>
       </c>
       <c r="B254" s="18" t="s">
-        <v>802</v>
+        <v>796</v>
       </c>
       <c r="C254" s="18" t="s">
-        <v>803</v>
+        <v>797</v>
       </c>
       <c r="D254" s="18" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="E254" s="18">
         <v>190</v>
       </c>
       <c r="F254" s="31">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="G254" s="32">
         <v>215</v>
@@ -9864,8 +10113,8 @@
       <c r="H254" s="18">
         <v>5.5</v>
       </c>
-      <c r="I254" s="53" t="s">
-        <v>769</v>
+      <c r="I254" s="54" t="s">
+        <v>786</v>
       </c>
     </row>
     <row r="255" spans="1:9">
@@ -9873,7 +10122,7 @@
         <v>571</v>
       </c>
       <c r="B255" s="18" t="s">
-        <v>804</v>
+        <v>798</v>
       </c>
       <c r="C255" s="18" t="s">
         <v>572</v>
@@ -9881,46 +10130,46 @@
       <c r="D255" s="18" t="s">
         <v>429</v>
       </c>
-      <c r="E255" s="58">
+      <c r="E255" s="59">
         <v>88</v>
       </c>
       <c r="F255" s="31">
         <v>130</v>
       </c>
-      <c r="G255" s="55">
+      <c r="G255" s="56">
         <v>208</v>
       </c>
-      <c r="H255" s="58">
-        <v>3.1</v>
-      </c>
-      <c r="I255" s="53"/>
+      <c r="H255" s="59">
+        <v>3</v>
+      </c>
+      <c r="I255" s="54"/>
     </row>
     <row r="256" spans="1:9">
       <c r="A256" s="9" t="s">
         <v>573</v>
       </c>
-      <c r="B256" s="36" t="s">
-        <v>805</v>
+      <c r="B256" s="52" t="s">
+        <v>799</v>
       </c>
       <c r="C256" s="18" t="s">
         <v>333</v>
       </c>
       <c r="D256" s="50" t="s">
-        <v>806</v>
-      </c>
-      <c r="E256" s="36">
+        <v>800</v>
+      </c>
+      <c r="E256" s="52">
         <v>185</v>
       </c>
       <c r="F256" s="36">
-        <v>260</v>
-      </c>
-      <c r="G256" s="52">
+        <v>250</v>
+      </c>
+      <c r="G256" s="53">
         <v>215</v>
       </c>
-      <c r="H256" s="59">
+      <c r="H256" s="60">
         <v>5.3</v>
       </c>
-      <c r="I256" s="53" t="s">
+      <c r="I256" s="54" t="s">
         <v>548</v>
       </c>
     </row>
@@ -9929,7 +10178,7 @@
         <v>574</v>
       </c>
       <c r="B257" s="36" t="s">
-        <v>807</v>
+        <v>801</v>
       </c>
       <c r="C257" s="36" t="s">
         <v>321</v>
@@ -9946,23 +10195,37 @@
       <c r="G257" s="36">
         <v>215</v>
       </c>
-      <c r="H257" s="59">
+      <c r="H257" s="60">
         <v>4.4000000000000004</v>
       </c>
-      <c r="I257" s="59"/>
+      <c r="I257" s="60"/>
     </row>
     <row r="258" spans="1:9">
       <c r="A258" s="9" t="s">
         <v>575</v>
       </c>
-      <c r="B258" s="36"/>
-      <c r="C258" s="36"/>
-      <c r="D258" s="36"/>
-      <c r="E258" s="36"/>
-      <c r="F258" s="36"/>
-      <c r="G258" s="36"/>
-      <c r="H258" s="59"/>
-      <c r="I258" s="59"/>
+      <c r="B258" s="18" t="s">
+        <v>792</v>
+      </c>
+      <c r="C258" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="D258" s="18" t="s">
+        <v>429</v>
+      </c>
+      <c r="E258" s="32">
+        <v>108</v>
+      </c>
+      <c r="F258" s="58">
+        <v>160</v>
+      </c>
+      <c r="G258" s="32">
+        <v>215</v>
+      </c>
+      <c r="H258" s="32">
+        <v>3.6</v>
+      </c>
+      <c r="I258" s="60"/>
     </row>
     <row r="259" spans="1:9">
       <c r="A259" s="9" t="s">
@@ -9974,8 +10237,8 @@
       <c r="E259" s="36"/>
       <c r="F259" s="36"/>
       <c r="G259" s="36"/>
-      <c r="H259" s="59"/>
-      <c r="I259" s="59"/>
+      <c r="H259" s="60"/>
+      <c r="I259" s="60"/>
     </row>
     <row r="260" spans="1:9">
       <c r="A260" s="9" t="s">
@@ -9987,8 +10250,8 @@
       <c r="E260" s="36"/>
       <c r="F260" s="36"/>
       <c r="G260" s="36"/>
-      <c r="H260" s="59"/>
-      <c r="I260" s="59"/>
+      <c r="H260" s="60"/>
+      <c r="I260" s="60"/>
     </row>
     <row r="261" spans="1:9">
       <c r="A261" s="9" t="s">
@@ -10001,7 +10264,7 @@
         <v>580</v>
       </c>
       <c r="D261" s="49" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="E261" s="10">
         <v>108</v>
@@ -10015,14 +10278,14 @@
       <c r="H261" s="10">
         <v>3.5</v>
       </c>
-      <c r="I261" s="59"/>
+      <c r="I261" s="60"/>
     </row>
     <row r="262" spans="1:9">
       <c r="A262" s="9" t="s">
         <v>581</v>
       </c>
       <c r="B262" s="10" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="C262" s="10" t="s">
         <v>582</v>
@@ -10042,7 +10305,7 @@
       <c r="H262" s="10">
         <v>3.8</v>
       </c>
-      <c r="I262" s="59"/>
+      <c r="I262" s="60"/>
     </row>
     <row r="263" spans="1:9">
       <c r="A263" s="9" t="s">
@@ -10067,9 +10330,9 @@
         <v>208</v>
       </c>
       <c r="H263" s="27">
-        <v>3.4</v>
-      </c>
-      <c r="I263" s="59"/>
+        <v>3.3</v>
+      </c>
+      <c r="I263" s="60"/>
     </row>
     <row r="264" spans="1:9">
       <c r="A264" s="9" t="s">
@@ -10096,7 +10359,7 @@
       <c r="H264" s="10">
         <v>3.7</v>
       </c>
-      <c r="I264" s="59"/>
+      <c r="I264" s="60"/>
     </row>
     <row r="265" spans="1:9">
       <c r="A265" s="9" t="s">
@@ -10123,20 +10386,20 @@
       <c r="H265" s="35">
         <v>3.6</v>
       </c>
-      <c r="I265" s="59"/>
+      <c r="I265" s="60"/>
     </row>
     <row r="266" spans="1:9">
       <c r="A266" s="9" t="s">
         <v>596</v>
       </c>
       <c r="B266" s="35" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="C266" s="35" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="D266" s="35" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="E266" s="35">
         <v>78</v>
@@ -10148,19 +10411,19 @@
         <v>215</v>
       </c>
       <c r="H266" s="35">
-        <v>3.8</v>
-      </c>
-      <c r="I266" s="59"/>
+        <v>3.6</v>
+      </c>
+      <c r="I266" s="60"/>
     </row>
     <row r="267" spans="1:9">
       <c r="A267" s="9" t="s">
         <v>597</v>
       </c>
       <c r="B267" s="10" t="s">
-        <v>813</v>
+        <v>807</v>
       </c>
       <c r="C267" s="10" t="s">
-        <v>814</v>
+        <v>808</v>
       </c>
       <c r="D267" s="49" t="s">
         <v>144</v>
@@ -10177,7 +10440,7 @@
       <c r="H267" s="10">
         <v>4.2</v>
       </c>
-      <c r="I267" s="60"/>
+      <c r="I267" s="61"/>
     </row>
     <row r="268" spans="1:9">
       <c r="A268" s="9" t="s">
@@ -10189,8 +10452,8 @@
       <c r="E268" s="36"/>
       <c r="F268" s="36"/>
       <c r="G268" s="36"/>
-      <c r="H268" s="59"/>
-      <c r="I268" s="59"/>
+      <c r="H268" s="60"/>
+      <c r="I268" s="60"/>
     </row>
     <row r="269" spans="1:9">
       <c r="A269" s="9" t="s">
@@ -10202,8 +10465,8 @@
       <c r="E269" s="36"/>
       <c r="F269" s="36"/>
       <c r="G269" s="36"/>
-      <c r="H269" s="59"/>
-      <c r="I269" s="59"/>
+      <c r="H269" s="60"/>
+      <c r="I269" s="60"/>
     </row>
     <row r="270" spans="1:9">
       <c r="A270" s="9" t="s">
@@ -10215,8 +10478,8 @@
       <c r="E270" s="36"/>
       <c r="F270" s="36"/>
       <c r="G270" s="36"/>
-      <c r="H270" s="59"/>
-      <c r="I270" s="59"/>
+      <c r="H270" s="60"/>
+      <c r="I270" s="60"/>
     </row>
     <row r="271" spans="1:9">
       <c r="A271" s="9" t="s">
@@ -10228,8 +10491,8 @@
       <c r="E271" s="36"/>
       <c r="F271" s="36"/>
       <c r="G271" s="36"/>
-      <c r="H271" s="59"/>
-      <c r="I271" s="59"/>
+      <c r="H271" s="60"/>
+      <c r="I271" s="60"/>
     </row>
     <row r="272" spans="1:9">
       <c r="A272" s="9" t="s">
@@ -10241,8 +10504,8 @@
       <c r="E272" s="36"/>
       <c r="F272" s="36"/>
       <c r="G272" s="36"/>
-      <c r="H272" s="59"/>
-      <c r="I272" s="59"/>
+      <c r="H272" s="60"/>
+      <c r="I272" s="60"/>
     </row>
     <row r="273" spans="1:9">
       <c r="A273" s="9" t="s">
@@ -10254,8 +10517,8 @@
       <c r="E273" s="36"/>
       <c r="F273" s="36"/>
       <c r="G273" s="36"/>
-      <c r="H273" s="59"/>
-      <c r="I273" s="59"/>
+      <c r="H273" s="60"/>
+      <c r="I273" s="60"/>
     </row>
     <row r="274" spans="1:9">
       <c r="A274" s="9" t="s">
@@ -10267,8 +10530,8 @@
       <c r="E274" s="36"/>
       <c r="F274" s="36"/>
       <c r="G274" s="36"/>
-      <c r="H274" s="59"/>
-      <c r="I274" s="59"/>
+      <c r="H274" s="60"/>
+      <c r="I274" s="60"/>
     </row>
     <row r="275" spans="1:9">
       <c r="A275" s="9" t="s">
@@ -10280,8 +10543,8 @@
       <c r="E275" s="36"/>
       <c r="F275" s="36"/>
       <c r="G275" s="36"/>
-      <c r="H275" s="59"/>
-      <c r="I275" s="59"/>
+      <c r="H275" s="60"/>
+      <c r="I275" s="60"/>
     </row>
     <row r="276" spans="1:9">
       <c r="A276" s="9" t="s">
@@ -10293,53 +10556,53 @@
       <c r="E276" s="36"/>
       <c r="F276" s="36"/>
       <c r="G276" s="36"/>
-      <c r="H276" s="59"/>
-      <c r="I276" s="59"/>
+      <c r="H276" s="60"/>
+      <c r="I276" s="60"/>
     </row>
     <row r="277" spans="1:9">
       <c r="A277" s="9" t="s">
         <v>607</v>
       </c>
-      <c r="B277" s="36" t="s">
+      <c r="B277" s="52" t="s">
         <v>608</v>
       </c>
-      <c r="C277" s="36" t="s">
+      <c r="C277" s="52" t="s">
         <v>609</v>
       </c>
-      <c r="D277" s="36" t="s">
+      <c r="D277" s="52" t="s">
         <v>610</v>
       </c>
-      <c r="E277" s="36">
+      <c r="E277" s="52">
         <v>105</v>
       </c>
       <c r="F277" s="36">
         <v>140</v>
       </c>
-      <c r="G277" s="52">
+      <c r="G277" s="53">
         <v>215</v>
       </c>
-      <c r="H277" s="36">
+      <c r="H277" s="52">
         <v>4</v>
       </c>
-      <c r="I277" s="59"/>
+      <c r="I277" s="60"/>
     </row>
     <row r="278" spans="1:9">
       <c r="A278" s="9" t="s">
         <v>611</v>
       </c>
       <c r="B278" s="27" t="s">
-        <v>815</v>
+        <v>809</v>
       </c>
       <c r="C278" s="27" t="s">
         <v>550</v>
       </c>
       <c r="D278" s="27" t="s">
-        <v>816</v>
+        <v>810</v>
       </c>
       <c r="E278" s="27">
         <v>159</v>
       </c>
-      <c r="F278" s="61">
+      <c r="F278" s="62">
         <v>230</v>
       </c>
       <c r="G278" s="20">
@@ -10348,17 +10611,17 @@
       <c r="H278" s="27">
         <v>4.9000000000000004</v>
       </c>
-      <c r="I278" s="59"/>
+      <c r="I278" s="60"/>
     </row>
     <row r="279" spans="1:9">
       <c r="A279" s="9" t="s">
         <v>612</v>
       </c>
       <c r="B279" s="10" t="s">
-        <v>817</v>
+        <v>811</v>
       </c>
       <c r="C279" s="49" t="s">
-        <v>818</v>
+        <v>812</v>
       </c>
       <c r="D279" s="10" t="s">
         <v>144</v>
@@ -10375,17 +10638,17 @@
       <c r="H279" s="10">
         <v>3.6</v>
       </c>
-      <c r="I279" s="59"/>
+      <c r="I279" s="60"/>
     </row>
     <row r="280" spans="1:9">
       <c r="A280" s="9" t="s">
         <v>613</v>
       </c>
       <c r="B280" s="10" t="s">
-        <v>819</v>
+        <v>813</v>
       </c>
       <c r="C280" s="49" t="s">
-        <v>820</v>
+        <v>814</v>
       </c>
       <c r="D280" s="10" t="s">
         <v>489</v>
@@ -10400,7 +10663,7 @@
       <c r="H280" s="10">
         <v>4.7</v>
       </c>
-      <c r="I280" s="59"/>
+      <c r="I280" s="60"/>
     </row>
     <row r="281" spans="1:9">
       <c r="A281" s="9" t="s">
@@ -10427,14 +10690,14 @@
       <c r="H281" s="10">
         <v>3.7</v>
       </c>
-      <c r="I281" s="59"/>
+      <c r="I281" s="60"/>
     </row>
     <row r="282" spans="1:9">
       <c r="A282" s="9" t="s">
         <v>617</v>
       </c>
       <c r="B282" s="10" t="s">
-        <v>821</v>
+        <v>815</v>
       </c>
       <c r="C282" s="49" t="s">
         <v>618</v>
@@ -10452,19 +10715,19 @@
         <v>215</v>
       </c>
       <c r="H282" s="10">
-        <v>3</v>
-      </c>
-      <c r="I282" s="59"/>
+        <v>2.9</v>
+      </c>
+      <c r="I282" s="60"/>
     </row>
     <row r="283" spans="1:9">
       <c r="A283" s="9" t="s">
         <v>619</v>
       </c>
       <c r="B283" s="10" t="s">
-        <v>822</v>
+        <v>816</v>
       </c>
       <c r="C283" s="49" t="s">
-        <v>823</v>
+        <v>817</v>
       </c>
       <c r="D283" s="10" t="s">
         <v>39</v>
@@ -10481,20 +10744,20 @@
       <c r="H283" s="10">
         <v>3.7</v>
       </c>
-      <c r="I283" s="59"/>
+      <c r="I283" s="60"/>
     </row>
     <row r="284" spans="1:9">
       <c r="A284" s="9" t="s">
         <v>620</v>
       </c>
       <c r="B284" s="27" t="s">
-        <v>824</v>
+        <v>818</v>
       </c>
       <c r="C284" s="36" t="s">
-        <v>825</v>
+        <v>819</v>
       </c>
       <c r="D284" s="36" t="s">
-        <v>826</v>
+        <v>820</v>
       </c>
       <c r="E284" s="36">
         <v>80</v>
@@ -10505,10 +10768,10 @@
       <c r="G284" s="36">
         <v>208</v>
       </c>
-      <c r="H284" s="59">
-        <v>4.8</v>
-      </c>
-      <c r="I284" s="59"/>
+      <c r="H284" s="60">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="I284" s="60"/>
     </row>
     <row r="285" spans="1:9">
       <c r="A285" s="9" t="s">
@@ -10521,7 +10784,7 @@
         <v>623</v>
       </c>
       <c r="D285" s="36" t="s">
-        <v>826</v>
+        <v>820</v>
       </c>
       <c r="E285" s="10">
         <v>73</v>
@@ -10533,70 +10796,70 @@
         <v>208</v>
       </c>
       <c r="H285" s="10">
-        <v>4</v>
-      </c>
-      <c r="I285" s="59"/>
+        <v>3.9</v>
+      </c>
+      <c r="I285" s="60"/>
     </row>
     <row r="286" spans="1:9">
       <c r="A286" s="9" t="s">
         <v>624</v>
       </c>
-      <c r="B286" s="36" t="s">
-        <v>827</v>
-      </c>
-      <c r="C286" s="36" t="s">
-        <v>828</v>
-      </c>
-      <c r="D286" s="36" t="s">
+      <c r="B286" s="52" t="s">
+        <v>821</v>
+      </c>
+      <c r="C286" s="52" t="s">
+        <v>822</v>
+      </c>
+      <c r="D286" s="52" t="s">
         <v>625</v>
       </c>
-      <c r="E286" s="36">
+      <c r="E286" s="52">
         <v>85</v>
       </c>
       <c r="F286" s="36">
         <v>121</v>
       </c>
-      <c r="G286" s="52">
+      <c r="G286" s="53">
         <v>208</v>
       </c>
-      <c r="H286" s="36">
+      <c r="H286" s="52">
         <v>4</v>
       </c>
-      <c r="I286" s="59"/>
+      <c r="I286" s="60"/>
     </row>
     <row r="287" spans="1:9">
       <c r="A287" s="9" t="s">
         <v>626</v>
       </c>
-      <c r="B287" s="36" t="s">
-        <v>829</v>
-      </c>
-      <c r="C287" s="36" t="s">
-        <v>830</v>
-      </c>
-      <c r="D287" s="36" t="s">
-        <v>831</v>
-      </c>
-      <c r="E287" s="36">
+      <c r="B287" s="52" t="s">
+        <v>823</v>
+      </c>
+      <c r="C287" s="52" t="s">
+        <v>824</v>
+      </c>
+      <c r="D287" s="52" t="s">
+        <v>825</v>
+      </c>
+      <c r="E287" s="52">
         <v>88</v>
       </c>
       <c r="F287" s="36">
         <v>140</v>
       </c>
-      <c r="G287" s="52">
+      <c r="G287" s="53">
         <v>218</v>
       </c>
-      <c r="H287" s="36">
-        <v>4.5</v>
-      </c>
-      <c r="I287" s="60"/>
+      <c r="H287" s="52">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="I287" s="61"/>
     </row>
     <row r="288" spans="1:9">
       <c r="A288" s="9" t="s">
         <v>627</v>
       </c>
       <c r="B288" s="27" t="s">
-        <v>832</v>
+        <v>826</v>
       </c>
       <c r="C288" s="27" t="s">
         <v>628</v>
@@ -10616,7 +10879,7 @@
       <c r="H288" s="27">
         <v>5</v>
       </c>
-      <c r="I288" s="60"/>
+      <c r="I288" s="61"/>
     </row>
     <row r="289" spans="1:9">
       <c r="A289" s="9" t="s">
@@ -10641,10 +10904,10 @@
         <v>215</v>
       </c>
       <c r="H289" s="10">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="I289" s="11" t="s">
-        <v>833</v>
+        <v>827</v>
       </c>
     </row>
     <row r="290" spans="1:9">
@@ -10657,7 +10920,7 @@
       <c r="C290" s="24" t="s">
         <v>635</v>
       </c>
-      <c r="D290" s="62" t="s">
+      <c r="D290" s="63" t="s">
         <v>39</v>
       </c>
       <c r="E290" s="24">
@@ -10666,107 +10929,107 @@
       <c r="F290" s="36">
         <v>100</v>
       </c>
-      <c r="G290" s="54">
+      <c r="G290" s="55">
         <v>220</v>
       </c>
       <c r="H290" s="24">
         <v>2.8</v>
       </c>
-      <c r="I290" s="60"/>
+      <c r="I290" s="61"/>
     </row>
     <row r="291" spans="1:9">
       <c r="A291" s="9" t="s">
         <v>636</v>
       </c>
-      <c r="B291" s="63" t="s">
-        <v>834</v>
-      </c>
-      <c r="C291" s="63" t="s">
+      <c r="B291" s="64" t="s">
+        <v>828</v>
+      </c>
+      <c r="C291" s="64" t="s">
         <v>637</v>
       </c>
-      <c r="D291" s="63" t="s">
+      <c r="D291" s="64" t="s">
         <v>638</v>
       </c>
-      <c r="E291" s="63">
+      <c r="E291" s="64">
         <v>88</v>
       </c>
       <c r="F291" s="36">
         <v>130</v>
       </c>
-      <c r="G291" s="53">
+      <c r="G291" s="54">
         <v>220</v>
       </c>
-      <c r="H291" s="63">
-        <v>3.8</v>
-      </c>
-      <c r="I291" s="60"/>
+      <c r="H291" s="64">
+        <v>3.7</v>
+      </c>
+      <c r="I291" s="61"/>
     </row>
     <row r="292" spans="1:9">
       <c r="A292" s="9" t="s">
         <v>639</v>
       </c>
-      <c r="B292" s="63" t="s">
-        <v>835</v>
-      </c>
-      <c r="C292" s="63" t="s">
+      <c r="B292" s="64" t="s">
+        <v>829</v>
+      </c>
+      <c r="C292" s="64" t="s">
         <v>640</v>
       </c>
-      <c r="D292" s="63" t="s">
+      <c r="D292" s="64" t="s">
         <v>641</v>
       </c>
-      <c r="E292" s="63">
+      <c r="E292" s="64">
         <v>80</v>
       </c>
       <c r="F292" s="36">
         <v>135</v>
       </c>
-      <c r="G292" s="53">
+      <c r="G292" s="54">
         <v>215</v>
       </c>
-      <c r="H292" s="63">
+      <c r="H292" s="64">
         <v>3.6</v>
       </c>
-      <c r="I292" s="60"/>
+      <c r="I292" s="61"/>
     </row>
     <row r="293" spans="1:9">
       <c r="A293" s="9" t="s">
         <v>642</v>
       </c>
-      <c r="B293" s="47" t="s">
-        <v>836</v>
-      </c>
-      <c r="C293" s="63" t="s">
-        <v>837</v>
-      </c>
-      <c r="D293" s="63" t="s">
+      <c r="B293" s="65" t="s">
+        <v>830</v>
+      </c>
+      <c r="C293" s="64" t="s">
+        <v>831</v>
+      </c>
+      <c r="D293" s="64" t="s">
         <v>39</v>
       </c>
-      <c r="E293" s="47">
+      <c r="E293" s="65">
         <v>106</v>
       </c>
       <c r="F293" s="36">
         <v>145</v>
       </c>
-      <c r="G293" s="52">
+      <c r="G293" s="53">
         <v>215</v>
       </c>
-      <c r="H293" s="47">
+      <c r="H293" s="65">
         <v>3.7</v>
       </c>
-      <c r="I293" s="60"/>
+      <c r="I293" s="61"/>
     </row>
     <row r="294" spans="1:9">
       <c r="A294" s="9" t="s">
         <v>643</v>
       </c>
       <c r="B294" s="18" t="s">
-        <v>838</v>
+        <v>832</v>
       </c>
       <c r="C294" s="18" t="s">
         <v>445</v>
       </c>
       <c r="D294" s="18" t="s">
-        <v>839</v>
+        <v>833</v>
       </c>
       <c r="E294" s="18">
         <v>150</v>
@@ -10778,16 +11041,16 @@
         <v>215</v>
       </c>
       <c r="H294" s="18">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="I294" s="60"/>
+        <v>5</v>
+      </c>
+      <c r="I294" s="61"/>
     </row>
     <row r="295" spans="1:9">
       <c r="A295" s="9" t="s">
         <v>644</v>
       </c>
       <c r="B295" s="10" t="s">
-        <v>840</v>
+        <v>834</v>
       </c>
       <c r="C295" s="10" t="s">
         <v>645</v>
@@ -10803,7 +11066,7 @@
       <c r="H295" s="10">
         <v>4.9000000000000004</v>
       </c>
-      <c r="I295" s="60"/>
+      <c r="I295" s="61"/>
     </row>
     <row r="296" spans="1:9">
       <c r="A296" s="9" t="s">
@@ -10828,20 +11091,20 @@
       <c r="H296" s="35">
         <v>3.8</v>
       </c>
-      <c r="I296" s="60"/>
+      <c r="I296" s="61"/>
     </row>
     <row r="297" spans="1:9">
       <c r="A297" s="9" t="s">
         <v>651</v>
       </c>
       <c r="B297" s="18" t="s">
-        <v>841</v>
+        <v>835</v>
       </c>
       <c r="C297" s="18" t="s">
-        <v>842</v>
+        <v>836</v>
       </c>
       <c r="D297" s="33" t="s">
-        <v>843</v>
+        <v>837</v>
       </c>
       <c r="E297" s="18">
         <v>125</v>
@@ -10855,19 +11118,19 @@
       <c r="H297" s="18">
         <v>4.7</v>
       </c>
-      <c r="I297" s="53"/>
+      <c r="I297" s="54"/>
     </row>
     <row r="298" spans="1:9">
       <c r="A298" s="9" t="s">
         <v>652</v>
       </c>
-      <c r="B298" s="47"/>
-      <c r="C298" s="63"/>
-      <c r="D298" s="63"/>
-      <c r="E298" s="47"/>
+      <c r="B298" s="65"/>
+      <c r="C298" s="64"/>
+      <c r="D298" s="64"/>
+      <c r="E298" s="65"/>
       <c r="F298" s="36"/>
-      <c r="G298" s="52"/>
-      <c r="H298" s="47"/>
+      <c r="G298" s="53"/>
+      <c r="H298" s="65"/>
       <c r="I298" s="38"/>
     </row>
     <row r="299" spans="1:9">
@@ -10875,13 +11138,13 @@
         <v>653</v>
       </c>
       <c r="B299" s="51" t="s">
-        <v>844</v>
+        <v>838</v>
       </c>
       <c r="C299" s="51" t="s">
-        <v>845</v>
+        <v>839</v>
       </c>
       <c r="D299" s="51" t="s">
-        <v>846</v>
+        <v>840</v>
       </c>
       <c r="E299" s="51">
         <v>124</v>
@@ -10889,14 +11152,14 @@
       <c r="F299" s="36">
         <v>180</v>
       </c>
-      <c r="G299" s="54">
+      <c r="G299" s="55">
         <v>218</v>
       </c>
       <c r="H299" s="51">
         <v>4.5999999999999996</v>
       </c>
-      <c r="I299" s="54" t="s">
-        <v>847</v>
+      <c r="I299" s="55" t="s">
+        <v>841</v>
       </c>
     </row>
     <row r="300" spans="1:9">
@@ -10909,8 +11172,8 @@
       <c r="E300" s="36"/>
       <c r="F300" s="36"/>
       <c r="G300" s="36"/>
-      <c r="H300" s="60"/>
-      <c r="I300" s="60"/>
+      <c r="H300" s="61"/>
+      <c r="I300" s="61"/>
     </row>
     <row r="301" spans="1:9">
       <c r="A301" s="9" t="s">
@@ -10922,18 +11185,18 @@
       <c r="E301" s="36"/>
       <c r="F301" s="36"/>
       <c r="G301" s="36"/>
-      <c r="H301" s="60"/>
-      <c r="I301" s="60"/>
+      <c r="H301" s="61"/>
+      <c r="I301" s="61"/>
     </row>
     <row r="302" spans="1:9">
       <c r="A302" s="9" t="s">
         <v>656</v>
       </c>
       <c r="B302" s="11" t="s">
-        <v>657</v>
+        <v>882</v>
       </c>
       <c r="C302" s="11" t="s">
-        <v>658</v>
+        <v>883</v>
       </c>
       <c r="D302" s="11" t="s">
         <v>555</v>
@@ -10950,20 +11213,20 @@
       <c r="H302" s="11">
         <v>4.5999999999999996</v>
       </c>
-      <c r="I302" s="60"/>
+      <c r="I302" s="61"/>
     </row>
     <row r="303" spans="1:9">
       <c r="A303" s="9" t="s">
+        <v>657</v>
+      </c>
+      <c r="B303" s="10" t="s">
+        <v>658</v>
+      </c>
+      <c r="C303" s="10" t="s">
         <v>659</v>
       </c>
-      <c r="B303" s="10" t="s">
+      <c r="D303" s="10" t="s">
         <v>660</v>
-      </c>
-      <c r="C303" s="10" t="s">
-        <v>661</v>
-      </c>
-      <c r="D303" s="10" t="s">
-        <v>662</v>
       </c>
       <c r="E303" s="11">
         <v>140</v>
@@ -10977,22 +11240,22 @@
       <c r="H303" s="10">
         <v>4.2</v>
       </c>
-      <c r="I303" s="60"/>
+      <c r="I303" s="61"/>
     </row>
     <row r="304" spans="1:9">
       <c r="A304" s="9" t="s">
+        <v>661</v>
+      </c>
+      <c r="B304" s="64" t="s">
+        <v>662</v>
+      </c>
+      <c r="C304" s="64" t="s">
+        <v>251</v>
+      </c>
+      <c r="D304" s="64" t="s">
         <v>663</v>
       </c>
-      <c r="B304" s="63" t="s">
-        <v>664</v>
-      </c>
-      <c r="C304" s="63" t="s">
-        <v>251</v>
-      </c>
-      <c r="D304" s="63" t="s">
-        <v>665</v>
-      </c>
-      <c r="E304" s="63">
+      <c r="E304" s="64">
         <v>90</v>
       </c>
       <c r="F304" s="36">
@@ -11001,25 +11264,25 @@
       <c r="G304" s="37">
         <v>218</v>
       </c>
-      <c r="H304" s="63">
+      <c r="H304" s="64">
         <v>4.5</v>
       </c>
       <c r="I304" s="37" t="s">
-        <v>848</v>
+        <v>842</v>
       </c>
     </row>
     <row r="305" spans="1:9">
       <c r="A305" s="9" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="B305" s="36" t="s">
-        <v>849</v>
+        <v>843</v>
       </c>
       <c r="C305" s="36" t="s">
-        <v>850</v>
+        <v>844</v>
       </c>
       <c r="D305" s="18" t="s">
-        <v>851</v>
+        <v>845</v>
       </c>
       <c r="E305" s="36">
         <v>215</v>
@@ -11030,14 +11293,14 @@
       <c r="G305" s="36">
         <v>225</v>
       </c>
-      <c r="H305" s="60">
+      <c r="H305" s="61">
         <v>6.8</v>
       </c>
-      <c r="I305" s="60"/>
+      <c r="I305" s="61"/>
     </row>
     <row r="306" spans="1:9">
       <c r="A306" s="9" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="B306" s="36"/>
       <c r="C306" s="36"/>
@@ -11045,12 +11308,12 @@
       <c r="E306" s="36"/>
       <c r="F306" s="36"/>
       <c r="G306" s="36"/>
-      <c r="H306" s="60"/>
-      <c r="I306" s="60"/>
+      <c r="H306" s="61"/>
+      <c r="I306" s="61"/>
     </row>
     <row r="307" spans="1:9">
       <c r="A307" s="9" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="B307" s="36"/>
       <c r="C307" s="36"/>
@@ -11058,12 +11321,12 @@
       <c r="E307" s="36"/>
       <c r="F307" s="36"/>
       <c r="G307" s="36"/>
-      <c r="H307" s="60"/>
-      <c r="I307" s="60"/>
+      <c r="H307" s="61"/>
+      <c r="I307" s="61"/>
     </row>
     <row r="308" spans="1:9">
       <c r="A308" s="9" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="B308" s="36"/>
       <c r="C308" s="36"/>
@@ -11071,12 +11334,12 @@
       <c r="E308" s="36"/>
       <c r="F308" s="36"/>
       <c r="G308" s="36"/>
-      <c r="H308" s="60"/>
-      <c r="I308" s="60"/>
+      <c r="H308" s="61"/>
+      <c r="I308" s="61"/>
     </row>
     <row r="309" spans="1:9">
       <c r="A309" s="9" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="B309" s="36"/>
       <c r="C309" s="36"/>
@@ -11084,12 +11347,12 @@
       <c r="E309" s="36"/>
       <c r="F309" s="36"/>
       <c r="G309" s="36"/>
-      <c r="H309" s="60"/>
-      <c r="I309" s="60"/>
+      <c r="H309" s="61"/>
+      <c r="I309" s="61"/>
     </row>
     <row r="310" spans="1:9">
       <c r="A310" s="9" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="B310" s="36"/>
       <c r="C310" s="36"/>
@@ -11097,21 +11360,21 @@
       <c r="E310" s="36"/>
       <c r="F310" s="36"/>
       <c r="G310" s="36"/>
-      <c r="H310" s="60"/>
-      <c r="I310" s="60"/>
+      <c r="H310" s="61"/>
+      <c r="I310" s="61"/>
     </row>
     <row r="311" spans="1:9">
       <c r="A311" s="9" t="s">
+        <v>670</v>
+      </c>
+      <c r="B311" s="35" t="s">
+        <v>671</v>
+      </c>
+      <c r="C311" s="35" t="s">
+        <v>675</v>
+      </c>
+      <c r="D311" s="35" t="s">
         <v>672</v>
-      </c>
-      <c r="B311" s="35" t="s">
-        <v>673</v>
-      </c>
-      <c r="C311" s="35" t="s">
-        <v>677</v>
-      </c>
-      <c r="D311" s="35" t="s">
-        <v>674</v>
       </c>
       <c r="E311" s="35">
         <v>85</v>
@@ -11123,22 +11386,22 @@
         <v>215</v>
       </c>
       <c r="H311" s="35">
-        <v>3.7</v>
-      </c>
-      <c r="I311" s="60"/>
+        <v>3.8</v>
+      </c>
+      <c r="I311" s="61"/>
     </row>
     <row r="312" spans="1:9">
       <c r="A312" s="9" t="s">
+        <v>673</v>
+      </c>
+      <c r="B312" s="10" t="s">
+        <v>674</v>
+      </c>
+      <c r="C312" s="10" t="s">
         <v>675</v>
       </c>
-      <c r="B312" s="10" t="s">
+      <c r="D312" s="10" t="s">
         <v>676</v>
-      </c>
-      <c r="C312" s="10" t="s">
-        <v>677</v>
-      </c>
-      <c r="D312" s="10" t="s">
-        <v>678</v>
       </c>
       <c r="E312" s="10">
         <v>73</v>
@@ -11152,11 +11415,11 @@
       <c r="H312" s="10">
         <v>3.7</v>
       </c>
-      <c r="I312" s="60"/>
+      <c r="I312" s="61"/>
     </row>
     <row r="313" spans="1:9">
       <c r="A313" s="9" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="B313" s="36"/>
       <c r="C313" s="36"/>
@@ -11164,12 +11427,12 @@
       <c r="E313" s="36"/>
       <c r="F313" s="36"/>
       <c r="G313" s="36"/>
-      <c r="H313" s="60"/>
-      <c r="I313" s="60"/>
+      <c r="H313" s="61"/>
+      <c r="I313" s="61"/>
     </row>
     <row r="314" spans="1:9">
       <c r="A314" s="9" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="B314" s="36"/>
       <c r="C314" s="36"/>
@@ -11177,21 +11440,21 @@
       <c r="E314" s="36"/>
       <c r="F314" s="36"/>
       <c r="G314" s="36"/>
-      <c r="H314" s="60"/>
-      <c r="I314" s="60"/>
+      <c r="H314" s="61"/>
+      <c r="I314" s="61"/>
     </row>
     <row r="315" spans="1:9">
       <c r="A315" s="9" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B315" s="36" t="s">
-        <v>852</v>
+        <v>846</v>
       </c>
       <c r="C315" s="36" t="s">
-        <v>853</v>
+        <v>847</v>
       </c>
       <c r="D315" s="11" t="s">
-        <v>854</v>
+        <v>848</v>
       </c>
       <c r="E315" s="36">
         <v>116</v>
@@ -11202,25 +11465,25 @@
       <c r="G315" s="36">
         <v>225</v>
       </c>
-      <c r="H315" s="60">
-        <v>5.4</v>
-      </c>
-      <c r="I315" s="60" t="s">
-        <v>855</v>
+      <c r="H315" s="61">
+        <v>5.3</v>
+      </c>
+      <c r="I315" s="61" t="s">
+        <v>849</v>
       </c>
     </row>
     <row r="316" spans="1:9">
       <c r="A316" s="9" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="B316" s="36" t="s">
-        <v>856</v>
+        <v>850</v>
       </c>
       <c r="C316" s="36" t="s">
-        <v>857</v>
+        <v>851</v>
       </c>
       <c r="D316" s="11" t="s">
-        <v>858</v>
+        <v>852</v>
       </c>
       <c r="E316" s="36">
         <v>160</v>
@@ -11231,25 +11494,25 @@
       <c r="G316" s="36">
         <v>215</v>
       </c>
-      <c r="H316" s="60">
+      <c r="H316" s="61">
         <v>5.2</v>
       </c>
-      <c r="I316" s="60" t="s">
-        <v>859</v>
+      <c r="I316" s="61" t="s">
+        <v>884</v>
       </c>
     </row>
     <row r="317" spans="1:9">
       <c r="A317" s="9" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="B317" s="11" t="s">
-        <v>860</v>
+        <v>853</v>
       </c>
       <c r="C317" s="11" t="s">
-        <v>861</v>
+        <v>854</v>
       </c>
       <c r="D317" s="11" t="s">
-        <v>862</v>
+        <v>855</v>
       </c>
       <c r="E317" s="11">
         <v>110</v>
@@ -11264,21 +11527,21 @@
         <v>3.7</v>
       </c>
       <c r="I317" s="11" t="s">
-        <v>863</v>
+        <v>856</v>
       </c>
     </row>
     <row r="318" spans="1:9">
       <c r="A318" s="9" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="B318" s="11" t="s">
-        <v>860</v>
+        <v>853</v>
       </c>
       <c r="C318" s="11" t="s">
-        <v>864</v>
+        <v>857</v>
       </c>
       <c r="D318" s="11" t="s">
-        <v>862</v>
+        <v>855</v>
       </c>
       <c r="E318" s="11">
         <v>110</v>
@@ -11290,22 +11553,22 @@
         <v>208</v>
       </c>
       <c r="H318" s="11">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="I318" s="11"/>
     </row>
     <row r="319" spans="1:9">
       <c r="A319" s="9" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="B319" s="18" t="s">
-        <v>865</v>
+        <v>858</v>
       </c>
       <c r="C319" s="18" t="s">
-        <v>866</v>
+        <v>859</v>
       </c>
       <c r="D319" s="18" t="s">
-        <v>867</v>
+        <v>860</v>
       </c>
       <c r="E319" s="18">
         <v>205</v>
@@ -11320,27 +11583,27 @@
         <v>5.5</v>
       </c>
       <c r="I319" s="11" t="s">
-        <v>868</v>
+        <v>861</v>
       </c>
     </row>
     <row r="320" spans="1:9">
       <c r="A320" s="9" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="B320" s="18" t="s">
-        <v>869</v>
+        <v>862</v>
       </c>
       <c r="C320" s="18" t="s">
-        <v>779</v>
+        <v>885</v>
       </c>
       <c r="D320" s="18" t="s">
-        <v>870</v>
+        <v>863</v>
       </c>
       <c r="E320" s="18">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="F320" s="31">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="G320" s="32">
         <v>218</v>
@@ -11349,21 +11612,21 @@
         <v>6</v>
       </c>
       <c r="I320" s="11" t="s">
-        <v>871</v>
+        <v>886</v>
       </c>
     </row>
     <row r="321" spans="1:9">
       <c r="A321" s="9" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="B321" s="18" t="s">
-        <v>872</v>
+        <v>864</v>
       </c>
       <c r="C321" s="18" t="s">
-        <v>873</v>
+        <v>865</v>
       </c>
       <c r="D321" s="18" t="s">
-        <v>874</v>
+        <v>866</v>
       </c>
       <c r="E321" s="18">
         <v>138</v>
@@ -11378,21 +11641,21 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="I321" s="11" t="s">
-        <v>875</v>
+        <v>867</v>
       </c>
     </row>
     <row r="322" spans="1:9">
       <c r="A322" s="9" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="B322" s="18" t="s">
-        <v>876</v>
+        <v>868</v>
       </c>
       <c r="C322" s="18" t="s">
-        <v>877</v>
+        <v>869</v>
       </c>
       <c r="D322" s="18" t="s">
-        <v>867</v>
+        <v>860</v>
       </c>
       <c r="E322" s="18">
         <v>225</v>
@@ -11407,21 +11670,21 @@
         <v>6</v>
       </c>
       <c r="I322" s="11" t="s">
-        <v>878</v>
+        <v>870</v>
       </c>
     </row>
     <row r="323" spans="1:9">
       <c r="A323" s="9" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="B323" s="18" t="s">
-        <v>879</v>
+        <v>871</v>
       </c>
       <c r="C323" s="18" t="s">
         <v>88</v>
       </c>
       <c r="D323" s="18" t="s">
-        <v>874</v>
+        <v>866</v>
       </c>
       <c r="E323" s="18">
         <v>155</v>
@@ -11436,21 +11699,21 @@
         <v>4.8</v>
       </c>
       <c r="I323" s="11" t="s">
-        <v>880</v>
+        <v>872</v>
       </c>
     </row>
     <row r="324" spans="1:9">
       <c r="A324" s="9" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="B324" s="18" t="s">
-        <v>881</v>
+        <v>873</v>
       </c>
       <c r="C324" s="18" t="s">
-        <v>882</v>
+        <v>874</v>
       </c>
       <c r="D324" s="18" t="s">
-        <v>867</v>
+        <v>860</v>
       </c>
       <c r="E324" s="18">
         <v>220</v>
@@ -11465,12 +11728,12 @@
         <v>6.2</v>
       </c>
       <c r="I324" s="11" t="s">
-        <v>878</v>
+        <v>870</v>
       </c>
     </row>
     <row r="325" spans="1:9">
       <c r="A325" s="9" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="B325" s="36"/>
       <c r="C325" s="36"/>
@@ -11478,8 +11741,996 @@
       <c r="E325" s="36"/>
       <c r="F325" s="36"/>
       <c r="G325" s="36"/>
-      <c r="H325" s="60"/>
-      <c r="I325" s="60"/>
+      <c r="H325" s="61"/>
+      <c r="I325" s="61"/>
+    </row>
+    <row r="326" spans="1:9">
+      <c r="A326" s="9" t="s">
+        <v>887</v>
+      </c>
+      <c r="B326" s="36"/>
+      <c r="C326" s="36"/>
+      <c r="D326" s="36"/>
+      <c r="E326" s="36"/>
+      <c r="F326" s="36"/>
+      <c r="G326" s="36"/>
+      <c r="H326" s="61"/>
+      <c r="I326" s="61"/>
+    </row>
+    <row r="327" spans="1:9">
+      <c r="A327" s="9" t="s">
+        <v>888</v>
+      </c>
+      <c r="B327" s="36"/>
+      <c r="C327" s="36"/>
+      <c r="D327" s="36"/>
+      <c r="E327" s="36"/>
+      <c r="F327" s="36"/>
+      <c r="G327" s="36"/>
+      <c r="H327" s="61"/>
+      <c r="I327" s="61"/>
+    </row>
+    <row r="328" spans="1:9">
+      <c r="A328" s="9" t="s">
+        <v>889</v>
+      </c>
+      <c r="B328" s="36"/>
+      <c r="C328" s="36"/>
+      <c r="D328" s="36"/>
+      <c r="E328" s="36"/>
+      <c r="F328" s="36"/>
+      <c r="G328" s="36"/>
+      <c r="H328" s="61"/>
+      <c r="I328" s="61"/>
+    </row>
+    <row r="329" spans="1:9">
+      <c r="A329" s="9" t="s">
+        <v>890</v>
+      </c>
+      <c r="B329" s="36"/>
+      <c r="C329" s="36"/>
+      <c r="D329" s="36"/>
+      <c r="E329" s="36"/>
+      <c r="F329" s="36"/>
+      <c r="G329" s="36"/>
+      <c r="H329" s="61"/>
+      <c r="I329" s="61"/>
+    </row>
+    <row r="330" spans="1:9">
+      <c r="A330" s="9" t="s">
+        <v>891</v>
+      </c>
+      <c r="B330" s="36"/>
+      <c r="C330" s="36"/>
+      <c r="D330" s="36"/>
+      <c r="E330" s="36"/>
+      <c r="F330" s="36"/>
+      <c r="G330" s="36"/>
+      <c r="H330" s="61"/>
+      <c r="I330" s="61"/>
+    </row>
+    <row r="331" spans="1:9">
+      <c r="A331" s="9" t="s">
+        <v>892</v>
+      </c>
+      <c r="B331" s="36"/>
+      <c r="C331" s="36"/>
+      <c r="D331" s="36"/>
+      <c r="E331" s="36"/>
+      <c r="F331" s="36"/>
+      <c r="G331" s="36"/>
+      <c r="H331" s="61"/>
+      <c r="I331" s="61"/>
+    </row>
+    <row r="332" spans="1:9">
+      <c r="A332" s="9" t="s">
+        <v>893</v>
+      </c>
+      <c r="B332" s="36"/>
+      <c r="C332" s="36"/>
+      <c r="D332" s="36"/>
+      <c r="E332" s="36"/>
+      <c r="F332" s="36"/>
+      <c r="G332" s="36"/>
+      <c r="H332" s="61"/>
+      <c r="I332" s="61"/>
+    </row>
+    <row r="333" spans="1:9">
+      <c r="A333" s="9" t="s">
+        <v>894</v>
+      </c>
+      <c r="B333" s="36"/>
+      <c r="C333" s="36"/>
+      <c r="D333" s="36"/>
+      <c r="E333" s="36"/>
+      <c r="F333" s="36"/>
+      <c r="G333" s="36"/>
+      <c r="H333" s="61"/>
+      <c r="I333" s="61"/>
+    </row>
+    <row r="334" spans="1:9">
+      <c r="A334" s="9" t="s">
+        <v>895</v>
+      </c>
+      <c r="B334" s="36"/>
+      <c r="C334" s="36"/>
+      <c r="D334" s="36"/>
+      <c r="E334" s="36"/>
+      <c r="F334" s="36"/>
+      <c r="G334" s="36"/>
+      <c r="H334" s="61"/>
+      <c r="I334" s="61"/>
+    </row>
+    <row r="335" spans="1:9">
+      <c r="A335" s="9" t="s">
+        <v>896</v>
+      </c>
+      <c r="B335" s="36"/>
+      <c r="C335" s="36"/>
+      <c r="D335" s="36"/>
+      <c r="E335" s="36"/>
+      <c r="F335" s="36"/>
+      <c r="G335" s="36"/>
+      <c r="H335" s="61"/>
+      <c r="I335" s="61"/>
+    </row>
+    <row r="336" spans="1:9">
+      <c r="A336" s="9" t="s">
+        <v>897</v>
+      </c>
+      <c r="B336" s="36"/>
+      <c r="C336" s="36"/>
+      <c r="D336" s="36"/>
+      <c r="E336" s="36"/>
+      <c r="F336" s="36"/>
+      <c r="G336" s="36"/>
+      <c r="H336" s="61"/>
+      <c r="I336" s="61"/>
+    </row>
+    <row r="337" spans="1:9">
+      <c r="A337" s="9" t="s">
+        <v>898</v>
+      </c>
+      <c r="B337" s="36"/>
+      <c r="C337" s="36"/>
+      <c r="D337" s="36"/>
+      <c r="E337" s="36"/>
+      <c r="F337" s="36"/>
+      <c r="G337" s="36"/>
+      <c r="H337" s="61"/>
+      <c r="I337" s="61"/>
+    </row>
+    <row r="338" spans="1:9">
+      <c r="A338" s="9" t="s">
+        <v>899</v>
+      </c>
+      <c r="B338" s="36"/>
+      <c r="C338" s="36"/>
+      <c r="D338" s="36"/>
+      <c r="E338" s="36"/>
+      <c r="F338" s="36"/>
+      <c r="G338" s="36"/>
+      <c r="H338" s="61"/>
+      <c r="I338" s="61"/>
+    </row>
+    <row r="339" spans="1:9">
+      <c r="A339" s="9" t="s">
+        <v>900</v>
+      </c>
+      <c r="B339" s="36"/>
+      <c r="C339" s="36"/>
+      <c r="D339" s="36"/>
+      <c r="E339" s="36"/>
+      <c r="F339" s="36"/>
+      <c r="G339" s="36"/>
+      <c r="H339" s="61"/>
+      <c r="I339" s="61"/>
+    </row>
+    <row r="340" spans="1:9">
+      <c r="A340" s="9" t="s">
+        <v>901</v>
+      </c>
+      <c r="B340" s="36"/>
+      <c r="C340" s="36"/>
+      <c r="D340" s="36"/>
+      <c r="E340" s="36"/>
+      <c r="F340" s="36"/>
+      <c r="G340" s="36"/>
+      <c r="H340" s="61"/>
+      <c r="I340" s="61"/>
+    </row>
+    <row r="341" spans="1:9">
+      <c r="A341" s="9" t="s">
+        <v>902</v>
+      </c>
+      <c r="B341" s="36"/>
+      <c r="C341" s="36"/>
+      <c r="D341" s="36"/>
+      <c r="E341" s="36"/>
+      <c r="F341" s="36"/>
+      <c r="G341" s="36"/>
+      <c r="H341" s="61"/>
+      <c r="I341" s="61"/>
+    </row>
+    <row r="342" spans="1:9">
+      <c r="A342" s="9" t="s">
+        <v>903</v>
+      </c>
+      <c r="B342" s="36"/>
+      <c r="C342" s="36"/>
+      <c r="D342" s="36"/>
+      <c r="E342" s="36"/>
+      <c r="F342" s="36"/>
+      <c r="G342" s="36"/>
+      <c r="H342" s="61"/>
+      <c r="I342" s="61"/>
+    </row>
+    <row r="343" spans="1:9">
+      <c r="A343" s="9" t="s">
+        <v>904</v>
+      </c>
+      <c r="B343" s="36"/>
+      <c r="C343" s="36"/>
+      <c r="D343" s="36"/>
+      <c r="E343" s="36"/>
+      <c r="F343" s="36"/>
+      <c r="G343" s="36"/>
+      <c r="H343" s="61"/>
+      <c r="I343" s="61"/>
+    </row>
+    <row r="344" spans="1:9">
+      <c r="A344" s="9" t="s">
+        <v>905</v>
+      </c>
+      <c r="B344" s="36"/>
+      <c r="C344" s="36"/>
+      <c r="D344" s="36"/>
+      <c r="E344" s="36"/>
+      <c r="F344" s="36"/>
+      <c r="G344" s="36"/>
+      <c r="H344" s="61"/>
+      <c r="I344" s="61"/>
+    </row>
+    <row r="345" spans="1:9">
+      <c r="A345" s="9" t="s">
+        <v>906</v>
+      </c>
+      <c r="B345" s="36"/>
+      <c r="C345" s="36"/>
+      <c r="D345" s="36"/>
+      <c r="E345" s="36"/>
+      <c r="F345" s="36"/>
+      <c r="G345" s="36"/>
+      <c r="H345" s="61"/>
+      <c r="I345" s="61"/>
+    </row>
+    <row r="346" spans="1:9">
+      <c r="A346" s="9" t="s">
+        <v>907</v>
+      </c>
+      <c r="B346" s="36"/>
+      <c r="C346" s="36"/>
+      <c r="D346" s="36"/>
+      <c r="E346" s="36"/>
+      <c r="F346" s="36"/>
+      <c r="G346" s="36"/>
+      <c r="H346" s="61"/>
+      <c r="I346" s="61"/>
+    </row>
+    <row r="347" spans="1:9">
+      <c r="A347" s="9" t="s">
+        <v>908</v>
+      </c>
+      <c r="B347" s="36"/>
+      <c r="C347" s="36"/>
+      <c r="D347" s="36"/>
+      <c r="E347" s="36"/>
+      <c r="F347" s="36"/>
+      <c r="G347" s="36"/>
+      <c r="H347" s="61"/>
+      <c r="I347" s="61"/>
+    </row>
+    <row r="348" spans="1:9">
+      <c r="A348" s="9" t="s">
+        <v>909</v>
+      </c>
+      <c r="B348" s="36"/>
+      <c r="C348" s="36"/>
+      <c r="D348" s="36"/>
+      <c r="E348" s="36"/>
+      <c r="F348" s="36"/>
+      <c r="G348" s="36"/>
+      <c r="H348" s="61"/>
+      <c r="I348" s="61"/>
+    </row>
+    <row r="349" spans="1:9">
+      <c r="A349" s="9" t="s">
+        <v>910</v>
+      </c>
+      <c r="B349" s="36"/>
+      <c r="C349" s="36"/>
+      <c r="D349" s="36"/>
+      <c r="E349" s="36"/>
+      <c r="F349" s="36"/>
+      <c r="G349" s="36"/>
+      <c r="H349" s="61"/>
+      <c r="I349" s="61"/>
+    </row>
+    <row r="350" spans="1:9">
+      <c r="A350" s="9" t="s">
+        <v>911</v>
+      </c>
+      <c r="B350" s="36"/>
+      <c r="C350" s="36"/>
+      <c r="D350" s="36"/>
+      <c r="E350" s="36"/>
+      <c r="F350" s="36"/>
+      <c r="G350" s="36"/>
+      <c r="H350" s="61"/>
+      <c r="I350" s="61"/>
+    </row>
+    <row r="351" spans="1:9">
+      <c r="A351" s="9" t="s">
+        <v>912</v>
+      </c>
+      <c r="B351" s="36"/>
+      <c r="C351" s="36"/>
+      <c r="D351" s="36"/>
+      <c r="E351" s="36"/>
+      <c r="F351" s="36"/>
+      <c r="G351" s="36"/>
+      <c r="H351" s="61"/>
+      <c r="I351" s="61"/>
+    </row>
+    <row r="352" spans="1:9">
+      <c r="A352" s="9" t="s">
+        <v>913</v>
+      </c>
+      <c r="B352" s="36"/>
+      <c r="C352" s="36"/>
+      <c r="D352" s="36"/>
+      <c r="E352" s="36"/>
+      <c r="F352" s="36"/>
+      <c r="G352" s="36"/>
+      <c r="H352" s="61"/>
+      <c r="I352" s="61"/>
+    </row>
+    <row r="353" spans="1:9">
+      <c r="A353" s="9" t="s">
+        <v>914</v>
+      </c>
+      <c r="B353" s="36"/>
+      <c r="C353" s="36"/>
+      <c r="D353" s="36"/>
+      <c r="E353" s="36"/>
+      <c r="F353" s="36"/>
+      <c r="G353" s="36"/>
+      <c r="H353" s="61"/>
+      <c r="I353" s="61"/>
+    </row>
+    <row r="354" spans="1:9">
+      <c r="A354" s="9" t="s">
+        <v>915</v>
+      </c>
+      <c r="B354" s="36"/>
+      <c r="C354" s="36"/>
+      <c r="D354" s="36"/>
+      <c r="E354" s="36"/>
+      <c r="F354" s="36"/>
+      <c r="G354" s="36"/>
+      <c r="H354" s="61"/>
+      <c r="I354" s="61"/>
+    </row>
+    <row r="355" spans="1:9">
+      <c r="A355" s="9" t="s">
+        <v>916</v>
+      </c>
+      <c r="B355" s="36"/>
+      <c r="C355" s="36"/>
+      <c r="D355" s="36"/>
+      <c r="E355" s="36"/>
+      <c r="F355" s="36"/>
+      <c r="G355" s="36"/>
+      <c r="H355" s="61"/>
+      <c r="I355" s="61"/>
+    </row>
+    <row r="356" spans="1:9">
+      <c r="A356" s="9" t="s">
+        <v>917</v>
+      </c>
+      <c r="B356" s="36"/>
+      <c r="C356" s="36"/>
+      <c r="D356" s="36"/>
+      <c r="E356" s="36"/>
+      <c r="F356" s="36"/>
+      <c r="G356" s="36"/>
+      <c r="H356" s="61"/>
+      <c r="I356" s="61"/>
+    </row>
+    <row r="357" spans="1:9">
+      <c r="A357" s="9" t="s">
+        <v>918</v>
+      </c>
+      <c r="B357" s="36"/>
+      <c r="C357" s="36"/>
+      <c r="D357" s="36"/>
+      <c r="E357" s="36"/>
+      <c r="F357" s="36"/>
+      <c r="G357" s="36"/>
+      <c r="H357" s="61"/>
+      <c r="I357" s="61"/>
+    </row>
+    <row r="358" spans="1:9">
+      <c r="A358" s="9" t="s">
+        <v>919</v>
+      </c>
+      <c r="B358" s="36"/>
+      <c r="C358" s="36"/>
+      <c r="D358" s="36"/>
+      <c r="E358" s="36"/>
+      <c r="F358" s="36"/>
+      <c r="G358" s="36"/>
+      <c r="H358" s="61"/>
+      <c r="I358" s="61"/>
+    </row>
+    <row r="359" spans="1:9">
+      <c r="A359" s="9" t="s">
+        <v>920</v>
+      </c>
+      <c r="B359" s="36"/>
+      <c r="C359" s="36"/>
+      <c r="D359" s="36"/>
+      <c r="E359" s="36"/>
+      <c r="F359" s="36"/>
+      <c r="G359" s="36"/>
+      <c r="H359" s="61"/>
+      <c r="I359" s="61"/>
+    </row>
+    <row r="360" spans="1:9">
+      <c r="A360" s="9" t="s">
+        <v>921</v>
+      </c>
+      <c r="B360" s="36"/>
+      <c r="C360" s="36"/>
+      <c r="D360" s="36"/>
+      <c r="E360" s="36"/>
+      <c r="F360" s="36"/>
+      <c r="G360" s="36"/>
+      <c r="H360" s="61"/>
+      <c r="I360" s="61"/>
+    </row>
+    <row r="361" spans="1:9">
+      <c r="A361" s="9" t="s">
+        <v>922</v>
+      </c>
+      <c r="B361" s="36"/>
+      <c r="C361" s="36"/>
+      <c r="D361" s="36"/>
+      <c r="E361" s="36"/>
+      <c r="F361" s="36"/>
+      <c r="G361" s="36"/>
+      <c r="H361" s="61"/>
+      <c r="I361" s="61"/>
+    </row>
+    <row r="362" spans="1:9">
+      <c r="A362" s="9" t="s">
+        <v>923</v>
+      </c>
+      <c r="B362" s="36"/>
+      <c r="C362" s="36"/>
+      <c r="D362" s="36"/>
+      <c r="E362" s="36"/>
+      <c r="F362" s="36"/>
+      <c r="G362" s="36"/>
+      <c r="H362" s="61"/>
+      <c r="I362" s="61"/>
+    </row>
+    <row r="363" spans="1:9">
+      <c r="A363" s="9" t="s">
+        <v>924</v>
+      </c>
+      <c r="B363" s="36"/>
+      <c r="C363" s="36"/>
+      <c r="D363" s="36"/>
+      <c r="E363" s="36"/>
+      <c r="F363" s="36"/>
+      <c r="G363" s="36"/>
+      <c r="H363" s="61"/>
+      <c r="I363" s="61"/>
+    </row>
+    <row r="364" spans="1:9">
+      <c r="A364" s="9" t="s">
+        <v>925</v>
+      </c>
+      <c r="B364" s="36"/>
+      <c r="C364" s="36"/>
+      <c r="D364" s="36"/>
+      <c r="E364" s="36"/>
+      <c r="F364" s="36"/>
+      <c r="G364" s="36"/>
+      <c r="H364" s="61"/>
+      <c r="I364" s="61"/>
+    </row>
+    <row r="365" spans="1:9">
+      <c r="A365" s="9" t="s">
+        <v>926</v>
+      </c>
+      <c r="B365" s="36"/>
+      <c r="C365" s="36"/>
+      <c r="D365" s="36"/>
+      <c r="E365" s="36"/>
+      <c r="F365" s="36"/>
+      <c r="G365" s="36"/>
+      <c r="H365" s="61"/>
+      <c r="I365" s="61"/>
+    </row>
+    <row r="366" spans="1:9">
+      <c r="A366" s="9" t="s">
+        <v>927</v>
+      </c>
+      <c r="B366" s="36"/>
+      <c r="C366" s="36"/>
+      <c r="D366" s="36"/>
+      <c r="E366" s="36"/>
+      <c r="F366" s="36"/>
+      <c r="G366" s="36"/>
+      <c r="H366" s="61"/>
+      <c r="I366" s="61"/>
+    </row>
+    <row r="367" spans="1:9">
+      <c r="A367" s="9" t="s">
+        <v>928</v>
+      </c>
+      <c r="B367" s="36"/>
+      <c r="C367" s="36"/>
+      <c r="D367" s="36"/>
+      <c r="E367" s="36"/>
+      <c r="F367" s="36"/>
+      <c r="G367" s="36"/>
+      <c r="H367" s="61"/>
+      <c r="I367" s="61"/>
+    </row>
+    <row r="368" spans="1:9">
+      <c r="A368" s="9" t="s">
+        <v>929</v>
+      </c>
+      <c r="B368" s="36"/>
+      <c r="C368" s="36"/>
+      <c r="D368" s="36"/>
+      <c r="E368" s="36"/>
+      <c r="F368" s="36"/>
+      <c r="G368" s="36"/>
+      <c r="H368" s="61"/>
+      <c r="I368" s="61"/>
+    </row>
+    <row r="369" spans="1:9">
+      <c r="A369" s="9" t="s">
+        <v>930</v>
+      </c>
+      <c r="B369" s="36"/>
+      <c r="C369" s="36"/>
+      <c r="D369" s="36"/>
+      <c r="E369" s="36"/>
+      <c r="F369" s="36"/>
+      <c r="G369" s="36"/>
+      <c r="H369" s="61"/>
+      <c r="I369" s="61"/>
+    </row>
+    <row r="370" spans="1:9">
+      <c r="A370" s="9" t="s">
+        <v>931</v>
+      </c>
+      <c r="B370" s="36"/>
+      <c r="C370" s="36"/>
+      <c r="D370" s="36"/>
+      <c r="E370" s="36"/>
+      <c r="F370" s="36"/>
+      <c r="G370" s="36"/>
+      <c r="H370" s="61"/>
+      <c r="I370" s="61"/>
+    </row>
+    <row r="371" spans="1:9">
+      <c r="A371" s="9" t="s">
+        <v>932</v>
+      </c>
+      <c r="B371" s="36"/>
+      <c r="C371" s="36"/>
+      <c r="D371" s="36"/>
+      <c r="E371" s="36"/>
+      <c r="F371" s="36"/>
+      <c r="G371" s="36"/>
+      <c r="H371" s="61"/>
+      <c r="I371" s="61"/>
+    </row>
+    <row r="372" spans="1:9">
+      <c r="A372" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="B372" s="36"/>
+      <c r="C372" s="36"/>
+      <c r="D372" s="36"/>
+      <c r="E372" s="36"/>
+      <c r="F372" s="36"/>
+      <c r="G372" s="36"/>
+      <c r="H372" s="61"/>
+      <c r="I372" s="61"/>
+    </row>
+    <row r="373" spans="1:9">
+      <c r="A373" s="9" t="s">
+        <v>934</v>
+      </c>
+      <c r="B373" s="36"/>
+      <c r="C373" s="36"/>
+      <c r="D373" s="36"/>
+      <c r="E373" s="36"/>
+      <c r="F373" s="36"/>
+      <c r="G373" s="36"/>
+      <c r="H373" s="61"/>
+      <c r="I373" s="61"/>
+    </row>
+    <row r="374" spans="1:9">
+      <c r="A374" s="9" t="s">
+        <v>935</v>
+      </c>
+      <c r="B374" s="36"/>
+      <c r="C374" s="36"/>
+      <c r="D374" s="36"/>
+      <c r="E374" s="36"/>
+      <c r="F374" s="36"/>
+      <c r="G374" s="36"/>
+      <c r="H374" s="61"/>
+      <c r="I374" s="61"/>
+    </row>
+    <row r="375" spans="1:9">
+      <c r="A375" s="9" t="s">
+        <v>936</v>
+      </c>
+      <c r="B375" s="36"/>
+      <c r="C375" s="36"/>
+      <c r="D375" s="36"/>
+      <c r="E375" s="36"/>
+      <c r="F375" s="36"/>
+      <c r="G375" s="36"/>
+      <c r="H375" s="61"/>
+      <c r="I375" s="61"/>
+    </row>
+    <row r="376" spans="1:9">
+      <c r="A376" s="9" t="s">
+        <v>937</v>
+      </c>
+      <c r="B376" s="36"/>
+      <c r="C376" s="36"/>
+      <c r="D376" s="36"/>
+      <c r="E376" s="36"/>
+      <c r="F376" s="36"/>
+      <c r="G376" s="36"/>
+      <c r="H376" s="61"/>
+      <c r="I376" s="61"/>
+    </row>
+    <row r="377" spans="1:9">
+      <c r="A377" s="9" t="s">
+        <v>938</v>
+      </c>
+      <c r="B377" s="36"/>
+      <c r="C377" s="36"/>
+      <c r="D377" s="36"/>
+      <c r="E377" s="36"/>
+      <c r="F377" s="36"/>
+      <c r="G377" s="36"/>
+      <c r="H377" s="61"/>
+      <c r="I377" s="61"/>
+    </row>
+    <row r="378" spans="1:9">
+      <c r="A378" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="B378" s="36"/>
+      <c r="C378" s="36"/>
+      <c r="D378" s="36"/>
+      <c r="E378" s="36"/>
+      <c r="F378" s="36"/>
+      <c r="G378" s="36"/>
+      <c r="H378" s="61"/>
+      <c r="I378" s="61"/>
+    </row>
+    <row r="379" spans="1:9">
+      <c r="A379" s="9" t="s">
+        <v>940</v>
+      </c>
+      <c r="B379" s="36"/>
+      <c r="C379" s="36"/>
+      <c r="D379" s="36"/>
+      <c r="E379" s="36"/>
+      <c r="F379" s="36"/>
+      <c r="G379" s="36"/>
+      <c r="H379" s="61"/>
+      <c r="I379" s="61"/>
+    </row>
+    <row r="380" spans="1:9">
+      <c r="A380" s="9" t="s">
+        <v>941</v>
+      </c>
+      <c r="B380" s="36"/>
+      <c r="C380" s="36"/>
+      <c r="D380" s="36"/>
+      <c r="E380" s="36"/>
+      <c r="F380" s="36"/>
+      <c r="G380" s="36"/>
+      <c r="H380" s="61"/>
+      <c r="I380" s="61"/>
+    </row>
+    <row r="381" spans="1:9">
+      <c r="A381" s="9" t="s">
+        <v>942</v>
+      </c>
+      <c r="B381" s="36"/>
+      <c r="C381" s="36"/>
+      <c r="D381" s="36"/>
+      <c r="E381" s="36"/>
+      <c r="F381" s="36"/>
+      <c r="G381" s="36"/>
+      <c r="H381" s="61"/>
+      <c r="I381" s="61"/>
+    </row>
+    <row r="382" spans="1:9">
+      <c r="A382" s="9" t="s">
+        <v>943</v>
+      </c>
+      <c r="B382" s="36"/>
+      <c r="C382" s="36"/>
+      <c r="D382" s="36"/>
+      <c r="E382" s="36"/>
+      <c r="F382" s="36"/>
+      <c r="G382" s="36"/>
+      <c r="H382" s="61"/>
+      <c r="I382" s="61"/>
+    </row>
+    <row r="383" spans="1:9">
+      <c r="A383" s="9" t="s">
+        <v>944</v>
+      </c>
+      <c r="B383" s="36"/>
+      <c r="C383" s="36"/>
+      <c r="D383" s="36"/>
+      <c r="E383" s="36"/>
+      <c r="F383" s="36"/>
+      <c r="G383" s="36"/>
+      <c r="H383" s="61"/>
+      <c r="I383" s="61"/>
+    </row>
+    <row r="384" spans="1:9">
+      <c r="A384" s="9" t="s">
+        <v>945</v>
+      </c>
+      <c r="B384" s="36"/>
+      <c r="C384" s="36"/>
+      <c r="D384" s="36"/>
+      <c r="E384" s="36"/>
+      <c r="F384" s="36"/>
+      <c r="G384" s="36"/>
+      <c r="H384" s="61"/>
+      <c r="I384" s="61"/>
+    </row>
+    <row r="385" spans="1:9">
+      <c r="A385" s="9" t="s">
+        <v>946</v>
+      </c>
+      <c r="B385" s="36"/>
+      <c r="C385" s="36"/>
+      <c r="D385" s="36"/>
+      <c r="E385" s="36"/>
+      <c r="F385" s="36"/>
+      <c r="G385" s="36"/>
+      <c r="H385" s="61"/>
+      <c r="I385" s="61"/>
+    </row>
+    <row r="386" spans="1:9">
+      <c r="A386" s="9" t="s">
+        <v>947</v>
+      </c>
+      <c r="B386" s="36"/>
+      <c r="C386" s="36"/>
+      <c r="D386" s="36"/>
+      <c r="E386" s="36"/>
+      <c r="F386" s="36"/>
+      <c r="G386" s="36"/>
+      <c r="H386" s="61"/>
+      <c r="I386" s="61"/>
+    </row>
+    <row r="387" spans="1:9">
+      <c r="A387" s="9" t="s">
+        <v>948</v>
+      </c>
+      <c r="B387" s="36"/>
+      <c r="C387" s="36"/>
+      <c r="D387" s="36"/>
+      <c r="E387" s="36"/>
+      <c r="F387" s="36"/>
+      <c r="G387" s="36"/>
+      <c r="H387" s="61"/>
+      <c r="I387" s="61"/>
+    </row>
+    <row r="388" spans="1:9">
+      <c r="A388" s="9" t="s">
+        <v>949</v>
+      </c>
+      <c r="B388" s="36"/>
+      <c r="C388" s="36"/>
+      <c r="D388" s="36"/>
+      <c r="E388" s="36"/>
+      <c r="F388" s="36"/>
+      <c r="G388" s="36"/>
+      <c r="H388" s="61"/>
+      <c r="I388" s="61"/>
+    </row>
+    <row r="389" spans="1:9">
+      <c r="A389" s="9" t="s">
+        <v>950</v>
+      </c>
+      <c r="B389" s="36"/>
+      <c r="C389" s="36"/>
+      <c r="D389" s="36"/>
+      <c r="E389" s="36"/>
+      <c r="F389" s="36"/>
+      <c r="G389" s="36"/>
+      <c r="H389" s="61"/>
+      <c r="I389" s="61"/>
+    </row>
+    <row r="390" spans="1:9">
+      <c r="A390" s="9" t="s">
+        <v>951</v>
+      </c>
+      <c r="B390" s="36"/>
+      <c r="C390" s="36"/>
+      <c r="D390" s="36"/>
+      <c r="E390" s="36"/>
+      <c r="F390" s="36"/>
+      <c r="G390" s="36"/>
+      <c r="H390" s="61"/>
+      <c r="I390" s="61"/>
+    </row>
+    <row r="391" spans="1:9">
+      <c r="A391" s="9" t="s">
+        <v>952</v>
+      </c>
+      <c r="B391" s="36"/>
+      <c r="C391" s="36"/>
+      <c r="D391" s="36"/>
+      <c r="E391" s="36"/>
+      <c r="F391" s="36"/>
+      <c r="G391" s="36"/>
+      <c r="H391" s="61"/>
+      <c r="I391" s="61"/>
+    </row>
+    <row r="392" spans="1:9">
+      <c r="A392" s="9" t="s">
+        <v>953</v>
+      </c>
+      <c r="B392" s="36"/>
+      <c r="C392" s="36"/>
+      <c r="D392" s="36"/>
+      <c r="E392" s="36"/>
+      <c r="F392" s="36"/>
+      <c r="G392" s="36"/>
+      <c r="H392" s="61"/>
+      <c r="I392" s="61"/>
+    </row>
+    <row r="393" spans="1:9">
+      <c r="A393" s="9" t="s">
+        <v>954</v>
+      </c>
+      <c r="B393" s="36"/>
+      <c r="C393" s="36"/>
+      <c r="D393" s="36"/>
+      <c r="E393" s="36"/>
+      <c r="F393" s="36"/>
+      <c r="G393" s="36"/>
+      <c r="H393" s="61"/>
+      <c r="I393" s="61"/>
+    </row>
+    <row r="394" spans="1:9">
+      <c r="A394" s="9" t="s">
+        <v>955</v>
+      </c>
+      <c r="B394" s="36"/>
+      <c r="C394" s="36"/>
+      <c r="D394" s="36"/>
+      <c r="E394" s="36"/>
+      <c r="F394" s="36"/>
+      <c r="G394" s="36"/>
+      <c r="H394" s="61"/>
+      <c r="I394" s="61"/>
+    </row>
+    <row r="395" spans="1:9">
+      <c r="A395" s="9" t="s">
+        <v>956</v>
+      </c>
+      <c r="B395" s="36"/>
+      <c r="C395" s="36"/>
+      <c r="D395" s="36"/>
+      <c r="E395" s="36"/>
+      <c r="F395" s="36"/>
+      <c r="G395" s="36"/>
+      <c r="H395" s="61"/>
+      <c r="I395" s="61"/>
+    </row>
+    <row r="396" spans="1:9">
+      <c r="A396" s="9" t="s">
+        <v>957</v>
+      </c>
+      <c r="B396" s="36"/>
+      <c r="C396" s="36"/>
+      <c r="D396" s="36"/>
+      <c r="E396" s="36"/>
+      <c r="F396" s="36"/>
+      <c r="G396" s="36"/>
+      <c r="H396" s="61"/>
+      <c r="I396" s="61"/>
+    </row>
+    <row r="397" spans="1:9">
+      <c r="A397" s="9" t="s">
+        <v>958</v>
+      </c>
+      <c r="B397" s="36"/>
+      <c r="C397" s="36"/>
+      <c r="D397" s="36"/>
+      <c r="E397" s="36"/>
+      <c r="F397" s="36"/>
+      <c r="G397" s="36"/>
+      <c r="H397" s="61"/>
+      <c r="I397" s="61"/>
+    </row>
+    <row r="398" spans="1:9">
+      <c r="A398" s="9" t="s">
+        <v>959</v>
+      </c>
+      <c r="B398" s="36"/>
+      <c r="C398" s="36"/>
+      <c r="D398" s="36"/>
+      <c r="E398" s="36"/>
+      <c r="F398" s="36"/>
+      <c r="G398" s="36"/>
+      <c r="H398" s="61"/>
+      <c r="I398" s="61"/>
+    </row>
+    <row r="399" spans="1:9">
+      <c r="A399" s="9" t="s">
+        <v>960</v>
+      </c>
+      <c r="B399" s="36"/>
+      <c r="C399" s="36"/>
+      <c r="D399" s="36"/>
+      <c r="E399" s="36"/>
+      <c r="F399" s="36"/>
+      <c r="G399" s="36"/>
+      <c r="H399" s="61"/>
+      <c r="I399" s="61"/>
+    </row>
+    <row r="400" spans="1:9">
+      <c r="A400" s="9" t="s">
+        <v>961</v>
+      </c>
+      <c r="B400" s="36"/>
+      <c r="C400" s="36"/>
+      <c r="D400" s="36"/>
+      <c r="E400" s="36"/>
+      <c r="F400" s="36"/>
+      <c r="G400" s="36"/>
+      <c r="H400" s="61"/>
+      <c r="I400" s="61"/>
+    </row>
+    <row r="401" spans="1:9">
+      <c r="A401" s="9" t="s">
+        <v>962</v>
+      </c>
+      <c r="B401" s="36"/>
+      <c r="C401" s="36"/>
+      <c r="D401" s="36"/>
+      <c r="E401" s="36"/>
+      <c r="F401" s="36"/>
+      <c r="G401" s="36"/>
+      <c r="H401" s="61"/>
+      <c r="I401" s="61"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/产品规格.xlsx
+++ b/产品规格.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4507"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="90" windowWidth="19200" windowHeight="11640"/>
@@ -11,12 +11,12 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1301" uniqueCount="966">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1293" uniqueCount="977">
   <si>
     <t>17.5*3*27</t>
   </si>
@@ -1660,9 +1660,6 @@
   </si>
   <si>
     <t>XC235</t>
-  </si>
-  <si>
-    <t>米克350</t>
   </si>
   <si>
     <t>XC236</t>
@@ -2137,537 +2134,841 @@
   </si>
   <si>
     <t>XC001</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>1*1半光横条</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>75*75*150</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>22*3*38</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>22*3*39</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>14*2*25</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>22*3*40</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>17*3*28</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>25梭T400无捻牛津</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>27梭T400无捻牛津</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>26梭T400无捻牛津</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>17*2*26</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">50S*50S弹力 酷丝棉平纹  </t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>17*2*30</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>50S*50S</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*40S弹力 酷丝棉平纹  </t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>18*2*27</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*40S</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*75T 酷丝棉平纹  </t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*75D 酷丝棉2/1</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*75D 酷丝棉2/2 </t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*150 酷丝棉26S平纹  </t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*150 酷丝棉2/1 </t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*150D 酷丝棉2/2 </t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*150 酷丝棉28S平纹  </t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*150 酷丝棉24S平纹  </t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*150 酷丝棉3/3斜  </t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">50S*75D 酷丝棉2/2 </t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>50S*75D 酷丝棉绮兵</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*75 酷丝棉3/3斜  </t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>13.5*4*35</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*75T400</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">50S*75D 酷丝棉2/1 </t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>XC186</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>17.5*3*35</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*75 酷丝棉3/2斜  </t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>17.5*3*34</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*75DT400</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*150 酷丝棉5/1斜  </t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100*150T8 4/2斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>17*4*215*40</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100D*150T800</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75*150T400 消3/3斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>17*4*36</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75*75T400消 3/3斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75*75 半光2/2 斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>18*4*46</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75*75 消光2/2 斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>18*4*43</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75*150 消光2/2 斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75*75-T800消光骑士斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>17*4*38</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75消*75T800</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>19*5*45</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>19*3*39</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>X字格</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>16*4*46</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>T400横条2*1</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>16*4+28</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>238克</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>T400横条1*4</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>17*4+38</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>75*75*150</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>白坯200米克</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>T400横条1*1</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>16*4*30</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>100*75*150</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*75闪电斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>18*3*38</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*75</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*150酷丝绵 小钻石斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*150酷丝绵 大钻石斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*300 3/2变化斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>13.5*4*28</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*150*2T400</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>米克385</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100D半光*35S-3/3斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>16*4*40</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100*35</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>100D消光*35S-3/3斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>100*35S</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>120D扁平3/3斜-45</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>16*4*45</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>120*35S</t>
-  </si>
-  <si>
-    <t>100D消光*35S-3/3斜</t>
-  </si>
-  <si>
-    <t>100*35S</t>
-  </si>
-  <si>
-    <t>16*4*45</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>米克370</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>120D扁平4/4斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>17*4*45</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>米克375</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100D消光多乐3/3斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>15*4*43</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>米克300</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>120D扁平1/2斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>17*4*34</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>米克350</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>120D扁平T800变化斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>17*4*29</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>120*150T800</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>米克380</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>120D扁平牛津</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>20*2*31</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*75 酷丝棉3/1斜 </t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>13.5*4*34</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*150 酷丝棉3/1斜 31</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*150 酷丝棉3/2斜 39</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*75D 酷丝棉2/1 30</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>17*3*30</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*75D 酷丝棉2/2 30</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*75D 酷丝棉2/2 38</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*75D 骑兵斜 30 </t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*75D 骑兵斜 38 </t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*300 酷丝棉3/2斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>13.5*4*27</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*75T 酷丝棉平纹 33S </t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*300酷丝绵珍珠点</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>17.5*3*25</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*150*300T400</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>米克368</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*75D酷丝绵细双斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>17.5*3*36</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*150T400+300T400</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>80S*75双线格酷丝绵</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75 T800半光0.5格</t>
-  </si>
-  <si>
-    <t>20*2*36</t>
-  </si>
-  <si>
-    <t>75*75*225</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>75*75*210</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>50D经纬 T8 0.5格</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>22*2*40</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>50*50</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>半光大猫眼</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>16*4*43</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100半低*150半T800</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>50D低弹*50T800 平纹</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>23*2*40</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>30D T8 平纹</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>22*3*57</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>30*30</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75D经纬T8平纹</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75经纬T8 2/2斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>19*3*38</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">50DT8*50DT8 骑兵斜  </t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>21*3*53</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>50DT8*50DT8</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>T8五面埋伏</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>14*4*38</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>50D*100D经纬T800珍珠点</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>21*3*49</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>50D*50D*100D T800</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>T800双链条</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>米克265</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>经消光低弹 双纬T800</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75D半光T800双纬平纹</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75消低弹*75T8002/2斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>17.5*4*38</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*150T800酷丝棉3/2斜  </t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*150T800</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>空变T8平纹</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*75T8酷丝棉3/1.超钛棉</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>17.5*3*44</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*75T800</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*300加厚超钛棉</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>14*4*27</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*300T800</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>白坯370克</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100D消光75DT800 3/3斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>15.5*4*48</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100*75T8</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>米克250</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>37梭多乐绵</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>16*4*37</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>100D*40S+150D T8</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>21*3*45</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>白坯188克</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">斜纹毛巾底 </t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>13.5*4*51</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*150T8*300低弹</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>18*3*43</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>网纹3/3-180</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>17*4*44</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75D*50S+10DT8</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>白坯米克245</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>网纹3/3-220</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>15*4*44</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100D*35S+150DT8</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>白坯3</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>00克</t>
+    </r>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>天丝棉</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>20*3*32</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>80S*三合一</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>白坯195克</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>21*3*31</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>270-钛金棉</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>14*4*26.5</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*35S*2</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>白坯365克</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*35S 酷3/3斜 </t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>16*4*44</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*35S</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>210-钛金棉</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>17*3*27</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*30S</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>白坯285克</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>加厚钛金棉</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>15.5*4*30</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>白坯390克</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>240-钛金棉</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>17.5*3*31</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>白坯310克</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*35S 酷3/3斜  加厚 </t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>16*4*31</t>
-  </si>
-  <si>
-    <t>17*4*215*40</t>
-  </si>
-  <si>
-    <t>16*4+28</t>
-  </si>
-  <si>
-    <t>238克</t>
-  </si>
-  <si>
-    <t>16*4*40</t>
-  </si>
-  <si>
-    <t>120*150T800</t>
-  </si>
-  <si>
-    <t>120D扁平牛津</t>
-  </si>
-  <si>
-    <t>20*2*31</t>
-  </si>
-  <si>
-    <t>37梭多乐绵</t>
-  </si>
-  <si>
-    <t>16*4*37</t>
-  </si>
-  <si>
-    <t>白坯300克</t>
-  </si>
-  <si>
-    <t>16*4*44</t>
-  </si>
-  <si>
-    <t>白坯368克</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>XC325</t>
@@ -2872,61 +3173,13 @@
   </si>
   <si>
     <t>XC392</t>
-  </si>
-  <si>
-    <t>XC393</t>
-  </si>
-  <si>
-    <t>XC394</t>
-  </si>
-  <si>
-    <t>XC395</t>
-  </si>
-  <si>
-    <t>XC396</t>
-  </si>
-  <si>
-    <t>XC397</t>
-  </si>
-  <si>
-    <t>XC398</t>
-  </si>
-  <si>
-    <t>XC399</t>
-  </si>
-  <si>
-    <t>XC400</t>
-  </si>
-  <si>
-    <t>120D扁平3/3斜-45</t>
-  </si>
-  <si>
-    <t>17*4*45</t>
-  </si>
-  <si>
-    <t>米克368</t>
-  </si>
-  <si>
-    <t>40S*300加厚超钛棉</t>
-  </si>
-  <si>
-    <t>14*4*27</t>
-  </si>
-  <si>
-    <t>40S*300T800</t>
-  </si>
-  <si>
-    <t>白坯370克</t>
-  </si>
-  <si>
-    <t>100D*40S+150D T8</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2999,6 +3252,13 @@
       <b/>
       <sz val="9"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -3745,7 +4005,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:M401"/>
+  <dimension ref="A1:M393"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="9" width="9" style="4"/>
@@ -3756,54 +4016,54 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
+        <v>691</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>692</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>693</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>694</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>695</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>696</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>697</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>698</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>699</v>
       </c>
-      <c r="I1" s="3" t="s">
-        <v>700</v>
-      </c>
       <c r="J1" s="5" t="s">
+        <v>689</v>
+      </c>
+      <c r="K1" s="5" t="s">
         <v>690</v>
       </c>
-      <c r="K1" s="5" t="s">
-        <v>691</v>
-      </c>
       <c r="L1" s="5" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="9" t="s">
+        <v>703</v>
+      </c>
+      <c r="B2" s="10" t="s">
         <v>704</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>705</v>
       </c>
       <c r="C2" s="10" t="s">
         <v>0</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>4</v>
+        <v>705</v>
       </c>
       <c r="E2" s="10">
         <v>79</v>
@@ -3817,13 +4077,13 @@
       </c>
       <c r="I2" s="11"/>
       <c r="J2" s="7" t="s">
+        <v>701</v>
+      </c>
+      <c r="K2" s="7" t="s">
+        <v>700</v>
+      </c>
+      <c r="L2" s="8" t="s">
         <v>702</v>
-      </c>
-      <c r="K2" s="7" t="s">
-        <v>701</v>
-      </c>
-      <c r="L2" s="8" t="s">
-        <v>703</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -5694,7 +5954,7 @@
         <v>193</v>
       </c>
       <c r="C77" s="10" t="s">
-        <v>73</v>
+        <v>709</v>
       </c>
       <c r="D77" s="10" t="s">
         <v>144</v>
@@ -6632,7 +6892,7 @@
         <v>165</v>
       </c>
       <c r="H114" s="11">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="I114" s="11"/>
     </row>
@@ -7044,7 +7304,7 @@
         <v>330</v>
       </c>
       <c r="C131" s="24" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="D131" s="24" t="s">
         <v>148</v>
@@ -7803,7 +8063,7 @@
         <v>412</v>
       </c>
       <c r="B161" s="22" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="C161" s="22" t="s">
         <v>413</v>
@@ -7884,7 +8144,7 @@
         <v>421</v>
       </c>
       <c r="B164" s="22" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C164" s="22" t="s">
         <v>422</v>
@@ -7911,10 +8171,10 @@
         <v>423</v>
       </c>
       <c r="B165" s="22" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="C165" s="22" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="D165" s="22" t="s">
         <v>414</v>
@@ -7951,13 +8211,13 @@
         <v>425</v>
       </c>
       <c r="B167" s="18" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C167" s="18" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="D167" s="18" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="E167" s="18">
         <v>80</v>
@@ -7978,13 +8238,13 @@
         <v>426</v>
       </c>
       <c r="B168" s="18" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="C168" s="18" t="s">
-        <v>417</v>
+        <v>719</v>
       </c>
       <c r="D168" s="18" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="E168" s="18">
         <v>110</v>
@@ -8005,7 +8265,7 @@
         <v>427</v>
       </c>
       <c r="B169" s="18" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="C169" s="18" t="s">
         <v>428</v>
@@ -8032,7 +8292,7 @@
         <v>430</v>
       </c>
       <c r="B170" s="18" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="C170" s="18" t="s">
         <v>431</v>
@@ -8059,7 +8319,7 @@
         <v>432</v>
       </c>
       <c r="B171" s="18" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="C171" s="18" t="s">
         <v>238</v>
@@ -8104,7 +8364,7 @@
         <v>215</v>
       </c>
       <c r="H172" s="18">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="I172" s="32"/>
     </row>
@@ -8113,7 +8373,7 @@
         <v>435</v>
       </c>
       <c r="B173" s="18" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="C173" s="18" t="s">
         <v>436</v>
@@ -8140,7 +8400,7 @@
         <v>438</v>
       </c>
       <c r="B174" s="18" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="C174" s="18" t="s">
         <v>439</v>
@@ -8167,7 +8427,7 @@
         <v>440</v>
       </c>
       <c r="B175" s="18" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="C175" s="18" t="s">
         <v>32</v>
@@ -8248,7 +8508,7 @@
         <v>446</v>
       </c>
       <c r="B178" s="18" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="C178" s="18" t="s">
         <v>420</v>
@@ -8302,7 +8562,7 @@
         <v>450</v>
       </c>
       <c r="B180" s="18" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="C180" s="18" t="s">
         <v>451</v>
@@ -8329,7 +8589,7 @@
         <v>452</v>
       </c>
       <c r="B181" s="18" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="C181" s="18" t="s">
         <v>445</v>
@@ -8356,7 +8616,7 @@
         <v>453</v>
       </c>
       <c r="B182" s="34" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="C182" s="34" t="s">
         <v>309</v>
@@ -8383,7 +8643,7 @@
         <v>455</v>
       </c>
       <c r="B183" s="34" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="C183" s="34" t="s">
         <v>309</v>
@@ -8437,13 +8697,13 @@
         <v>460</v>
       </c>
       <c r="B185" s="18" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="C185" s="18" t="s">
-        <v>445</v>
+        <v>733</v>
       </c>
       <c r="D185" s="18" t="s">
-        <v>429</v>
+        <v>734</v>
       </c>
       <c r="E185" s="18">
         <v>112</v>
@@ -8464,7 +8724,7 @@
         <v>461</v>
       </c>
       <c r="B186" s="34" t="s">
-        <v>731</v>
+        <v>735</v>
       </c>
       <c r="C186" s="34" t="s">
         <v>309</v>
@@ -8488,13 +8748,13 @@
     </row>
     <row r="187" spans="1:9">
       <c r="A187" s="9" t="s">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="B187" s="18" t="s">
         <v>442</v>
       </c>
       <c r="C187" s="18" t="s">
-        <v>238</v>
+        <v>737</v>
       </c>
       <c r="D187" s="18" t="s">
         <v>437</v>
@@ -8518,13 +8778,13 @@
         <v>462</v>
       </c>
       <c r="B188" s="18" t="s">
-        <v>733</v>
+        <v>738</v>
       </c>
       <c r="C188" s="18" t="s">
-        <v>272</v>
+        <v>739</v>
       </c>
       <c r="D188" s="18" t="s">
-        <v>734</v>
+        <v>740</v>
       </c>
       <c r="E188" s="18">
         <v>110</v>
@@ -8545,7 +8805,7 @@
         <v>463</v>
       </c>
       <c r="B189" s="18" t="s">
-        <v>735</v>
+        <v>741</v>
       </c>
       <c r="C189" s="18" t="s">
         <v>445</v>
@@ -8572,13 +8832,13 @@
         <v>464</v>
       </c>
       <c r="B190" s="10" t="s">
-        <v>736</v>
+        <v>742</v>
       </c>
       <c r="C190" s="10" t="s">
-        <v>870</v>
+        <v>743</v>
       </c>
       <c r="D190" s="10" t="s">
-        <v>737</v>
+        <v>744</v>
       </c>
       <c r="E190" s="11">
         <v>152</v>
@@ -8599,10 +8859,10 @@
         <v>465</v>
       </c>
       <c r="B191" s="18" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="C191" s="18" t="s">
-        <v>238</v>
+        <v>737</v>
       </c>
       <c r="D191" s="18" t="s">
         <v>437</v>
@@ -8652,10 +8912,10 @@
         <v>468</v>
       </c>
       <c r="B194" s="41" t="s">
-        <v>738</v>
+        <v>745</v>
       </c>
       <c r="C194" s="42" t="s">
-        <v>385</v>
+        <v>746</v>
       </c>
       <c r="D194" s="43" t="s">
         <v>148</v>
@@ -8679,7 +8939,7 @@
         <v>469</v>
       </c>
       <c r="B195" s="41" t="s">
-        <v>739</v>
+        <v>747</v>
       </c>
       <c r="C195" s="42" t="s">
         <v>470</v>
@@ -8706,10 +8966,10 @@
         <v>471</v>
       </c>
       <c r="B196" s="45" t="s">
-        <v>740</v>
+        <v>748</v>
       </c>
       <c r="C196" s="45" t="s">
-        <v>741</v>
+        <v>749</v>
       </c>
       <c r="D196" s="45" t="s">
         <v>472</v>
@@ -8733,10 +8993,10 @@
         <v>473</v>
       </c>
       <c r="B197" s="45" t="s">
-        <v>742</v>
+        <v>750</v>
       </c>
       <c r="C197" s="45" t="s">
-        <v>389</v>
+        <v>751</v>
       </c>
       <c r="D197" s="45" t="s">
         <v>386</v>
@@ -8760,7 +9020,7 @@
         <v>474</v>
       </c>
       <c r="B198" s="45" t="s">
-        <v>743</v>
+        <v>752</v>
       </c>
       <c r="C198" s="45" t="s">
         <v>475</v>
@@ -8787,13 +9047,13 @@
         <v>477</v>
       </c>
       <c r="B199" s="45" t="s">
-        <v>744</v>
+        <v>753</v>
       </c>
       <c r="C199" s="45" t="s">
-        <v>401</v>
+        <v>754</v>
       </c>
       <c r="D199" s="45" t="s">
-        <v>745</v>
+        <v>755</v>
       </c>
       <c r="E199" s="45">
         <v>95</v>
@@ -8971,13 +9231,13 @@
         <v>496</v>
       </c>
       <c r="C208" s="10" t="s">
-        <v>746</v>
+        <v>756</v>
       </c>
       <c r="D208" s="10" t="s">
         <v>39</v>
       </c>
       <c r="E208" s="10">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="F208" s="36">
         <v>150</v>
@@ -8986,7 +9246,7 @@
         <v>170</v>
       </c>
       <c r="H208" s="10">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="I208" s="11"/>
     </row>
@@ -9034,7 +9294,7 @@
         <v>501</v>
       </c>
       <c r="C211" s="10" t="s">
-        <v>747</v>
+        <v>757</v>
       </c>
       <c r="D211" s="10" t="s">
         <v>39</v>
@@ -9056,10 +9316,10 @@
         <v>502</v>
       </c>
       <c r="B212" s="35" t="s">
-        <v>748</v>
+        <v>758</v>
       </c>
       <c r="C212" s="35" t="s">
-        <v>749</v>
+        <v>759</v>
       </c>
       <c r="D212" s="35" t="s">
         <v>144</v>
@@ -9111,7 +9371,7 @@
         <v>507</v>
       </c>
       <c r="C214" s="35" t="s">
-        <v>749</v>
+        <v>759</v>
       </c>
       <c r="D214" s="35" t="s">
         <v>144</v>
@@ -9224,10 +9484,10 @@
         <v>519</v>
       </c>
       <c r="B220" s="10" t="s">
-        <v>750</v>
+        <v>760</v>
       </c>
       <c r="C220" s="10" t="s">
-        <v>871</v>
+        <v>761</v>
       </c>
       <c r="D220" s="49" t="s">
         <v>520</v>
@@ -9245,7 +9505,7 @@
         <v>3.4</v>
       </c>
       <c r="I220" s="11" t="s">
-        <v>872</v>
+        <v>762</v>
       </c>
     </row>
     <row r="221" spans="1:9">
@@ -9253,13 +9513,13 @@
         <v>521</v>
       </c>
       <c r="B221" s="10" t="s">
-        <v>751</v>
+        <v>763</v>
       </c>
       <c r="C221" s="10" t="s">
-        <v>752</v>
+        <v>764</v>
       </c>
       <c r="D221" s="49" t="s">
-        <v>4</v>
+        <v>765</v>
       </c>
       <c r="E221" s="10">
         <v>100</v>
@@ -9274,7 +9534,7 @@
         <v>3.3</v>
       </c>
       <c r="I221" s="37" t="s">
-        <v>753</v>
+        <v>766</v>
       </c>
     </row>
     <row r="222" spans="1:9">
@@ -9282,13 +9542,13 @@
         <v>522</v>
       </c>
       <c r="B222" s="10" t="s">
-        <v>754</v>
+        <v>767</v>
       </c>
       <c r="C222" s="10" t="s">
-        <v>755</v>
+        <v>768</v>
       </c>
       <c r="D222" s="49" t="s">
-        <v>520</v>
+        <v>769</v>
       </c>
       <c r="E222" s="10">
         <v>115</v>
@@ -9336,13 +9596,13 @@
         <v>526</v>
       </c>
       <c r="B224" s="35" t="s">
-        <v>756</v>
+        <v>770</v>
       </c>
       <c r="C224" s="35" t="s">
-        <v>757</v>
+        <v>771</v>
       </c>
       <c r="D224" s="35" t="s">
-        <v>758</v>
+        <v>772</v>
       </c>
       <c r="E224" s="35">
         <v>120</v>
@@ -9354,7 +9614,7 @@
         <v>215</v>
       </c>
       <c r="H224" s="35">
-        <v>5</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="I224" s="37"/>
     </row>
@@ -9381,7 +9641,7 @@
         <v>215</v>
       </c>
       <c r="H225" s="35">
-        <v>4.9000000000000004</v>
+        <v>4.8</v>
       </c>
       <c r="I225" s="11"/>
     </row>
@@ -9390,10 +9650,10 @@
         <v>530</v>
       </c>
       <c r="B226" s="35" t="s">
-        <v>759</v>
+        <v>773</v>
       </c>
       <c r="C226" s="35" t="s">
-        <v>238</v>
+        <v>737</v>
       </c>
       <c r="D226" s="35" t="s">
         <v>437</v>
@@ -9417,10 +9677,10 @@
         <v>531</v>
       </c>
       <c r="B227" s="35" t="s">
-        <v>760</v>
+        <v>774</v>
       </c>
       <c r="C227" s="35" t="s">
-        <v>238</v>
+        <v>737</v>
       </c>
       <c r="D227" s="35" t="s">
         <v>437</v>
@@ -9516,7 +9776,7 @@
         <v>215</v>
       </c>
       <c r="H230" s="51">
-        <v>4.9000000000000004</v>
+        <v>4.8</v>
       </c>
       <c r="I230" s="11"/>
     </row>
@@ -9574,13 +9834,13 @@
         <v>544</v>
       </c>
       <c r="B234" s="52" t="s">
-        <v>761</v>
+        <v>775</v>
       </c>
       <c r="C234" s="52" t="s">
-        <v>762</v>
+        <v>776</v>
       </c>
       <c r="D234" s="50" t="s">
-        <v>763</v>
+        <v>777</v>
       </c>
       <c r="E234" s="52">
         <v>190</v>
@@ -9595,7 +9855,7 @@
         <v>5.8</v>
       </c>
       <c r="I234" s="54" t="s">
-        <v>764</v>
+        <v>778</v>
       </c>
     </row>
     <row r="235" spans="1:9">
@@ -9603,13 +9863,13 @@
         <v>545</v>
       </c>
       <c r="B235" s="51" t="s">
-        <v>765</v>
+        <v>779</v>
       </c>
       <c r="C235" s="51" t="s">
-        <v>873</v>
+        <v>780</v>
       </c>
       <c r="D235" s="51" t="s">
-        <v>766</v>
+        <v>781</v>
       </c>
       <c r="E235" s="51">
         <v>155</v>
@@ -9642,16 +9902,16 @@
     </row>
     <row r="237" spans="1:9">
       <c r="A237" s="9" t="s">
+        <v>548</v>
+      </c>
+      <c r="B237" s="51" t="s">
+        <v>782</v>
+      </c>
+      <c r="C237" s="51" t="s">
         <v>549</v>
       </c>
-      <c r="B237" s="51" t="s">
-        <v>768</v>
-      </c>
-      <c r="C237" s="51" t="s">
-        <v>550</v>
-      </c>
       <c r="D237" s="51" t="s">
-        <v>769</v>
+        <v>783</v>
       </c>
       <c r="E237" s="51">
         <v>155</v>
@@ -9663,7 +9923,7 @@
         <v>218</v>
       </c>
       <c r="H237" s="51">
-        <v>4.9000000000000004</v>
+        <v>4.8</v>
       </c>
       <c r="I237" s="55" t="s">
         <v>546</v>
@@ -9671,7 +9931,7 @@
     </row>
     <row r="238" spans="1:9">
       <c r="A238" s="9" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B238" s="38"/>
       <c r="C238" s="38"/>
@@ -9684,16 +9944,16 @@
     </row>
     <row r="239" spans="1:9">
       <c r="A239" s="9" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B239" s="51" t="s">
-        <v>958</v>
+        <v>784</v>
       </c>
       <c r="C239" s="51" t="s">
-        <v>770</v>
+        <v>785</v>
       </c>
       <c r="D239" s="51" t="s">
-        <v>767</v>
+        <v>786</v>
       </c>
       <c r="E239" s="52">
         <v>180</v>
@@ -9705,24 +9965,24 @@
         <v>220</v>
       </c>
       <c r="H239" s="51">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="I239" s="54" t="s">
-        <v>771</v>
+        <v>787</v>
       </c>
     </row>
     <row r="240" spans="1:9">
       <c r="A240" s="9" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B240" s="51" t="s">
-        <v>772</v>
+        <v>788</v>
       </c>
       <c r="C240" s="51" t="s">
-        <v>959</v>
+        <v>789</v>
       </c>
       <c r="D240" s="51" t="s">
-        <v>767</v>
+        <v>786</v>
       </c>
       <c r="E240" s="52">
         <v>190</v>
@@ -9734,24 +9994,24 @@
         <v>225</v>
       </c>
       <c r="H240" s="35">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="I240" s="54" t="s">
-        <v>773</v>
+        <v>790</v>
       </c>
     </row>
     <row r="241" spans="1:9">
       <c r="A241" s="9" t="s">
+        <v>553</v>
+      </c>
+      <c r="B241" s="51" t="s">
+        <v>791</v>
+      </c>
+      <c r="C241" s="51" t="s">
+        <v>792</v>
+      </c>
+      <c r="D241" s="11" t="s">
         <v>554</v>
-      </c>
-      <c r="B241" s="51" t="s">
-        <v>774</v>
-      </c>
-      <c r="C241" s="51" t="s">
-        <v>775</v>
-      </c>
-      <c r="D241" s="11" t="s">
-        <v>555</v>
       </c>
       <c r="E241" s="51">
         <v>150</v>
@@ -9766,21 +10026,21 @@
         <v>5.2</v>
       </c>
       <c r="I241" s="55" t="s">
-        <v>776</v>
+        <v>793</v>
       </c>
     </row>
     <row r="242" spans="1:9">
       <c r="A242" s="9" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B242" s="51" t="s">
-        <v>777</v>
+        <v>794</v>
       </c>
       <c r="C242" s="51" t="s">
-        <v>778</v>
+        <v>795</v>
       </c>
       <c r="D242" s="51" t="s">
-        <v>767</v>
+        <v>786</v>
       </c>
       <c r="E242" s="52">
         <v>160</v>
@@ -9795,21 +10055,21 @@
         <v>4.9000000000000004</v>
       </c>
       <c r="I242" s="54" t="s">
-        <v>548</v>
+        <v>796</v>
       </c>
     </row>
     <row r="243" spans="1:9">
       <c r="A243" s="9" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B243" s="51" t="s">
-        <v>779</v>
+        <v>797</v>
       </c>
       <c r="C243" s="51" t="s">
-        <v>780</v>
+        <v>798</v>
       </c>
       <c r="D243" s="51" t="s">
-        <v>874</v>
+        <v>799</v>
       </c>
       <c r="E243" s="52">
         <v>190</v>
@@ -9824,21 +10084,21 @@
         <v>5.6</v>
       </c>
       <c r="I243" s="54" t="s">
-        <v>781</v>
+        <v>800</v>
       </c>
     </row>
     <row r="244" spans="1:9">
       <c r="A244" s="9" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B244" s="51" t="s">
-        <v>875</v>
+        <v>801</v>
       </c>
       <c r="C244" s="51" t="s">
-        <v>876</v>
+        <v>802</v>
       </c>
       <c r="D244" s="51" t="s">
-        <v>874</v>
+        <v>799</v>
       </c>
       <c r="E244" s="51">
         <v>150</v>
@@ -9848,13 +10108,13 @@
         <v>220</v>
       </c>
       <c r="H244" s="35">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="I244" s="54"/>
     </row>
     <row r="245" spans="1:9">
       <c r="A245" s="9" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B245" s="38"/>
       <c r="C245" s="38"/>
@@ -9867,16 +10127,16 @@
     </row>
     <row r="246" spans="1:9">
       <c r="A246" s="9" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B246" s="18" t="s">
-        <v>782</v>
+        <v>803</v>
       </c>
       <c r="C246" s="18" t="s">
-        <v>783</v>
+        <v>804</v>
       </c>
       <c r="D246" s="33" t="s">
-        <v>429</v>
+        <v>734</v>
       </c>
       <c r="E246" s="18">
         <v>112</v>
@@ -9888,16 +10148,16 @@
         <v>215</v>
       </c>
       <c r="H246" s="18">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="I246" s="37"/>
     </row>
     <row r="247" spans="1:9">
       <c r="A247" s="31" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B247" s="18" t="s">
-        <v>784</v>
+        <v>805</v>
       </c>
       <c r="C247" s="18" t="s">
         <v>529</v>
@@ -9921,13 +10181,13 @@
     </row>
     <row r="248" spans="1:9">
       <c r="A248" s="31" t="s">
+        <v>561</v>
+      </c>
+      <c r="B248" s="18" t="s">
+        <v>806</v>
+      </c>
+      <c r="C248" s="18" t="s">
         <v>562</v>
-      </c>
-      <c r="B248" s="18" t="s">
-        <v>785</v>
-      </c>
-      <c r="C248" s="18" t="s">
-        <v>563</v>
       </c>
       <c r="D248" s="18" t="s">
         <v>437</v>
@@ -9942,19 +10202,19 @@
         <v>215</v>
       </c>
       <c r="H248" s="18">
-        <v>5</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="I248" s="57"/>
     </row>
     <row r="249" spans="1:9">
       <c r="A249" s="31" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B249" s="18" t="s">
-        <v>786</v>
+        <v>807</v>
       </c>
       <c r="C249" s="18" t="s">
-        <v>439</v>
+        <v>808</v>
       </c>
       <c r="D249" s="18" t="s">
         <v>429</v>
@@ -9975,10 +10235,10 @@
     </row>
     <row r="250" spans="1:9">
       <c r="A250" s="31" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B250" s="18" t="s">
-        <v>787</v>
+        <v>809</v>
       </c>
       <c r="C250" s="18" t="s">
         <v>153</v>
@@ -10002,13 +10262,13 @@
     </row>
     <row r="251" spans="1:9">
       <c r="A251" s="31" t="s">
+        <v>565</v>
+      </c>
+      <c r="B251" s="18" t="s">
+        <v>810</v>
+      </c>
+      <c r="C251" s="18" t="s">
         <v>566</v>
-      </c>
-      <c r="B251" s="18" t="s">
-        <v>788</v>
-      </c>
-      <c r="C251" s="18" t="s">
-        <v>567</v>
       </c>
       <c r="D251" s="18" t="s">
         <v>429</v>
@@ -10023,19 +10283,19 @@
         <v>215</v>
       </c>
       <c r="H251" s="18">
-        <v>4.2</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="I251" s="32"/>
     </row>
     <row r="252" spans="1:9">
       <c r="A252" s="31" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B252" s="18" t="s">
-        <v>789</v>
+        <v>811</v>
       </c>
       <c r="C252" s="18" t="s">
-        <v>439</v>
+        <v>808</v>
       </c>
       <c r="D252" s="18" t="s">
         <v>429</v>
@@ -10050,19 +10310,19 @@
         <v>215</v>
       </c>
       <c r="H252" s="18">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="I252" s="32"/>
     </row>
     <row r="253" spans="1:9">
       <c r="A253" s="31" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B253" s="18" t="s">
-        <v>790</v>
+        <v>812</v>
       </c>
       <c r="C253" s="18" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="D253" s="18" t="s">
         <v>429</v>
@@ -10083,16 +10343,16 @@
     </row>
     <row r="254" spans="1:9">
       <c r="A254" s="31" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B254" s="18" t="s">
-        <v>791</v>
+        <v>813</v>
       </c>
       <c r="C254" s="18" t="s">
-        <v>792</v>
+        <v>814</v>
       </c>
       <c r="D254" s="18" t="s">
-        <v>763</v>
+        <v>777</v>
       </c>
       <c r="E254" s="18">
         <v>190</v>
@@ -10104,21 +10364,21 @@
         <v>215</v>
       </c>
       <c r="H254" s="18">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="I254" s="54" t="s">
-        <v>781</v>
+        <v>800</v>
       </c>
     </row>
     <row r="255" spans="1:9">
       <c r="A255" s="31" t="s">
+        <v>570</v>
+      </c>
+      <c r="B255" s="18" t="s">
+        <v>815</v>
+      </c>
+      <c r="C255" s="18" t="s">
         <v>571</v>
-      </c>
-      <c r="B255" s="18" t="s">
-        <v>793</v>
-      </c>
-      <c r="C255" s="18" t="s">
-        <v>572</v>
       </c>
       <c r="D255" s="18" t="s">
         <v>429</v>
@@ -10139,16 +10399,16 @@
     </row>
     <row r="256" spans="1:9">
       <c r="A256" s="9" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B256" s="52" t="s">
-        <v>794</v>
+        <v>816</v>
       </c>
       <c r="C256" s="18" t="s">
-        <v>161</v>
+        <v>817</v>
       </c>
       <c r="D256" s="50" t="s">
-        <v>795</v>
+        <v>818</v>
       </c>
       <c r="E256" s="52">
         <v>190</v>
@@ -10160,24 +10420,24 @@
         <v>215</v>
       </c>
       <c r="H256" s="60">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="I256" s="54" t="s">
-        <v>960</v>
+        <v>819</v>
       </c>
     </row>
     <row r="257" spans="1:9">
       <c r="A257" s="9" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B257" s="36" t="s">
-        <v>796</v>
+        <v>820</v>
       </c>
       <c r="C257" s="36" t="s">
-        <v>321</v>
+        <v>821</v>
       </c>
       <c r="D257" s="36" t="s">
-        <v>429</v>
+        <v>734</v>
       </c>
       <c r="E257" s="36">
         <v>118</v>
@@ -10189,16 +10449,16 @@
         <v>215</v>
       </c>
       <c r="H257" s="60">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I257" s="60"/>
     </row>
     <row r="258" spans="1:9">
       <c r="A258" s="9" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B258" s="18" t="s">
-        <v>787</v>
+        <v>809</v>
       </c>
       <c r="C258" s="18" t="s">
         <v>153</v>
@@ -10216,13 +10476,13 @@
         <v>215</v>
       </c>
       <c r="H258" s="32">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="I258" s="60"/>
     </row>
     <row r="259" spans="1:9">
       <c r="A259" s="9" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B259" s="36"/>
       <c r="C259" s="36"/>
@@ -10235,7 +10495,7 @@
     </row>
     <row r="260" spans="1:9">
       <c r="A260" s="9" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B260" s="36"/>
       <c r="C260" s="36"/>
@@ -10248,16 +10508,16 @@
     </row>
     <row r="261" spans="1:9">
       <c r="A261" s="9" t="s">
+        <v>577</v>
+      </c>
+      <c r="B261" s="10" t="s">
         <v>578</v>
       </c>
-      <c r="B261" s="10" t="s">
+      <c r="C261" s="10" t="s">
         <v>579</v>
       </c>
-      <c r="C261" s="10" t="s">
-        <v>580</v>
-      </c>
       <c r="D261" s="49" t="s">
-        <v>797</v>
+        <v>822</v>
       </c>
       <c r="E261" s="10">
         <v>108</v>
@@ -10275,16 +10535,16 @@
     </row>
     <row r="262" spans="1:9">
       <c r="A262" s="9" t="s">
+        <v>580</v>
+      </c>
+      <c r="B262" s="10" t="s">
+        <v>823</v>
+      </c>
+      <c r="C262" s="10" t="s">
         <v>581</v>
       </c>
-      <c r="B262" s="10" t="s">
-        <v>798</v>
-      </c>
-      <c r="C262" s="10" t="s">
+      <c r="D262" s="49" t="s">
         <v>582</v>
-      </c>
-      <c r="D262" s="49" t="s">
-        <v>583</v>
       </c>
       <c r="E262" s="10">
         <v>87</v>
@@ -10296,22 +10556,22 @@
         <v>208</v>
       </c>
       <c r="H262" s="10">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="I262" s="60"/>
     </row>
     <row r="263" spans="1:9">
       <c r="A263" s="9" t="s">
+        <v>583</v>
+      </c>
+      <c r="B263" s="27" t="s">
         <v>584</v>
       </c>
-      <c r="B263" s="27" t="s">
+      <c r="C263" s="27" t="s">
         <v>585</v>
       </c>
-      <c r="C263" s="27" t="s">
+      <c r="D263" s="27" t="s">
         <v>586</v>
-      </c>
-      <c r="D263" s="27" t="s">
-        <v>587</v>
       </c>
       <c r="E263" s="27">
         <v>115</v>
@@ -10329,16 +10589,16 @@
     </row>
     <row r="264" spans="1:9">
       <c r="A264" s="9" t="s">
+        <v>587</v>
+      </c>
+      <c r="B264" s="10" t="s">
         <v>588</v>
       </c>
-      <c r="B264" s="10" t="s">
+      <c r="C264" s="10" t="s">
         <v>589</v>
       </c>
-      <c r="C264" s="10" t="s">
+      <c r="D264" s="10" t="s">
         <v>590</v>
-      </c>
-      <c r="D264" s="10" t="s">
-        <v>591</v>
       </c>
       <c r="E264" s="10">
         <v>70</v>
@@ -10356,16 +10616,16 @@
     </row>
     <row r="265" spans="1:9">
       <c r="A265" s="9" t="s">
+        <v>591</v>
+      </c>
+      <c r="B265" s="35" t="s">
         <v>592</v>
       </c>
-      <c r="B265" s="35" t="s">
+      <c r="C265" s="35" t="s">
         <v>593</v>
       </c>
-      <c r="C265" s="35" t="s">
+      <c r="D265" s="35" t="s">
         <v>594</v>
-      </c>
-      <c r="D265" s="35" t="s">
-        <v>595</v>
       </c>
       <c r="E265" s="35">
         <v>102</v>
@@ -10383,16 +10643,16 @@
     </row>
     <row r="266" spans="1:9">
       <c r="A266" s="9" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B266" s="35" t="s">
-        <v>799</v>
+        <v>824</v>
       </c>
       <c r="C266" s="35" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="D266" s="35" t="s">
-        <v>801</v>
+        <v>825</v>
       </c>
       <c r="E266" s="35">
         <v>78</v>
@@ -10410,16 +10670,16 @@
     </row>
     <row r="267" spans="1:9">
       <c r="A267" s="9" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B267" s="10" t="s">
-        <v>802</v>
+        <v>826</v>
       </c>
       <c r="C267" s="10" t="s">
-        <v>803</v>
+        <v>827</v>
       </c>
       <c r="D267" s="49" t="s">
-        <v>144</v>
+        <v>828</v>
       </c>
       <c r="E267" s="10">
         <v>60</v>
@@ -10437,7 +10697,7 @@
     </row>
     <row r="268" spans="1:9">
       <c r="A268" s="9" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B268" s="36"/>
       <c r="C268" s="36"/>
@@ -10450,7 +10710,7 @@
     </row>
     <row r="269" spans="1:9">
       <c r="A269" s="9" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B269" s="36"/>
       <c r="C269" s="36"/>
@@ -10463,7 +10723,7 @@
     </row>
     <row r="270" spans="1:9">
       <c r="A270" s="9" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B270" s="36"/>
       <c r="C270" s="36"/>
@@ -10476,7 +10736,7 @@
     </row>
     <row r="271" spans="1:9">
       <c r="A271" s="9" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B271" s="36"/>
       <c r="C271" s="36"/>
@@ -10489,7 +10749,7 @@
     </row>
     <row r="272" spans="1:9">
       <c r="A272" s="9" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B272" s="36"/>
       <c r="C272" s="36"/>
@@ -10502,7 +10762,7 @@
     </row>
     <row r="273" spans="1:9">
       <c r="A273" s="9" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B273" s="36"/>
       <c r="C273" s="36"/>
@@ -10515,7 +10775,7 @@
     </row>
     <row r="274" spans="1:9">
       <c r="A274" s="9" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B274" s="36"/>
       <c r="C274" s="36"/>
@@ -10528,7 +10788,7 @@
     </row>
     <row r="275" spans="1:9">
       <c r="A275" s="9" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B275" s="36"/>
       <c r="C275" s="36"/>
@@ -10541,7 +10801,7 @@
     </row>
     <row r="276" spans="1:9">
       <c r="A276" s="9" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B276" s="36"/>
       <c r="C276" s="36"/>
@@ -10554,16 +10814,16 @@
     </row>
     <row r="277" spans="1:9">
       <c r="A277" s="9" t="s">
+        <v>606</v>
+      </c>
+      <c r="B277" s="52" t="s">
         <v>607</v>
       </c>
-      <c r="B277" s="52" t="s">
+      <c r="C277" s="52" t="s">
         <v>608</v>
       </c>
-      <c r="C277" s="52" t="s">
+      <c r="D277" s="52" t="s">
         <v>609</v>
-      </c>
-      <c r="D277" s="52" t="s">
-        <v>610</v>
       </c>
       <c r="E277" s="52">
         <v>105</v>
@@ -10581,16 +10841,16 @@
     </row>
     <row r="278" spans="1:9">
       <c r="A278" s="9" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B278" s="27" t="s">
-        <v>804</v>
+        <v>829</v>
       </c>
       <c r="C278" s="27" t="s">
-        <v>550</v>
+        <v>830</v>
       </c>
       <c r="D278" s="27" t="s">
-        <v>805</v>
+        <v>831</v>
       </c>
       <c r="E278" s="27">
         <v>159</v>
@@ -10608,13 +10868,13 @@
     </row>
     <row r="279" spans="1:9">
       <c r="A279" s="9" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B279" s="10" t="s">
-        <v>806</v>
+        <v>832</v>
       </c>
       <c r="C279" s="49" t="s">
-        <v>807</v>
+        <v>833</v>
       </c>
       <c r="D279" s="10" t="s">
         <v>144</v>
@@ -10635,16 +10895,16 @@
     </row>
     <row r="280" spans="1:9">
       <c r="A280" s="9" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B280" s="10" t="s">
-        <v>808</v>
+        <v>834</v>
       </c>
       <c r="C280" s="49" t="s">
-        <v>809</v>
+        <v>835</v>
       </c>
       <c r="D280" s="10" t="s">
-        <v>489</v>
+        <v>836</v>
       </c>
       <c r="E280" s="10"/>
       <c r="F280" s="9">
@@ -10660,13 +10920,13 @@
     </row>
     <row r="281" spans="1:9">
       <c r="A281" s="9" t="s">
+        <v>613</v>
+      </c>
+      <c r="B281" s="10" t="s">
         <v>614</v>
       </c>
-      <c r="B281" s="10" t="s">
+      <c r="C281" s="49" t="s">
         <v>615</v>
-      </c>
-      <c r="C281" s="49" t="s">
-        <v>616</v>
       </c>
       <c r="D281" s="10" t="s">
         <v>144</v>
@@ -10687,13 +10947,13 @@
     </row>
     <row r="282" spans="1:9">
       <c r="A282" s="9" t="s">
+        <v>616</v>
+      </c>
+      <c r="B282" s="10" t="s">
+        <v>837</v>
+      </c>
+      <c r="C282" s="49" t="s">
         <v>617</v>
-      </c>
-      <c r="B282" s="10" t="s">
-        <v>810</v>
-      </c>
-      <c r="C282" s="49" t="s">
-        <v>618</v>
       </c>
       <c r="D282" s="10" t="s">
         <v>39</v>
@@ -10714,13 +10974,13 @@
     </row>
     <row r="283" spans="1:9">
       <c r="A283" s="9" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B283" s="10" t="s">
-        <v>811</v>
+        <v>838</v>
       </c>
       <c r="C283" s="49" t="s">
-        <v>812</v>
+        <v>839</v>
       </c>
       <c r="D283" s="10" t="s">
         <v>39</v>
@@ -10741,16 +11001,16 @@
     </row>
     <row r="284" spans="1:9">
       <c r="A284" s="9" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B284" s="27" t="s">
-        <v>813</v>
+        <v>840</v>
       </c>
       <c r="C284" s="36" t="s">
-        <v>814</v>
+        <v>841</v>
       </c>
       <c r="D284" s="36" t="s">
-        <v>815</v>
+        <v>842</v>
       </c>
       <c r="E284" s="36">
         <v>80</v>
@@ -10768,16 +11028,16 @@
     </row>
     <row r="285" spans="1:9">
       <c r="A285" s="9" t="s">
+        <v>620</v>
+      </c>
+      <c r="B285" s="10" t="s">
         <v>621</v>
       </c>
-      <c r="B285" s="10" t="s">
+      <c r="C285" s="49" t="s">
         <v>622</v>
       </c>
-      <c r="C285" s="49" t="s">
-        <v>623</v>
-      </c>
       <c r="D285" s="36" t="s">
-        <v>815</v>
+        <v>842</v>
       </c>
       <c r="E285" s="10">
         <v>73</v>
@@ -10795,16 +11055,16 @@
     </row>
     <row r="286" spans="1:9">
       <c r="A286" s="9" t="s">
+        <v>623</v>
+      </c>
+      <c r="B286" s="52" t="s">
+        <v>843</v>
+      </c>
+      <c r="C286" s="52" t="s">
+        <v>844</v>
+      </c>
+      <c r="D286" s="52" t="s">
         <v>624</v>
-      </c>
-      <c r="B286" s="52" t="s">
-        <v>816</v>
-      </c>
-      <c r="C286" s="52" t="s">
-        <v>817</v>
-      </c>
-      <c r="D286" s="52" t="s">
-        <v>625</v>
       </c>
       <c r="E286" s="52">
         <v>85</v>
@@ -10822,16 +11082,16 @@
     </row>
     <row r="287" spans="1:9">
       <c r="A287" s="9" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B287" s="52" t="s">
-        <v>818</v>
+        <v>845</v>
       </c>
       <c r="C287" s="52" t="s">
-        <v>819</v>
+        <v>846</v>
       </c>
       <c r="D287" s="52" t="s">
-        <v>820</v>
+        <v>847</v>
       </c>
       <c r="E287" s="52">
         <v>88</v>
@@ -10849,13 +11109,13 @@
     </row>
     <row r="288" spans="1:9">
       <c r="A288" s="9" t="s">
+        <v>626</v>
+      </c>
+      <c r="B288" s="27" t="s">
+        <v>848</v>
+      </c>
+      <c r="C288" s="27" t="s">
         <v>627</v>
-      </c>
-      <c r="B288" s="27" t="s">
-        <v>821</v>
-      </c>
-      <c r="C288" s="27" t="s">
-        <v>628</v>
       </c>
       <c r="D288" s="50" t="s">
         <v>4</v>
@@ -10876,16 +11136,16 @@
     </row>
     <row r="289" spans="1:9">
       <c r="A289" s="9" t="s">
+        <v>628</v>
+      </c>
+      <c r="B289" s="10" t="s">
         <v>629</v>
       </c>
-      <c r="B289" s="10" t="s">
+      <c r="C289" s="10" t="s">
         <v>630</v>
       </c>
-      <c r="C289" s="10" t="s">
+      <c r="D289" s="49" t="s">
         <v>631</v>
-      </c>
-      <c r="D289" s="49" t="s">
-        <v>632</v>
       </c>
       <c r="E289" s="10">
         <v>135</v>
@@ -10900,18 +11160,18 @@
         <v>3.9</v>
       </c>
       <c r="I289" s="11" t="s">
-        <v>822</v>
+        <v>849</v>
       </c>
     </row>
     <row r="290" spans="1:9">
       <c r="A290" s="9" t="s">
+        <v>632</v>
+      </c>
+      <c r="B290" s="24" t="s">
         <v>633</v>
       </c>
-      <c r="B290" s="24" t="s">
+      <c r="C290" s="24" t="s">
         <v>634</v>
-      </c>
-      <c r="C290" s="24" t="s">
-        <v>635</v>
       </c>
       <c r="D290" s="63" t="s">
         <v>39</v>
@@ -10926,22 +11186,22 @@
         <v>220</v>
       </c>
       <c r="H290" s="24">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="I290" s="61"/>
     </row>
     <row r="291" spans="1:9">
       <c r="A291" s="9" t="s">
+        <v>635</v>
+      </c>
+      <c r="B291" s="64" t="s">
+        <v>850</v>
+      </c>
+      <c r="C291" s="64" t="s">
         <v>636</v>
       </c>
-      <c r="B291" s="64" t="s">
-        <v>823</v>
-      </c>
-      <c r="C291" s="64" t="s">
+      <c r="D291" s="64" t="s">
         <v>637</v>
-      </c>
-      <c r="D291" s="64" t="s">
-        <v>638</v>
       </c>
       <c r="E291" s="64">
         <v>88</v>
@@ -10953,22 +11213,22 @@
         <v>220</v>
       </c>
       <c r="H291" s="64">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="I291" s="61"/>
     </row>
     <row r="292" spans="1:9">
       <c r="A292" s="9" t="s">
+        <v>638</v>
+      </c>
+      <c r="B292" s="64" t="s">
+        <v>851</v>
+      </c>
+      <c r="C292" s="64" t="s">
         <v>639</v>
       </c>
-      <c r="B292" s="64" t="s">
-        <v>824</v>
-      </c>
-      <c r="C292" s="64" t="s">
+      <c r="D292" s="64" t="s">
         <v>640</v>
-      </c>
-      <c r="D292" s="64" t="s">
-        <v>641</v>
       </c>
       <c r="E292" s="64">
         <v>80</v>
@@ -10986,13 +11246,13 @@
     </row>
     <row r="293" spans="1:9">
       <c r="A293" s="9" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B293" s="65" t="s">
-        <v>825</v>
+        <v>852</v>
       </c>
       <c r="C293" s="64" t="s">
-        <v>826</v>
+        <v>853</v>
       </c>
       <c r="D293" s="64" t="s">
         <v>39</v>
@@ -11013,16 +11273,16 @@
     </row>
     <row r="294" spans="1:9">
       <c r="A294" s="9" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B294" s="18" t="s">
-        <v>827</v>
+        <v>854</v>
       </c>
       <c r="C294" s="18" t="s">
-        <v>445</v>
+        <v>733</v>
       </c>
       <c r="D294" s="18" t="s">
-        <v>828</v>
+        <v>855</v>
       </c>
       <c r="E294" s="18">
         <v>150</v>
@@ -11040,16 +11300,16 @@
     </row>
     <row r="295" spans="1:9">
       <c r="A295" s="9" t="s">
+        <v>643</v>
+      </c>
+      <c r="B295" s="10" t="s">
+        <v>856</v>
+      </c>
+      <c r="C295" s="10" t="s">
         <v>644</v>
       </c>
-      <c r="B295" s="10" t="s">
-        <v>829</v>
-      </c>
-      <c r="C295" s="10" t="s">
+      <c r="D295" s="10" t="s">
         <v>645</v>
-      </c>
-      <c r="D295" s="10" t="s">
-        <v>646</v>
       </c>
       <c r="E295" s="10"/>
       <c r="F295" s="9"/>
@@ -11063,16 +11323,16 @@
     </row>
     <row r="296" spans="1:9">
       <c r="A296" s="9" t="s">
+        <v>646</v>
+      </c>
+      <c r="B296" s="35" t="s">
         <v>647</v>
       </c>
-      <c r="B296" s="35" t="s">
+      <c r="C296" s="35" t="s">
         <v>648</v>
       </c>
-      <c r="C296" s="35" t="s">
+      <c r="D296" s="35" t="s">
         <v>649</v>
-      </c>
-      <c r="D296" s="35" t="s">
-        <v>650</v>
       </c>
       <c r="E296" s="35"/>
       <c r="F296" s="36">
@@ -11088,16 +11348,16 @@
     </row>
     <row r="297" spans="1:9">
       <c r="A297" s="9" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B297" s="18" t="s">
-        <v>830</v>
+        <v>857</v>
       </c>
       <c r="C297" s="18" t="s">
-        <v>831</v>
+        <v>858</v>
       </c>
       <c r="D297" s="33" t="s">
-        <v>832</v>
+        <v>859</v>
       </c>
       <c r="E297" s="18">
         <v>125</v>
@@ -11109,51 +11369,51 @@
         <v>215</v>
       </c>
       <c r="H297" s="18">
-        <v>4.5999999999999996</v>
+        <v>4.5</v>
       </c>
       <c r="I297" s="54"/>
     </row>
     <row r="298" spans="1:9">
       <c r="A298" s="9" t="s">
-        <v>652</v>
-      </c>
-      <c r="B298" s="65" t="s">
-        <v>961</v>
-      </c>
-      <c r="C298" s="64" t="s">
-        <v>962</v>
-      </c>
-      <c r="D298" s="64" t="s">
-        <v>963</v>
-      </c>
-      <c r="E298" s="65">
+        <v>651</v>
+      </c>
+      <c r="B298" s="18" t="s">
+        <v>860</v>
+      </c>
+      <c r="C298" s="18" t="s">
+        <v>861</v>
+      </c>
+      <c r="D298" s="33" t="s">
+        <v>862</v>
+      </c>
+      <c r="E298" s="18">
         <v>190</v>
       </c>
-      <c r="F298" s="36">
+      <c r="F298" s="31">
         <v>270</v>
       </c>
-      <c r="G298" s="53">
+      <c r="G298" s="32">
         <v>225</v>
       </c>
-      <c r="H298" s="65">
-        <v>5.8</v>
-      </c>
-      <c r="I298" s="38" t="s">
-        <v>964</v>
+      <c r="H298" s="18">
+        <v>5.7</v>
+      </c>
+      <c r="I298" s="11" t="s">
+        <v>863</v>
       </c>
     </row>
     <row r="299" spans="1:9">
       <c r="A299" s="9" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B299" s="51" t="s">
-        <v>833</v>
+        <v>864</v>
       </c>
       <c r="C299" s="51" t="s">
-        <v>834</v>
+        <v>865</v>
       </c>
       <c r="D299" s="51" t="s">
-        <v>835</v>
+        <v>866</v>
       </c>
       <c r="E299" s="51">
         <v>124</v>
@@ -11168,12 +11428,12 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="I299" s="55" t="s">
-        <v>836</v>
+        <v>867</v>
       </c>
     </row>
     <row r="300" spans="1:9">
       <c r="A300" s="9" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B300" s="36"/>
       <c r="C300" s="36"/>
@@ -11186,7 +11446,7 @@
     </row>
     <row r="301" spans="1:9">
       <c r="A301" s="9" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B301" s="36"/>
       <c r="C301" s="36"/>
@@ -11199,16 +11459,16 @@
     </row>
     <row r="302" spans="1:9">
       <c r="A302" s="9" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B302" s="11" t="s">
-        <v>877</v>
+        <v>868</v>
       </c>
       <c r="C302" s="11" t="s">
-        <v>878</v>
+        <v>869</v>
       </c>
       <c r="D302" s="11" t="s">
-        <v>965</v>
+        <v>870</v>
       </c>
       <c r="E302" s="11">
         <v>150</v>
@@ -11220,22 +11480,22 @@
         <v>215</v>
       </c>
       <c r="H302" s="11">
-        <v>4.5999999999999996</v>
+        <v>4.5</v>
       </c>
       <c r="I302" s="61"/>
     </row>
     <row r="303" spans="1:9">
       <c r="A303" s="9" t="s">
+        <v>656</v>
+      </c>
+      <c r="B303" s="10" t="s">
         <v>657</v>
       </c>
-      <c r="B303" s="10" t="s">
+      <c r="C303" s="10" t="s">
         <v>658</v>
       </c>
-      <c r="C303" s="10" t="s">
-        <v>659</v>
-      </c>
       <c r="D303" s="10" t="s">
-        <v>965</v>
+        <v>870</v>
       </c>
       <c r="E303" s="11">
         <v>140</v>
@@ -11247,22 +11507,22 @@
         <v>215</v>
       </c>
       <c r="H303" s="10">
-        <v>4.2</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="I303" s="61"/>
     </row>
     <row r="304" spans="1:9">
       <c r="A304" s="9" t="s">
+        <v>659</v>
+      </c>
+      <c r="B304" s="64" t="s">
         <v>660</v>
       </c>
-      <c r="B304" s="64" t="s">
+      <c r="C304" s="64" t="s">
+        <v>871</v>
+      </c>
+      <c r="D304" s="64" t="s">
         <v>661</v>
-      </c>
-      <c r="C304" s="64" t="s">
-        <v>251</v>
-      </c>
-      <c r="D304" s="64" t="s">
-        <v>662</v>
       </c>
       <c r="E304" s="64">
         <v>90</v>
@@ -11277,21 +11537,21 @@
         <v>4.5</v>
       </c>
       <c r="I304" s="37" t="s">
-        <v>837</v>
+        <v>872</v>
       </c>
     </row>
     <row r="305" spans="1:9">
       <c r="A305" s="9" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B305" s="36" t="s">
-        <v>838</v>
+        <v>873</v>
       </c>
       <c r="C305" s="36" t="s">
-        <v>839</v>
+        <v>874</v>
       </c>
       <c r="D305" s="18" t="s">
-        <v>840</v>
+        <v>875</v>
       </c>
       <c r="E305" s="36">
         <v>215</v>
@@ -11309,7 +11569,7 @@
     </row>
     <row r="306" spans="1:9">
       <c r="A306" s="9" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B306" s="36"/>
       <c r="C306" s="36"/>
@@ -11322,7 +11582,7 @@
     </row>
     <row r="307" spans="1:9">
       <c r="A307" s="9" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B307" s="36"/>
       <c r="C307" s="36"/>
@@ -11335,7 +11595,7 @@
     </row>
     <row r="308" spans="1:9">
       <c r="A308" s="9" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B308" s="36"/>
       <c r="C308" s="36"/>
@@ -11348,7 +11608,7 @@
     </row>
     <row r="309" spans="1:9">
       <c r="A309" s="9" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B309" s="36"/>
       <c r="C309" s="36"/>
@@ -11361,7 +11621,7 @@
     </row>
     <row r="310" spans="1:9">
       <c r="A310" s="9" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B310" s="36"/>
       <c r="C310" s="36"/>
@@ -11374,16 +11634,16 @@
     </row>
     <row r="311" spans="1:9">
       <c r="A311" s="9" t="s">
+        <v>668</v>
+      </c>
+      <c r="B311" s="35" t="s">
         <v>669</v>
       </c>
-      <c r="B311" s="35" t="s">
+      <c r="C311" s="35" t="s">
+        <v>876</v>
+      </c>
+      <c r="D311" s="35" t="s">
         <v>670</v>
-      </c>
-      <c r="C311" s="35" t="s">
-        <v>674</v>
-      </c>
-      <c r="D311" s="35" t="s">
-        <v>671</v>
       </c>
       <c r="E311" s="35">
         <v>85</v>
@@ -11401,16 +11661,16 @@
     </row>
     <row r="312" spans="1:9">
       <c r="A312" s="9" t="s">
+        <v>671</v>
+      </c>
+      <c r="B312" s="10" t="s">
         <v>672</v>
       </c>
-      <c r="B312" s="10" t="s">
+      <c r="C312" s="10" t="s">
         <v>673</v>
       </c>
-      <c r="C312" s="10" t="s">
+      <c r="D312" s="10" t="s">
         <v>674</v>
-      </c>
-      <c r="D312" s="10" t="s">
-        <v>675</v>
       </c>
       <c r="E312" s="10">
         <v>73</v>
@@ -11422,13 +11682,13 @@
         <v>208</v>
       </c>
       <c r="H312" s="10">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="I312" s="61"/>
     </row>
     <row r="313" spans="1:9">
       <c r="A313" s="9" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B313" s="36"/>
       <c r="C313" s="36"/>
@@ -11441,7 +11701,7 @@
     </row>
     <row r="314" spans="1:9">
       <c r="A314" s="9" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B314" s="36"/>
       <c r="C314" s="36"/>
@@ -11454,16 +11714,16 @@
     </row>
     <row r="315" spans="1:9">
       <c r="A315" s="9" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B315" s="36" t="s">
-        <v>841</v>
+        <v>877</v>
       </c>
       <c r="C315" s="36" t="s">
-        <v>842</v>
+        <v>878</v>
       </c>
       <c r="D315" s="11" t="s">
-        <v>843</v>
+        <v>879</v>
       </c>
       <c r="E315" s="36">
         <v>116</v>
@@ -11478,21 +11738,21 @@
         <v>5</v>
       </c>
       <c r="I315" s="61" t="s">
-        <v>844</v>
+        <v>880</v>
       </c>
     </row>
     <row r="316" spans="1:9">
       <c r="A316" s="9" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B316" s="36" t="s">
-        <v>845</v>
+        <v>881</v>
       </c>
       <c r="C316" s="36" t="s">
-        <v>846</v>
+        <v>882</v>
       </c>
       <c r="D316" s="11" t="s">
-        <v>847</v>
+        <v>883</v>
       </c>
       <c r="E316" s="36">
         <v>160</v>
@@ -11507,21 +11767,21 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="I316" s="61" t="s">
-        <v>879</v>
+        <v>884</v>
       </c>
     </row>
     <row r="317" spans="1:9">
       <c r="A317" s="9" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B317" s="11" t="s">
-        <v>848</v>
+        <v>885</v>
       </c>
       <c r="C317" s="11" t="s">
-        <v>849</v>
+        <v>886</v>
       </c>
       <c r="D317" s="11" t="s">
-        <v>850</v>
+        <v>887</v>
       </c>
       <c r="E317" s="11">
         <v>110</v>
@@ -11536,21 +11796,21 @@
         <v>3.6</v>
       </c>
       <c r="I317" s="11" t="s">
-        <v>851</v>
+        <v>888</v>
       </c>
     </row>
     <row r="318" spans="1:9">
       <c r="A318" s="9" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B318" s="11" t="s">
-        <v>848</v>
+        <v>885</v>
       </c>
       <c r="C318" s="11" t="s">
-        <v>852</v>
+        <v>889</v>
       </c>
       <c r="D318" s="11" t="s">
-        <v>850</v>
+        <v>887</v>
       </c>
       <c r="E318" s="11">
         <v>110</v>
@@ -11568,16 +11828,16 @@
     </row>
     <row r="319" spans="1:9">
       <c r="A319" s="9" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B319" s="18" t="s">
-        <v>853</v>
+        <v>890</v>
       </c>
       <c r="C319" s="18" t="s">
-        <v>854</v>
+        <v>891</v>
       </c>
       <c r="D319" s="18" t="s">
-        <v>855</v>
+        <v>892</v>
       </c>
       <c r="E319" s="18">
         <v>205</v>
@@ -11592,21 +11852,21 @@
         <v>5.4</v>
       </c>
       <c r="I319" s="11" t="s">
-        <v>856</v>
+        <v>893</v>
       </c>
     </row>
     <row r="320" spans="1:9">
       <c r="A320" s="9" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B320" s="18" t="s">
-        <v>857</v>
+        <v>894</v>
       </c>
       <c r="C320" s="18" t="s">
-        <v>880</v>
+        <v>895</v>
       </c>
       <c r="D320" s="18" t="s">
-        <v>858</v>
+        <v>896</v>
       </c>
       <c r="E320" s="18">
         <v>182</v>
@@ -11615,27 +11875,27 @@
         <v>265</v>
       </c>
       <c r="G320" s="32">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="H320" s="18">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="I320" s="11" t="s">
-        <v>881</v>
+        <v>863</v>
       </c>
     </row>
     <row r="321" spans="1:9">
       <c r="A321" s="9" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B321" s="18" t="s">
-        <v>859</v>
+        <v>897</v>
       </c>
       <c r="C321" s="18" t="s">
-        <v>860</v>
+        <v>898</v>
       </c>
       <c r="D321" s="18" t="s">
-        <v>861</v>
+        <v>899</v>
       </c>
       <c r="E321" s="18">
         <v>138</v>
@@ -11650,21 +11910,21 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="I321" s="11" t="s">
-        <v>862</v>
+        <v>900</v>
       </c>
     </row>
     <row r="322" spans="1:9">
       <c r="A322" s="9" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B322" s="18" t="s">
-        <v>863</v>
+        <v>901</v>
       </c>
       <c r="C322" s="18" t="s">
-        <v>864</v>
+        <v>902</v>
       </c>
       <c r="D322" s="18" t="s">
-        <v>855</v>
+        <v>892</v>
       </c>
       <c r="E322" s="18">
         <v>225</v>
@@ -11679,21 +11939,21 @@
         <v>5.8</v>
       </c>
       <c r="I322" s="11" t="s">
-        <v>865</v>
+        <v>903</v>
       </c>
     </row>
     <row r="323" spans="1:9">
       <c r="A323" s="9" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B323" s="18" t="s">
-        <v>866</v>
+        <v>904</v>
       </c>
       <c r="C323" s="18" t="s">
-        <v>88</v>
+        <v>905</v>
       </c>
       <c r="D323" s="18" t="s">
-        <v>861</v>
+        <v>899</v>
       </c>
       <c r="E323" s="18">
         <v>155</v>
@@ -11705,24 +11965,24 @@
         <v>215</v>
       </c>
       <c r="H323" s="18">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="I323" s="11" t="s">
-        <v>867</v>
+        <v>906</v>
       </c>
     </row>
     <row r="324" spans="1:9">
       <c r="A324" s="9" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B324" s="18" t="s">
-        <v>868</v>
+        <v>907</v>
       </c>
       <c r="C324" s="18" t="s">
-        <v>869</v>
+        <v>908</v>
       </c>
       <c r="D324" s="18" t="s">
-        <v>855</v>
+        <v>892</v>
       </c>
       <c r="E324" s="18">
         <v>220</v>
@@ -11737,12 +11997,12 @@
         <v>6.1</v>
       </c>
       <c r="I324" s="11" t="s">
-        <v>865</v>
+        <v>903</v>
       </c>
     </row>
     <row r="325" spans="1:9">
       <c r="A325" s="9" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B325" s="36"/>
       <c r="C325" s="36"/>
@@ -11755,7 +12015,7 @@
     </row>
     <row r="326" spans="1:9">
       <c r="A326" s="9" t="s">
-        <v>882</v>
+        <v>909</v>
       </c>
       <c r="B326" s="36"/>
       <c r="C326" s="36"/>
@@ -11768,7 +12028,7 @@
     </row>
     <row r="327" spans="1:9">
       <c r="A327" s="9" t="s">
-        <v>883</v>
+        <v>910</v>
       </c>
       <c r="B327" s="36"/>
       <c r="C327" s="36"/>
@@ -11781,7 +12041,7 @@
     </row>
     <row r="328" spans="1:9">
       <c r="A328" s="9" t="s">
-        <v>884</v>
+        <v>911</v>
       </c>
       <c r="B328" s="36"/>
       <c r="C328" s="36"/>
@@ -11794,7 +12054,7 @@
     </row>
     <row r="329" spans="1:9">
       <c r="A329" s="9" t="s">
-        <v>885</v>
+        <v>912</v>
       </c>
       <c r="B329" s="36"/>
       <c r="C329" s="36"/>
@@ -11807,7 +12067,7 @@
     </row>
     <row r="330" spans="1:9">
       <c r="A330" s="9" t="s">
-        <v>886</v>
+        <v>913</v>
       </c>
       <c r="B330" s="36"/>
       <c r="C330" s="36"/>
@@ -11820,7 +12080,7 @@
     </row>
     <row r="331" spans="1:9">
       <c r="A331" s="9" t="s">
-        <v>887</v>
+        <v>914</v>
       </c>
       <c r="B331" s="36"/>
       <c r="C331" s="36"/>
@@ -11833,7 +12093,7 @@
     </row>
     <row r="332" spans="1:9">
       <c r="A332" s="9" t="s">
-        <v>888</v>
+        <v>915</v>
       </c>
       <c r="B332" s="36"/>
       <c r="C332" s="36"/>
@@ -11846,7 +12106,7 @@
     </row>
     <row r="333" spans="1:9">
       <c r="A333" s="9" t="s">
-        <v>889</v>
+        <v>916</v>
       </c>
       <c r="B333" s="36"/>
       <c r="C333" s="36"/>
@@ -11859,7 +12119,7 @@
     </row>
     <row r="334" spans="1:9">
       <c r="A334" s="9" t="s">
-        <v>890</v>
+        <v>917</v>
       </c>
       <c r="B334" s="36"/>
       <c r="C334" s="36"/>
@@ -11872,7 +12132,7 @@
     </row>
     <row r="335" spans="1:9">
       <c r="A335" s="9" t="s">
-        <v>891</v>
+        <v>918</v>
       </c>
       <c r="B335" s="36"/>
       <c r="C335" s="36"/>
@@ -11885,7 +12145,7 @@
     </row>
     <row r="336" spans="1:9">
       <c r="A336" s="9" t="s">
-        <v>892</v>
+        <v>919</v>
       </c>
       <c r="B336" s="36"/>
       <c r="C336" s="36"/>
@@ -11898,7 +12158,7 @@
     </row>
     <row r="337" spans="1:9">
       <c r="A337" s="9" t="s">
-        <v>893</v>
+        <v>920</v>
       </c>
       <c r="B337" s="36"/>
       <c r="C337" s="36"/>
@@ -11911,7 +12171,7 @@
     </row>
     <row r="338" spans="1:9">
       <c r="A338" s="9" t="s">
-        <v>894</v>
+        <v>921</v>
       </c>
       <c r="B338" s="36"/>
       <c r="C338" s="36"/>
@@ -11924,7 +12184,7 @@
     </row>
     <row r="339" spans="1:9">
       <c r="A339" s="9" t="s">
-        <v>895</v>
+        <v>922</v>
       </c>
       <c r="B339" s="36"/>
       <c r="C339" s="36"/>
@@ -11937,7 +12197,7 @@
     </row>
     <row r="340" spans="1:9">
       <c r="A340" s="9" t="s">
-        <v>896</v>
+        <v>923</v>
       </c>
       <c r="B340" s="36"/>
       <c r="C340" s="36"/>
@@ -11950,7 +12210,7 @@
     </row>
     <row r="341" spans="1:9">
       <c r="A341" s="9" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="B341" s="36"/>
       <c r="C341" s="36"/>
@@ -11963,7 +12223,7 @@
     </row>
     <row r="342" spans="1:9">
       <c r="A342" s="9" t="s">
-        <v>898</v>
+        <v>925</v>
       </c>
       <c r="B342" s="36"/>
       <c r="C342" s="36"/>
@@ -11976,7 +12236,7 @@
     </row>
     <row r="343" spans="1:9">
       <c r="A343" s="9" t="s">
-        <v>899</v>
+        <v>926</v>
       </c>
       <c r="B343" s="36"/>
       <c r="C343" s="36"/>
@@ -11989,7 +12249,7 @@
     </row>
     <row r="344" spans="1:9">
       <c r="A344" s="9" t="s">
-        <v>900</v>
+        <v>927</v>
       </c>
       <c r="B344" s="36"/>
       <c r="C344" s="36"/>
@@ -12002,7 +12262,7 @@
     </row>
     <row r="345" spans="1:9">
       <c r="A345" s="9" t="s">
-        <v>901</v>
+        <v>928</v>
       </c>
       <c r="B345" s="36"/>
       <c r="C345" s="36"/>
@@ -12015,7 +12275,7 @@
     </row>
     <row r="346" spans="1:9">
       <c r="A346" s="9" t="s">
-        <v>902</v>
+        <v>929</v>
       </c>
       <c r="B346" s="36"/>
       <c r="C346" s="36"/>
@@ -12028,7 +12288,7 @@
     </row>
     <row r="347" spans="1:9">
       <c r="A347" s="9" t="s">
-        <v>903</v>
+        <v>930</v>
       </c>
       <c r="B347" s="36"/>
       <c r="C347" s="36"/>
@@ -12041,7 +12301,7 @@
     </row>
     <row r="348" spans="1:9">
       <c r="A348" s="9" t="s">
-        <v>904</v>
+        <v>931</v>
       </c>
       <c r="B348" s="36"/>
       <c r="C348" s="36"/>
@@ -12054,7 +12314,7 @@
     </row>
     <row r="349" spans="1:9">
       <c r="A349" s="9" t="s">
-        <v>905</v>
+        <v>932</v>
       </c>
       <c r="B349" s="36"/>
       <c r="C349" s="36"/>
@@ -12067,7 +12327,7 @@
     </row>
     <row r="350" spans="1:9">
       <c r="A350" s="9" t="s">
-        <v>906</v>
+        <v>933</v>
       </c>
       <c r="B350" s="36"/>
       <c r="C350" s="36"/>
@@ -12080,7 +12340,7 @@
     </row>
     <row r="351" spans="1:9">
       <c r="A351" s="9" t="s">
-        <v>907</v>
+        <v>934</v>
       </c>
       <c r="B351" s="36"/>
       <c r="C351" s="36"/>
@@ -12093,7 +12353,7 @@
     </row>
     <row r="352" spans="1:9">
       <c r="A352" s="9" t="s">
-        <v>908</v>
+        <v>935</v>
       </c>
       <c r="B352" s="36"/>
       <c r="C352" s="36"/>
@@ -12106,7 +12366,7 @@
     </row>
     <row r="353" spans="1:9">
       <c r="A353" s="9" t="s">
-        <v>909</v>
+        <v>936</v>
       </c>
       <c r="B353" s="36"/>
       <c r="C353" s="36"/>
@@ -12119,7 +12379,7 @@
     </row>
     <row r="354" spans="1:9">
       <c r="A354" s="9" t="s">
-        <v>910</v>
+        <v>937</v>
       </c>
       <c r="B354" s="36"/>
       <c r="C354" s="36"/>
@@ -12132,7 +12392,7 @@
     </row>
     <row r="355" spans="1:9">
       <c r="A355" s="9" t="s">
-        <v>911</v>
+        <v>938</v>
       </c>
       <c r="B355" s="36"/>
       <c r="C355" s="36"/>
@@ -12145,7 +12405,7 @@
     </row>
     <row r="356" spans="1:9">
       <c r="A356" s="9" t="s">
-        <v>912</v>
+        <v>939</v>
       </c>
       <c r="B356" s="36"/>
       <c r="C356" s="36"/>
@@ -12158,7 +12418,7 @@
     </row>
     <row r="357" spans="1:9">
       <c r="A357" s="9" t="s">
-        <v>913</v>
+        <v>940</v>
       </c>
       <c r="B357" s="36"/>
       <c r="C357" s="36"/>
@@ -12171,7 +12431,7 @@
     </row>
     <row r="358" spans="1:9">
       <c r="A358" s="9" t="s">
-        <v>914</v>
+        <v>941</v>
       </c>
       <c r="B358" s="36"/>
       <c r="C358" s="36"/>
@@ -12184,7 +12444,7 @@
     </row>
     <row r="359" spans="1:9">
       <c r="A359" s="9" t="s">
-        <v>915</v>
+        <v>942</v>
       </c>
       <c r="B359" s="36"/>
       <c r="C359" s="36"/>
@@ -12197,7 +12457,7 @@
     </row>
     <row r="360" spans="1:9">
       <c r="A360" s="9" t="s">
-        <v>916</v>
+        <v>943</v>
       </c>
       <c r="B360" s="36"/>
       <c r="C360" s="36"/>
@@ -12210,7 +12470,7 @@
     </row>
     <row r="361" spans="1:9">
       <c r="A361" s="9" t="s">
-        <v>917</v>
+        <v>944</v>
       </c>
       <c r="B361" s="36"/>
       <c r="C361" s="36"/>
@@ -12223,7 +12483,7 @@
     </row>
     <row r="362" spans="1:9">
       <c r="A362" s="9" t="s">
-        <v>918</v>
+        <v>945</v>
       </c>
       <c r="B362" s="36"/>
       <c r="C362" s="36"/>
@@ -12236,7 +12496,7 @@
     </row>
     <row r="363" spans="1:9">
       <c r="A363" s="9" t="s">
-        <v>919</v>
+        <v>946</v>
       </c>
       <c r="B363" s="36"/>
       <c r="C363" s="36"/>
@@ -12249,7 +12509,7 @@
     </row>
     <row r="364" spans="1:9">
       <c r="A364" s="9" t="s">
-        <v>920</v>
+        <v>947</v>
       </c>
       <c r="B364" s="36"/>
       <c r="C364" s="36"/>
@@ -12262,7 +12522,7 @@
     </row>
     <row r="365" spans="1:9">
       <c r="A365" s="9" t="s">
-        <v>921</v>
+        <v>948</v>
       </c>
       <c r="B365" s="36"/>
       <c r="C365" s="36"/>
@@ -12275,7 +12535,7 @@
     </row>
     <row r="366" spans="1:9">
       <c r="A366" s="9" t="s">
-        <v>922</v>
+        <v>949</v>
       </c>
       <c r="B366" s="36"/>
       <c r="C366" s="36"/>
@@ -12288,7 +12548,7 @@
     </row>
     <row r="367" spans="1:9">
       <c r="A367" s="9" t="s">
-        <v>923</v>
+        <v>950</v>
       </c>
       <c r="B367" s="36"/>
       <c r="C367" s="36"/>
@@ -12301,7 +12561,7 @@
     </row>
     <row r="368" spans="1:9">
       <c r="A368" s="9" t="s">
-        <v>924</v>
+        <v>951</v>
       </c>
       <c r="B368" s="36"/>
       <c r="C368" s="36"/>
@@ -12314,7 +12574,7 @@
     </row>
     <row r="369" spans="1:9">
       <c r="A369" s="9" t="s">
-        <v>925</v>
+        <v>952</v>
       </c>
       <c r="B369" s="36"/>
       <c r="C369" s="36"/>
@@ -12327,7 +12587,7 @@
     </row>
     <row r="370" spans="1:9">
       <c r="A370" s="9" t="s">
-        <v>926</v>
+        <v>953</v>
       </c>
       <c r="B370" s="36"/>
       <c r="C370" s="36"/>
@@ -12340,7 +12600,7 @@
     </row>
     <row r="371" spans="1:9">
       <c r="A371" s="9" t="s">
-        <v>927</v>
+        <v>954</v>
       </c>
       <c r="B371" s="36"/>
       <c r="C371" s="36"/>
@@ -12353,7 +12613,7 @@
     </row>
     <row r="372" spans="1:9">
       <c r="A372" s="9" t="s">
-        <v>928</v>
+        <v>955</v>
       </c>
       <c r="B372" s="36"/>
       <c r="C372" s="36"/>
@@ -12366,7 +12626,7 @@
     </row>
     <row r="373" spans="1:9">
       <c r="A373" s="9" t="s">
-        <v>929</v>
+        <v>956</v>
       </c>
       <c r="B373" s="36"/>
       <c r="C373" s="36"/>
@@ -12379,7 +12639,7 @@
     </row>
     <row r="374" spans="1:9">
       <c r="A374" s="9" t="s">
-        <v>930</v>
+        <v>957</v>
       </c>
       <c r="B374" s="36"/>
       <c r="C374" s="36"/>
@@ -12392,7 +12652,7 @@
     </row>
     <row r="375" spans="1:9">
       <c r="A375" s="9" t="s">
-        <v>931</v>
+        <v>958</v>
       </c>
       <c r="B375" s="36"/>
       <c r="C375" s="36"/>
@@ -12405,7 +12665,7 @@
     </row>
     <row r="376" spans="1:9">
       <c r="A376" s="9" t="s">
-        <v>932</v>
+        <v>959</v>
       </c>
       <c r="B376" s="36"/>
       <c r="C376" s="36"/>
@@ -12418,7 +12678,7 @@
     </row>
     <row r="377" spans="1:9">
       <c r="A377" s="9" t="s">
-        <v>933</v>
+        <v>960</v>
       </c>
       <c r="B377" s="36"/>
       <c r="C377" s="36"/>
@@ -12431,7 +12691,7 @@
     </row>
     <row r="378" spans="1:9">
       <c r="A378" s="9" t="s">
-        <v>934</v>
+        <v>961</v>
       </c>
       <c r="B378" s="36"/>
       <c r="C378" s="36"/>
@@ -12444,7 +12704,7 @@
     </row>
     <row r="379" spans="1:9">
       <c r="A379" s="9" t="s">
-        <v>935</v>
+        <v>962</v>
       </c>
       <c r="B379" s="36"/>
       <c r="C379" s="36"/>
@@ -12457,7 +12717,7 @@
     </row>
     <row r="380" spans="1:9">
       <c r="A380" s="9" t="s">
-        <v>936</v>
+        <v>963</v>
       </c>
       <c r="B380" s="36"/>
       <c r="C380" s="36"/>
@@ -12470,7 +12730,7 @@
     </row>
     <row r="381" spans="1:9">
       <c r="A381" s="9" t="s">
-        <v>937</v>
+        <v>964</v>
       </c>
       <c r="B381" s="36"/>
       <c r="C381" s="36"/>
@@ -12483,7 +12743,7 @@
     </row>
     <row r="382" spans="1:9">
       <c r="A382" s="9" t="s">
-        <v>938</v>
+        <v>965</v>
       </c>
       <c r="B382" s="36"/>
       <c r="C382" s="36"/>
@@ -12496,7 +12756,7 @@
     </row>
     <row r="383" spans="1:9">
       <c r="A383" s="9" t="s">
-        <v>939</v>
+        <v>966</v>
       </c>
       <c r="B383" s="36"/>
       <c r="C383" s="36"/>
@@ -12509,7 +12769,7 @@
     </row>
     <row r="384" spans="1:9">
       <c r="A384" s="9" t="s">
-        <v>940</v>
+        <v>967</v>
       </c>
       <c r="B384" s="36"/>
       <c r="C384" s="36"/>
@@ -12522,7 +12782,7 @@
     </row>
     <row r="385" spans="1:9">
       <c r="A385" s="9" t="s">
-        <v>941</v>
+        <v>968</v>
       </c>
       <c r="B385" s="36"/>
       <c r="C385" s="36"/>
@@ -12535,7 +12795,7 @@
     </row>
     <row r="386" spans="1:9">
       <c r="A386" s="9" t="s">
-        <v>942</v>
+        <v>969</v>
       </c>
       <c r="B386" s="36"/>
       <c r="C386" s="36"/>
@@ -12548,7 +12808,7 @@
     </row>
     <row r="387" spans="1:9">
       <c r="A387" s="9" t="s">
-        <v>943</v>
+        <v>970</v>
       </c>
       <c r="B387" s="36"/>
       <c r="C387" s="36"/>
@@ -12561,7 +12821,7 @@
     </row>
     <row r="388" spans="1:9">
       <c r="A388" s="9" t="s">
-        <v>944</v>
+        <v>971</v>
       </c>
       <c r="B388" s="36"/>
       <c r="C388" s="36"/>
@@ -12574,7 +12834,7 @@
     </row>
     <row r="389" spans="1:9">
       <c r="A389" s="9" t="s">
-        <v>945</v>
+        <v>972</v>
       </c>
       <c r="B389" s="36"/>
       <c r="C389" s="36"/>
@@ -12587,7 +12847,7 @@
     </row>
     <row r="390" spans="1:9">
       <c r="A390" s="9" t="s">
-        <v>946</v>
+        <v>973</v>
       </c>
       <c r="B390" s="36"/>
       <c r="C390" s="36"/>
@@ -12600,7 +12860,7 @@
     </row>
     <row r="391" spans="1:9">
       <c r="A391" s="9" t="s">
-        <v>947</v>
+        <v>974</v>
       </c>
       <c r="B391" s="36"/>
       <c r="C391" s="36"/>
@@ -12613,7 +12873,7 @@
     </row>
     <row r="392" spans="1:9">
       <c r="A392" s="9" t="s">
-        <v>948</v>
+        <v>975</v>
       </c>
       <c r="B392" s="36"/>
       <c r="C392" s="36"/>
@@ -12626,7 +12886,7 @@
     </row>
     <row r="393" spans="1:9">
       <c r="A393" s="9" t="s">
-        <v>949</v>
+        <v>976</v>
       </c>
       <c r="B393" s="36"/>
       <c r="C393" s="36"/>
@@ -12636,110 +12896,6 @@
       <c r="G393" s="36"/>
       <c r="H393" s="61"/>
       <c r="I393" s="61"/>
-    </row>
-    <row r="394" spans="1:9">
-      <c r="A394" s="9" t="s">
-        <v>950</v>
-      </c>
-      <c r="B394" s="36"/>
-      <c r="C394" s="36"/>
-      <c r="D394" s="36"/>
-      <c r="E394" s="36"/>
-      <c r="F394" s="36"/>
-      <c r="G394" s="36"/>
-      <c r="H394" s="61"/>
-      <c r="I394" s="61"/>
-    </row>
-    <row r="395" spans="1:9">
-      <c r="A395" s="9" t="s">
-        <v>951</v>
-      </c>
-      <c r="B395" s="36"/>
-      <c r="C395" s="36"/>
-      <c r="D395" s="36"/>
-      <c r="E395" s="36"/>
-      <c r="F395" s="36"/>
-      <c r="G395" s="36"/>
-      <c r="H395" s="61"/>
-      <c r="I395" s="61"/>
-    </row>
-    <row r="396" spans="1:9">
-      <c r="A396" s="9" t="s">
-        <v>952</v>
-      </c>
-      <c r="B396" s="36"/>
-      <c r="C396" s="36"/>
-      <c r="D396" s="36"/>
-      <c r="E396" s="36"/>
-      <c r="F396" s="36"/>
-      <c r="G396" s="36"/>
-      <c r="H396" s="61"/>
-      <c r="I396" s="61"/>
-    </row>
-    <row r="397" spans="1:9">
-      <c r="A397" s="9" t="s">
-        <v>953</v>
-      </c>
-      <c r="B397" s="36"/>
-      <c r="C397" s="36"/>
-      <c r="D397" s="36"/>
-      <c r="E397" s="36"/>
-      <c r="F397" s="36"/>
-      <c r="G397" s="36"/>
-      <c r="H397" s="61"/>
-      <c r="I397" s="61"/>
-    </row>
-    <row r="398" spans="1:9">
-      <c r="A398" s="9" t="s">
-        <v>954</v>
-      </c>
-      <c r="B398" s="36"/>
-      <c r="C398" s="36"/>
-      <c r="D398" s="36"/>
-      <c r="E398" s="36"/>
-      <c r="F398" s="36"/>
-      <c r="G398" s="36"/>
-      <c r="H398" s="61"/>
-      <c r="I398" s="61"/>
-    </row>
-    <row r="399" spans="1:9">
-      <c r="A399" s="9" t="s">
-        <v>955</v>
-      </c>
-      <c r="B399" s="36"/>
-      <c r="C399" s="36"/>
-      <c r="D399" s="36"/>
-      <c r="E399" s="36"/>
-      <c r="F399" s="36"/>
-      <c r="G399" s="36"/>
-      <c r="H399" s="61"/>
-      <c r="I399" s="61"/>
-    </row>
-    <row r="400" spans="1:9">
-      <c r="A400" s="9" t="s">
-        <v>956</v>
-      </c>
-      <c r="B400" s="36"/>
-      <c r="C400" s="36"/>
-      <c r="D400" s="36"/>
-      <c r="E400" s="36"/>
-      <c r="F400" s="36"/>
-      <c r="G400" s="36"/>
-      <c r="H400" s="61"/>
-      <c r="I400" s="61"/>
-    </row>
-    <row r="401" spans="1:9">
-      <c r="A401" s="9" t="s">
-        <v>957</v>
-      </c>
-      <c r="B401" s="36"/>
-      <c r="C401" s="36"/>
-      <c r="D401" s="36"/>
-      <c r="E401" s="36"/>
-      <c r="F401" s="36"/>
-      <c r="G401" s="36"/>
-      <c r="H401" s="61"/>
-      <c r="I401" s="61"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/产品规格.xlsx
+++ b/产品规格.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1293" uniqueCount="977">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1297" uniqueCount="957">
   <si>
     <t>17.5*3*27</t>
   </si>
@@ -2133,1053 +2133,773 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>XC325</t>
+  </si>
+  <si>
+    <t>XC326</t>
+  </si>
+  <si>
+    <t>XC327</t>
+  </si>
+  <si>
+    <t>XC328</t>
+  </si>
+  <si>
+    <t>XC329</t>
+  </si>
+  <si>
+    <t>XC330</t>
+  </si>
+  <si>
+    <t>XC331</t>
+  </si>
+  <si>
+    <t>XC332</t>
+  </si>
+  <si>
+    <t>XC333</t>
+  </si>
+  <si>
+    <t>XC334</t>
+  </si>
+  <si>
+    <t>XC335</t>
+  </si>
+  <si>
+    <t>XC336</t>
+  </si>
+  <si>
+    <t>XC337</t>
+  </si>
+  <si>
+    <t>XC338</t>
+  </si>
+  <si>
+    <t>XC339</t>
+  </si>
+  <si>
+    <t>XC340</t>
+  </si>
+  <si>
+    <t>XC341</t>
+  </si>
+  <si>
+    <t>XC342</t>
+  </si>
+  <si>
+    <t>XC343</t>
+  </si>
+  <si>
+    <t>XC344</t>
+  </si>
+  <si>
+    <t>XC345</t>
+  </si>
+  <si>
+    <t>XC346</t>
+  </si>
+  <si>
+    <t>XC347</t>
+  </si>
+  <si>
+    <t>XC348</t>
+  </si>
+  <si>
+    <t>XC349</t>
+  </si>
+  <si>
+    <t>XC350</t>
+  </si>
+  <si>
+    <t>XC351</t>
+  </si>
+  <si>
+    <t>XC352</t>
+  </si>
+  <si>
+    <t>XC353</t>
+  </si>
+  <si>
+    <t>XC354</t>
+  </si>
+  <si>
+    <t>XC355</t>
+  </si>
+  <si>
+    <t>XC356</t>
+  </si>
+  <si>
+    <t>XC357</t>
+  </si>
+  <si>
+    <t>XC358</t>
+  </si>
+  <si>
+    <t>XC359</t>
+  </si>
+  <si>
+    <t>XC360</t>
+  </si>
+  <si>
+    <t>XC361</t>
+  </si>
+  <si>
+    <t>XC362</t>
+  </si>
+  <si>
+    <t>XC363</t>
+  </si>
+  <si>
+    <t>XC364</t>
+  </si>
+  <si>
+    <t>XC365</t>
+  </si>
+  <si>
+    <t>XC366</t>
+  </si>
+  <si>
+    <t>XC367</t>
+  </si>
+  <si>
+    <t>XC368</t>
+  </si>
+  <si>
+    <t>XC369</t>
+  </si>
+  <si>
+    <t>XC370</t>
+  </si>
+  <si>
+    <t>XC371</t>
+  </si>
+  <si>
+    <t>XC372</t>
+  </si>
+  <si>
+    <t>XC373</t>
+  </si>
+  <si>
+    <t>XC374</t>
+  </si>
+  <si>
+    <t>XC375</t>
+  </si>
+  <si>
+    <t>XC376</t>
+  </si>
+  <si>
+    <t>XC377</t>
+  </si>
+  <si>
+    <t>XC378</t>
+  </si>
+  <si>
+    <t>XC379</t>
+  </si>
+  <si>
+    <t>XC380</t>
+  </si>
+  <si>
+    <t>XC381</t>
+  </si>
+  <si>
+    <t>XC382</t>
+  </si>
+  <si>
+    <t>XC383</t>
+  </si>
+  <si>
+    <t>XC384</t>
+  </si>
+  <si>
+    <t>XC385</t>
+  </si>
+  <si>
+    <t>XC386</t>
+  </si>
+  <si>
+    <t>XC387</t>
+  </si>
+  <si>
+    <t>XC388</t>
+  </si>
+  <si>
+    <t>XC389</t>
+  </si>
+  <si>
+    <t>XC390</t>
+  </si>
+  <si>
+    <t>XC391</t>
+  </si>
+  <si>
+    <t>XC392</t>
+  </si>
+  <si>
     <t>XC001</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>1*1半光横条</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>75*75*150</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>22*3*38</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>22*3*39</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>14*2*25</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>22*3*40</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>17*3*28</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>25梭T400无捻牛津</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>27梭T400无捻牛津</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>26梭T400无捻牛津</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>17*2*26</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">50S*50S弹力 酷丝棉平纹  </t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>17*2*30</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>50S*50S</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*40S弹力 酷丝棉平纹  </t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>18*2*27</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*40S</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*75T 酷丝棉平纹  </t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*75D 酷丝棉2/1</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*75D 酷丝棉2/2 </t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*150 酷丝棉26S平纹  </t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*150 酷丝棉2/1 </t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*150D 酷丝棉2/2 </t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*150 酷丝棉28S平纹  </t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*150 酷丝棉24S平纹  </t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*150 酷丝棉3/3斜  </t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">50S*75D 酷丝棉2/2 </t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>50S*75D 酷丝棉绮兵</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*75 酷丝棉3/3斜  </t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>13.5*4*35</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*75T400</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">50S*75D 酷丝棉2/1 </t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>XC186</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>17.5*3*35</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*75 酷丝棉3/2斜  </t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>17.5*3*34</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*75DT400</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*150 酷丝棉5/1斜  </t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100*150T8 4/2斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>17*4*215*40</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100D*150T800</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75*150T400 消3/3斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>17*4*36</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75*75T400消 3/3斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75*75 半光2/2 斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>18*4*46</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75*75 消光2/2 斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>18*4*43</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75*150 消光2/2 斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75*75-T800消光骑士斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>17*4*38</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75消*75T800</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>19*5*45</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>19*3*39</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>X字格</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>16*4*46</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>T400横条2*1</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>16*4+28</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>238克</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>T400横条1*4</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>17*4+38</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>75*75*150</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>白坯200米克</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>T400横条1*1</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>16*4*30</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>100*75*150</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*75闪电斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>18*3*38</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*75</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*150酷丝绵 小钻石斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*150酷丝绵 大钻石斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*300 3/2变化斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>13.5*4*28</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*150*2T400</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>米克385</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100D半光*35S-3/3斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>16*4*40</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100*35</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100D消光*35S-3/3斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100*35S</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>120D扁平0.5格</t>
+  </si>
+  <si>
+    <t>17*4*44</t>
+  </si>
+  <si>
+    <t>120*35S</t>
+  </si>
+  <si>
+    <t>米克370</t>
   </si>
   <si>
     <t>120D扁平3/3斜-45</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>16*4*45</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>120*35S</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>米克370</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>120D扁平4/4斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>17*4*45</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>米克375</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100D消光多乐3/3斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>15*4*43</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>米克300</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>120D扁平1/2斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>17*4*34</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>米克350</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>120D扁平T800变化斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>17*4*29</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>120*150T800</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>米克380</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>120D扁平牛津</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>20*2*31</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*75 酷丝棉3/1斜 </t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>13.5*4*34</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*150 酷丝棉3/1斜 31</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*150 酷丝棉3/2斜 39</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*75D 酷丝棉2/1 30</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>17*3*30</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*75D 酷丝棉2/2 30</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*75D 酷丝棉2/2 38</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*75D 骑兵斜 30 </t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*75D 骑兵斜 38 </t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*300 酷丝棉3/2斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>13.5*4*27</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*75T 酷丝棉平纹 33S </t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*300酷丝绵珍珠点</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>17.5*3*25</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*150*300T400</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>米克368</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*75D酷丝绵细双斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>17.5*3*36</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*150T400+300T400</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>80S*75双线格酷丝绵</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75 T800半光0.5格</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75*75*210</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>50D经纬 T8 0.5格</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>22*2*40</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>50*50</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>半光大猫眼</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>16*4*43</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100半低*150半T800</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>50D低弹*50T800 平纹</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>23*2*40</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>30D T8 平纹</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>22*3*57</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>30*30</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75D经纬T8平纹</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75经纬T8 2/2斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>19*3*38</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">50DT8*50DT8 骑兵斜  </t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>21*3*53</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>50DT8*50DT8</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>T8五面埋伏</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>14*4*38</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>50D*100D经纬T800珍珠点</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>21*3*49</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>50D*50D*100D T800</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>T800双链条</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>米克265</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>经消光低弹 双纬T800</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75D半光T800双纬平纹</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75消低弹*75T8002/2斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>17.5*4*38</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*150T800酷丝棉3/2斜  </t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*150T800</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>空变T8平纹</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*75T8酷丝棉3/1.超钛棉</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>17.5*3*44</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*75T800</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*300加厚超钛棉</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>14*4*27</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*300T800</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>白坯370克</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100D消光75DT800 3/3斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>15.5*4*48</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100*75T8</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>米克250</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>37梭多乐绵</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>16*4*37</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100D*40S+150D T8</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>21*3*45</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>白坯188克</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">斜纹毛巾底 </t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>13.5*4*51</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*150T8*300低弹</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>18*3*43</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>网纹3/3-180</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>17*4*44</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75D*50S+10DT8</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>白坯米克245</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>网纹3/3-220</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>15*4*44</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100D*35S+150DT8</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>白坯3</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>00克</t>
-    </r>
-    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>白坯300克</t>
   </si>
   <si>
     <t>天丝棉</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>20*3*32</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>80S*三合一</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>白坯195克</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>21*3*31</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>270-钛金棉</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>14*4*26.5</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*35S*2</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>白坯365克</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">40S*35S 酷3/3斜 </t>
-    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>生态棉</t>
   </si>
   <si>
     <t>16*4*44</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*35S</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>210-钛金棉</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>17*3*27</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*30S</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>白坯285克</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>加厚钛金棉</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>15.5*4*30</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>白坯390克</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>240-钛金棉</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>17.5*3*31</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>白坯310克</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">40S*35S 酷3/3斜  加厚 </t>
-    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">生态棉 加厚 </t>
   </si>
   <si>
     <t>16*4*31</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>XC325</t>
-  </si>
-  <si>
-    <t>XC326</t>
-  </si>
-  <si>
-    <t>XC327</t>
-  </si>
-  <si>
-    <t>XC328</t>
-  </si>
-  <si>
-    <t>XC329</t>
-  </si>
-  <si>
-    <t>XC330</t>
-  </si>
-  <si>
-    <t>XC331</t>
-  </si>
-  <si>
-    <t>XC332</t>
-  </si>
-  <si>
-    <t>XC333</t>
-  </si>
-  <si>
-    <t>XC334</t>
-  </si>
-  <si>
-    <t>XC335</t>
-  </si>
-  <si>
-    <t>XC336</t>
-  </si>
-  <si>
-    <t>XC337</t>
-  </si>
-  <si>
-    <t>XC338</t>
-  </si>
-  <si>
-    <t>XC339</t>
-  </si>
-  <si>
-    <t>XC340</t>
-  </si>
-  <si>
-    <t>XC341</t>
-  </si>
-  <si>
-    <t>XC342</t>
-  </si>
-  <si>
-    <t>XC343</t>
-  </si>
-  <si>
-    <t>XC344</t>
-  </si>
-  <si>
-    <t>XC345</t>
-  </si>
-  <si>
-    <t>XC346</t>
-  </si>
-  <si>
-    <t>XC347</t>
-  </si>
-  <si>
-    <t>XC348</t>
-  </si>
-  <si>
-    <t>XC349</t>
-  </si>
-  <si>
-    <t>XC350</t>
-  </si>
-  <si>
-    <t>XC351</t>
-  </si>
-  <si>
-    <t>XC352</t>
-  </si>
-  <si>
-    <t>XC353</t>
-  </si>
-  <si>
-    <t>XC354</t>
-  </si>
-  <si>
-    <t>XC355</t>
-  </si>
-  <si>
-    <t>XC356</t>
-  </si>
-  <si>
-    <t>XC357</t>
-  </si>
-  <si>
-    <t>XC358</t>
-  </si>
-  <si>
-    <t>XC359</t>
-  </si>
-  <si>
-    <t>XC360</t>
-  </si>
-  <si>
-    <t>XC361</t>
-  </si>
-  <si>
-    <t>XC362</t>
-  </si>
-  <si>
-    <t>XC363</t>
-  </si>
-  <si>
-    <t>XC364</t>
-  </si>
-  <si>
-    <t>XC365</t>
-  </si>
-  <si>
-    <t>XC366</t>
-  </si>
-  <si>
-    <t>XC367</t>
-  </si>
-  <si>
-    <t>XC368</t>
-  </si>
-  <si>
-    <t>XC369</t>
-  </si>
-  <si>
-    <t>XC370</t>
-  </si>
-  <si>
-    <t>XC371</t>
-  </si>
-  <si>
-    <t>XC372</t>
-  </si>
-  <si>
-    <t>XC373</t>
-  </si>
-  <si>
-    <t>XC374</t>
-  </si>
-  <si>
-    <t>XC375</t>
-  </si>
-  <si>
-    <t>XC376</t>
-  </si>
-  <si>
-    <t>XC377</t>
-  </si>
-  <si>
-    <t>XC378</t>
-  </si>
-  <si>
-    <t>XC379</t>
-  </si>
-  <si>
-    <t>XC380</t>
-  </si>
-  <si>
-    <t>XC381</t>
-  </si>
-  <si>
-    <t>XC382</t>
-  </si>
-  <si>
-    <t>XC383</t>
-  </si>
-  <si>
-    <t>XC384</t>
-  </si>
-  <si>
-    <t>XC385</t>
-  </si>
-  <si>
-    <t>XC386</t>
-  </si>
-  <si>
-    <t>XC387</t>
-  </si>
-  <si>
-    <t>XC388</t>
-  </si>
-  <si>
-    <t>XC389</t>
-  </si>
-  <si>
-    <t>XC390</t>
-  </si>
-  <si>
-    <t>XC391</t>
-  </si>
-  <si>
-    <t>XC392</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3252,13 +2972,6 @@
       <b/>
       <sz val="9"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -4054,16 +3767,16 @@
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="9" t="s">
-        <v>703</v>
+        <v>771</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>704</v>
+        <v>772</v>
       </c>
       <c r="C2" s="10" t="s">
         <v>0</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>705</v>
+        <v>4</v>
       </c>
       <c r="E2" s="10">
         <v>79</v>
@@ -4750,7 +4463,7 @@
         <v>68</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>706</v>
+        <v>773</v>
       </c>
       <c r="D29" s="10" t="s">
         <v>46</v>
@@ -4775,7 +4488,7 @@
         <v>70</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>707</v>
+        <v>774</v>
       </c>
       <c r="D30" s="10" t="s">
         <v>46</v>
@@ -5427,7 +5140,7 @@
         <v>137</v>
       </c>
       <c r="C56" s="13" t="s">
-        <v>708</v>
+        <v>775</v>
       </c>
       <c r="D56" s="13" t="s">
         <v>135</v>
@@ -5954,7 +5667,7 @@
         <v>193</v>
       </c>
       <c r="C77" s="10" t="s">
-        <v>709</v>
+        <v>73</v>
       </c>
       <c r="D77" s="10" t="s">
         <v>144</v>
@@ -7304,7 +7017,7 @@
         <v>330</v>
       </c>
       <c r="C131" s="24" t="s">
-        <v>710</v>
+        <v>776</v>
       </c>
       <c r="D131" s="24" t="s">
         <v>148</v>
@@ -7842,7 +7555,7 @@
         <v>208</v>
       </c>
       <c r="H152" s="13">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="I152" s="11"/>
     </row>
@@ -8063,7 +7776,7 @@
         <v>412</v>
       </c>
       <c r="B161" s="22" t="s">
-        <v>711</v>
+        <v>777</v>
       </c>
       <c r="C161" s="22" t="s">
         <v>413</v>
@@ -8144,7 +7857,7 @@
         <v>421</v>
       </c>
       <c r="B164" s="22" t="s">
-        <v>712</v>
+        <v>778</v>
       </c>
       <c r="C164" s="22" t="s">
         <v>422</v>
@@ -8171,10 +7884,10 @@
         <v>423</v>
       </c>
       <c r="B165" s="22" t="s">
-        <v>713</v>
+        <v>779</v>
       </c>
       <c r="C165" s="22" t="s">
-        <v>714</v>
+        <v>780</v>
       </c>
       <c r="D165" s="22" t="s">
         <v>414</v>
@@ -8211,13 +7924,13 @@
         <v>425</v>
       </c>
       <c r="B167" s="18" t="s">
-        <v>715</v>
+        <v>781</v>
       </c>
       <c r="C167" s="18" t="s">
-        <v>716</v>
+        <v>782</v>
       </c>
       <c r="D167" s="18" t="s">
-        <v>717</v>
+        <v>783</v>
       </c>
       <c r="E167" s="18">
         <v>80</v>
@@ -8229,7 +7942,7 @@
         <v>220</v>
       </c>
       <c r="H167" s="18">
-        <v>4.0999999999999996</v>
+        <v>4</v>
       </c>
       <c r="I167" s="11"/>
     </row>
@@ -8238,13 +7951,13 @@
         <v>426</v>
       </c>
       <c r="B168" s="18" t="s">
-        <v>718</v>
+        <v>784</v>
       </c>
       <c r="C168" s="18" t="s">
-        <v>719</v>
+        <v>417</v>
       </c>
       <c r="D168" s="18" t="s">
-        <v>720</v>
+        <v>785</v>
       </c>
       <c r="E168" s="18">
         <v>110</v>
@@ -8256,7 +7969,7 @@
         <v>208</v>
       </c>
       <c r="H168" s="18">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="I168" s="11"/>
     </row>
@@ -8265,7 +7978,7 @@
         <v>427</v>
       </c>
       <c r="B169" s="18" t="s">
-        <v>721</v>
+        <v>786</v>
       </c>
       <c r="C169" s="18" t="s">
         <v>428</v>
@@ -8292,7 +8005,7 @@
         <v>430</v>
       </c>
       <c r="B170" s="18" t="s">
-        <v>722</v>
+        <v>787</v>
       </c>
       <c r="C170" s="18" t="s">
         <v>431</v>
@@ -8319,7 +8032,7 @@
         <v>432</v>
       </c>
       <c r="B171" s="18" t="s">
-        <v>723</v>
+        <v>788</v>
       </c>
       <c r="C171" s="18" t="s">
         <v>238</v>
@@ -8373,7 +8086,7 @@
         <v>435</v>
       </c>
       <c r="B173" s="18" t="s">
-        <v>724</v>
+        <v>789</v>
       </c>
       <c r="C173" s="18" t="s">
         <v>436</v>
@@ -8400,7 +8113,7 @@
         <v>438</v>
       </c>
       <c r="B174" s="18" t="s">
-        <v>725</v>
+        <v>790</v>
       </c>
       <c r="C174" s="18" t="s">
         <v>439</v>
@@ -8427,7 +8140,7 @@
         <v>440</v>
       </c>
       <c r="B175" s="18" t="s">
-        <v>726</v>
+        <v>791</v>
       </c>
       <c r="C175" s="18" t="s">
         <v>32</v>
@@ -8508,7 +8221,7 @@
         <v>446</v>
       </c>
       <c r="B178" s="18" t="s">
-        <v>727</v>
+        <v>792</v>
       </c>
       <c r="C178" s="18" t="s">
         <v>420</v>
@@ -8562,7 +8275,7 @@
         <v>450</v>
       </c>
       <c r="B180" s="18" t="s">
-        <v>728</v>
+        <v>793</v>
       </c>
       <c r="C180" s="18" t="s">
         <v>451</v>
@@ -8589,7 +8302,7 @@
         <v>452</v>
       </c>
       <c r="B181" s="18" t="s">
-        <v>729</v>
+        <v>794</v>
       </c>
       <c r="C181" s="18" t="s">
         <v>445</v>
@@ -8616,7 +8329,7 @@
         <v>453</v>
       </c>
       <c r="B182" s="34" t="s">
-        <v>730</v>
+        <v>795</v>
       </c>
       <c r="C182" s="34" t="s">
         <v>309</v>
@@ -8643,7 +8356,7 @@
         <v>455</v>
       </c>
       <c r="B183" s="34" t="s">
-        <v>731</v>
+        <v>796</v>
       </c>
       <c r="C183" s="34" t="s">
         <v>309</v>
@@ -8697,13 +8410,13 @@
         <v>460</v>
       </c>
       <c r="B185" s="18" t="s">
-        <v>732</v>
+        <v>797</v>
       </c>
       <c r="C185" s="18" t="s">
-        <v>733</v>
+        <v>445</v>
       </c>
       <c r="D185" s="18" t="s">
-        <v>734</v>
+        <v>429</v>
       </c>
       <c r="E185" s="18">
         <v>112</v>
@@ -8724,7 +8437,7 @@
         <v>461</v>
       </c>
       <c r="B186" s="34" t="s">
-        <v>735</v>
+        <v>798</v>
       </c>
       <c r="C186" s="34" t="s">
         <v>309</v>
@@ -8748,13 +8461,13 @@
     </row>
     <row r="187" spans="1:9">
       <c r="A187" s="9" t="s">
-        <v>736</v>
+        <v>799</v>
       </c>
       <c r="B187" s="18" t="s">
         <v>442</v>
       </c>
       <c r="C187" s="18" t="s">
-        <v>737</v>
+        <v>238</v>
       </c>
       <c r="D187" s="18" t="s">
         <v>437</v>
@@ -8778,13 +8491,13 @@
         <v>462</v>
       </c>
       <c r="B188" s="18" t="s">
-        <v>738</v>
+        <v>800</v>
       </c>
       <c r="C188" s="18" t="s">
-        <v>739</v>
+        <v>272</v>
       </c>
       <c r="D188" s="18" t="s">
-        <v>740</v>
+        <v>801</v>
       </c>
       <c r="E188" s="18">
         <v>110</v>
@@ -8805,7 +8518,7 @@
         <v>463</v>
       </c>
       <c r="B189" s="18" t="s">
-        <v>741</v>
+        <v>802</v>
       </c>
       <c r="C189" s="18" t="s">
         <v>445</v>
@@ -8823,7 +8536,7 @@
         <v>215</v>
       </c>
       <c r="H189" s="18">
-        <v>4.5</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="I189" s="11"/>
     </row>
@@ -8832,13 +8545,13 @@
         <v>464</v>
       </c>
       <c r="B190" s="10" t="s">
-        <v>742</v>
+        <v>803</v>
       </c>
       <c r="C190" s="10" t="s">
-        <v>743</v>
+        <v>804</v>
       </c>
       <c r="D190" s="10" t="s">
-        <v>744</v>
+        <v>805</v>
       </c>
       <c r="E190" s="11">
         <v>152</v>
@@ -8859,10 +8572,10 @@
         <v>465</v>
       </c>
       <c r="B191" s="18" t="s">
-        <v>726</v>
+        <v>791</v>
       </c>
       <c r="C191" s="18" t="s">
-        <v>737</v>
+        <v>238</v>
       </c>
       <c r="D191" s="18" t="s">
         <v>437</v>
@@ -8912,10 +8625,10 @@
         <v>468</v>
       </c>
       <c r="B194" s="41" t="s">
-        <v>745</v>
+        <v>806</v>
       </c>
       <c r="C194" s="42" t="s">
-        <v>746</v>
+        <v>385</v>
       </c>
       <c r="D194" s="43" t="s">
         <v>148</v>
@@ -8939,7 +8652,7 @@
         <v>469</v>
       </c>
       <c r="B195" s="41" t="s">
-        <v>747</v>
+        <v>807</v>
       </c>
       <c r="C195" s="42" t="s">
         <v>470</v>
@@ -8966,10 +8679,10 @@
         <v>471</v>
       </c>
       <c r="B196" s="45" t="s">
-        <v>748</v>
+        <v>808</v>
       </c>
       <c r="C196" s="45" t="s">
-        <v>749</v>
+        <v>809</v>
       </c>
       <c r="D196" s="45" t="s">
         <v>472</v>
@@ -8993,10 +8706,10 @@
         <v>473</v>
       </c>
       <c r="B197" s="45" t="s">
-        <v>750</v>
+        <v>810</v>
       </c>
       <c r="C197" s="45" t="s">
-        <v>751</v>
+        <v>389</v>
       </c>
       <c r="D197" s="45" t="s">
         <v>386</v>
@@ -9020,7 +8733,7 @@
         <v>474</v>
       </c>
       <c r="B198" s="45" t="s">
-        <v>752</v>
+        <v>811</v>
       </c>
       <c r="C198" s="45" t="s">
         <v>475</v>
@@ -9047,13 +8760,13 @@
         <v>477</v>
       </c>
       <c r="B199" s="45" t="s">
-        <v>753</v>
+        <v>812</v>
       </c>
       <c r="C199" s="45" t="s">
-        <v>754</v>
+        <v>401</v>
       </c>
       <c r="D199" s="45" t="s">
-        <v>755</v>
+        <v>813</v>
       </c>
       <c r="E199" s="45">
         <v>95</v>
@@ -9065,7 +8778,7 @@
         <v>215</v>
       </c>
       <c r="H199" s="45">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="I199" s="37"/>
     </row>
@@ -9231,7 +8944,7 @@
         <v>496</v>
       </c>
       <c r="C208" s="10" t="s">
-        <v>756</v>
+        <v>814</v>
       </c>
       <c r="D208" s="10" t="s">
         <v>39</v>
@@ -9246,7 +8959,7 @@
         <v>170</v>
       </c>
       <c r="H208" s="10">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="I208" s="11"/>
     </row>
@@ -9294,7 +9007,7 @@
         <v>501</v>
       </c>
       <c r="C211" s="10" t="s">
-        <v>757</v>
+        <v>815</v>
       </c>
       <c r="D211" s="10" t="s">
         <v>39</v>
@@ -9316,10 +9029,10 @@
         <v>502</v>
       </c>
       <c r="B212" s="35" t="s">
-        <v>758</v>
+        <v>816</v>
       </c>
       <c r="C212" s="35" t="s">
-        <v>759</v>
+        <v>817</v>
       </c>
       <c r="D212" s="35" t="s">
         <v>144</v>
@@ -9359,7 +9072,7 @@
         <v>178</v>
       </c>
       <c r="H213" s="10">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="I213" s="37"/>
     </row>
@@ -9371,7 +9084,7 @@
         <v>507</v>
       </c>
       <c r="C214" s="35" t="s">
-        <v>759</v>
+        <v>817</v>
       </c>
       <c r="D214" s="35" t="s">
         <v>144</v>
@@ -9484,10 +9197,10 @@
         <v>519</v>
       </c>
       <c r="B220" s="10" t="s">
-        <v>760</v>
+        <v>818</v>
       </c>
       <c r="C220" s="10" t="s">
-        <v>761</v>
+        <v>819</v>
       </c>
       <c r="D220" s="49" t="s">
         <v>520</v>
@@ -9505,7 +9218,7 @@
         <v>3.4</v>
       </c>
       <c r="I220" s="11" t="s">
-        <v>762</v>
+        <v>820</v>
       </c>
     </row>
     <row r="221" spans="1:9">
@@ -9513,13 +9226,13 @@
         <v>521</v>
       </c>
       <c r="B221" s="10" t="s">
-        <v>763</v>
+        <v>821</v>
       </c>
       <c r="C221" s="10" t="s">
-        <v>764</v>
+        <v>822</v>
       </c>
       <c r="D221" s="49" t="s">
-        <v>765</v>
+        <v>4</v>
       </c>
       <c r="E221" s="10">
         <v>100</v>
@@ -9534,7 +9247,7 @@
         <v>3.3</v>
       </c>
       <c r="I221" s="37" t="s">
-        <v>766</v>
+        <v>823</v>
       </c>
     </row>
     <row r="222" spans="1:9">
@@ -9542,13 +9255,13 @@
         <v>522</v>
       </c>
       <c r="B222" s="10" t="s">
-        <v>767</v>
+        <v>824</v>
       </c>
       <c r="C222" s="10" t="s">
-        <v>768</v>
+        <v>825</v>
       </c>
       <c r="D222" s="49" t="s">
-        <v>769</v>
+        <v>520</v>
       </c>
       <c r="E222" s="10">
         <v>115</v>
@@ -9596,13 +9309,13 @@
         <v>526</v>
       </c>
       <c r="B224" s="35" t="s">
-        <v>770</v>
+        <v>826</v>
       </c>
       <c r="C224" s="35" t="s">
-        <v>771</v>
+        <v>827</v>
       </c>
       <c r="D224" s="35" t="s">
-        <v>772</v>
+        <v>828</v>
       </c>
       <c r="E224" s="35">
         <v>120</v>
@@ -9650,10 +9363,10 @@
         <v>530</v>
       </c>
       <c r="B226" s="35" t="s">
-        <v>773</v>
+        <v>829</v>
       </c>
       <c r="C226" s="35" t="s">
-        <v>737</v>
+        <v>238</v>
       </c>
       <c r="D226" s="35" t="s">
         <v>437</v>
@@ -9677,10 +9390,10 @@
         <v>531</v>
       </c>
       <c r="B227" s="35" t="s">
-        <v>774</v>
+        <v>830</v>
       </c>
       <c r="C227" s="35" t="s">
-        <v>737</v>
+        <v>238</v>
       </c>
       <c r="D227" s="35" t="s">
         <v>437</v>
@@ -9834,13 +9547,13 @@
         <v>544</v>
       </c>
       <c r="B234" s="52" t="s">
-        <v>775</v>
+        <v>831</v>
       </c>
       <c r="C234" s="52" t="s">
-        <v>776</v>
+        <v>832</v>
       </c>
       <c r="D234" s="50" t="s">
-        <v>777</v>
+        <v>833</v>
       </c>
       <c r="E234" s="52">
         <v>190</v>
@@ -9855,7 +9568,7 @@
         <v>5.8</v>
       </c>
       <c r="I234" s="54" t="s">
-        <v>778</v>
+        <v>834</v>
       </c>
     </row>
     <row r="235" spans="1:9">
@@ -9863,13 +9576,13 @@
         <v>545</v>
       </c>
       <c r="B235" s="51" t="s">
-        <v>779</v>
+        <v>835</v>
       </c>
       <c r="C235" s="51" t="s">
-        <v>780</v>
+        <v>836</v>
       </c>
       <c r="D235" s="51" t="s">
-        <v>781</v>
+        <v>837</v>
       </c>
       <c r="E235" s="51">
         <v>155</v>
@@ -9905,13 +9618,13 @@
         <v>548</v>
       </c>
       <c r="B237" s="51" t="s">
-        <v>782</v>
+        <v>838</v>
       </c>
       <c r="C237" s="51" t="s">
         <v>549</v>
       </c>
       <c r="D237" s="51" t="s">
-        <v>783</v>
+        <v>839</v>
       </c>
       <c r="E237" s="51">
         <v>155</v>
@@ -9933,27 +9646,43 @@
       <c r="A238" s="9" t="s">
         <v>550</v>
       </c>
-      <c r="B238" s="38"/>
-      <c r="C238" s="38"/>
-      <c r="D238" s="38"/>
-      <c r="E238" s="38"/>
-      <c r="F238" s="38"/>
-      <c r="G238" s="38"/>
-      <c r="H238" s="38"/>
-      <c r="I238" s="38"/>
+      <c r="B238" s="38" t="s">
+        <v>840</v>
+      </c>
+      <c r="C238" s="38" t="s">
+        <v>841</v>
+      </c>
+      <c r="D238" s="38" t="s">
+        <v>842</v>
+      </c>
+      <c r="E238" s="38">
+        <v>190</v>
+      </c>
+      <c r="F238" s="38">
+        <v>270</v>
+      </c>
+      <c r="G238" s="38">
+        <v>216</v>
+      </c>
+      <c r="H238" s="38">
+        <v>5.8</v>
+      </c>
+      <c r="I238" s="38" t="s">
+        <v>843</v>
+      </c>
     </row>
     <row r="239" spans="1:9">
       <c r="A239" s="9" t="s">
         <v>551</v>
       </c>
       <c r="B239" s="51" t="s">
-        <v>784</v>
+        <v>844</v>
       </c>
       <c r="C239" s="51" t="s">
-        <v>785</v>
+        <v>845</v>
       </c>
       <c r="D239" s="51" t="s">
-        <v>786</v>
+        <v>842</v>
       </c>
       <c r="E239" s="52">
         <v>180</v>
@@ -9965,10 +9694,10 @@
         <v>220</v>
       </c>
       <c r="H239" s="51">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I239" s="54" t="s">
-        <v>787</v>
+        <v>843</v>
       </c>
     </row>
     <row r="240" spans="1:9">
@@ -9976,13 +9705,13 @@
         <v>552</v>
       </c>
       <c r="B240" s="51" t="s">
-        <v>788</v>
+        <v>846</v>
       </c>
       <c r="C240" s="51" t="s">
-        <v>789</v>
+        <v>847</v>
       </c>
       <c r="D240" s="51" t="s">
-        <v>786</v>
+        <v>842</v>
       </c>
       <c r="E240" s="52">
         <v>190</v>
@@ -9997,7 +9726,7 @@
         <v>5.5</v>
       </c>
       <c r="I240" s="54" t="s">
-        <v>790</v>
+        <v>848</v>
       </c>
     </row>
     <row r="241" spans="1:9">
@@ -10005,10 +9734,10 @@
         <v>553</v>
       </c>
       <c r="B241" s="51" t="s">
-        <v>791</v>
+        <v>849</v>
       </c>
       <c r="C241" s="51" t="s">
-        <v>792</v>
+        <v>850</v>
       </c>
       <c r="D241" s="11" t="s">
         <v>554</v>
@@ -10026,7 +9755,7 @@
         <v>5.2</v>
       </c>
       <c r="I241" s="55" t="s">
-        <v>793</v>
+        <v>851</v>
       </c>
     </row>
     <row r="242" spans="1:9">
@@ -10034,13 +9763,13 @@
         <v>555</v>
       </c>
       <c r="B242" s="51" t="s">
-        <v>794</v>
+        <v>852</v>
       </c>
       <c r="C242" s="51" t="s">
-        <v>795</v>
+        <v>853</v>
       </c>
       <c r="D242" s="51" t="s">
-        <v>786</v>
+        <v>842</v>
       </c>
       <c r="E242" s="52">
         <v>160</v>
@@ -10055,7 +9784,7 @@
         <v>4.9000000000000004</v>
       </c>
       <c r="I242" s="54" t="s">
-        <v>796</v>
+        <v>854</v>
       </c>
     </row>
     <row r="243" spans="1:9">
@@ -10063,13 +9792,13 @@
         <v>556</v>
       </c>
       <c r="B243" s="51" t="s">
-        <v>797</v>
+        <v>855</v>
       </c>
       <c r="C243" s="51" t="s">
-        <v>798</v>
+        <v>856</v>
       </c>
       <c r="D243" s="51" t="s">
-        <v>799</v>
+        <v>857</v>
       </c>
       <c r="E243" s="52">
         <v>190</v>
@@ -10084,7 +9813,7 @@
         <v>5.6</v>
       </c>
       <c r="I243" s="54" t="s">
-        <v>800</v>
+        <v>858</v>
       </c>
     </row>
     <row r="244" spans="1:9">
@@ -10092,13 +9821,13 @@
         <v>557</v>
       </c>
       <c r="B244" s="51" t="s">
-        <v>801</v>
+        <v>859</v>
       </c>
       <c r="C244" s="51" t="s">
-        <v>802</v>
+        <v>860</v>
       </c>
       <c r="D244" s="51" t="s">
-        <v>799</v>
+        <v>857</v>
       </c>
       <c r="E244" s="51">
         <v>150</v>
@@ -10130,13 +9859,13 @@
         <v>559</v>
       </c>
       <c r="B246" s="18" t="s">
-        <v>803</v>
+        <v>861</v>
       </c>
       <c r="C246" s="18" t="s">
-        <v>804</v>
+        <v>862</v>
       </c>
       <c r="D246" s="33" t="s">
-        <v>734</v>
+        <v>429</v>
       </c>
       <c r="E246" s="18">
         <v>112</v>
@@ -10157,7 +9886,7 @@
         <v>560</v>
       </c>
       <c r="B247" s="18" t="s">
-        <v>805</v>
+        <v>863</v>
       </c>
       <c r="C247" s="18" t="s">
         <v>529</v>
@@ -10184,7 +9913,7 @@
         <v>561</v>
       </c>
       <c r="B248" s="18" t="s">
-        <v>806</v>
+        <v>864</v>
       </c>
       <c r="C248" s="18" t="s">
         <v>562</v>
@@ -10211,10 +9940,10 @@
         <v>563</v>
       </c>
       <c r="B249" s="18" t="s">
-        <v>807</v>
+        <v>865</v>
       </c>
       <c r="C249" s="18" t="s">
-        <v>808</v>
+        <v>439</v>
       </c>
       <c r="D249" s="18" t="s">
         <v>429</v>
@@ -10238,7 +9967,7 @@
         <v>564</v>
       </c>
       <c r="B250" s="18" t="s">
-        <v>809</v>
+        <v>866</v>
       </c>
       <c r="C250" s="18" t="s">
         <v>153</v>
@@ -10265,7 +9994,7 @@
         <v>565</v>
       </c>
       <c r="B251" s="18" t="s">
-        <v>810</v>
+        <v>867</v>
       </c>
       <c r="C251" s="18" t="s">
         <v>566</v>
@@ -10292,10 +10021,10 @@
         <v>567</v>
       </c>
       <c r="B252" s="18" t="s">
-        <v>811</v>
+        <v>868</v>
       </c>
       <c r="C252" s="18" t="s">
-        <v>808</v>
+        <v>439</v>
       </c>
       <c r="D252" s="18" t="s">
         <v>429</v>
@@ -10319,7 +10048,7 @@
         <v>568</v>
       </c>
       <c r="B253" s="18" t="s">
-        <v>812</v>
+        <v>869</v>
       </c>
       <c r="C253" s="18" t="s">
         <v>566</v>
@@ -10346,13 +10075,13 @@
         <v>569</v>
       </c>
       <c r="B254" s="18" t="s">
-        <v>813</v>
+        <v>870</v>
       </c>
       <c r="C254" s="18" t="s">
-        <v>814</v>
+        <v>871</v>
       </c>
       <c r="D254" s="18" t="s">
-        <v>777</v>
+        <v>833</v>
       </c>
       <c r="E254" s="18">
         <v>190</v>
@@ -10367,7 +10096,7 @@
         <v>5.2</v>
       </c>
       <c r="I254" s="54" t="s">
-        <v>800</v>
+        <v>858</v>
       </c>
     </row>
     <row r="255" spans="1:9">
@@ -10375,7 +10104,7 @@
         <v>570</v>
       </c>
       <c r="B255" s="18" t="s">
-        <v>815</v>
+        <v>872</v>
       </c>
       <c r="C255" s="18" t="s">
         <v>571</v>
@@ -10402,13 +10131,13 @@
         <v>572</v>
       </c>
       <c r="B256" s="52" t="s">
-        <v>816</v>
+        <v>873</v>
       </c>
       <c r="C256" s="18" t="s">
-        <v>817</v>
+        <v>161</v>
       </c>
       <c r="D256" s="50" t="s">
-        <v>818</v>
+        <v>874</v>
       </c>
       <c r="E256" s="52">
         <v>190</v>
@@ -10423,7 +10152,7 @@
         <v>5.2</v>
       </c>
       <c r="I256" s="54" t="s">
-        <v>819</v>
+        <v>875</v>
       </c>
     </row>
     <row r="257" spans="1:9">
@@ -10431,13 +10160,13 @@
         <v>573</v>
       </c>
       <c r="B257" s="36" t="s">
-        <v>820</v>
+        <v>876</v>
       </c>
       <c r="C257" s="36" t="s">
-        <v>821</v>
+        <v>321</v>
       </c>
       <c r="D257" s="36" t="s">
-        <v>734</v>
+        <v>429</v>
       </c>
       <c r="E257" s="36">
         <v>118</v>
@@ -10458,7 +10187,7 @@
         <v>574</v>
       </c>
       <c r="B258" s="18" t="s">
-        <v>809</v>
+        <v>866</v>
       </c>
       <c r="C258" s="18" t="s">
         <v>153</v>
@@ -10517,7 +10246,7 @@
         <v>579</v>
       </c>
       <c r="D261" s="49" t="s">
-        <v>822</v>
+        <v>877</v>
       </c>
       <c r="E261" s="10">
         <v>108</v>
@@ -10538,7 +10267,7 @@
         <v>580</v>
       </c>
       <c r="B262" s="10" t="s">
-        <v>823</v>
+        <v>878</v>
       </c>
       <c r="C262" s="10" t="s">
         <v>581</v>
@@ -10637,7 +10366,7 @@
         <v>215</v>
       </c>
       <c r="H265" s="35">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="I265" s="60"/>
     </row>
@@ -10646,13 +10375,13 @@
         <v>595</v>
       </c>
       <c r="B266" s="35" t="s">
-        <v>824</v>
+        <v>879</v>
       </c>
       <c r="C266" s="35" t="s">
-        <v>802</v>
+        <v>860</v>
       </c>
       <c r="D266" s="35" t="s">
-        <v>825</v>
+        <v>880</v>
       </c>
       <c r="E266" s="35">
         <v>78</v>
@@ -10673,13 +10402,13 @@
         <v>596</v>
       </c>
       <c r="B267" s="10" t="s">
-        <v>826</v>
+        <v>881</v>
       </c>
       <c r="C267" s="10" t="s">
-        <v>827</v>
+        <v>882</v>
       </c>
       <c r="D267" s="49" t="s">
-        <v>828</v>
+        <v>144</v>
       </c>
       <c r="E267" s="10">
         <v>60</v>
@@ -10844,13 +10573,13 @@
         <v>610</v>
       </c>
       <c r="B278" s="27" t="s">
-        <v>829</v>
+        <v>883</v>
       </c>
       <c r="C278" s="27" t="s">
-        <v>830</v>
+        <v>549</v>
       </c>
       <c r="D278" s="27" t="s">
-        <v>831</v>
+        <v>884</v>
       </c>
       <c r="E278" s="27">
         <v>159</v>
@@ -10871,10 +10600,10 @@
         <v>611</v>
       </c>
       <c r="B279" s="10" t="s">
-        <v>832</v>
+        <v>885</v>
       </c>
       <c r="C279" s="49" t="s">
-        <v>833</v>
+        <v>886</v>
       </c>
       <c r="D279" s="10" t="s">
         <v>144</v>
@@ -10898,13 +10627,13 @@
         <v>612</v>
       </c>
       <c r="B280" s="10" t="s">
-        <v>834</v>
+        <v>887</v>
       </c>
       <c r="C280" s="49" t="s">
-        <v>835</v>
+        <v>888</v>
       </c>
       <c r="D280" s="10" t="s">
-        <v>836</v>
+        <v>489</v>
       </c>
       <c r="E280" s="10"/>
       <c r="F280" s="9">
@@ -10950,7 +10679,7 @@
         <v>616</v>
       </c>
       <c r="B282" s="10" t="s">
-        <v>837</v>
+        <v>889</v>
       </c>
       <c r="C282" s="49" t="s">
         <v>617</v>
@@ -10977,10 +10706,10 @@
         <v>618</v>
       </c>
       <c r="B283" s="10" t="s">
-        <v>838</v>
+        <v>890</v>
       </c>
       <c r="C283" s="49" t="s">
-        <v>839</v>
+        <v>891</v>
       </c>
       <c r="D283" s="10" t="s">
         <v>39</v>
@@ -11004,13 +10733,13 @@
         <v>619</v>
       </c>
       <c r="B284" s="27" t="s">
-        <v>840</v>
+        <v>892</v>
       </c>
       <c r="C284" s="36" t="s">
-        <v>841</v>
+        <v>893</v>
       </c>
       <c r="D284" s="36" t="s">
-        <v>842</v>
+        <v>894</v>
       </c>
       <c r="E284" s="36">
         <v>80</v>
@@ -11037,7 +10766,7 @@
         <v>622</v>
       </c>
       <c r="D285" s="36" t="s">
-        <v>842</v>
+        <v>894</v>
       </c>
       <c r="E285" s="10">
         <v>73</v>
@@ -11058,10 +10787,10 @@
         <v>623</v>
       </c>
       <c r="B286" s="52" t="s">
-        <v>843</v>
+        <v>895</v>
       </c>
       <c r="C286" s="52" t="s">
-        <v>844</v>
+        <v>896</v>
       </c>
       <c r="D286" s="52" t="s">
         <v>624</v>
@@ -11085,13 +10814,13 @@
         <v>625</v>
       </c>
       <c r="B287" s="52" t="s">
-        <v>845</v>
+        <v>897</v>
       </c>
       <c r="C287" s="52" t="s">
-        <v>846</v>
+        <v>898</v>
       </c>
       <c r="D287" s="52" t="s">
-        <v>847</v>
+        <v>899</v>
       </c>
       <c r="E287" s="52">
         <v>88</v>
@@ -11112,7 +10841,7 @@
         <v>626</v>
       </c>
       <c r="B288" s="27" t="s">
-        <v>848</v>
+        <v>900</v>
       </c>
       <c r="C288" s="27" t="s">
         <v>627</v>
@@ -11160,7 +10889,7 @@
         <v>3.9</v>
       </c>
       <c r="I289" s="11" t="s">
-        <v>849</v>
+        <v>901</v>
       </c>
     </row>
     <row r="290" spans="1:9">
@@ -11195,7 +10924,7 @@
         <v>635</v>
       </c>
       <c r="B291" s="64" t="s">
-        <v>850</v>
+        <v>902</v>
       </c>
       <c r="C291" s="64" t="s">
         <v>636</v>
@@ -11222,7 +10951,7 @@
         <v>638</v>
       </c>
       <c r="B292" s="64" t="s">
-        <v>851</v>
+        <v>903</v>
       </c>
       <c r="C292" s="64" t="s">
         <v>639</v>
@@ -11249,10 +10978,10 @@
         <v>641</v>
       </c>
       <c r="B293" s="65" t="s">
-        <v>852</v>
+        <v>904</v>
       </c>
       <c r="C293" s="64" t="s">
-        <v>853</v>
+        <v>905</v>
       </c>
       <c r="D293" s="64" t="s">
         <v>39</v>
@@ -11276,13 +11005,13 @@
         <v>642</v>
       </c>
       <c r="B294" s="18" t="s">
-        <v>854</v>
+        <v>906</v>
       </c>
       <c r="C294" s="18" t="s">
-        <v>733</v>
+        <v>445</v>
       </c>
       <c r="D294" s="18" t="s">
-        <v>855</v>
+        <v>907</v>
       </c>
       <c r="E294" s="18">
         <v>150</v>
@@ -11303,7 +11032,7 @@
         <v>643</v>
       </c>
       <c r="B295" s="10" t="s">
-        <v>856</v>
+        <v>908</v>
       </c>
       <c r="C295" s="10" t="s">
         <v>644</v>
@@ -11351,13 +11080,13 @@
         <v>650</v>
       </c>
       <c r="B297" s="18" t="s">
-        <v>857</v>
+        <v>909</v>
       </c>
       <c r="C297" s="18" t="s">
-        <v>858</v>
+        <v>910</v>
       </c>
       <c r="D297" s="33" t="s">
-        <v>859</v>
+        <v>911</v>
       </c>
       <c r="E297" s="18">
         <v>125</v>
@@ -11378,13 +11107,13 @@
         <v>651</v>
       </c>
       <c r="B298" s="18" t="s">
-        <v>860</v>
+        <v>912</v>
       </c>
       <c r="C298" s="18" t="s">
-        <v>861</v>
+        <v>913</v>
       </c>
       <c r="D298" s="33" t="s">
-        <v>862</v>
+        <v>914</v>
       </c>
       <c r="E298" s="18">
         <v>190</v>
@@ -11399,7 +11128,7 @@
         <v>5.7</v>
       </c>
       <c r="I298" s="11" t="s">
-        <v>863</v>
+        <v>915</v>
       </c>
     </row>
     <row r="299" spans="1:9">
@@ -11407,13 +11136,13 @@
         <v>652</v>
       </c>
       <c r="B299" s="51" t="s">
-        <v>864</v>
+        <v>916</v>
       </c>
       <c r="C299" s="51" t="s">
-        <v>865</v>
+        <v>917</v>
       </c>
       <c r="D299" s="51" t="s">
-        <v>866</v>
+        <v>918</v>
       </c>
       <c r="E299" s="51">
         <v>124</v>
@@ -11428,7 +11157,7 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="I299" s="55" t="s">
-        <v>867</v>
+        <v>919</v>
       </c>
     </row>
     <row r="300" spans="1:9">
@@ -11462,13 +11191,13 @@
         <v>655</v>
       </c>
       <c r="B302" s="11" t="s">
-        <v>868</v>
+        <v>920</v>
       </c>
       <c r="C302" s="11" t="s">
-        <v>869</v>
+        <v>921</v>
       </c>
       <c r="D302" s="11" t="s">
-        <v>870</v>
+        <v>922</v>
       </c>
       <c r="E302" s="11">
         <v>150</v>
@@ -11495,7 +11224,7 @@
         <v>658</v>
       </c>
       <c r="D303" s="10" t="s">
-        <v>870</v>
+        <v>922</v>
       </c>
       <c r="E303" s="11">
         <v>140</v>
@@ -11519,7 +11248,7 @@
         <v>660</v>
       </c>
       <c r="C304" s="64" t="s">
-        <v>871</v>
+        <v>251</v>
       </c>
       <c r="D304" s="64" t="s">
         <v>661</v>
@@ -11537,7 +11266,7 @@
         <v>4.5</v>
       </c>
       <c r="I304" s="37" t="s">
-        <v>872</v>
+        <v>923</v>
       </c>
     </row>
     <row r="305" spans="1:9">
@@ -11545,13 +11274,13 @@
         <v>662</v>
       </c>
       <c r="B305" s="36" t="s">
-        <v>873</v>
+        <v>924</v>
       </c>
       <c r="C305" s="36" t="s">
-        <v>874</v>
+        <v>925</v>
       </c>
       <c r="D305" s="18" t="s">
-        <v>875</v>
+        <v>926</v>
       </c>
       <c r="E305" s="36">
         <v>215</v>
@@ -11640,7 +11369,7 @@
         <v>669</v>
       </c>
       <c r="C311" s="35" t="s">
-        <v>876</v>
+        <v>673</v>
       </c>
       <c r="D311" s="35" t="s">
         <v>670</v>
@@ -11717,13 +11446,13 @@
         <v>677</v>
       </c>
       <c r="B315" s="36" t="s">
-        <v>877</v>
+        <v>927</v>
       </c>
       <c r="C315" s="36" t="s">
-        <v>878</v>
+        <v>841</v>
       </c>
       <c r="D315" s="11" t="s">
-        <v>879</v>
+        <v>928</v>
       </c>
       <c r="E315" s="36">
         <v>116</v>
@@ -11738,7 +11467,7 @@
         <v>5</v>
       </c>
       <c r="I315" s="61" t="s">
-        <v>880</v>
+        <v>929</v>
       </c>
     </row>
     <row r="316" spans="1:9">
@@ -11746,13 +11475,13 @@
         <v>678</v>
       </c>
       <c r="B316" s="36" t="s">
-        <v>881</v>
+        <v>930</v>
       </c>
       <c r="C316" s="36" t="s">
-        <v>882</v>
+        <v>931</v>
       </c>
       <c r="D316" s="11" t="s">
-        <v>883</v>
+        <v>932</v>
       </c>
       <c r="E316" s="36">
         <v>160</v>
@@ -11764,10 +11493,10 @@
         <v>215</v>
       </c>
       <c r="H316" s="61">
-        <v>5.0999999999999996</v>
+        <v>5.2</v>
       </c>
       <c r="I316" s="61" t="s">
-        <v>884</v>
+        <v>933</v>
       </c>
     </row>
     <row r="317" spans="1:9">
@@ -11775,13 +11504,13 @@
         <v>679</v>
       </c>
       <c r="B317" s="11" t="s">
-        <v>885</v>
+        <v>934</v>
       </c>
       <c r="C317" s="11" t="s">
-        <v>886</v>
+        <v>935</v>
       </c>
       <c r="D317" s="11" t="s">
-        <v>887</v>
+        <v>936</v>
       </c>
       <c r="E317" s="11">
         <v>110</v>
@@ -11796,7 +11525,7 @@
         <v>3.6</v>
       </c>
       <c r="I317" s="11" t="s">
-        <v>888</v>
+        <v>937</v>
       </c>
     </row>
     <row r="318" spans="1:9">
@@ -11804,13 +11533,13 @@
         <v>680</v>
       </c>
       <c r="B318" s="11" t="s">
-        <v>885</v>
+        <v>934</v>
       </c>
       <c r="C318" s="11" t="s">
-        <v>889</v>
+        <v>938</v>
       </c>
       <c r="D318" s="11" t="s">
-        <v>887</v>
+        <v>936</v>
       </c>
       <c r="E318" s="11">
         <v>110</v>
@@ -11831,13 +11560,13 @@
         <v>681</v>
       </c>
       <c r="B319" s="18" t="s">
-        <v>890</v>
+        <v>939</v>
       </c>
       <c r="C319" s="18" t="s">
-        <v>891</v>
+        <v>940</v>
       </c>
       <c r="D319" s="18" t="s">
-        <v>892</v>
+        <v>941</v>
       </c>
       <c r="E319" s="18">
         <v>205</v>
@@ -11849,10 +11578,10 @@
         <v>215</v>
       </c>
       <c r="H319" s="18">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="I319" s="11" t="s">
-        <v>893</v>
+        <v>942</v>
       </c>
     </row>
     <row r="320" spans="1:9">
@@ -11860,13 +11589,13 @@
         <v>682</v>
       </c>
       <c r="B320" s="18" t="s">
-        <v>894</v>
+        <v>943</v>
       </c>
       <c r="C320" s="18" t="s">
-        <v>895</v>
+        <v>944</v>
       </c>
       <c r="D320" s="18" t="s">
-        <v>896</v>
+        <v>945</v>
       </c>
       <c r="E320" s="18">
         <v>182</v>
@@ -11881,7 +11610,7 @@
         <v>5.6</v>
       </c>
       <c r="I320" s="11" t="s">
-        <v>863</v>
+        <v>915</v>
       </c>
     </row>
     <row r="321" spans="1:9">
@@ -11889,13 +11618,13 @@
         <v>683</v>
       </c>
       <c r="B321" s="18" t="s">
-        <v>897</v>
+        <v>946</v>
       </c>
       <c r="C321" s="18" t="s">
-        <v>898</v>
+        <v>947</v>
       </c>
       <c r="D321" s="18" t="s">
-        <v>899</v>
+        <v>948</v>
       </c>
       <c r="E321" s="18">
         <v>138</v>
@@ -11910,7 +11639,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="I321" s="11" t="s">
-        <v>900</v>
+        <v>949</v>
       </c>
     </row>
     <row r="322" spans="1:9">
@@ -11918,28 +11647,28 @@
         <v>684</v>
       </c>
       <c r="B322" s="18" t="s">
-        <v>901</v>
+        <v>950</v>
       </c>
       <c r="C322" s="18" t="s">
-        <v>902</v>
+        <v>951</v>
       </c>
       <c r="D322" s="18" t="s">
-        <v>892</v>
+        <v>941</v>
       </c>
       <c r="E322" s="18">
         <v>225</v>
       </c>
       <c r="F322" s="31">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="G322" s="32">
         <v>215</v>
       </c>
       <c r="H322" s="18">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="I322" s="11" t="s">
-        <v>903</v>
+        <v>952</v>
       </c>
     </row>
     <row r="323" spans="1:9">
@@ -11947,13 +11676,13 @@
         <v>685</v>
       </c>
       <c r="B323" s="18" t="s">
-        <v>904</v>
+        <v>953</v>
       </c>
       <c r="C323" s="18" t="s">
-        <v>905</v>
+        <v>88</v>
       </c>
       <c r="D323" s="18" t="s">
-        <v>899</v>
+        <v>948</v>
       </c>
       <c r="E323" s="18">
         <v>155</v>
@@ -11965,10 +11694,10 @@
         <v>215</v>
       </c>
       <c r="H323" s="18">
-        <v>4.5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="I323" s="11" t="s">
-        <v>906</v>
+        <v>954</v>
       </c>
     </row>
     <row r="324" spans="1:9">
@@ -11976,13 +11705,13 @@
         <v>686</v>
       </c>
       <c r="B324" s="18" t="s">
-        <v>907</v>
+        <v>955</v>
       </c>
       <c r="C324" s="18" t="s">
-        <v>908</v>
+        <v>956</v>
       </c>
       <c r="D324" s="18" t="s">
-        <v>892</v>
+        <v>941</v>
       </c>
       <c r="E324" s="18">
         <v>220</v>
@@ -11997,7 +11726,7 @@
         <v>6.1</v>
       </c>
       <c r="I324" s="11" t="s">
-        <v>903</v>
+        <v>952</v>
       </c>
     </row>
     <row r="325" spans="1:9">
@@ -12015,7 +11744,7 @@
     </row>
     <row r="326" spans="1:9">
       <c r="A326" s="9" t="s">
-        <v>909</v>
+        <v>703</v>
       </c>
       <c r="B326" s="36"/>
       <c r="C326" s="36"/>
@@ -12028,7 +11757,7 @@
     </row>
     <row r="327" spans="1:9">
       <c r="A327" s="9" t="s">
-        <v>910</v>
+        <v>704</v>
       </c>
       <c r="B327" s="36"/>
       <c r="C327" s="36"/>
@@ -12041,7 +11770,7 @@
     </row>
     <row r="328" spans="1:9">
       <c r="A328" s="9" t="s">
-        <v>911</v>
+        <v>705</v>
       </c>
       <c r="B328" s="36"/>
       <c r="C328" s="36"/>
@@ -12054,7 +11783,7 @@
     </row>
     <row r="329" spans="1:9">
       <c r="A329" s="9" t="s">
-        <v>912</v>
+        <v>706</v>
       </c>
       <c r="B329" s="36"/>
       <c r="C329" s="36"/>
@@ -12067,7 +11796,7 @@
     </row>
     <row r="330" spans="1:9">
       <c r="A330" s="9" t="s">
-        <v>913</v>
+        <v>707</v>
       </c>
       <c r="B330" s="36"/>
       <c r="C330" s="36"/>
@@ -12080,7 +11809,7 @@
     </row>
     <row r="331" spans="1:9">
       <c r="A331" s="9" t="s">
-        <v>914</v>
+        <v>708</v>
       </c>
       <c r="B331" s="36"/>
       <c r="C331" s="36"/>
@@ -12093,7 +11822,7 @@
     </row>
     <row r="332" spans="1:9">
       <c r="A332" s="9" t="s">
-        <v>915</v>
+        <v>709</v>
       </c>
       <c r="B332" s="36"/>
       <c r="C332" s="36"/>
@@ -12106,7 +11835,7 @@
     </row>
     <row r="333" spans="1:9">
       <c r="A333" s="9" t="s">
-        <v>916</v>
+        <v>710</v>
       </c>
       <c r="B333" s="36"/>
       <c r="C333" s="36"/>
@@ -12119,7 +11848,7 @@
     </row>
     <row r="334" spans="1:9">
       <c r="A334" s="9" t="s">
-        <v>917</v>
+        <v>711</v>
       </c>
       <c r="B334" s="36"/>
       <c r="C334" s="36"/>
@@ -12132,7 +11861,7 @@
     </row>
     <row r="335" spans="1:9">
       <c r="A335" s="9" t="s">
-        <v>918</v>
+        <v>712</v>
       </c>
       <c r="B335" s="36"/>
       <c r="C335" s="36"/>
@@ -12145,7 +11874,7 @@
     </row>
     <row r="336" spans="1:9">
       <c r="A336" s="9" t="s">
-        <v>919</v>
+        <v>713</v>
       </c>
       <c r="B336" s="36"/>
       <c r="C336" s="36"/>
@@ -12158,7 +11887,7 @@
     </row>
     <row r="337" spans="1:9">
       <c r="A337" s="9" t="s">
-        <v>920</v>
+        <v>714</v>
       </c>
       <c r="B337" s="36"/>
       <c r="C337" s="36"/>
@@ -12171,7 +11900,7 @@
     </row>
     <row r="338" spans="1:9">
       <c r="A338" s="9" t="s">
-        <v>921</v>
+        <v>715</v>
       </c>
       <c r="B338" s="36"/>
       <c r="C338" s="36"/>
@@ -12184,7 +11913,7 @@
     </row>
     <row r="339" spans="1:9">
       <c r="A339" s="9" t="s">
-        <v>922</v>
+        <v>716</v>
       </c>
       <c r="B339" s="36"/>
       <c r="C339" s="36"/>
@@ -12197,7 +11926,7 @@
     </row>
     <row r="340" spans="1:9">
       <c r="A340" s="9" t="s">
-        <v>923</v>
+        <v>717</v>
       </c>
       <c r="B340" s="36"/>
       <c r="C340" s="36"/>
@@ -12210,7 +11939,7 @@
     </row>
     <row r="341" spans="1:9">
       <c r="A341" s="9" t="s">
-        <v>924</v>
+        <v>718</v>
       </c>
       <c r="B341" s="36"/>
       <c r="C341" s="36"/>
@@ -12223,7 +11952,7 @@
     </row>
     <row r="342" spans="1:9">
       <c r="A342" s="9" t="s">
-        <v>925</v>
+        <v>719</v>
       </c>
       <c r="B342" s="36"/>
       <c r="C342" s="36"/>
@@ -12236,7 +11965,7 @@
     </row>
     <row r="343" spans="1:9">
       <c r="A343" s="9" t="s">
-        <v>926</v>
+        <v>720</v>
       </c>
       <c r="B343" s="36"/>
       <c r="C343" s="36"/>
@@ -12249,7 +11978,7 @@
     </row>
     <row r="344" spans="1:9">
       <c r="A344" s="9" t="s">
-        <v>927</v>
+        <v>721</v>
       </c>
       <c r="B344" s="36"/>
       <c r="C344" s="36"/>
@@ -12262,7 +11991,7 @@
     </row>
     <row r="345" spans="1:9">
       <c r="A345" s="9" t="s">
-        <v>928</v>
+        <v>722</v>
       </c>
       <c r="B345" s="36"/>
       <c r="C345" s="36"/>
@@ -12275,7 +12004,7 @@
     </row>
     <row r="346" spans="1:9">
       <c r="A346" s="9" t="s">
-        <v>929</v>
+        <v>723</v>
       </c>
       <c r="B346" s="36"/>
       <c r="C346" s="36"/>
@@ -12288,7 +12017,7 @@
     </row>
     <row r="347" spans="1:9">
       <c r="A347" s="9" t="s">
-        <v>930</v>
+        <v>724</v>
       </c>
       <c r="B347" s="36"/>
       <c r="C347" s="36"/>
@@ -12301,7 +12030,7 @@
     </row>
     <row r="348" spans="1:9">
       <c r="A348" s="9" t="s">
-        <v>931</v>
+        <v>725</v>
       </c>
       <c r="B348" s="36"/>
       <c r="C348" s="36"/>
@@ -12314,7 +12043,7 @@
     </row>
     <row r="349" spans="1:9">
       <c r="A349" s="9" t="s">
-        <v>932</v>
+        <v>726</v>
       </c>
       <c r="B349" s="36"/>
       <c r="C349" s="36"/>
@@ -12327,7 +12056,7 @@
     </row>
     <row r="350" spans="1:9">
       <c r="A350" s="9" t="s">
-        <v>933</v>
+        <v>727</v>
       </c>
       <c r="B350" s="36"/>
       <c r="C350" s="36"/>
@@ -12340,7 +12069,7 @@
     </row>
     <row r="351" spans="1:9">
       <c r="A351" s="9" t="s">
-        <v>934</v>
+        <v>728</v>
       </c>
       <c r="B351" s="36"/>
       <c r="C351" s="36"/>
@@ -12353,7 +12082,7 @@
     </row>
     <row r="352" spans="1:9">
       <c r="A352" s="9" t="s">
-        <v>935</v>
+        <v>729</v>
       </c>
       <c r="B352" s="36"/>
       <c r="C352" s="36"/>
@@ -12366,7 +12095,7 @@
     </row>
     <row r="353" spans="1:9">
       <c r="A353" s="9" t="s">
-        <v>936</v>
+        <v>730</v>
       </c>
       <c r="B353" s="36"/>
       <c r="C353" s="36"/>
@@ -12379,7 +12108,7 @@
     </row>
     <row r="354" spans="1:9">
       <c r="A354" s="9" t="s">
-        <v>937</v>
+        <v>731</v>
       </c>
       <c r="B354" s="36"/>
       <c r="C354" s="36"/>
@@ -12392,7 +12121,7 @@
     </row>
     <row r="355" spans="1:9">
       <c r="A355" s="9" t="s">
-        <v>938</v>
+        <v>732</v>
       </c>
       <c r="B355" s="36"/>
       <c r="C355" s="36"/>
@@ -12405,7 +12134,7 @@
     </row>
     <row r="356" spans="1:9">
       <c r="A356" s="9" t="s">
-        <v>939</v>
+        <v>733</v>
       </c>
       <c r="B356" s="36"/>
       <c r="C356" s="36"/>
@@ -12418,7 +12147,7 @@
     </row>
     <row r="357" spans="1:9">
       <c r="A357" s="9" t="s">
-        <v>940</v>
+        <v>734</v>
       </c>
       <c r="B357" s="36"/>
       <c r="C357" s="36"/>
@@ -12431,7 +12160,7 @@
     </row>
     <row r="358" spans="1:9">
       <c r="A358" s="9" t="s">
-        <v>941</v>
+        <v>735</v>
       </c>
       <c r="B358" s="36"/>
       <c r="C358" s="36"/>
@@ -12444,7 +12173,7 @@
     </row>
     <row r="359" spans="1:9">
       <c r="A359" s="9" t="s">
-        <v>942</v>
+        <v>736</v>
       </c>
       <c r="B359" s="36"/>
       <c r="C359" s="36"/>
@@ -12457,7 +12186,7 @@
     </row>
     <row r="360" spans="1:9">
       <c r="A360" s="9" t="s">
-        <v>943</v>
+        <v>737</v>
       </c>
       <c r="B360" s="36"/>
       <c r="C360" s="36"/>
@@ -12470,7 +12199,7 @@
     </row>
     <row r="361" spans="1:9">
       <c r="A361" s="9" t="s">
-        <v>944</v>
+        <v>738</v>
       </c>
       <c r="B361" s="36"/>
       <c r="C361" s="36"/>
@@ -12483,7 +12212,7 @@
     </row>
     <row r="362" spans="1:9">
       <c r="A362" s="9" t="s">
-        <v>945</v>
+        <v>739</v>
       </c>
       <c r="B362" s="36"/>
       <c r="C362" s="36"/>
@@ -12496,7 +12225,7 @@
     </row>
     <row r="363" spans="1:9">
       <c r="A363" s="9" t="s">
-        <v>946</v>
+        <v>740</v>
       </c>
       <c r="B363" s="36"/>
       <c r="C363" s="36"/>
@@ -12509,7 +12238,7 @@
     </row>
     <row r="364" spans="1:9">
       <c r="A364" s="9" t="s">
-        <v>947</v>
+        <v>741</v>
       </c>
       <c r="B364" s="36"/>
       <c r="C364" s="36"/>
@@ -12522,7 +12251,7 @@
     </row>
     <row r="365" spans="1:9">
       <c r="A365" s="9" t="s">
-        <v>948</v>
+        <v>742</v>
       </c>
       <c r="B365" s="36"/>
       <c r="C365" s="36"/>
@@ -12535,7 +12264,7 @@
     </row>
     <row r="366" spans="1:9">
       <c r="A366" s="9" t="s">
-        <v>949</v>
+        <v>743</v>
       </c>
       <c r="B366" s="36"/>
       <c r="C366" s="36"/>
@@ -12548,7 +12277,7 @@
     </row>
     <row r="367" spans="1:9">
       <c r="A367" s="9" t="s">
-        <v>950</v>
+        <v>744</v>
       </c>
       <c r="B367" s="36"/>
       <c r="C367" s="36"/>
@@ -12561,7 +12290,7 @@
     </row>
     <row r="368" spans="1:9">
       <c r="A368" s="9" t="s">
-        <v>951</v>
+        <v>745</v>
       </c>
       <c r="B368" s="36"/>
       <c r="C368" s="36"/>
@@ -12574,7 +12303,7 @@
     </row>
     <row r="369" spans="1:9">
       <c r="A369" s="9" t="s">
-        <v>952</v>
+        <v>746</v>
       </c>
       <c r="B369" s="36"/>
       <c r="C369" s="36"/>
@@ -12587,7 +12316,7 @@
     </row>
     <row r="370" spans="1:9">
       <c r="A370" s="9" t="s">
-        <v>953</v>
+        <v>747</v>
       </c>
       <c r="B370" s="36"/>
       <c r="C370" s="36"/>
@@ -12600,7 +12329,7 @@
     </row>
     <row r="371" spans="1:9">
       <c r="A371" s="9" t="s">
-        <v>954</v>
+        <v>748</v>
       </c>
       <c r="B371" s="36"/>
       <c r="C371" s="36"/>
@@ -12613,7 +12342,7 @@
     </row>
     <row r="372" spans="1:9">
       <c r="A372" s="9" t="s">
-        <v>955</v>
+        <v>749</v>
       </c>
       <c r="B372" s="36"/>
       <c r="C372" s="36"/>
@@ -12626,7 +12355,7 @@
     </row>
     <row r="373" spans="1:9">
       <c r="A373" s="9" t="s">
-        <v>956</v>
+        <v>750</v>
       </c>
       <c r="B373" s="36"/>
       <c r="C373" s="36"/>
@@ -12639,7 +12368,7 @@
     </row>
     <row r="374" spans="1:9">
       <c r="A374" s="9" t="s">
-        <v>957</v>
+        <v>751</v>
       </c>
       <c r="B374" s="36"/>
       <c r="C374" s="36"/>
@@ -12652,7 +12381,7 @@
     </row>
     <row r="375" spans="1:9">
       <c r="A375" s="9" t="s">
-        <v>958</v>
+        <v>752</v>
       </c>
       <c r="B375" s="36"/>
       <c r="C375" s="36"/>
@@ -12665,7 +12394,7 @@
     </row>
     <row r="376" spans="1:9">
       <c r="A376" s="9" t="s">
-        <v>959</v>
+        <v>753</v>
       </c>
       <c r="B376" s="36"/>
       <c r="C376" s="36"/>
@@ -12678,7 +12407,7 @@
     </row>
     <row r="377" spans="1:9">
       <c r="A377" s="9" t="s">
-        <v>960</v>
+        <v>754</v>
       </c>
       <c r="B377" s="36"/>
       <c r="C377" s="36"/>
@@ -12691,7 +12420,7 @@
     </row>
     <row r="378" spans="1:9">
       <c r="A378" s="9" t="s">
-        <v>961</v>
+        <v>755</v>
       </c>
       <c r="B378" s="36"/>
       <c r="C378" s="36"/>
@@ -12704,7 +12433,7 @@
     </row>
     <row r="379" spans="1:9">
       <c r="A379" s="9" t="s">
-        <v>962</v>
+        <v>756</v>
       </c>
       <c r="B379" s="36"/>
       <c r="C379" s="36"/>
@@ -12717,7 +12446,7 @@
     </row>
     <row r="380" spans="1:9">
       <c r="A380" s="9" t="s">
-        <v>963</v>
+        <v>757</v>
       </c>
       <c r="B380" s="36"/>
       <c r="C380" s="36"/>
@@ -12730,7 +12459,7 @@
     </row>
     <row r="381" spans="1:9">
       <c r="A381" s="9" t="s">
-        <v>964</v>
+        <v>758</v>
       </c>
       <c r="B381" s="36"/>
       <c r="C381" s="36"/>
@@ -12743,7 +12472,7 @@
     </row>
     <row r="382" spans="1:9">
       <c r="A382" s="9" t="s">
-        <v>965</v>
+        <v>759</v>
       </c>
       <c r="B382" s="36"/>
       <c r="C382" s="36"/>
@@ -12756,7 +12485,7 @@
     </row>
     <row r="383" spans="1:9">
       <c r="A383" s="9" t="s">
-        <v>966</v>
+        <v>760</v>
       </c>
       <c r="B383" s="36"/>
       <c r="C383" s="36"/>
@@ -12769,7 +12498,7 @@
     </row>
     <row r="384" spans="1:9">
       <c r="A384" s="9" t="s">
-        <v>967</v>
+        <v>761</v>
       </c>
       <c r="B384" s="36"/>
       <c r="C384" s="36"/>
@@ -12782,7 +12511,7 @@
     </row>
     <row r="385" spans="1:9">
       <c r="A385" s="9" t="s">
-        <v>968</v>
+        <v>762</v>
       </c>
       <c r="B385" s="36"/>
       <c r="C385" s="36"/>
@@ -12795,7 +12524,7 @@
     </row>
     <row r="386" spans="1:9">
       <c r="A386" s="9" t="s">
-        <v>969</v>
+        <v>763</v>
       </c>
       <c r="B386" s="36"/>
       <c r="C386" s="36"/>
@@ -12808,7 +12537,7 @@
     </row>
     <row r="387" spans="1:9">
       <c r="A387" s="9" t="s">
-        <v>970</v>
+        <v>764</v>
       </c>
       <c r="B387" s="36"/>
       <c r="C387" s="36"/>
@@ -12821,7 +12550,7 @@
     </row>
     <row r="388" spans="1:9">
       <c r="A388" s="9" t="s">
-        <v>971</v>
+        <v>765</v>
       </c>
       <c r="B388" s="36"/>
       <c r="C388" s="36"/>
@@ -12834,7 +12563,7 @@
     </row>
     <row r="389" spans="1:9">
       <c r="A389" s="9" t="s">
-        <v>972</v>
+        <v>766</v>
       </c>
       <c r="B389" s="36"/>
       <c r="C389" s="36"/>
@@ -12847,7 +12576,7 @@
     </row>
     <row r="390" spans="1:9">
       <c r="A390" s="9" t="s">
-        <v>973</v>
+        <v>767</v>
       </c>
       <c r="B390" s="36"/>
       <c r="C390" s="36"/>
@@ -12860,7 +12589,7 @@
     </row>
     <row r="391" spans="1:9">
       <c r="A391" s="9" t="s">
-        <v>974</v>
+        <v>768</v>
       </c>
       <c r="B391" s="36"/>
       <c r="C391" s="36"/>
@@ -12873,7 +12602,7 @@
     </row>
     <row r="392" spans="1:9">
       <c r="A392" s="9" t="s">
-        <v>975</v>
+        <v>769</v>
       </c>
       <c r="B392" s="36"/>
       <c r="C392" s="36"/>
@@ -12886,7 +12615,7 @@
     </row>
     <row r="393" spans="1:9">
       <c r="A393" s="9" t="s">
-        <v>976</v>
+        <v>770</v>
       </c>
       <c r="B393" s="36"/>
       <c r="C393" s="36"/>

--- a/产品规格.xlsx
+++ b/产品规格.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1297" uniqueCount="957">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1297" uniqueCount="984">
   <si>
     <t>17.5*3*27</t>
   </si>
@@ -1924,9 +1924,6 @@
   </si>
   <si>
     <t>XC290</t>
-  </si>
-  <si>
-    <t>20*2*28</t>
   </si>
   <si>
     <t>75*75*2</t>
@@ -2338,568 +2335,880 @@
   </si>
   <si>
     <t>XC001</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>1*1半光横条</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>75*75*150</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>22*3*38</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>22*3*39</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>14*2*25</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>22*3*40</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>17*3*28</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>25梭T400无捻牛津</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>27梭T400无捻牛津</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>26梭T400无捻牛津</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>17*2*26</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">50S*50S弹力 酷丝棉平纹  </t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>17*2*30</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>50S*50S</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*40S弹力 酷丝棉平纹  </t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>18*2*27</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*40S</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*75T 酷丝棉平纹  </t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*75D 酷丝棉2/1</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*75D 酷丝棉2/2 </t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*150 酷丝棉26S平纹  </t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*150 酷丝棉2/1 </t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*150D 酷丝棉2/2 </t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*150 酷丝棉28S平纹  </t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*150 酷丝棉24S平纹  </t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*150 酷丝棉3/3斜  </t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">50S*75D 酷丝棉2/2 </t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>50S*75D 酷丝棉绮兵</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*75 酷丝棉3/3斜  </t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>13.5*4*35</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*75T400</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">50S*75D 酷丝棉2/1 </t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>XC186</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>17.5*3*35</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*75 酷丝棉3/2斜  </t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>17.5*3*34</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*75DT400</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*150 酷丝棉5/1斜  </t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100*150T8 4/2斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>17*4*215*40</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100D*150T800</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75*150T400 消3/3斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>17*4*36</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75*75T400消 3/3斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75*75 半光2/2 斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>18*4*46</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75*75 消光2/2 斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>18*4*43</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75*150 消光2/2 斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75*75-T800消光骑士斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>17*4*38</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75消*75T800</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>19*5*45</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>19*3*39</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>X字格</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>16*4*46</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>T400横条2*1</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>16*4+28</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>238克</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>T400横条1*4</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>17*4+38</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>75*75*150</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>白坯200米克</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>T400横条1*1</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>16*4*30</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>100*75*150</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*75闪电斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>18*3*38</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*75</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*150酷丝绵 小钻石斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>17.5*3*35</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*150酷丝绵 大钻石斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*300 3/2变化斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>13.5*4*28</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*150*2T400</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>米克385</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100D半光*35S-3/3斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>16*4*40</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100*35</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100D消光*35S-3/3斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100*35S</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>120D扁平0.5格</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>17*4*44</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>120*35S</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>米克370</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>120D扁平3/3斜-45</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>16*4*45</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>120D扁平4/4斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>17*4*45</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>120*35S</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>米克375</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100D消光多乐3/3斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>15*4*43</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>米克300</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>120D扁平1/2斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>17*4*34</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>米克350</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>120D扁平T800变化斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>17*4*29</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>120*150T800</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>米克380</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>120D扁平牛津</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>20*2*31</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*75 酷丝棉3/1斜 </t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>13.5*4*34</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*75T400</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*150 酷丝棉3/1斜 31</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*150 酷丝棉3/2斜 39</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*75D 酷丝棉2/1 30</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>17*3*30</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*75D 酷丝棉2/2 30</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*75D 酷丝棉2/2 38</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*75D 骑兵斜 30 </t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*75D 骑兵斜 38 </t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*300 酷丝棉3/2斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>13.5*4*27</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*150*2T400</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*75T 酷丝棉平纹 33S </t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*300酷丝绵珍珠点</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>17.5*3*25</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*150*300T400</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>米克368</t>
-  </si>
-  <si>
-    <t>40S*75D酷丝绵细双斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*75D酷丝绵变化斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>17.5*3*36</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*150T400+300T400</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>80S*75双线格酷丝绵</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75 T800半光0.5格</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75*75*210</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>50D经纬 T8 0.5格</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>22*2*40</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>50*50</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>半光大猫眼</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>16*4*43</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100半低*150半T800</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>50D低弹*50T800 平纹</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>23*2*40</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>30D T8 平纹</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>22*3*57</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>30*30</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75D经纬T8平纹</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75经纬T8 2/2斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>19*3*38</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">50DT8*50DT8 骑兵斜  </t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>21*3*53</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>50DT8*50DT8</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>T8五面埋伏</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>14*4*38</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>50D*100D经纬T800珍珠点</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>21*3*49</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>50D*50D*100D T800</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>T800双链条</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>米克265</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>经消光低弹 双纬T800</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>20*2*26</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75D半光T800双纬平纹</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75消低弹*75T8002/2斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>17.5*4*38</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*150T800酷丝棉3/2斜  </t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>13.5*4*35</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*150T800</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>空变T8平纹</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*75T8酷丝棉3/1.超钛棉</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>17.5*3*44</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*75T800</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*300加厚超钛棉</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>14*4*27</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*300T800</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>白坯370克</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100D消光75DT800 3/3斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>15.5*4*48</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100*75T8</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>米克250</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>37梭多乐绵</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>16*4*37</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100D*40S+150D T8</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>21*3*45</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>白坯188克</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">斜纹毛巾底 </t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>13.5*4*51</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*150T8*300低弹</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>18*3*43</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>网纹3/3-180</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>17*4*44</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75D*50S+10DT8</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>白坯米克245</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>网纹3/3-220</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>15*4*44</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100D*35S+150DT8</t>
-  </si>
-  <si>
-    <t>白坯300克</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>白坯3</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>00克</t>
+    </r>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>天丝棉</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>20*3*32</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>80S*三合一</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>白坯195克</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>21*3*31</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>270-钛金棉</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>14*4*26.5</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*35S*2</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>白坯365克</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>生态棉</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>16*4*44</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*35S</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>210-钛金棉</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>17*3*27</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*30S</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>白坯285克</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>加厚钛金棉</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>15.5*4*30</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>白坯390克</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>240-钛金棉</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>17.5*3*31</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>白坯310克</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">生态棉 加厚 </t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>16*4*31</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2972,6 +3281,13 @@
       <b/>
       <sz val="9"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -3729,54 +4045,54 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
+        <v>690</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>692</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>693</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>694</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>695</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>696</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>697</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>698</v>
       </c>
-      <c r="I1" s="3" t="s">
-        <v>699</v>
-      </c>
       <c r="J1" s="5" t="s">
+        <v>688</v>
+      </c>
+      <c r="K1" s="5" t="s">
         <v>689</v>
       </c>
-      <c r="K1" s="5" t="s">
-        <v>690</v>
-      </c>
       <c r="L1" s="5" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="9" t="s">
+        <v>770</v>
+      </c>
+      <c r="B2" s="10" t="s">
         <v>771</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>772</v>
       </c>
       <c r="C2" s="10" t="s">
         <v>0</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>4</v>
+        <v>772</v>
       </c>
       <c r="E2" s="10">
         <v>79</v>
@@ -3790,13 +4106,13 @@
       </c>
       <c r="I2" s="11"/>
       <c r="J2" s="7" t="s">
+        <v>700</v>
+      </c>
+      <c r="K2" s="7" t="s">
+        <v>699</v>
+      </c>
+      <c r="L2" s="8" t="s">
         <v>701</v>
-      </c>
-      <c r="K2" s="7" t="s">
-        <v>700</v>
-      </c>
-      <c r="L2" s="8" t="s">
-        <v>702</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -5667,7 +5983,7 @@
         <v>193</v>
       </c>
       <c r="C77" s="10" t="s">
-        <v>73</v>
+        <v>776</v>
       </c>
       <c r="D77" s="10" t="s">
         <v>144</v>
@@ -7017,7 +7333,7 @@
         <v>330</v>
       </c>
       <c r="C131" s="24" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="D131" s="24" t="s">
         <v>148</v>
@@ -7609,7 +7925,7 @@
         <v>208</v>
       </c>
       <c r="H154" s="10">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="I154" s="11"/>
     </row>
@@ -7636,7 +7952,7 @@
         <v>220</v>
       </c>
       <c r="H155" s="10">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="I155" s="11"/>
     </row>
@@ -7776,7 +8092,7 @@
         <v>412</v>
       </c>
       <c r="B161" s="22" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="C161" s="22" t="s">
         <v>413</v>
@@ -7857,7 +8173,7 @@
         <v>421</v>
       </c>
       <c r="B164" s="22" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="C164" s="22" t="s">
         <v>422</v>
@@ -7884,10 +8200,10 @@
         <v>423</v>
       </c>
       <c r="B165" s="22" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="C165" s="22" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="D165" s="22" t="s">
         <v>414</v>
@@ -7924,13 +8240,13 @@
         <v>425</v>
       </c>
       <c r="B167" s="18" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="C167" s="18" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="D167" s="18" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="E167" s="18">
         <v>80</v>
@@ -7951,13 +8267,13 @@
         <v>426</v>
       </c>
       <c r="B168" s="18" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="C168" s="18" t="s">
-        <v>417</v>
+        <v>786</v>
       </c>
       <c r="D168" s="18" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="E168" s="18">
         <v>110</v>
@@ -7978,7 +8294,7 @@
         <v>427</v>
       </c>
       <c r="B169" s="18" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="C169" s="18" t="s">
         <v>428</v>
@@ -8005,7 +8321,7 @@
         <v>430</v>
       </c>
       <c r="B170" s="18" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="C170" s="18" t="s">
         <v>431</v>
@@ -8032,7 +8348,7 @@
         <v>432</v>
       </c>
       <c r="B171" s="18" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="C171" s="18" t="s">
         <v>238</v>
@@ -8086,7 +8402,7 @@
         <v>435</v>
       </c>
       <c r="B173" s="18" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="C173" s="18" t="s">
         <v>436</v>
@@ -8113,7 +8429,7 @@
         <v>438</v>
       </c>
       <c r="B174" s="18" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="C174" s="18" t="s">
         <v>439</v>
@@ -8140,7 +8456,7 @@
         <v>440</v>
       </c>
       <c r="B175" s="18" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="C175" s="18" t="s">
         <v>32</v>
@@ -8221,7 +8537,7 @@
         <v>446</v>
       </c>
       <c r="B178" s="18" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="C178" s="18" t="s">
         <v>420</v>
@@ -8275,7 +8591,7 @@
         <v>450</v>
       </c>
       <c r="B180" s="18" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="C180" s="18" t="s">
         <v>451</v>
@@ -8302,7 +8618,7 @@
         <v>452</v>
       </c>
       <c r="B181" s="18" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="C181" s="18" t="s">
         <v>445</v>
@@ -8329,7 +8645,7 @@
         <v>453</v>
       </c>
       <c r="B182" s="34" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="C182" s="34" t="s">
         <v>309</v>
@@ -8347,7 +8663,7 @@
         <v>215</v>
       </c>
       <c r="H182" s="34">
-        <v>4.5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="I182" s="11"/>
     </row>
@@ -8356,7 +8672,7 @@
         <v>455</v>
       </c>
       <c r="B183" s="34" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="C183" s="34" t="s">
         <v>309</v>
@@ -8374,7 +8690,7 @@
         <v>215</v>
       </c>
       <c r="H183" s="34">
-        <v>4.5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="I183" s="11"/>
     </row>
@@ -8401,7 +8717,7 @@
         <v>215</v>
       </c>
       <c r="H184" s="35">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="I184" s="38"/>
     </row>
@@ -8410,13 +8726,13 @@
         <v>460</v>
       </c>
       <c r="B185" s="18" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="C185" s="18" t="s">
-        <v>445</v>
+        <v>800</v>
       </c>
       <c r="D185" s="18" t="s">
-        <v>429</v>
+        <v>801</v>
       </c>
       <c r="E185" s="18">
         <v>112</v>
@@ -8437,7 +8753,7 @@
         <v>461</v>
       </c>
       <c r="B186" s="34" t="s">
-        <v>798</v>
+        <v>802</v>
       </c>
       <c r="C186" s="34" t="s">
         <v>309</v>
@@ -8461,13 +8777,13 @@
     </row>
     <row r="187" spans="1:9">
       <c r="A187" s="9" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="B187" s="18" t="s">
         <v>442</v>
       </c>
       <c r="C187" s="18" t="s">
-        <v>238</v>
+        <v>804</v>
       </c>
       <c r="D187" s="18" t="s">
         <v>437</v>
@@ -8491,13 +8807,13 @@
         <v>462</v>
       </c>
       <c r="B188" s="18" t="s">
-        <v>800</v>
+        <v>805</v>
       </c>
       <c r="C188" s="18" t="s">
-        <v>272</v>
+        <v>806</v>
       </c>
       <c r="D188" s="18" t="s">
-        <v>801</v>
+        <v>807</v>
       </c>
       <c r="E188" s="18">
         <v>110</v>
@@ -8518,7 +8834,7 @@
         <v>463</v>
       </c>
       <c r="B189" s="18" t="s">
-        <v>802</v>
+        <v>808</v>
       </c>
       <c r="C189" s="18" t="s">
         <v>445</v>
@@ -8545,13 +8861,13 @@
         <v>464</v>
       </c>
       <c r="B190" s="10" t="s">
-        <v>803</v>
+        <v>809</v>
       </c>
       <c r="C190" s="10" t="s">
-        <v>804</v>
+        <v>810</v>
       </c>
       <c r="D190" s="10" t="s">
-        <v>805</v>
+        <v>811</v>
       </c>
       <c r="E190" s="11">
         <v>152</v>
@@ -8563,7 +8879,7 @@
         <v>215</v>
       </c>
       <c r="H190" s="10">
-        <v>5.2</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="I190" s="11"/>
     </row>
@@ -8572,10 +8888,10 @@
         <v>465</v>
       </c>
       <c r="B191" s="18" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="C191" s="18" t="s">
-        <v>238</v>
+        <v>804</v>
       </c>
       <c r="D191" s="18" t="s">
         <v>437</v>
@@ -8625,10 +8941,10 @@
         <v>468</v>
       </c>
       <c r="B194" s="41" t="s">
-        <v>806</v>
+        <v>812</v>
       </c>
       <c r="C194" s="42" t="s">
-        <v>385</v>
+        <v>813</v>
       </c>
       <c r="D194" s="43" t="s">
         <v>148</v>
@@ -8643,7 +8959,7 @@
         <v>225</v>
       </c>
       <c r="H194" s="41">
-        <v>4.2</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="I194" s="37"/>
     </row>
@@ -8652,7 +8968,7 @@
         <v>469</v>
       </c>
       <c r="B195" s="41" t="s">
-        <v>807</v>
+        <v>814</v>
       </c>
       <c r="C195" s="42" t="s">
         <v>470</v>
@@ -8670,7 +8986,7 @@
         <v>208</v>
       </c>
       <c r="H195" s="41">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="I195" s="37"/>
     </row>
@@ -8679,10 +8995,10 @@
         <v>471</v>
       </c>
       <c r="B196" s="45" t="s">
-        <v>808</v>
+        <v>815</v>
       </c>
       <c r="C196" s="45" t="s">
-        <v>809</v>
+        <v>816</v>
       </c>
       <c r="D196" s="45" t="s">
         <v>472</v>
@@ -8697,7 +9013,7 @@
         <v>215</v>
       </c>
       <c r="H196" s="45">
-        <v>4.0999999999999996</v>
+        <v>4</v>
       </c>
       <c r="I196" s="11"/>
     </row>
@@ -8706,10 +9022,10 @@
         <v>473</v>
       </c>
       <c r="B197" s="45" t="s">
-        <v>810</v>
+        <v>817</v>
       </c>
       <c r="C197" s="45" t="s">
-        <v>389</v>
+        <v>818</v>
       </c>
       <c r="D197" s="45" t="s">
         <v>386</v>
@@ -8733,7 +9049,7 @@
         <v>474</v>
       </c>
       <c r="B198" s="45" t="s">
-        <v>811</v>
+        <v>819</v>
       </c>
       <c r="C198" s="45" t="s">
         <v>475</v>
@@ -8760,13 +9076,13 @@
         <v>477</v>
       </c>
       <c r="B199" s="45" t="s">
-        <v>812</v>
+        <v>820</v>
       </c>
       <c r="C199" s="45" t="s">
-        <v>401</v>
+        <v>821</v>
       </c>
       <c r="D199" s="45" t="s">
-        <v>813</v>
+        <v>822</v>
       </c>
       <c r="E199" s="45">
         <v>95</v>
@@ -8944,7 +9260,7 @@
         <v>496</v>
       </c>
       <c r="C208" s="10" t="s">
-        <v>814</v>
+        <v>823</v>
       </c>
       <c r="D208" s="10" t="s">
         <v>39</v>
@@ -8959,7 +9275,7 @@
         <v>170</v>
       </c>
       <c r="H208" s="10">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="I208" s="11"/>
     </row>
@@ -9007,7 +9323,7 @@
         <v>501</v>
       </c>
       <c r="C211" s="10" t="s">
-        <v>815</v>
+        <v>824</v>
       </c>
       <c r="D211" s="10" t="s">
         <v>39</v>
@@ -9029,10 +9345,10 @@
         <v>502</v>
       </c>
       <c r="B212" s="35" t="s">
-        <v>816</v>
+        <v>825</v>
       </c>
       <c r="C212" s="35" t="s">
-        <v>817</v>
+        <v>826</v>
       </c>
       <c r="D212" s="35" t="s">
         <v>144</v>
@@ -9084,7 +9400,7 @@
         <v>507</v>
       </c>
       <c r="C214" s="35" t="s">
-        <v>817</v>
+        <v>826</v>
       </c>
       <c r="D214" s="35" t="s">
         <v>144</v>
@@ -9197,10 +9513,10 @@
         <v>519</v>
       </c>
       <c r="B220" s="10" t="s">
-        <v>818</v>
+        <v>827</v>
       </c>
       <c r="C220" s="10" t="s">
-        <v>819</v>
+        <v>828</v>
       </c>
       <c r="D220" s="49" t="s">
         <v>520</v>
@@ -9218,7 +9534,7 @@
         <v>3.4</v>
       </c>
       <c r="I220" s="11" t="s">
-        <v>820</v>
+        <v>829</v>
       </c>
     </row>
     <row r="221" spans="1:9">
@@ -9226,13 +9542,13 @@
         <v>521</v>
       </c>
       <c r="B221" s="10" t="s">
-        <v>821</v>
+        <v>830</v>
       </c>
       <c r="C221" s="10" t="s">
-        <v>822</v>
+        <v>831</v>
       </c>
       <c r="D221" s="49" t="s">
-        <v>4</v>
+        <v>832</v>
       </c>
       <c r="E221" s="10">
         <v>100</v>
@@ -9247,7 +9563,7 @@
         <v>3.3</v>
       </c>
       <c r="I221" s="37" t="s">
-        <v>823</v>
+        <v>833</v>
       </c>
     </row>
     <row r="222" spans="1:9">
@@ -9255,13 +9571,13 @@
         <v>522</v>
       </c>
       <c r="B222" s="10" t="s">
-        <v>824</v>
+        <v>834</v>
       </c>
       <c r="C222" s="10" t="s">
-        <v>825</v>
+        <v>835</v>
       </c>
       <c r="D222" s="49" t="s">
-        <v>520</v>
+        <v>836</v>
       </c>
       <c r="E222" s="10">
         <v>115</v>
@@ -9309,13 +9625,13 @@
         <v>526</v>
       </c>
       <c r="B224" s="35" t="s">
-        <v>826</v>
+        <v>837</v>
       </c>
       <c r="C224" s="35" t="s">
-        <v>827</v>
+        <v>838</v>
       </c>
       <c r="D224" s="35" t="s">
-        <v>828</v>
+        <v>839</v>
       </c>
       <c r="E224" s="35">
         <v>120</v>
@@ -9363,10 +9679,10 @@
         <v>530</v>
       </c>
       <c r="B226" s="35" t="s">
-        <v>829</v>
+        <v>840</v>
       </c>
       <c r="C226" s="35" t="s">
-        <v>238</v>
+        <v>841</v>
       </c>
       <c r="D226" s="35" t="s">
         <v>437</v>
@@ -9390,10 +9706,10 @@
         <v>531</v>
       </c>
       <c r="B227" s="35" t="s">
-        <v>830</v>
+        <v>842</v>
       </c>
       <c r="C227" s="35" t="s">
-        <v>238</v>
+        <v>841</v>
       </c>
       <c r="D227" s="35" t="s">
         <v>437</v>
@@ -9547,13 +9863,13 @@
         <v>544</v>
       </c>
       <c r="B234" s="52" t="s">
-        <v>831</v>
+        <v>843</v>
       </c>
       <c r="C234" s="52" t="s">
-        <v>832</v>
+        <v>844</v>
       </c>
       <c r="D234" s="50" t="s">
-        <v>833</v>
+        <v>845</v>
       </c>
       <c r="E234" s="52">
         <v>190</v>
@@ -9568,7 +9884,7 @@
         <v>5.8</v>
       </c>
       <c r="I234" s="54" t="s">
-        <v>834</v>
+        <v>846</v>
       </c>
     </row>
     <row r="235" spans="1:9">
@@ -9576,13 +9892,13 @@
         <v>545</v>
       </c>
       <c r="B235" s="51" t="s">
-        <v>835</v>
+        <v>847</v>
       </c>
       <c r="C235" s="51" t="s">
-        <v>836</v>
+        <v>848</v>
       </c>
       <c r="D235" s="51" t="s">
-        <v>837</v>
+        <v>849</v>
       </c>
       <c r="E235" s="51">
         <v>155</v>
@@ -9618,13 +9934,13 @@
         <v>548</v>
       </c>
       <c r="B237" s="51" t="s">
-        <v>838</v>
+        <v>850</v>
       </c>
       <c r="C237" s="51" t="s">
         <v>549</v>
       </c>
       <c r="D237" s="51" t="s">
-        <v>839</v>
+        <v>851</v>
       </c>
       <c r="E237" s="51">
         <v>155</v>
@@ -9636,7 +9952,7 @@
         <v>218</v>
       </c>
       <c r="H237" s="51">
-        <v>4.8</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="I237" s="55" t="s">
         <v>546</v>
@@ -9646,29 +9962,29 @@
       <c r="A238" s="9" t="s">
         <v>550</v>
       </c>
-      <c r="B238" s="38" t="s">
-        <v>840</v>
-      </c>
-      <c r="C238" s="38" t="s">
-        <v>841</v>
-      </c>
-      <c r="D238" s="38" t="s">
-        <v>842</v>
-      </c>
-      <c r="E238" s="38">
+      <c r="B238" s="51" t="s">
+        <v>852</v>
+      </c>
+      <c r="C238" s="51" t="s">
+        <v>853</v>
+      </c>
+      <c r="D238" s="51" t="s">
+        <v>854</v>
+      </c>
+      <c r="E238" s="52">
         <v>190</v>
       </c>
-      <c r="F238" s="38">
+      <c r="F238" s="36">
         <v>270</v>
       </c>
-      <c r="G238" s="38">
+      <c r="G238" s="55">
         <v>216</v>
       </c>
-      <c r="H238" s="38">
-        <v>5.8</v>
-      </c>
-      <c r="I238" s="38" t="s">
-        <v>843</v>
+      <c r="H238" s="51">
+        <v>5.7</v>
+      </c>
+      <c r="I238" s="54" t="s">
+        <v>855</v>
       </c>
     </row>
     <row r="239" spans="1:9">
@@ -9676,13 +9992,13 @@
         <v>551</v>
       </c>
       <c r="B239" s="51" t="s">
-        <v>844</v>
+        <v>856</v>
       </c>
       <c r="C239" s="51" t="s">
-        <v>845</v>
+        <v>857</v>
       </c>
       <c r="D239" s="51" t="s">
-        <v>842</v>
+        <v>854</v>
       </c>
       <c r="E239" s="52">
         <v>180</v>
@@ -9694,10 +10010,10 @@
         <v>220</v>
       </c>
       <c r="H239" s="51">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="I239" s="54" t="s">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="240" spans="1:9">
@@ -9705,13 +10021,13 @@
         <v>552</v>
       </c>
       <c r="B240" s="51" t="s">
-        <v>846</v>
+        <v>858</v>
       </c>
       <c r="C240" s="51" t="s">
-        <v>847</v>
+        <v>859</v>
       </c>
       <c r="D240" s="51" t="s">
-        <v>842</v>
+        <v>860</v>
       </c>
       <c r="E240" s="52">
         <v>190</v>
@@ -9723,10 +10039,10 @@
         <v>225</v>
       </c>
       <c r="H240" s="35">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="I240" s="54" t="s">
-        <v>848</v>
+        <v>861</v>
       </c>
     </row>
     <row r="241" spans="1:9">
@@ -9734,10 +10050,10 @@
         <v>553</v>
       </c>
       <c r="B241" s="51" t="s">
-        <v>849</v>
+        <v>862</v>
       </c>
       <c r="C241" s="51" t="s">
-        <v>850</v>
+        <v>863</v>
       </c>
       <c r="D241" s="11" t="s">
         <v>554</v>
@@ -9755,7 +10071,7 @@
         <v>5.2</v>
       </c>
       <c r="I241" s="55" t="s">
-        <v>851</v>
+        <v>864</v>
       </c>
     </row>
     <row r="242" spans="1:9">
@@ -9763,13 +10079,13 @@
         <v>555</v>
       </c>
       <c r="B242" s="51" t="s">
-        <v>852</v>
+        <v>865</v>
       </c>
       <c r="C242" s="51" t="s">
-        <v>853</v>
+        <v>866</v>
       </c>
       <c r="D242" s="51" t="s">
-        <v>842</v>
+        <v>860</v>
       </c>
       <c r="E242" s="52">
         <v>160</v>
@@ -9784,7 +10100,7 @@
         <v>4.9000000000000004</v>
       </c>
       <c r="I242" s="54" t="s">
-        <v>854</v>
+        <v>867</v>
       </c>
     </row>
     <row r="243" spans="1:9">
@@ -9792,13 +10108,13 @@
         <v>556</v>
       </c>
       <c r="B243" s="51" t="s">
-        <v>855</v>
+        <v>868</v>
       </c>
       <c r="C243" s="51" t="s">
-        <v>856</v>
+        <v>869</v>
       </c>
       <c r="D243" s="51" t="s">
-        <v>857</v>
+        <v>870</v>
       </c>
       <c r="E243" s="52">
         <v>190</v>
@@ -9813,7 +10129,7 @@
         <v>5.6</v>
       </c>
       <c r="I243" s="54" t="s">
-        <v>858</v>
+        <v>871</v>
       </c>
     </row>
     <row r="244" spans="1:9">
@@ -9821,13 +10137,13 @@
         <v>557</v>
       </c>
       <c r="B244" s="51" t="s">
-        <v>859</v>
+        <v>872</v>
       </c>
       <c r="C244" s="51" t="s">
-        <v>860</v>
+        <v>873</v>
       </c>
       <c r="D244" s="51" t="s">
-        <v>857</v>
+        <v>870</v>
       </c>
       <c r="E244" s="51">
         <v>150</v>
@@ -9859,13 +10175,13 @@
         <v>559</v>
       </c>
       <c r="B246" s="18" t="s">
-        <v>861</v>
+        <v>874</v>
       </c>
       <c r="C246" s="18" t="s">
-        <v>862</v>
+        <v>875</v>
       </c>
       <c r="D246" s="33" t="s">
-        <v>429</v>
+        <v>876</v>
       </c>
       <c r="E246" s="18">
         <v>112</v>
@@ -9886,7 +10202,7 @@
         <v>560</v>
       </c>
       <c r="B247" s="18" t="s">
-        <v>863</v>
+        <v>877</v>
       </c>
       <c r="C247" s="18" t="s">
         <v>529</v>
@@ -9913,7 +10229,7 @@
         <v>561</v>
       </c>
       <c r="B248" s="18" t="s">
-        <v>864</v>
+        <v>878</v>
       </c>
       <c r="C248" s="18" t="s">
         <v>562</v>
@@ -9940,10 +10256,10 @@
         <v>563</v>
       </c>
       <c r="B249" s="18" t="s">
-        <v>865</v>
+        <v>879</v>
       </c>
       <c r="C249" s="18" t="s">
-        <v>439</v>
+        <v>880</v>
       </c>
       <c r="D249" s="18" t="s">
         <v>429</v>
@@ -9952,7 +10268,7 @@
         <v>105</v>
       </c>
       <c r="F249" s="58">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="G249" s="32">
         <v>208</v>
@@ -9967,7 +10283,7 @@
         <v>564</v>
       </c>
       <c r="B250" s="18" t="s">
-        <v>866</v>
+        <v>881</v>
       </c>
       <c r="C250" s="18" t="s">
         <v>153</v>
@@ -9994,7 +10310,7 @@
         <v>565</v>
       </c>
       <c r="B251" s="18" t="s">
-        <v>867</v>
+        <v>882</v>
       </c>
       <c r="C251" s="18" t="s">
         <v>566</v>
@@ -10021,10 +10337,10 @@
         <v>567</v>
       </c>
       <c r="B252" s="18" t="s">
-        <v>868</v>
+        <v>883</v>
       </c>
       <c r="C252" s="18" t="s">
-        <v>439</v>
+        <v>880</v>
       </c>
       <c r="D252" s="18" t="s">
         <v>429</v>
@@ -10048,7 +10364,7 @@
         <v>568</v>
       </c>
       <c r="B253" s="18" t="s">
-        <v>869</v>
+        <v>884</v>
       </c>
       <c r="C253" s="18" t="s">
         <v>566</v>
@@ -10075,13 +10391,13 @@
         <v>569</v>
       </c>
       <c r="B254" s="18" t="s">
-        <v>870</v>
+        <v>885</v>
       </c>
       <c r="C254" s="18" t="s">
-        <v>871</v>
+        <v>886</v>
       </c>
       <c r="D254" s="18" t="s">
-        <v>833</v>
+        <v>887</v>
       </c>
       <c r="E254" s="18">
         <v>190</v>
@@ -10093,10 +10409,10 @@
         <v>215</v>
       </c>
       <c r="H254" s="18">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I254" s="54" t="s">
-        <v>858</v>
+        <v>871</v>
       </c>
     </row>
     <row r="255" spans="1:9">
@@ -10104,7 +10420,7 @@
         <v>570</v>
       </c>
       <c r="B255" s="18" t="s">
-        <v>872</v>
+        <v>888</v>
       </c>
       <c r="C255" s="18" t="s">
         <v>571</v>
@@ -10131,13 +10447,13 @@
         <v>572</v>
       </c>
       <c r="B256" s="52" t="s">
-        <v>873</v>
+        <v>889</v>
       </c>
       <c r="C256" s="18" t="s">
-        <v>161</v>
+        <v>890</v>
       </c>
       <c r="D256" s="50" t="s">
-        <v>874</v>
+        <v>891</v>
       </c>
       <c r="E256" s="52">
         <v>190</v>
@@ -10152,7 +10468,7 @@
         <v>5.2</v>
       </c>
       <c r="I256" s="54" t="s">
-        <v>875</v>
+        <v>892</v>
       </c>
     </row>
     <row r="257" spans="1:9">
@@ -10160,13 +10476,13 @@
         <v>573</v>
       </c>
       <c r="B257" s="36" t="s">
+        <v>893</v>
+      </c>
+      <c r="C257" s="36" t="s">
+        <v>894</v>
+      </c>
+      <c r="D257" s="36" t="s">
         <v>876</v>
-      </c>
-      <c r="C257" s="36" t="s">
-        <v>321</v>
-      </c>
-      <c r="D257" s="36" t="s">
-        <v>429</v>
       </c>
       <c r="E257" s="36">
         <v>118</v>
@@ -10178,7 +10494,7 @@
         <v>215</v>
       </c>
       <c r="H257" s="60">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="I257" s="60"/>
     </row>
@@ -10187,7 +10503,7 @@
         <v>574</v>
       </c>
       <c r="B258" s="18" t="s">
-        <v>866</v>
+        <v>881</v>
       </c>
       <c r="C258" s="18" t="s">
         <v>153</v>
@@ -10246,7 +10562,7 @@
         <v>579</v>
       </c>
       <c r="D261" s="49" t="s">
-        <v>877</v>
+        <v>895</v>
       </c>
       <c r="E261" s="10">
         <v>108</v>
@@ -10267,7 +10583,7 @@
         <v>580</v>
       </c>
       <c r="B262" s="10" t="s">
-        <v>878</v>
+        <v>896</v>
       </c>
       <c r="C262" s="10" t="s">
         <v>581</v>
@@ -10375,13 +10691,13 @@
         <v>595</v>
       </c>
       <c r="B266" s="35" t="s">
-        <v>879</v>
+        <v>897</v>
       </c>
       <c r="C266" s="35" t="s">
-        <v>860</v>
+        <v>873</v>
       </c>
       <c r="D266" s="35" t="s">
-        <v>880</v>
+        <v>898</v>
       </c>
       <c r="E266" s="35">
         <v>78</v>
@@ -10402,13 +10718,13 @@
         <v>596</v>
       </c>
       <c r="B267" s="10" t="s">
-        <v>881</v>
+        <v>899</v>
       </c>
       <c r="C267" s="10" t="s">
-        <v>882</v>
+        <v>900</v>
       </c>
       <c r="D267" s="49" t="s">
-        <v>144</v>
+        <v>901</v>
       </c>
       <c r="E267" s="10">
         <v>60</v>
@@ -10573,13 +10889,13 @@
         <v>610</v>
       </c>
       <c r="B278" s="27" t="s">
-        <v>883</v>
+        <v>902</v>
       </c>
       <c r="C278" s="27" t="s">
-        <v>549</v>
+        <v>903</v>
       </c>
       <c r="D278" s="27" t="s">
-        <v>884</v>
+        <v>904</v>
       </c>
       <c r="E278" s="27">
         <v>159</v>
@@ -10591,7 +10907,7 @@
         <v>212</v>
       </c>
       <c r="H278" s="27">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="I278" s="60"/>
     </row>
@@ -10600,10 +10916,10 @@
         <v>611</v>
       </c>
       <c r="B279" s="10" t="s">
-        <v>885</v>
+        <v>905</v>
       </c>
       <c r="C279" s="49" t="s">
-        <v>886</v>
+        <v>906</v>
       </c>
       <c r="D279" s="10" t="s">
         <v>144</v>
@@ -10627,13 +10943,13 @@
         <v>612</v>
       </c>
       <c r="B280" s="10" t="s">
-        <v>887</v>
+        <v>907</v>
       </c>
       <c r="C280" s="49" t="s">
-        <v>888</v>
+        <v>908</v>
       </c>
       <c r="D280" s="10" t="s">
-        <v>489</v>
+        <v>909</v>
       </c>
       <c r="E280" s="10"/>
       <c r="F280" s="9">
@@ -10679,7 +10995,7 @@
         <v>616</v>
       </c>
       <c r="B282" s="10" t="s">
-        <v>889</v>
+        <v>910</v>
       </c>
       <c r="C282" s="49" t="s">
         <v>617</v>
@@ -10706,10 +11022,10 @@
         <v>618</v>
       </c>
       <c r="B283" s="10" t="s">
-        <v>890</v>
+        <v>911</v>
       </c>
       <c r="C283" s="49" t="s">
-        <v>891</v>
+        <v>912</v>
       </c>
       <c r="D283" s="10" t="s">
         <v>39</v>
@@ -10733,13 +11049,13 @@
         <v>619</v>
       </c>
       <c r="B284" s="27" t="s">
-        <v>892</v>
+        <v>913</v>
       </c>
       <c r="C284" s="36" t="s">
-        <v>893</v>
+        <v>914</v>
       </c>
       <c r="D284" s="36" t="s">
-        <v>894</v>
+        <v>915</v>
       </c>
       <c r="E284" s="36">
         <v>80</v>
@@ -10766,7 +11082,7 @@
         <v>622</v>
       </c>
       <c r="D285" s="36" t="s">
-        <v>894</v>
+        <v>915</v>
       </c>
       <c r="E285" s="10">
         <v>73</v>
@@ -10787,10 +11103,10 @@
         <v>623</v>
       </c>
       <c r="B286" s="52" t="s">
-        <v>895</v>
+        <v>916</v>
       </c>
       <c r="C286" s="52" t="s">
-        <v>896</v>
+        <v>917</v>
       </c>
       <c r="D286" s="52" t="s">
         <v>624</v>
@@ -10814,13 +11130,13 @@
         <v>625</v>
       </c>
       <c r="B287" s="52" t="s">
-        <v>897</v>
+        <v>918</v>
       </c>
       <c r="C287" s="52" t="s">
-        <v>898</v>
+        <v>919</v>
       </c>
       <c r="D287" s="52" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="E287" s="52">
         <v>88</v>
@@ -10832,7 +11148,7 @@
         <v>218</v>
       </c>
       <c r="H287" s="52">
-        <v>4.5</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="I287" s="61"/>
     </row>
@@ -10841,7 +11157,7 @@
         <v>626</v>
       </c>
       <c r="B288" s="27" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="C288" s="27" t="s">
         <v>627</v>
@@ -10889,7 +11205,7 @@
         <v>3.9</v>
       </c>
       <c r="I289" s="11" t="s">
-        <v>901</v>
+        <v>922</v>
       </c>
     </row>
     <row r="290" spans="1:9">
@@ -10924,13 +11240,13 @@
         <v>635</v>
       </c>
       <c r="B291" s="64" t="s">
-        <v>902</v>
+        <v>923</v>
       </c>
       <c r="C291" s="64" t="s">
+        <v>924</v>
+      </c>
+      <c r="D291" s="64" t="s">
         <v>636</v>
-      </c>
-      <c r="D291" s="64" t="s">
-        <v>637</v>
       </c>
       <c r="E291" s="64">
         <v>88</v>
@@ -10942,22 +11258,22 @@
         <v>220</v>
       </c>
       <c r="H291" s="64">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="I291" s="61"/>
     </row>
     <row r="292" spans="1:9">
       <c r="A292" s="9" t="s">
+        <v>637</v>
+      </c>
+      <c r="B292" s="64" t="s">
+        <v>925</v>
+      </c>
+      <c r="C292" s="64" t="s">
         <v>638</v>
       </c>
-      <c r="B292" s="64" t="s">
-        <v>903</v>
-      </c>
-      <c r="C292" s="64" t="s">
+      <c r="D292" s="64" t="s">
         <v>639</v>
-      </c>
-      <c r="D292" s="64" t="s">
-        <v>640</v>
       </c>
       <c r="E292" s="64">
         <v>80</v>
@@ -10975,13 +11291,13 @@
     </row>
     <row r="293" spans="1:9">
       <c r="A293" s="9" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B293" s="65" t="s">
-        <v>904</v>
+        <v>926</v>
       </c>
       <c r="C293" s="64" t="s">
-        <v>905</v>
+        <v>927</v>
       </c>
       <c r="D293" s="64" t="s">
         <v>39</v>
@@ -11002,16 +11318,16 @@
     </row>
     <row r="294" spans="1:9">
       <c r="A294" s="9" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B294" s="18" t="s">
-        <v>906</v>
+        <v>928</v>
       </c>
       <c r="C294" s="18" t="s">
-        <v>445</v>
+        <v>929</v>
       </c>
       <c r="D294" s="18" t="s">
-        <v>907</v>
+        <v>930</v>
       </c>
       <c r="E294" s="18">
         <v>150</v>
@@ -11029,16 +11345,16 @@
     </row>
     <row r="295" spans="1:9">
       <c r="A295" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="B295" s="10" t="s">
+        <v>931</v>
+      </c>
+      <c r="C295" s="10" t="s">
         <v>643</v>
       </c>
-      <c r="B295" s="10" t="s">
-        <v>908</v>
-      </c>
-      <c r="C295" s="10" t="s">
+      <c r="D295" s="10" t="s">
         <v>644</v>
-      </c>
-      <c r="D295" s="10" t="s">
-        <v>645</v>
       </c>
       <c r="E295" s="10"/>
       <c r="F295" s="9"/>
@@ -11052,16 +11368,16 @@
     </row>
     <row r="296" spans="1:9">
       <c r="A296" s="9" t="s">
+        <v>645</v>
+      </c>
+      <c r="B296" s="35" t="s">
         <v>646</v>
       </c>
-      <c r="B296" s="35" t="s">
+      <c r="C296" s="35" t="s">
         <v>647</v>
       </c>
-      <c r="C296" s="35" t="s">
+      <c r="D296" s="35" t="s">
         <v>648</v>
-      </c>
-      <c r="D296" s="35" t="s">
-        <v>649</v>
       </c>
       <c r="E296" s="35"/>
       <c r="F296" s="36">
@@ -11077,16 +11393,16 @@
     </row>
     <row r="297" spans="1:9">
       <c r="A297" s="9" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B297" s="18" t="s">
-        <v>909</v>
+        <v>932</v>
       </c>
       <c r="C297" s="18" t="s">
-        <v>910</v>
+        <v>933</v>
       </c>
       <c r="D297" s="33" t="s">
-        <v>911</v>
+        <v>934</v>
       </c>
       <c r="E297" s="18">
         <v>125</v>
@@ -11104,16 +11420,16 @@
     </row>
     <row r="298" spans="1:9">
       <c r="A298" s="9" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B298" s="18" t="s">
-        <v>912</v>
+        <v>935</v>
       </c>
       <c r="C298" s="18" t="s">
-        <v>913</v>
+        <v>936</v>
       </c>
       <c r="D298" s="33" t="s">
-        <v>914</v>
+        <v>937</v>
       </c>
       <c r="E298" s="18">
         <v>190</v>
@@ -11125,24 +11441,24 @@
         <v>225</v>
       </c>
       <c r="H298" s="18">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="I298" s="11" t="s">
-        <v>915</v>
+        <v>938</v>
       </c>
     </row>
     <row r="299" spans="1:9">
       <c r="A299" s="9" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B299" s="51" t="s">
-        <v>916</v>
+        <v>939</v>
       </c>
       <c r="C299" s="51" t="s">
-        <v>917</v>
+        <v>940</v>
       </c>
       <c r="D299" s="51" t="s">
-        <v>918</v>
+        <v>941</v>
       </c>
       <c r="E299" s="51">
         <v>124</v>
@@ -11157,12 +11473,12 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="I299" s="55" t="s">
-        <v>919</v>
+        <v>942</v>
       </c>
     </row>
     <row r="300" spans="1:9">
       <c r="A300" s="9" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B300" s="36"/>
       <c r="C300" s="36"/>
@@ -11175,7 +11491,7 @@
     </row>
     <row r="301" spans="1:9">
       <c r="A301" s="9" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B301" s="36"/>
       <c r="C301" s="36"/>
@@ -11188,16 +11504,16 @@
     </row>
     <row r="302" spans="1:9">
       <c r="A302" s="9" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B302" s="11" t="s">
-        <v>920</v>
+        <v>943</v>
       </c>
       <c r="C302" s="11" t="s">
-        <v>921</v>
+        <v>944</v>
       </c>
       <c r="D302" s="11" t="s">
-        <v>922</v>
+        <v>945</v>
       </c>
       <c r="E302" s="11">
         <v>150</v>
@@ -11215,16 +11531,16 @@
     </row>
     <row r="303" spans="1:9">
       <c r="A303" s="9" t="s">
+        <v>655</v>
+      </c>
+      <c r="B303" s="10" t="s">
         <v>656</v>
       </c>
-      <c r="B303" s="10" t="s">
+      <c r="C303" s="10" t="s">
         <v>657</v>
       </c>
-      <c r="C303" s="10" t="s">
-        <v>658</v>
-      </c>
       <c r="D303" s="10" t="s">
-        <v>922</v>
+        <v>945</v>
       </c>
       <c r="E303" s="11">
         <v>140</v>
@@ -11242,16 +11558,16 @@
     </row>
     <row r="304" spans="1:9">
       <c r="A304" s="9" t="s">
+        <v>658</v>
+      </c>
+      <c r="B304" s="64" t="s">
         <v>659</v>
       </c>
-      <c r="B304" s="64" t="s">
+      <c r="C304" s="64" t="s">
+        <v>946</v>
+      </c>
+      <c r="D304" s="64" t="s">
         <v>660</v>
-      </c>
-      <c r="C304" s="64" t="s">
-        <v>251</v>
-      </c>
-      <c r="D304" s="64" t="s">
-        <v>661</v>
       </c>
       <c r="E304" s="64">
         <v>90</v>
@@ -11266,21 +11582,21 @@
         <v>4.5</v>
       </c>
       <c r="I304" s="37" t="s">
-        <v>923</v>
+        <v>947</v>
       </c>
     </row>
     <row r="305" spans="1:9">
       <c r="A305" s="9" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B305" s="36" t="s">
-        <v>924</v>
+        <v>948</v>
       </c>
       <c r="C305" s="36" t="s">
-        <v>925</v>
+        <v>949</v>
       </c>
       <c r="D305" s="18" t="s">
-        <v>926</v>
+        <v>950</v>
       </c>
       <c r="E305" s="36">
         <v>215</v>
@@ -11292,13 +11608,13 @@
         <v>225</v>
       </c>
       <c r="H305" s="61">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="I305" s="61"/>
     </row>
     <row r="306" spans="1:9">
       <c r="A306" s="9" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B306" s="36"/>
       <c r="C306" s="36"/>
@@ -11311,7 +11627,7 @@
     </row>
     <row r="307" spans="1:9">
       <c r="A307" s="9" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B307" s="36"/>
       <c r="C307" s="36"/>
@@ -11324,7 +11640,7 @@
     </row>
     <row r="308" spans="1:9">
       <c r="A308" s="9" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B308" s="36"/>
       <c r="C308" s="36"/>
@@ -11337,7 +11653,7 @@
     </row>
     <row r="309" spans="1:9">
       <c r="A309" s="9" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B309" s="36"/>
       <c r="C309" s="36"/>
@@ -11350,7 +11666,7 @@
     </row>
     <row r="310" spans="1:9">
       <c r="A310" s="9" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B310" s="36"/>
       <c r="C310" s="36"/>
@@ -11363,16 +11679,16 @@
     </row>
     <row r="311" spans="1:9">
       <c r="A311" s="9" t="s">
+        <v>667</v>
+      </c>
+      <c r="B311" s="35" t="s">
         <v>668</v>
       </c>
-      <c r="B311" s="35" t="s">
+      <c r="C311" s="35" t="s">
+        <v>951</v>
+      </c>
+      <c r="D311" s="35" t="s">
         <v>669</v>
-      </c>
-      <c r="C311" s="35" t="s">
-        <v>673</v>
-      </c>
-      <c r="D311" s="35" t="s">
-        <v>670</v>
       </c>
       <c r="E311" s="35">
         <v>85</v>
@@ -11390,16 +11706,16 @@
     </row>
     <row r="312" spans="1:9">
       <c r="A312" s="9" t="s">
+        <v>670</v>
+      </c>
+      <c r="B312" s="10" t="s">
         <v>671</v>
       </c>
-      <c r="B312" s="10" t="s">
+      <c r="C312" s="10" t="s">
         <v>672</v>
       </c>
-      <c r="C312" s="10" t="s">
+      <c r="D312" s="10" t="s">
         <v>673</v>
-      </c>
-      <c r="D312" s="10" t="s">
-        <v>674</v>
       </c>
       <c r="E312" s="10">
         <v>73</v>
@@ -11417,7 +11733,7 @@
     </row>
     <row r="313" spans="1:9">
       <c r="A313" s="9" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B313" s="36"/>
       <c r="C313" s="36"/>
@@ -11430,7 +11746,7 @@
     </row>
     <row r="314" spans="1:9">
       <c r="A314" s="9" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B314" s="36"/>
       <c r="C314" s="36"/>
@@ -11443,16 +11759,16 @@
     </row>
     <row r="315" spans="1:9">
       <c r="A315" s="9" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B315" s="36" t="s">
-        <v>927</v>
+        <v>952</v>
       </c>
       <c r="C315" s="36" t="s">
-        <v>841</v>
+        <v>953</v>
       </c>
       <c r="D315" s="11" t="s">
-        <v>928</v>
+        <v>954</v>
       </c>
       <c r="E315" s="36">
         <v>116</v>
@@ -11467,21 +11783,21 @@
         <v>5</v>
       </c>
       <c r="I315" s="61" t="s">
-        <v>929</v>
+        <v>955</v>
       </c>
     </row>
     <row r="316" spans="1:9">
       <c r="A316" s="9" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B316" s="36" t="s">
-        <v>930</v>
+        <v>956</v>
       </c>
       <c r="C316" s="36" t="s">
-        <v>931</v>
+        <v>957</v>
       </c>
       <c r="D316" s="11" t="s">
-        <v>932</v>
+        <v>958</v>
       </c>
       <c r="E316" s="36">
         <v>160</v>
@@ -11496,21 +11812,21 @@
         <v>5.2</v>
       </c>
       <c r="I316" s="61" t="s">
-        <v>933</v>
+        <v>959</v>
       </c>
     </row>
     <row r="317" spans="1:9">
       <c r="A317" s="9" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B317" s="11" t="s">
-        <v>934</v>
+        <v>960</v>
       </c>
       <c r="C317" s="11" t="s">
-        <v>935</v>
+        <v>961</v>
       </c>
       <c r="D317" s="11" t="s">
-        <v>936</v>
+        <v>962</v>
       </c>
       <c r="E317" s="11">
         <v>110</v>
@@ -11525,21 +11841,21 @@
         <v>3.6</v>
       </c>
       <c r="I317" s="11" t="s">
-        <v>937</v>
+        <v>963</v>
       </c>
     </row>
     <row r="318" spans="1:9">
       <c r="A318" s="9" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B318" s="11" t="s">
-        <v>934</v>
+        <v>960</v>
       </c>
       <c r="C318" s="11" t="s">
-        <v>938</v>
+        <v>964</v>
       </c>
       <c r="D318" s="11" t="s">
-        <v>936</v>
+        <v>962</v>
       </c>
       <c r="E318" s="11">
         <v>110</v>
@@ -11557,16 +11873,16 @@
     </row>
     <row r="319" spans="1:9">
       <c r="A319" s="9" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B319" s="18" t="s">
-        <v>939</v>
+        <v>965</v>
       </c>
       <c r="C319" s="18" t="s">
-        <v>940</v>
+        <v>966</v>
       </c>
       <c r="D319" s="18" t="s">
-        <v>941</v>
+        <v>967</v>
       </c>
       <c r="E319" s="18">
         <v>205</v>
@@ -11578,24 +11894,24 @@
         <v>215</v>
       </c>
       <c r="H319" s="18">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="I319" s="11" t="s">
-        <v>942</v>
+        <v>968</v>
       </c>
     </row>
     <row r="320" spans="1:9">
       <c r="A320" s="9" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B320" s="18" t="s">
-        <v>943</v>
+        <v>969</v>
       </c>
       <c r="C320" s="18" t="s">
-        <v>944</v>
+        <v>970</v>
       </c>
       <c r="D320" s="18" t="s">
-        <v>945</v>
+        <v>971</v>
       </c>
       <c r="E320" s="18">
         <v>182</v>
@@ -11607,24 +11923,24 @@
         <v>220</v>
       </c>
       <c r="H320" s="18">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="I320" s="11" t="s">
-        <v>915</v>
+        <v>938</v>
       </c>
     </row>
     <row r="321" spans="1:9">
       <c r="A321" s="9" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B321" s="18" t="s">
-        <v>946</v>
+        <v>972</v>
       </c>
       <c r="C321" s="18" t="s">
-        <v>947</v>
+        <v>973</v>
       </c>
       <c r="D321" s="18" t="s">
-        <v>948</v>
+        <v>974</v>
       </c>
       <c r="E321" s="18">
         <v>138</v>
@@ -11639,21 +11955,21 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="I321" s="11" t="s">
-        <v>949</v>
+        <v>975</v>
       </c>
     </row>
     <row r="322" spans="1:9">
       <c r="A322" s="9" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B322" s="18" t="s">
-        <v>950</v>
+        <v>976</v>
       </c>
       <c r="C322" s="18" t="s">
-        <v>951</v>
+        <v>977</v>
       </c>
       <c r="D322" s="18" t="s">
-        <v>941</v>
+        <v>967</v>
       </c>
       <c r="E322" s="18">
         <v>225</v>
@@ -11665,24 +11981,24 @@
         <v>215</v>
       </c>
       <c r="H322" s="18">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I322" s="11" t="s">
-        <v>952</v>
+        <v>978</v>
       </c>
     </row>
     <row r="323" spans="1:9">
       <c r="A323" s="9" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B323" s="18" t="s">
-        <v>953</v>
+        <v>979</v>
       </c>
       <c r="C323" s="18" t="s">
-        <v>88</v>
+        <v>980</v>
       </c>
       <c r="D323" s="18" t="s">
-        <v>948</v>
+        <v>974</v>
       </c>
       <c r="E323" s="18">
         <v>155</v>
@@ -11697,21 +12013,21 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="I323" s="11" t="s">
-        <v>954</v>
+        <v>981</v>
       </c>
     </row>
     <row r="324" spans="1:9">
       <c r="A324" s="9" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B324" s="18" t="s">
-        <v>955</v>
+        <v>982</v>
       </c>
       <c r="C324" s="18" t="s">
-        <v>956</v>
+        <v>983</v>
       </c>
       <c r="D324" s="18" t="s">
-        <v>941</v>
+        <v>967</v>
       </c>
       <c r="E324" s="18">
         <v>220</v>
@@ -11723,15 +12039,15 @@
         <v>218</v>
       </c>
       <c r="H324" s="18">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
       <c r="I324" s="11" t="s">
-        <v>952</v>
+        <v>978</v>
       </c>
     </row>
     <row r="325" spans="1:9">
       <c r="A325" s="9" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B325" s="36"/>
       <c r="C325" s="36"/>
@@ -11744,7 +12060,7 @@
     </row>
     <row r="326" spans="1:9">
       <c r="A326" s="9" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B326" s="36"/>
       <c r="C326" s="36"/>
@@ -11757,7 +12073,7 @@
     </row>
     <row r="327" spans="1:9">
       <c r="A327" s="9" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B327" s="36"/>
       <c r="C327" s="36"/>
@@ -11770,7 +12086,7 @@
     </row>
     <row r="328" spans="1:9">
       <c r="A328" s="9" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B328" s="36"/>
       <c r="C328" s="36"/>
@@ -11783,7 +12099,7 @@
     </row>
     <row r="329" spans="1:9">
       <c r="A329" s="9" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B329" s="36"/>
       <c r="C329" s="36"/>
@@ -11796,7 +12112,7 @@
     </row>
     <row r="330" spans="1:9">
       <c r="A330" s="9" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B330" s="36"/>
       <c r="C330" s="36"/>
@@ -11809,7 +12125,7 @@
     </row>
     <row r="331" spans="1:9">
       <c r="A331" s="9" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B331" s="36"/>
       <c r="C331" s="36"/>
@@ -11822,7 +12138,7 @@
     </row>
     <row r="332" spans="1:9">
       <c r="A332" s="9" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B332" s="36"/>
       <c r="C332" s="36"/>
@@ -11835,7 +12151,7 @@
     </row>
     <row r="333" spans="1:9">
       <c r="A333" s="9" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B333" s="36"/>
       <c r="C333" s="36"/>
@@ -11848,7 +12164,7 @@
     </row>
     <row r="334" spans="1:9">
       <c r="A334" s="9" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B334" s="36"/>
       <c r="C334" s="36"/>
@@ -11861,7 +12177,7 @@
     </row>
     <row r="335" spans="1:9">
       <c r="A335" s="9" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B335" s="36"/>
       <c r="C335" s="36"/>
@@ -11874,7 +12190,7 @@
     </row>
     <row r="336" spans="1:9">
       <c r="A336" s="9" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B336" s="36"/>
       <c r="C336" s="36"/>
@@ -11887,7 +12203,7 @@
     </row>
     <row r="337" spans="1:9">
       <c r="A337" s="9" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B337" s="36"/>
       <c r="C337" s="36"/>
@@ -11900,7 +12216,7 @@
     </row>
     <row r="338" spans="1:9">
       <c r="A338" s="9" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B338" s="36"/>
       <c r="C338" s="36"/>
@@ -11913,7 +12229,7 @@
     </row>
     <row r="339" spans="1:9">
       <c r="A339" s="9" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B339" s="36"/>
       <c r="C339" s="36"/>
@@ -11926,7 +12242,7 @@
     </row>
     <row r="340" spans="1:9">
       <c r="A340" s="9" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B340" s="36"/>
       <c r="C340" s="36"/>
@@ -11939,7 +12255,7 @@
     </row>
     <row r="341" spans="1:9">
       <c r="A341" s="9" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B341" s="36"/>
       <c r="C341" s="36"/>
@@ -11952,7 +12268,7 @@
     </row>
     <row r="342" spans="1:9">
       <c r="A342" s="9" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B342" s="36"/>
       <c r="C342" s="36"/>
@@ -11965,7 +12281,7 @@
     </row>
     <row r="343" spans="1:9">
       <c r="A343" s="9" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B343" s="36"/>
       <c r="C343" s="36"/>
@@ -11978,7 +12294,7 @@
     </row>
     <row r="344" spans="1:9">
       <c r="A344" s="9" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B344" s="36"/>
       <c r="C344" s="36"/>
@@ -11991,7 +12307,7 @@
     </row>
     <row r="345" spans="1:9">
       <c r="A345" s="9" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B345" s="36"/>
       <c r="C345" s="36"/>
@@ -12004,7 +12320,7 @@
     </row>
     <row r="346" spans="1:9">
       <c r="A346" s="9" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B346" s="36"/>
       <c r="C346" s="36"/>
@@ -12017,7 +12333,7 @@
     </row>
     <row r="347" spans="1:9">
       <c r="A347" s="9" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B347" s="36"/>
       <c r="C347" s="36"/>
@@ -12030,7 +12346,7 @@
     </row>
     <row r="348" spans="1:9">
       <c r="A348" s="9" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B348" s="36"/>
       <c r="C348" s="36"/>
@@ -12043,7 +12359,7 @@
     </row>
     <row r="349" spans="1:9">
       <c r="A349" s="9" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B349" s="36"/>
       <c r="C349" s="36"/>
@@ -12056,7 +12372,7 @@
     </row>
     <row r="350" spans="1:9">
       <c r="A350" s="9" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B350" s="36"/>
       <c r="C350" s="36"/>
@@ -12069,7 +12385,7 @@
     </row>
     <row r="351" spans="1:9">
       <c r="A351" s="9" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B351" s="36"/>
       <c r="C351" s="36"/>
@@ -12082,7 +12398,7 @@
     </row>
     <row r="352" spans="1:9">
       <c r="A352" s="9" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B352" s="36"/>
       <c r="C352" s="36"/>
@@ -12095,7 +12411,7 @@
     </row>
     <row r="353" spans="1:9">
       <c r="A353" s="9" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B353" s="36"/>
       <c r="C353" s="36"/>
@@ -12108,7 +12424,7 @@
     </row>
     <row r="354" spans="1:9">
       <c r="A354" s="9" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B354" s="36"/>
       <c r="C354" s="36"/>
@@ -12121,7 +12437,7 @@
     </row>
     <row r="355" spans="1:9">
       <c r="A355" s="9" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B355" s="36"/>
       <c r="C355" s="36"/>
@@ -12134,7 +12450,7 @@
     </row>
     <row r="356" spans="1:9">
       <c r="A356" s="9" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B356" s="36"/>
       <c r="C356" s="36"/>
@@ -12147,7 +12463,7 @@
     </row>
     <row r="357" spans="1:9">
       <c r="A357" s="9" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B357" s="36"/>
       <c r="C357" s="36"/>
@@ -12160,7 +12476,7 @@
     </row>
     <row r="358" spans="1:9">
       <c r="A358" s="9" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B358" s="36"/>
       <c r="C358" s="36"/>
@@ -12173,7 +12489,7 @@
     </row>
     <row r="359" spans="1:9">
       <c r="A359" s="9" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B359" s="36"/>
       <c r="C359" s="36"/>
@@ -12186,7 +12502,7 @@
     </row>
     <row r="360" spans="1:9">
       <c r="A360" s="9" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B360" s="36"/>
       <c r="C360" s="36"/>
@@ -12199,7 +12515,7 @@
     </row>
     <row r="361" spans="1:9">
       <c r="A361" s="9" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="B361" s="36"/>
       <c r="C361" s="36"/>
@@ -12212,7 +12528,7 @@
     </row>
     <row r="362" spans="1:9">
       <c r="A362" s="9" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="B362" s="36"/>
       <c r="C362" s="36"/>
@@ -12225,7 +12541,7 @@
     </row>
     <row r="363" spans="1:9">
       <c r="A363" s="9" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="B363" s="36"/>
       <c r="C363" s="36"/>
@@ -12238,7 +12554,7 @@
     </row>
     <row r="364" spans="1:9">
       <c r="A364" s="9" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B364" s="36"/>
       <c r="C364" s="36"/>
@@ -12251,7 +12567,7 @@
     </row>
     <row r="365" spans="1:9">
       <c r="A365" s="9" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="B365" s="36"/>
       <c r="C365" s="36"/>
@@ -12264,7 +12580,7 @@
     </row>
     <row r="366" spans="1:9">
       <c r="A366" s="9" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="B366" s="36"/>
       <c r="C366" s="36"/>
@@ -12277,7 +12593,7 @@
     </row>
     <row r="367" spans="1:9">
       <c r="A367" s="9" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="B367" s="36"/>
       <c r="C367" s="36"/>
@@ -12290,7 +12606,7 @@
     </row>
     <row r="368" spans="1:9">
       <c r="A368" s="9" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="B368" s="36"/>
       <c r="C368" s="36"/>
@@ -12303,7 +12619,7 @@
     </row>
     <row r="369" spans="1:9">
       <c r="A369" s="9" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="B369" s="36"/>
       <c r="C369" s="36"/>
@@ -12316,7 +12632,7 @@
     </row>
     <row r="370" spans="1:9">
       <c r="A370" s="9" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B370" s="36"/>
       <c r="C370" s="36"/>
@@ -12329,7 +12645,7 @@
     </row>
     <row r="371" spans="1:9">
       <c r="A371" s="9" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B371" s="36"/>
       <c r="C371" s="36"/>
@@ -12342,7 +12658,7 @@
     </row>
     <row r="372" spans="1:9">
       <c r="A372" s="9" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B372" s="36"/>
       <c r="C372" s="36"/>
@@ -12355,7 +12671,7 @@
     </row>
     <row r="373" spans="1:9">
       <c r="A373" s="9" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="B373" s="36"/>
       <c r="C373" s="36"/>
@@ -12368,7 +12684,7 @@
     </row>
     <row r="374" spans="1:9">
       <c r="A374" s="9" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B374" s="36"/>
       <c r="C374" s="36"/>
@@ -12381,7 +12697,7 @@
     </row>
     <row r="375" spans="1:9">
       <c r="A375" s="9" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B375" s="36"/>
       <c r="C375" s="36"/>
@@ -12394,7 +12710,7 @@
     </row>
     <row r="376" spans="1:9">
       <c r="A376" s="9" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B376" s="36"/>
       <c r="C376" s="36"/>
@@ -12407,7 +12723,7 @@
     </row>
     <row r="377" spans="1:9">
       <c r="A377" s="9" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B377" s="36"/>
       <c r="C377" s="36"/>
@@ -12420,7 +12736,7 @@
     </row>
     <row r="378" spans="1:9">
       <c r="A378" s="9" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B378" s="36"/>
       <c r="C378" s="36"/>
@@ -12433,7 +12749,7 @@
     </row>
     <row r="379" spans="1:9">
       <c r="A379" s="9" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B379" s="36"/>
       <c r="C379" s="36"/>
@@ -12446,7 +12762,7 @@
     </row>
     <row r="380" spans="1:9">
       <c r="A380" s="9" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B380" s="36"/>
       <c r="C380" s="36"/>
@@ -12459,7 +12775,7 @@
     </row>
     <row r="381" spans="1:9">
       <c r="A381" s="9" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B381" s="36"/>
       <c r="C381" s="36"/>
@@ -12472,7 +12788,7 @@
     </row>
     <row r="382" spans="1:9">
       <c r="A382" s="9" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="B382" s="36"/>
       <c r="C382" s="36"/>
@@ -12485,7 +12801,7 @@
     </row>
     <row r="383" spans="1:9">
       <c r="A383" s="9" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="B383" s="36"/>
       <c r="C383" s="36"/>
@@ -12498,7 +12814,7 @@
     </row>
     <row r="384" spans="1:9">
       <c r="A384" s="9" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B384" s="36"/>
       <c r="C384" s="36"/>
@@ -12511,7 +12827,7 @@
     </row>
     <row r="385" spans="1:9">
       <c r="A385" s="9" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="B385" s="36"/>
       <c r="C385" s="36"/>
@@ -12524,7 +12840,7 @@
     </row>
     <row r="386" spans="1:9">
       <c r="A386" s="9" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B386" s="36"/>
       <c r="C386" s="36"/>
@@ -12537,7 +12853,7 @@
     </row>
     <row r="387" spans="1:9">
       <c r="A387" s="9" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="B387" s="36"/>
       <c r="C387" s="36"/>
@@ -12550,7 +12866,7 @@
     </row>
     <row r="388" spans="1:9">
       <c r="A388" s="9" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B388" s="36"/>
       <c r="C388" s="36"/>
@@ -12563,7 +12879,7 @@
     </row>
     <row r="389" spans="1:9">
       <c r="A389" s="9" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="B389" s="36"/>
       <c r="C389" s="36"/>
@@ -12576,7 +12892,7 @@
     </row>
     <row r="390" spans="1:9">
       <c r="A390" s="9" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="B390" s="36"/>
       <c r="C390" s="36"/>
@@ -12589,7 +12905,7 @@
     </row>
     <row r="391" spans="1:9">
       <c r="A391" s="9" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="B391" s="36"/>
       <c r="C391" s="36"/>
@@ -12602,7 +12918,7 @@
     </row>
     <row r="392" spans="1:9">
       <c r="A392" s="9" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="B392" s="36"/>
       <c r="C392" s="36"/>
@@ -12615,7 +12931,7 @@
     </row>
     <row r="393" spans="1:9">
       <c r="A393" s="9" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B393" s="36"/>
       <c r="C393" s="36"/>

--- a/产品规格.xlsx
+++ b/产品规格.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1297" uniqueCount="984">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1301" uniqueCount="981">
   <si>
     <t>17.5*3*27</t>
   </si>
@@ -1228,9 +1228,6 @@
   </si>
   <si>
     <t>T400王者归来</t>
-  </si>
-  <si>
-    <t>18*3*47</t>
   </si>
   <si>
     <t>XC158</t>
@@ -2126,10 +2123,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>张18962500118 盛泽温州商区13幢1号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>XC325</t>
   </si>
   <si>
@@ -2366,6 +2359,10 @@
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
+    <t>17*3*44</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
     <t>25梭T400无捻牛津</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
@@ -2618,10 +2615,6 @@
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>17.5*3*35</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
     <t>40S*150酷丝绵 大钻石斜</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
@@ -2694,10 +2687,6 @@
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>120*35S</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
     <t>米克375</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
@@ -2758,10 +2747,6 @@
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>40S*75T400</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
     <t>40S*150 酷丝棉3/1斜 31</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
@@ -2802,10 +2787,6 @@
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>40S*150*2T400</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">40S*75T 酷丝棉平纹 33S </t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
@@ -2970,10 +2951,6 @@
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>13.5*4*35</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
     <t>40S*150T800</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
@@ -3063,10 +3040,6 @@
   </si>
   <si>
     <t>网纹3/3-180</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>17*4*44</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
@@ -3132,15 +3105,11 @@
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>14*4*26.5</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
     <t>40S*35S*2</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>白坯365克</t>
+    <t>白坯368克</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
@@ -3184,15 +3153,15 @@
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>240-钛金棉</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>17.5*3*31</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>白坯310克</t>
+    <t>230-钛金棉</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>17*3*31</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>白坯300克</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
@@ -3202,6 +3171,40 @@
   <si>
     <t>16*4*31</t>
     <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>登山布</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>12.5*4*215*44</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>100*75*450</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>白坯3</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>10克</t>
+    </r>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>张：18962500118  盛泽温州商区13幢1号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -4045,54 +4048,54 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
+        <v>689</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>692</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>693</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>694</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>695</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>696</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>697</v>
       </c>
-      <c r="I1" s="3" t="s">
-        <v>698</v>
-      </c>
       <c r="J1" s="5" t="s">
+        <v>687</v>
+      </c>
+      <c r="K1" s="5" t="s">
         <v>688</v>
       </c>
-      <c r="K1" s="5" t="s">
-        <v>689</v>
-      </c>
       <c r="L1" s="5" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="9" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="C2" s="10" t="s">
         <v>0</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="E2" s="10">
         <v>79</v>
@@ -4106,13 +4109,13 @@
       </c>
       <c r="I2" s="11"/>
       <c r="J2" s="7" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="L2" s="8" t="s">
-        <v>701</v>
+        <v>980</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -4779,7 +4782,7 @@
         <v>68</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="D29" s="10" t="s">
         <v>46</v>
@@ -4804,7 +4807,7 @@
         <v>70</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="D30" s="10" t="s">
         <v>46</v>
@@ -5456,7 +5459,7 @@
         <v>137</v>
       </c>
       <c r="C56" s="13" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="D56" s="13" t="s">
         <v>135</v>
@@ -5983,7 +5986,7 @@
         <v>193</v>
       </c>
       <c r="C77" s="10" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="D77" s="10" t="s">
         <v>144</v>
@@ -6146,7 +6149,7 @@
         <v>165</v>
       </c>
       <c r="H83" s="10">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="I83" s="11"/>
     </row>
@@ -7333,7 +7336,7 @@
         <v>330</v>
       </c>
       <c r="C131" s="24" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="D131" s="24" t="s">
         <v>148</v>
@@ -7346,7 +7349,7 @@
         <v>165</v>
       </c>
       <c r="H131" s="24">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="I131" s="11"/>
     </row>
@@ -7594,7 +7597,7 @@
         <v>165</v>
       </c>
       <c r="H141" s="26">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="I141" s="11"/>
     </row>
@@ -8018,7 +8021,7 @@
         <v>403</v>
       </c>
       <c r="C158" s="27" t="s">
-        <v>404</v>
+        <v>776</v>
       </c>
       <c r="D158" s="27" t="s">
         <v>393</v>
@@ -8039,13 +8042,13 @@
     </row>
     <row r="159" spans="1:9">
       <c r="A159" s="9" t="s">
+        <v>404</v>
+      </c>
+      <c r="B159" s="10" t="s">
         <v>405</v>
       </c>
-      <c r="B159" s="10" t="s">
+      <c r="C159" s="10" t="s">
         <v>406</v>
-      </c>
-      <c r="C159" s="10" t="s">
-        <v>407</v>
       </c>
       <c r="D159" s="10" t="s">
         <v>135</v>
@@ -8064,16 +8067,16 @@
     </row>
     <row r="160" spans="1:9">
       <c r="A160" s="9" t="s">
+        <v>407</v>
+      </c>
+      <c r="B160" s="10" t="s">
         <v>408</v>
       </c>
-      <c r="B160" s="10" t="s">
+      <c r="C160" s="10" t="s">
         <v>409</v>
       </c>
-      <c r="C160" s="10" t="s">
+      <c r="D160" s="10" t="s">
         <v>410</v>
-      </c>
-      <c r="D160" s="10" t="s">
-        <v>411</v>
       </c>
       <c r="E160" s="10">
         <v>85</v>
@@ -8089,16 +8092,16 @@
     </row>
     <row r="161" spans="1:9">
       <c r="A161" s="9" t="s">
+        <v>411</v>
+      </c>
+      <c r="B161" s="22" t="s">
+        <v>777</v>
+      </c>
+      <c r="C161" s="22" t="s">
         <v>412</v>
       </c>
-      <c r="B161" s="22" t="s">
-        <v>778</v>
-      </c>
-      <c r="C161" s="22" t="s">
+      <c r="D161" s="22" t="s">
         <v>413</v>
-      </c>
-      <c r="D161" s="22" t="s">
-        <v>414</v>
       </c>
       <c r="E161" s="22">
         <v>104</v>
@@ -8116,16 +8119,16 @@
     </row>
     <row r="162" spans="1:9">
       <c r="A162" s="9" t="s">
+        <v>414</v>
+      </c>
+      <c r="B162" s="22" t="s">
         <v>415</v>
       </c>
-      <c r="B162" s="22" t="s">
+      <c r="C162" s="22" t="s">
         <v>416</v>
       </c>
-      <c r="C162" s="22" t="s">
-        <v>417</v>
-      </c>
       <c r="D162" s="22" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E162" s="22">
         <v>117</v>
@@ -8143,16 +8146,16 @@
     </row>
     <row r="163" spans="1:9">
       <c r="A163" s="9" t="s">
+        <v>417</v>
+      </c>
+      <c r="B163" s="22" t="s">
         <v>418</v>
       </c>
-      <c r="B163" s="22" t="s">
+      <c r="C163" s="22" t="s">
         <v>419</v>
       </c>
-      <c r="C163" s="22" t="s">
-        <v>420</v>
-      </c>
       <c r="D163" s="22" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E163" s="22">
         <v>117</v>
@@ -8170,16 +8173,16 @@
     </row>
     <row r="164" spans="1:9">
       <c r="A164" s="9" t="s">
+        <v>420</v>
+      </c>
+      <c r="B164" s="22" t="s">
+        <v>778</v>
+      </c>
+      <c r="C164" s="22" t="s">
         <v>421</v>
       </c>
-      <c r="B164" s="22" t="s">
-        <v>779</v>
-      </c>
-      <c r="C164" s="22" t="s">
-        <v>422</v>
-      </c>
       <c r="D164" s="22" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E164" s="22">
         <v>110</v>
@@ -8197,16 +8200,16 @@
     </row>
     <row r="165" spans="1:9">
       <c r="A165" s="9" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B165" s="22" t="s">
+        <v>779</v>
+      </c>
+      <c r="C165" s="22" t="s">
         <v>780</v>
       </c>
-      <c r="C165" s="22" t="s">
-        <v>781</v>
-      </c>
       <c r="D165" s="22" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E165" s="22">
         <v>108</v>
@@ -8224,7 +8227,7 @@
     </row>
     <row r="166" spans="1:9">
       <c r="A166" s="9" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B166" s="30"/>
       <c r="C166" s="30"/>
@@ -8237,16 +8240,16 @@
     </row>
     <row r="167" spans="1:9">
       <c r="A167" s="9" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B167" s="18" t="s">
+        <v>781</v>
+      </c>
+      <c r="C167" s="18" t="s">
         <v>782</v>
       </c>
-      <c r="C167" s="18" t="s">
+      <c r="D167" s="18" t="s">
         <v>783</v>
-      </c>
-      <c r="D167" s="18" t="s">
-        <v>784</v>
       </c>
       <c r="E167" s="18">
         <v>80</v>
@@ -8264,16 +8267,16 @@
     </row>
     <row r="168" spans="1:9">
       <c r="A168" s="9" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B168" s="18" t="s">
+        <v>784</v>
+      </c>
+      <c r="C168" s="18" t="s">
         <v>785</v>
       </c>
-      <c r="C168" s="18" t="s">
+      <c r="D168" s="18" t="s">
         <v>786</v>
-      </c>
-      <c r="D168" s="18" t="s">
-        <v>787</v>
       </c>
       <c r="E168" s="18">
         <v>110</v>
@@ -8291,16 +8294,16 @@
     </row>
     <row r="169" spans="1:9">
       <c r="A169" s="31" t="s">
+        <v>426</v>
+      </c>
+      <c r="B169" s="18" t="s">
+        <v>787</v>
+      </c>
+      <c r="C169" s="18" t="s">
         <v>427</v>
       </c>
-      <c r="B169" s="18" t="s">
-        <v>788</v>
-      </c>
-      <c r="C169" s="18" t="s">
+      <c r="D169" s="18" t="s">
         <v>428</v>
-      </c>
-      <c r="D169" s="18" t="s">
-        <v>429</v>
       </c>
       <c r="E169" s="18">
         <v>83</v>
@@ -8318,16 +8321,16 @@
     </row>
     <row r="170" spans="1:9">
       <c r="A170" s="31" t="s">
+        <v>429</v>
+      </c>
+      <c r="B170" s="18" t="s">
+        <v>788</v>
+      </c>
+      <c r="C170" s="18" t="s">
         <v>430</v>
       </c>
-      <c r="B170" s="18" t="s">
-        <v>789</v>
-      </c>
-      <c r="C170" s="18" t="s">
-        <v>431</v>
-      </c>
       <c r="D170" s="18" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E170" s="32">
         <v>110</v>
@@ -8345,16 +8348,16 @@
     </row>
     <row r="171" spans="1:9">
       <c r="A171" s="31" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B171" s="18" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="C171" s="18" t="s">
         <v>238</v>
       </c>
       <c r="D171" s="18" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E171" s="32">
         <v>112</v>
@@ -8372,16 +8375,16 @@
     </row>
     <row r="172" spans="1:9">
       <c r="A172" s="31" t="s">
+        <v>432</v>
+      </c>
+      <c r="B172" s="18" t="s">
         <v>433</v>
-      </c>
-      <c r="B172" s="18" t="s">
-        <v>434</v>
       </c>
       <c r="C172" s="18" t="s">
         <v>238</v>
       </c>
       <c r="D172" s="18" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E172" s="18">
         <v>112</v>
@@ -8399,16 +8402,16 @@
     </row>
     <row r="173" spans="1:9">
       <c r="A173" s="31" t="s">
+        <v>434</v>
+      </c>
+      <c r="B173" s="18" t="s">
+        <v>790</v>
+      </c>
+      <c r="C173" s="18" t="s">
         <v>435</v>
       </c>
-      <c r="B173" s="18" t="s">
-        <v>791</v>
-      </c>
-      <c r="C173" s="18" t="s">
+      <c r="D173" s="18" t="s">
         <v>436</v>
-      </c>
-      <c r="D173" s="18" t="s">
-        <v>437</v>
       </c>
       <c r="E173" s="18">
         <v>102</v>
@@ -8426,16 +8429,16 @@
     </row>
     <row r="174" spans="1:9">
       <c r="A174" s="31" t="s">
+        <v>437</v>
+      </c>
+      <c r="B174" s="18" t="s">
+        <v>791</v>
+      </c>
+      <c r="C174" s="18" t="s">
         <v>438</v>
       </c>
-      <c r="B174" s="18" t="s">
-        <v>792</v>
-      </c>
-      <c r="C174" s="18" t="s">
-        <v>439</v>
-      </c>
       <c r="D174" s="18" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E174" s="32">
         <v>130</v>
@@ -8447,22 +8450,22 @@
         <v>215</v>
       </c>
       <c r="H174" s="32">
-        <v>4</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="I174" s="32"/>
     </row>
     <row r="175" spans="1:9">
       <c r="A175" s="31" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B175" s="18" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="C175" s="18" t="s">
         <v>32</v>
       </c>
       <c r="D175" s="18" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E175" s="32">
         <v>135</v>
@@ -8474,22 +8477,22 @@
         <v>215</v>
       </c>
       <c r="H175" s="32">
-        <v>4.0999999999999996</v>
+        <v>4.2</v>
       </c>
       <c r="I175" s="32"/>
     </row>
     <row r="176" spans="1:9">
       <c r="A176" s="31" t="s">
+        <v>440</v>
+      </c>
+      <c r="B176" s="18" t="s">
         <v>441</v>
-      </c>
-      <c r="B176" s="18" t="s">
-        <v>442</v>
       </c>
       <c r="C176" s="18" t="s">
         <v>32</v>
       </c>
       <c r="D176" s="18" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E176" s="18">
         <v>135</v>
@@ -8501,22 +8504,22 @@
         <v>215</v>
       </c>
       <c r="H176" s="18">
-        <v>4.0999999999999996</v>
+        <v>4.2</v>
       </c>
       <c r="I176" s="32"/>
     </row>
     <row r="177" spans="1:9">
       <c r="A177" s="31" t="s">
+        <v>442</v>
+      </c>
+      <c r="B177" s="18" t="s">
         <v>443</v>
       </c>
-      <c r="B177" s="18" t="s">
+      <c r="C177" s="18" t="s">
         <v>444</v>
       </c>
-      <c r="C177" s="18" t="s">
-        <v>445</v>
-      </c>
       <c r="D177" s="18" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E177" s="18">
         <v>150</v>
@@ -8534,16 +8537,16 @@
     </row>
     <row r="178" spans="1:9">
       <c r="A178" s="31" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B178" s="18" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="C178" s="18" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D178" s="18" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E178" s="18">
         <v>106</v>
@@ -8561,16 +8564,16 @@
     </row>
     <row r="179" spans="1:9">
       <c r="A179" s="31" t="s">
+        <v>446</v>
+      </c>
+      <c r="B179" s="18" t="s">
         <v>447</v>
       </c>
-      <c r="B179" s="18" t="s">
+      <c r="C179" s="18" t="s">
         <v>448</v>
       </c>
-      <c r="C179" s="18" t="s">
-        <v>449</v>
-      </c>
       <c r="D179" s="33" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E179" s="18">
         <v>110</v>
@@ -8588,16 +8591,16 @@
     </row>
     <row r="180" spans="1:9">
       <c r="A180" s="31" t="s">
+        <v>449</v>
+      </c>
+      <c r="B180" s="18" t="s">
+        <v>794</v>
+      </c>
+      <c r="C180" s="18" t="s">
         <v>450</v>
       </c>
-      <c r="B180" s="18" t="s">
-        <v>795</v>
-      </c>
-      <c r="C180" s="18" t="s">
-        <v>451</v>
-      </c>
       <c r="D180" s="18" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E180" s="18">
         <v>96</v>
@@ -8615,16 +8618,16 @@
     </row>
     <row r="181" spans="1:9">
       <c r="A181" s="9" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B181" s="18" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="C181" s="18" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D181" s="18" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E181" s="18">
         <v>150</v>
@@ -8642,16 +8645,16 @@
     </row>
     <row r="182" spans="1:9">
       <c r="A182" s="9" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B182" s="34" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="C182" s="34" t="s">
         <v>309</v>
       </c>
       <c r="D182" s="34" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E182" s="34">
         <v>108</v>
@@ -8669,16 +8672,16 @@
     </row>
     <row r="183" spans="1:9">
       <c r="A183" s="9" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B183" s="34" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="C183" s="34" t="s">
         <v>309</v>
       </c>
       <c r="D183" s="34" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E183" s="34">
         <v>108</v>
@@ -8696,16 +8699,16 @@
     </row>
     <row r="184" spans="1:9">
       <c r="A184" s="9" t="s">
+        <v>455</v>
+      </c>
+      <c r="B184" s="35" t="s">
         <v>456</v>
       </c>
-      <c r="B184" s="35" t="s">
+      <c r="C184" s="35" t="s">
         <v>457</v>
       </c>
-      <c r="C184" s="35" t="s">
+      <c r="D184" s="35" t="s">
         <v>458</v>
-      </c>
-      <c r="D184" s="35" t="s">
-        <v>459</v>
       </c>
       <c r="E184" s="35">
         <v>150</v>
@@ -8723,16 +8726,16 @@
     </row>
     <row r="185" spans="1:9">
       <c r="A185" s="9" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B185" s="18" t="s">
+        <v>798</v>
+      </c>
+      <c r="C185" s="18" t="s">
         <v>799</v>
       </c>
-      <c r="C185" s="18" t="s">
+      <c r="D185" s="18" t="s">
         <v>800</v>
-      </c>
-      <c r="D185" s="18" t="s">
-        <v>801</v>
       </c>
       <c r="E185" s="18">
         <v>112</v>
@@ -8750,16 +8753,16 @@
     </row>
     <row r="186" spans="1:9">
       <c r="A186" s="9" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B186" s="34" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="C186" s="34" t="s">
         <v>309</v>
       </c>
       <c r="D186" s="34" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E186" s="34">
         <v>108</v>
@@ -8777,16 +8780,16 @@
     </row>
     <row r="187" spans="1:9">
       <c r="A187" s="9" t="s">
+        <v>802</v>
+      </c>
+      <c r="B187" s="18" t="s">
+        <v>441</v>
+      </c>
+      <c r="C187" s="18" t="s">
         <v>803</v>
       </c>
-      <c r="B187" s="18" t="s">
-        <v>442</v>
-      </c>
-      <c r="C187" s="18" t="s">
-        <v>804</v>
-      </c>
       <c r="D187" s="18" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E187" s="18">
         <v>150</v>
@@ -8804,16 +8807,16 @@
     </row>
     <row r="188" spans="1:9">
       <c r="A188" s="9" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B188" s="18" t="s">
+        <v>804</v>
+      </c>
+      <c r="C188" s="18" t="s">
         <v>805</v>
       </c>
-      <c r="C188" s="18" t="s">
+      <c r="D188" s="18" t="s">
         <v>806</v>
-      </c>
-      <c r="D188" s="18" t="s">
-        <v>807</v>
       </c>
       <c r="E188" s="18">
         <v>110</v>
@@ -8831,16 +8834,16 @@
     </row>
     <row r="189" spans="1:9">
       <c r="A189" s="9" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B189" s="18" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="C189" s="18" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D189" s="18" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E189" s="18">
         <v>150</v>
@@ -8858,16 +8861,16 @@
     </row>
     <row r="190" spans="1:9">
       <c r="A190" s="9" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B190" s="10" t="s">
+        <v>808</v>
+      </c>
+      <c r="C190" s="10" t="s">
         <v>809</v>
       </c>
-      <c r="C190" s="10" t="s">
+      <c r="D190" s="10" t="s">
         <v>810</v>
-      </c>
-      <c r="D190" s="10" t="s">
-        <v>811</v>
       </c>
       <c r="E190" s="11">
         <v>152</v>
@@ -8879,22 +8882,22 @@
         <v>215</v>
       </c>
       <c r="H190" s="10">
-        <v>5.0999999999999996</v>
+        <v>5.4</v>
       </c>
       <c r="I190" s="11"/>
     </row>
     <row r="191" spans="1:9">
       <c r="A191" s="9" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B191" s="18" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="C191" s="18" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="D191" s="18" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E191" s="32">
         <v>150</v>
@@ -8912,7 +8915,7 @@
     </row>
     <row r="192" spans="1:9">
       <c r="A192" s="9" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B192" s="27"/>
       <c r="C192" s="27"/>
@@ -8925,7 +8928,7 @@
     </row>
     <row r="193" spans="1:9">
       <c r="A193" s="9" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B193" s="27"/>
       <c r="C193" s="27"/>
@@ -8938,13 +8941,13 @@
     </row>
     <row r="194" spans="1:9">
       <c r="A194" s="9" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B194" s="41" t="s">
+        <v>811</v>
+      </c>
+      <c r="C194" s="42" t="s">
         <v>812</v>
-      </c>
-      <c r="C194" s="42" t="s">
-        <v>813</v>
       </c>
       <c r="D194" s="43" t="s">
         <v>148</v>
@@ -8965,13 +8968,13 @@
     </row>
     <row r="195" spans="1:9">
       <c r="A195" s="9" t="s">
+        <v>468</v>
+      </c>
+      <c r="B195" s="41" t="s">
+        <v>813</v>
+      </c>
+      <c r="C195" s="42" t="s">
         <v>469</v>
-      </c>
-      <c r="B195" s="41" t="s">
-        <v>814</v>
-      </c>
-      <c r="C195" s="42" t="s">
-        <v>470</v>
       </c>
       <c r="D195" s="43" t="s">
         <v>39</v>
@@ -8992,16 +8995,16 @@
     </row>
     <row r="196" spans="1:9">
       <c r="A196" s="9" t="s">
+        <v>470</v>
+      </c>
+      <c r="B196" s="45" t="s">
+        <v>814</v>
+      </c>
+      <c r="C196" s="45" t="s">
+        <v>815</v>
+      </c>
+      <c r="D196" s="45" t="s">
         <v>471</v>
-      </c>
-      <c r="B196" s="45" t="s">
-        <v>815</v>
-      </c>
-      <c r="C196" s="45" t="s">
-        <v>816</v>
-      </c>
-      <c r="D196" s="45" t="s">
-        <v>472</v>
       </c>
       <c r="E196" s="45">
         <v>105</v>
@@ -9019,13 +9022,13 @@
     </row>
     <row r="197" spans="1:9">
       <c r="A197" s="9" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B197" s="45" t="s">
+        <v>816</v>
+      </c>
+      <c r="C197" s="45" t="s">
         <v>817</v>
-      </c>
-      <c r="C197" s="45" t="s">
-        <v>818</v>
       </c>
       <c r="D197" s="45" t="s">
         <v>386</v>
@@ -9046,16 +9049,16 @@
     </row>
     <row r="198" spans="1:9">
       <c r="A198" s="9" t="s">
+        <v>473</v>
+      </c>
+      <c r="B198" s="45" t="s">
+        <v>818</v>
+      </c>
+      <c r="C198" s="45" t="s">
         <v>474</v>
       </c>
-      <c r="B198" s="45" t="s">
-        <v>819</v>
-      </c>
-      <c r="C198" s="45" t="s">
+      <c r="D198" s="45" t="s">
         <v>475</v>
-      </c>
-      <c r="D198" s="45" t="s">
-        <v>476</v>
       </c>
       <c r="E198" s="45">
         <v>129</v>
@@ -9073,16 +9076,16 @@
     </row>
     <row r="199" spans="1:9">
       <c r="A199" s="9" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B199" s="45" t="s">
+        <v>819</v>
+      </c>
+      <c r="C199" s="45" t="s">
         <v>820</v>
       </c>
-      <c r="C199" s="45" t="s">
+      <c r="D199" s="45" t="s">
         <v>821</v>
-      </c>
-      <c r="D199" s="45" t="s">
-        <v>822</v>
       </c>
       <c r="E199" s="45">
         <v>95</v>
@@ -9100,7 +9103,7 @@
     </row>
     <row r="200" spans="1:9">
       <c r="A200" s="9" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B200" s="30"/>
       <c r="C200" s="30"/>
@@ -9113,7 +9116,7 @@
     </row>
     <row r="201" spans="1:9">
       <c r="A201" s="9" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B201" s="10"/>
       <c r="C201" s="10"/>
@@ -9126,7 +9129,7 @@
     </row>
     <row r="202" spans="1:9">
       <c r="A202" s="9" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B202" s="10"/>
       <c r="C202" s="10"/>
@@ -9139,7 +9142,7 @@
     </row>
     <row r="203" spans="1:9">
       <c r="A203" s="9" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B203" s="10"/>
       <c r="C203" s="10"/>
@@ -9152,16 +9155,16 @@
     </row>
     <row r="204" spans="1:9">
       <c r="A204" s="9" t="s">
+        <v>481</v>
+      </c>
+      <c r="B204" s="24" t="s">
         <v>482</v>
       </c>
-      <c r="B204" s="24" t="s">
+      <c r="C204" s="24" t="s">
         <v>483</v>
       </c>
-      <c r="C204" s="24" t="s">
+      <c r="D204" s="24" t="s">
         <v>484</v>
-      </c>
-      <c r="D204" s="24" t="s">
-        <v>485</v>
       </c>
       <c r="E204" s="24"/>
       <c r="F204" s="47">
@@ -9177,16 +9180,16 @@
     </row>
     <row r="205" spans="1:9">
       <c r="A205" s="9" t="s">
+        <v>485</v>
+      </c>
+      <c r="B205" s="24" t="s">
         <v>486</v>
       </c>
-      <c r="B205" s="24" t="s">
+      <c r="C205" s="24" t="s">
         <v>487</v>
       </c>
-      <c r="C205" s="24" t="s">
+      <c r="D205" s="48" t="s">
         <v>488</v>
-      </c>
-      <c r="D205" s="48" t="s">
-        <v>489</v>
       </c>
       <c r="E205" s="24">
         <v>47</v>
@@ -9204,16 +9207,16 @@
     </row>
     <row r="206" spans="1:9">
       <c r="A206" s="9" t="s">
+        <v>489</v>
+      </c>
+      <c r="B206" s="24" t="s">
         <v>490</v>
       </c>
-      <c r="B206" s="24" t="s">
+      <c r="C206" s="24" t="s">
         <v>491</v>
       </c>
-      <c r="C206" s="24" t="s">
-        <v>492</v>
-      </c>
       <c r="D206" s="48" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E206" s="24">
         <v>47</v>
@@ -9231,10 +9234,10 @@
     </row>
     <row r="207" spans="1:9">
       <c r="A207" s="9" t="s">
+        <v>492</v>
+      </c>
+      <c r="B207" s="27" t="s">
         <v>493</v>
-      </c>
-      <c r="B207" s="27" t="s">
-        <v>494</v>
       </c>
       <c r="C207" s="10" t="s">
         <v>53</v>
@@ -9254,22 +9257,22 @@
     </row>
     <row r="208" spans="1:9">
       <c r="A208" s="9" t="s">
+        <v>494</v>
+      </c>
+      <c r="B208" s="27" t="s">
         <v>495</v>
       </c>
-      <c r="B208" s="27" t="s">
-        <v>496</v>
-      </c>
       <c r="C208" s="10" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="D208" s="10" t="s">
         <v>39</v>
       </c>
       <c r="E208" s="10">
+        <v>125</v>
+      </c>
+      <c r="F208" s="36">
         <v>145</v>
-      </c>
-      <c r="F208" s="36">
-        <v>150</v>
       </c>
       <c r="G208" s="11">
         <v>170</v>
@@ -9281,10 +9284,10 @@
     </row>
     <row r="209" spans="1:9">
       <c r="A209" s="9" t="s">
+        <v>496</v>
+      </c>
+      <c r="B209" s="10" t="s">
         <v>497</v>
-      </c>
-      <c r="B209" s="10" t="s">
-        <v>498</v>
       </c>
       <c r="C209" s="10" t="s">
         <v>153</v>
@@ -9304,7 +9307,7 @@
     </row>
     <row r="210" spans="1:9">
       <c r="A210" s="9" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B210" s="10"/>
       <c r="C210" s="10"/>
@@ -9317,13 +9320,13 @@
     </row>
     <row r="211" spans="1:9">
       <c r="A211" s="9" t="s">
+        <v>499</v>
+      </c>
+      <c r="B211" s="10" t="s">
         <v>500</v>
       </c>
-      <c r="B211" s="10" t="s">
-        <v>501</v>
-      </c>
       <c r="C211" s="10" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="D211" s="10" t="s">
         <v>39</v>
@@ -9342,13 +9345,13 @@
     </row>
     <row r="212" spans="1:9">
       <c r="A212" s="9" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B212" s="35" t="s">
+        <v>824</v>
+      </c>
+      <c r="C212" s="35" t="s">
         <v>825</v>
-      </c>
-      <c r="C212" s="35" t="s">
-        <v>826</v>
       </c>
       <c r="D212" s="35" t="s">
         <v>144</v>
@@ -9367,16 +9370,16 @@
     </row>
     <row r="213" spans="1:9">
       <c r="A213" s="9" t="s">
+        <v>502</v>
+      </c>
+      <c r="B213" s="10" t="s">
         <v>503</v>
       </c>
-      <c r="B213" s="10" t="s">
+      <c r="C213" s="10" t="s">
         <v>504</v>
       </c>
-      <c r="C213" s="10" t="s">
-        <v>505</v>
-      </c>
       <c r="D213" s="10" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E213" s="10">
         <v>52</v>
@@ -9394,13 +9397,13 @@
     </row>
     <row r="214" spans="1:9">
       <c r="A214" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="B214" s="10" t="s">
         <v>506</v>
       </c>
-      <c r="B214" s="10" t="s">
-        <v>507</v>
-      </c>
       <c r="C214" s="35" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="D214" s="35" t="s">
         <v>144</v>
@@ -9419,7 +9422,7 @@
     </row>
     <row r="215" spans="1:9">
       <c r="A215" s="9" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B215" s="30"/>
       <c r="C215" s="30"/>
@@ -9432,16 +9435,16 @@
     </row>
     <row r="216" spans="1:9">
       <c r="A216" s="9" t="s">
+        <v>508</v>
+      </c>
+      <c r="B216" s="10" t="s">
         <v>509</v>
       </c>
-      <c r="B216" s="10" t="s">
+      <c r="C216" s="10" t="s">
         <v>510</v>
       </c>
-      <c r="C216" s="10" t="s">
+      <c r="D216" s="10" t="s">
         <v>511</v>
-      </c>
-      <c r="D216" s="10" t="s">
-        <v>512</v>
       </c>
       <c r="E216" s="10">
         <v>69</v>
@@ -9457,7 +9460,7 @@
     </row>
     <row r="217" spans="1:9">
       <c r="A217" s="9" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B217" s="30"/>
       <c r="C217" s="30"/>
@@ -9470,7 +9473,7 @@
     </row>
     <row r="218" spans="1:9">
       <c r="A218" s="9" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B218" s="10"/>
       <c r="C218" s="10"/>
@@ -9483,16 +9486,16 @@
     </row>
     <row r="219" spans="1:9">
       <c r="A219" s="9" t="s">
+        <v>514</v>
+      </c>
+      <c r="B219" s="35" t="s">
         <v>515</v>
       </c>
-      <c r="B219" s="35" t="s">
+      <c r="C219" s="35" t="s">
         <v>516</v>
       </c>
-      <c r="C219" s="35" t="s">
+      <c r="D219" s="35" t="s">
         <v>517</v>
-      </c>
-      <c r="D219" s="35" t="s">
-        <v>518</v>
       </c>
       <c r="E219" s="35">
         <v>90</v>
@@ -9510,16 +9513,16 @@
     </row>
     <row r="220" spans="1:9">
       <c r="A220" s="9" t="s">
+        <v>518</v>
+      </c>
+      <c r="B220" s="10" t="s">
+        <v>826</v>
+      </c>
+      <c r="C220" s="10" t="s">
+        <v>827</v>
+      </c>
+      <c r="D220" s="49" t="s">
         <v>519</v>
-      </c>
-      <c r="B220" s="10" t="s">
-        <v>827</v>
-      </c>
-      <c r="C220" s="10" t="s">
-        <v>828</v>
-      </c>
-      <c r="D220" s="49" t="s">
-        <v>520</v>
       </c>
       <c r="E220" s="10">
         <v>120</v>
@@ -9534,21 +9537,21 @@
         <v>3.4</v>
       </c>
       <c r="I220" s="11" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
     </row>
     <row r="221" spans="1:9">
       <c r="A221" s="9" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B221" s="10" t="s">
+        <v>829</v>
+      </c>
+      <c r="C221" s="10" t="s">
         <v>830</v>
       </c>
-      <c r="C221" s="10" t="s">
+      <c r="D221" s="49" t="s">
         <v>831</v>
-      </c>
-      <c r="D221" s="49" t="s">
-        <v>832</v>
       </c>
       <c r="E221" s="10">
         <v>100</v>
@@ -9563,21 +9566,21 @@
         <v>3.3</v>
       </c>
       <c r="I221" s="37" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
     </row>
     <row r="222" spans="1:9">
       <c r="A222" s="9" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B222" s="10" t="s">
+        <v>833</v>
+      </c>
+      <c r="C222" s="10" t="s">
         <v>834</v>
       </c>
-      <c r="C222" s="10" t="s">
+      <c r="D222" s="49" t="s">
         <v>835</v>
-      </c>
-      <c r="D222" s="49" t="s">
-        <v>836</v>
       </c>
       <c r="E222" s="10">
         <v>115</v>
@@ -9595,13 +9598,13 @@
     </row>
     <row r="223" spans="1:9">
       <c r="A223" s="9" t="s">
+        <v>522</v>
+      </c>
+      <c r="B223" s="35" t="s">
         <v>523</v>
       </c>
-      <c r="B223" s="35" t="s">
+      <c r="C223" s="35" t="s">
         <v>524</v>
-      </c>
-      <c r="C223" s="35" t="s">
-        <v>525</v>
       </c>
       <c r="D223" s="50" t="s">
         <v>4</v>
@@ -9622,16 +9625,16 @@
     </row>
     <row r="224" spans="1:9">
       <c r="A224" s="9" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B224" s="35" t="s">
+        <v>836</v>
+      </c>
+      <c r="C224" s="35" t="s">
         <v>837</v>
       </c>
-      <c r="C224" s="35" t="s">
+      <c r="D224" s="35" t="s">
         <v>838</v>
-      </c>
-      <c r="D224" s="35" t="s">
-        <v>839</v>
       </c>
       <c r="E224" s="35">
         <v>120</v>
@@ -9649,16 +9652,16 @@
     </row>
     <row r="225" spans="1:9">
       <c r="A225" s="9" t="s">
+        <v>526</v>
+      </c>
+      <c r="B225" s="27" t="s">
         <v>527</v>
       </c>
-      <c r="B225" s="27" t="s">
+      <c r="C225" s="35" t="s">
         <v>528</v>
       </c>
-      <c r="C225" s="35" t="s">
-        <v>529</v>
-      </c>
       <c r="D225" s="35" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E225" s="35">
         <v>135</v>
@@ -9676,16 +9679,16 @@
     </row>
     <row r="226" spans="1:9">
       <c r="A226" s="9" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B226" s="35" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C226" s="35" t="s">
-        <v>841</v>
+        <v>803</v>
       </c>
       <c r="D226" s="35" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E226" s="35">
         <v>145</v>
@@ -9703,16 +9706,16 @@
     </row>
     <row r="227" spans="1:9">
       <c r="A227" s="9" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B227" s="35" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="C227" s="35" t="s">
-        <v>841</v>
+        <v>803</v>
       </c>
       <c r="D227" s="35" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E227" s="35">
         <v>145</v>
@@ -9730,16 +9733,16 @@
     </row>
     <row r="228" spans="1:9">
       <c r="A228" s="9" t="s">
+        <v>531</v>
+      </c>
+      <c r="B228" s="35" t="s">
         <v>532</v>
       </c>
-      <c r="B228" s="35" t="s">
-        <v>533</v>
-      </c>
       <c r="C228" s="35" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D228" s="35" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E228" s="35">
         <v>150</v>
@@ -9757,16 +9760,16 @@
     </row>
     <row r="229" spans="1:9">
       <c r="A229" s="9" t="s">
+        <v>533</v>
+      </c>
+      <c r="B229" s="35" t="s">
         <v>534</v>
       </c>
-      <c r="B229" s="35" t="s">
-        <v>535</v>
-      </c>
       <c r="C229" s="35" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D229" s="35" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E229" s="35">
         <v>150</v>
@@ -9784,16 +9787,16 @@
     </row>
     <row r="230" spans="1:9">
       <c r="A230" s="9" t="s">
+        <v>535</v>
+      </c>
+      <c r="B230" s="51" t="s">
         <v>536</v>
       </c>
-      <c r="B230" s="51" t="s">
-        <v>537</v>
-      </c>
       <c r="C230" s="51" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="D230" s="51" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E230" s="51">
         <v>145</v>
@@ -9811,7 +9814,7 @@
     </row>
     <row r="231" spans="1:9">
       <c r="A231" s="9" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B231" s="18"/>
       <c r="C231" s="18"/>
@@ -9824,7 +9827,7 @@
     </row>
     <row r="232" spans="1:9">
       <c r="A232" s="9" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B232" s="35"/>
       <c r="C232" s="35"/>
@@ -9837,16 +9840,16 @@
     </row>
     <row r="233" spans="1:9">
       <c r="A233" s="9" t="s">
+        <v>539</v>
+      </c>
+      <c r="B233" s="35" t="s">
         <v>540</v>
       </c>
-      <c r="B233" s="35" t="s">
+      <c r="C233" s="35" t="s">
         <v>541</v>
       </c>
-      <c r="C233" s="35" t="s">
+      <c r="D233" s="35" t="s">
         <v>542</v>
-      </c>
-      <c r="D233" s="35" t="s">
-        <v>543</v>
       </c>
       <c r="E233" s="35"/>
       <c r="F233" s="36"/>
@@ -9860,16 +9863,16 @@
     </row>
     <row r="234" spans="1:9">
       <c r="A234" s="9" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B234" s="52" t="s">
+        <v>841</v>
+      </c>
+      <c r="C234" s="52" t="s">
+        <v>842</v>
+      </c>
+      <c r="D234" s="50" t="s">
         <v>843</v>
-      </c>
-      <c r="C234" s="52" t="s">
-        <v>844</v>
-      </c>
-      <c r="D234" s="50" t="s">
-        <v>845</v>
       </c>
       <c r="E234" s="52">
         <v>190</v>
@@ -9884,21 +9887,21 @@
         <v>5.8</v>
       </c>
       <c r="I234" s="54" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
     </row>
     <row r="235" spans="1:9">
       <c r="A235" s="9" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B235" s="51" t="s">
+        <v>845</v>
+      </c>
+      <c r="C235" s="51" t="s">
+        <v>846</v>
+      </c>
+      <c r="D235" s="51" t="s">
         <v>847</v>
-      </c>
-      <c r="C235" s="51" t="s">
-        <v>848</v>
-      </c>
-      <c r="D235" s="51" t="s">
-        <v>849</v>
       </c>
       <c r="E235" s="51">
         <v>155</v>
@@ -9913,12 +9916,12 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="I235" s="55" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="236" spans="1:9">
       <c r="A236" s="9" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B236" s="51"/>
       <c r="C236" s="51"/>
@@ -9931,16 +9934,16 @@
     </row>
     <row r="237" spans="1:9">
       <c r="A237" s="9" t="s">
+        <v>547</v>
+      </c>
+      <c r="B237" s="51" t="s">
+        <v>848</v>
+      </c>
+      <c r="C237" s="51" t="s">
         <v>548</v>
       </c>
-      <c r="B237" s="51" t="s">
-        <v>850</v>
-      </c>
-      <c r="C237" s="51" t="s">
-        <v>549</v>
-      </c>
       <c r="D237" s="51" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="E237" s="51">
         <v>155</v>
@@ -9955,21 +9958,21 @@
         <v>4.9000000000000004</v>
       </c>
       <c r="I237" s="55" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="238" spans="1:9">
       <c r="A238" s="9" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B238" s="51" t="s">
+        <v>850</v>
+      </c>
+      <c r="C238" s="51" t="s">
+        <v>851</v>
+      </c>
+      <c r="D238" s="51" t="s">
         <v>852</v>
-      </c>
-      <c r="C238" s="51" t="s">
-        <v>853</v>
-      </c>
-      <c r="D238" s="51" t="s">
-        <v>854</v>
       </c>
       <c r="E238" s="52">
         <v>190</v>
@@ -9984,21 +9987,21 @@
         <v>5.7</v>
       </c>
       <c r="I238" s="54" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="239" spans="1:9">
       <c r="A239" s="9" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B239" s="51" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="C239" s="51" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="D239" s="51" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="E239" s="52">
         <v>180</v>
@@ -10013,21 +10016,21 @@
         <v>5.5</v>
       </c>
       <c r="I239" s="54" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="240" spans="1:9">
       <c r="A240" s="9" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B240" s="51" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="C240" s="51" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="D240" s="51" t="s">
-        <v>860</v>
+        <v>852</v>
       </c>
       <c r="E240" s="52">
         <v>190</v>
@@ -10042,21 +10045,21 @@
         <v>5.6</v>
       </c>
       <c r="I240" s="54" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
     </row>
     <row r="241" spans="1:9">
       <c r="A241" s="9" t="s">
+        <v>552</v>
+      </c>
+      <c r="B241" s="51" t="s">
+        <v>859</v>
+      </c>
+      <c r="C241" s="51" t="s">
+        <v>860</v>
+      </c>
+      <c r="D241" s="11" t="s">
         <v>553</v>
-      </c>
-      <c r="B241" s="51" t="s">
-        <v>862</v>
-      </c>
-      <c r="C241" s="51" t="s">
-        <v>863</v>
-      </c>
-      <c r="D241" s="11" t="s">
-        <v>554</v>
       </c>
       <c r="E241" s="51">
         <v>150</v>
@@ -10068,24 +10071,24 @@
         <v>220</v>
       </c>
       <c r="H241" s="52">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I241" s="55" t="s">
-        <v>864</v>
+        <v>861</v>
       </c>
     </row>
     <row r="242" spans="1:9">
       <c r="A242" s="9" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B242" s="51" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="C242" s="51" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="D242" s="51" t="s">
-        <v>860</v>
+        <v>852</v>
       </c>
       <c r="E242" s="52">
         <v>160</v>
@@ -10100,21 +10103,21 @@
         <v>4.9000000000000004</v>
       </c>
       <c r="I242" s="54" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
     </row>
     <row r="243" spans="1:9">
       <c r="A243" s="9" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B243" s="51" t="s">
-        <v>868</v>
+        <v>865</v>
       </c>
       <c r="C243" s="51" t="s">
-        <v>869</v>
+        <v>866</v>
       </c>
       <c r="D243" s="51" t="s">
-        <v>870</v>
+        <v>867</v>
       </c>
       <c r="E243" s="52">
         <v>190</v>
@@ -10129,21 +10132,21 @@
         <v>5.6</v>
       </c>
       <c r="I243" s="54" t="s">
-        <v>871</v>
+        <v>868</v>
       </c>
     </row>
     <row r="244" spans="1:9">
       <c r="A244" s="9" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B244" s="51" t="s">
-        <v>872</v>
+        <v>869</v>
       </c>
       <c r="C244" s="51" t="s">
-        <v>873</v>
+        <v>870</v>
       </c>
       <c r="D244" s="51" t="s">
-        <v>870</v>
+        <v>867</v>
       </c>
       <c r="E244" s="51">
         <v>150</v>
@@ -10159,7 +10162,7 @@
     </row>
     <row r="245" spans="1:9">
       <c r="A245" s="9" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B245" s="38"/>
       <c r="C245" s="38"/>
@@ -10172,16 +10175,16 @@
     </row>
     <row r="246" spans="1:9">
       <c r="A246" s="9" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B246" s="18" t="s">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="C246" s="18" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="D246" s="33" t="s">
-        <v>876</v>
+        <v>800</v>
       </c>
       <c r="E246" s="18">
         <v>112</v>
@@ -10199,16 +10202,16 @@
     </row>
     <row r="247" spans="1:9">
       <c r="A247" s="31" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B247" s="18" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="C247" s="18" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="D247" s="33" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E247" s="18">
         <v>135</v>
@@ -10226,16 +10229,16 @@
     </row>
     <row r="248" spans="1:9">
       <c r="A248" s="31" t="s">
+        <v>560</v>
+      </c>
+      <c r="B248" s="18" t="s">
+        <v>874</v>
+      </c>
+      <c r="C248" s="18" t="s">
         <v>561</v>
       </c>
-      <c r="B248" s="18" t="s">
-        <v>878</v>
-      </c>
-      <c r="C248" s="18" t="s">
-        <v>562</v>
-      </c>
       <c r="D248" s="18" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E248" s="18">
         <v>160</v>
@@ -10253,16 +10256,16 @@
     </row>
     <row r="249" spans="1:9">
       <c r="A249" s="31" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B249" s="18" t="s">
-        <v>879</v>
+        <v>875</v>
       </c>
       <c r="C249" s="18" t="s">
-        <v>880</v>
+        <v>876</v>
       </c>
       <c r="D249" s="18" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E249" s="32">
         <v>105</v>
@@ -10280,16 +10283,16 @@
     </row>
     <row r="250" spans="1:9">
       <c r="A250" s="31" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B250" s="18" t="s">
-        <v>881</v>
+        <v>877</v>
       </c>
       <c r="C250" s="18" t="s">
         <v>153</v>
       </c>
       <c r="D250" s="18" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E250" s="32">
         <v>108</v>
@@ -10307,16 +10310,16 @@
     </row>
     <row r="251" spans="1:9">
       <c r="A251" s="31" t="s">
+        <v>564</v>
+      </c>
+      <c r="B251" s="18" t="s">
+        <v>878</v>
+      </c>
+      <c r="C251" s="18" t="s">
         <v>565</v>
       </c>
-      <c r="B251" s="18" t="s">
-        <v>882</v>
-      </c>
-      <c r="C251" s="18" t="s">
-        <v>566</v>
-      </c>
       <c r="D251" s="18" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E251" s="18">
         <v>116</v>
@@ -10334,16 +10337,16 @@
     </row>
     <row r="252" spans="1:9">
       <c r="A252" s="31" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B252" s="18" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
       <c r="C252" s="18" t="s">
-        <v>880</v>
+        <v>876</v>
       </c>
       <c r="D252" s="18" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E252" s="18">
         <v>105</v>
@@ -10361,16 +10364,16 @@
     </row>
     <row r="253" spans="1:9">
       <c r="A253" s="31" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B253" s="18" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
       <c r="C253" s="18" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="D253" s="18" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E253" s="18">
         <v>116</v>
@@ -10388,16 +10391,16 @@
     </row>
     <row r="254" spans="1:9">
       <c r="A254" s="31" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B254" s="18" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="C254" s="18" t="s">
-        <v>886</v>
+        <v>882</v>
       </c>
       <c r="D254" s="18" t="s">
-        <v>887</v>
+        <v>843</v>
       </c>
       <c r="E254" s="18">
         <v>190</v>
@@ -10412,21 +10415,21 @@
         <v>5.3</v>
       </c>
       <c r="I254" s="54" t="s">
-        <v>871</v>
+        <v>868</v>
       </c>
     </row>
     <row r="255" spans="1:9">
       <c r="A255" s="31" t="s">
+        <v>569</v>
+      </c>
+      <c r="B255" s="18" t="s">
+        <v>883</v>
+      </c>
+      <c r="C255" s="18" t="s">
         <v>570</v>
       </c>
-      <c r="B255" s="18" t="s">
-        <v>888</v>
-      </c>
-      <c r="C255" s="18" t="s">
-        <v>571</v>
-      </c>
       <c r="D255" s="18" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E255" s="59">
         <v>88</v>
@@ -10438,22 +10441,22 @@
         <v>208</v>
       </c>
       <c r="H255" s="59">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="I255" s="54"/>
     </row>
     <row r="256" spans="1:9">
       <c r="A256" s="9" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B256" s="52" t="s">
-        <v>889</v>
+        <v>884</v>
       </c>
       <c r="C256" s="18" t="s">
-        <v>890</v>
+        <v>885</v>
       </c>
       <c r="D256" s="50" t="s">
-        <v>891</v>
+        <v>886</v>
       </c>
       <c r="E256" s="52">
         <v>190</v>
@@ -10468,21 +10471,21 @@
         <v>5.2</v>
       </c>
       <c r="I256" s="54" t="s">
-        <v>892</v>
+        <v>887</v>
       </c>
     </row>
     <row r="257" spans="1:9">
       <c r="A257" s="9" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B257" s="36" t="s">
-        <v>893</v>
+        <v>888</v>
       </c>
       <c r="C257" s="36" t="s">
-        <v>894</v>
+        <v>889</v>
       </c>
       <c r="D257" s="36" t="s">
-        <v>876</v>
+        <v>800</v>
       </c>
       <c r="E257" s="36">
         <v>118</v>
@@ -10494,22 +10497,22 @@
         <v>215</v>
       </c>
       <c r="H257" s="60">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="I257" s="60"/>
     </row>
     <row r="258" spans="1:9">
       <c r="A258" s="9" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B258" s="18" t="s">
-        <v>881</v>
+        <v>877</v>
       </c>
       <c r="C258" s="18" t="s">
         <v>153</v>
       </c>
       <c r="D258" s="18" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E258" s="32">
         <v>108</v>
@@ -10527,7 +10530,7 @@
     </row>
     <row r="259" spans="1:9">
       <c r="A259" s="9" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B259" s="36"/>
       <c r="C259" s="36"/>
@@ -10540,7 +10543,7 @@
     </row>
     <row r="260" spans="1:9">
       <c r="A260" s="9" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B260" s="36"/>
       <c r="C260" s="36"/>
@@ -10553,16 +10556,16 @@
     </row>
     <row r="261" spans="1:9">
       <c r="A261" s="9" t="s">
+        <v>576</v>
+      </c>
+      <c r="B261" s="10" t="s">
         <v>577</v>
       </c>
-      <c r="B261" s="10" t="s">
+      <c r="C261" s="10" t="s">
         <v>578</v>
       </c>
-      <c r="C261" s="10" t="s">
-        <v>579</v>
-      </c>
       <c r="D261" s="49" t="s">
-        <v>895</v>
+        <v>890</v>
       </c>
       <c r="E261" s="10">
         <v>108</v>
@@ -10580,16 +10583,16 @@
     </row>
     <row r="262" spans="1:9">
       <c r="A262" s="9" t="s">
+        <v>579</v>
+      </c>
+      <c r="B262" s="10" t="s">
+        <v>891</v>
+      </c>
+      <c r="C262" s="10" t="s">
         <v>580</v>
       </c>
-      <c r="B262" s="10" t="s">
-        <v>896</v>
-      </c>
-      <c r="C262" s="10" t="s">
+      <c r="D262" s="49" t="s">
         <v>581</v>
-      </c>
-      <c r="D262" s="49" t="s">
-        <v>582</v>
       </c>
       <c r="E262" s="10">
         <v>87</v>
@@ -10607,16 +10610,16 @@
     </row>
     <row r="263" spans="1:9">
       <c r="A263" s="9" t="s">
+        <v>582</v>
+      </c>
+      <c r="B263" s="27" t="s">
         <v>583</v>
       </c>
-      <c r="B263" s="27" t="s">
+      <c r="C263" s="27" t="s">
         <v>584</v>
       </c>
-      <c r="C263" s="27" t="s">
+      <c r="D263" s="27" t="s">
         <v>585</v>
-      </c>
-      <c r="D263" s="27" t="s">
-        <v>586</v>
       </c>
       <c r="E263" s="27">
         <v>115</v>
@@ -10634,16 +10637,16 @@
     </row>
     <row r="264" spans="1:9">
       <c r="A264" s="9" t="s">
+        <v>586</v>
+      </c>
+      <c r="B264" s="10" t="s">
         <v>587</v>
       </c>
-      <c r="B264" s="10" t="s">
+      <c r="C264" s="10" t="s">
         <v>588</v>
       </c>
-      <c r="C264" s="10" t="s">
+      <c r="D264" s="10" t="s">
         <v>589</v>
-      </c>
-      <c r="D264" s="10" t="s">
-        <v>590</v>
       </c>
       <c r="E264" s="10">
         <v>70</v>
@@ -10655,22 +10658,22 @@
         <v>208</v>
       </c>
       <c r="H264" s="10">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="I264" s="60"/>
     </row>
     <row r="265" spans="1:9">
       <c r="A265" s="9" t="s">
+        <v>590</v>
+      </c>
+      <c r="B265" s="35" t="s">
         <v>591</v>
       </c>
-      <c r="B265" s="35" t="s">
+      <c r="C265" s="35" t="s">
         <v>592</v>
       </c>
-      <c r="C265" s="35" t="s">
+      <c r="D265" s="35" t="s">
         <v>593</v>
-      </c>
-      <c r="D265" s="35" t="s">
-        <v>594</v>
       </c>
       <c r="E265" s="35">
         <v>102</v>
@@ -10688,16 +10691,16 @@
     </row>
     <row r="266" spans="1:9">
       <c r="A266" s="9" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B266" s="35" t="s">
-        <v>897</v>
+        <v>892</v>
       </c>
       <c r="C266" s="35" t="s">
-        <v>873</v>
+        <v>870</v>
       </c>
       <c r="D266" s="35" t="s">
-        <v>898</v>
+        <v>893</v>
       </c>
       <c r="E266" s="35">
         <v>78</v>
@@ -10715,16 +10718,16 @@
     </row>
     <row r="267" spans="1:9">
       <c r="A267" s="9" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B267" s="10" t="s">
-        <v>899</v>
+        <v>894</v>
       </c>
       <c r="C267" s="10" t="s">
-        <v>900</v>
+        <v>895</v>
       </c>
       <c r="D267" s="49" t="s">
-        <v>901</v>
+        <v>896</v>
       </c>
       <c r="E267" s="10">
         <v>60</v>
@@ -10742,7 +10745,7 @@
     </row>
     <row r="268" spans="1:9">
       <c r="A268" s="9" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B268" s="36"/>
       <c r="C268" s="36"/>
@@ -10755,7 +10758,7 @@
     </row>
     <row r="269" spans="1:9">
       <c r="A269" s="9" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B269" s="36"/>
       <c r="C269" s="36"/>
@@ -10768,7 +10771,7 @@
     </row>
     <row r="270" spans="1:9">
       <c r="A270" s="9" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B270" s="36"/>
       <c r="C270" s="36"/>
@@ -10781,7 +10784,7 @@
     </row>
     <row r="271" spans="1:9">
       <c r="A271" s="9" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B271" s="36"/>
       <c r="C271" s="36"/>
@@ -10794,7 +10797,7 @@
     </row>
     <row r="272" spans="1:9">
       <c r="A272" s="9" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B272" s="36"/>
       <c r="C272" s="36"/>
@@ -10807,7 +10810,7 @@
     </row>
     <row r="273" spans="1:9">
       <c r="A273" s="9" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B273" s="36"/>
       <c r="C273" s="36"/>
@@ -10820,7 +10823,7 @@
     </row>
     <row r="274" spans="1:9">
       <c r="A274" s="9" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B274" s="36"/>
       <c r="C274" s="36"/>
@@ -10833,7 +10836,7 @@
     </row>
     <row r="275" spans="1:9">
       <c r="A275" s="9" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B275" s="36"/>
       <c r="C275" s="36"/>
@@ -10846,7 +10849,7 @@
     </row>
     <row r="276" spans="1:9">
       <c r="A276" s="9" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B276" s="36"/>
       <c r="C276" s="36"/>
@@ -10859,16 +10862,16 @@
     </row>
     <row r="277" spans="1:9">
       <c r="A277" s="9" t="s">
+        <v>605</v>
+      </c>
+      <c r="B277" s="52" t="s">
         <v>606</v>
       </c>
-      <c r="B277" s="52" t="s">
+      <c r="C277" s="52" t="s">
         <v>607</v>
       </c>
-      <c r="C277" s="52" t="s">
+      <c r="D277" s="52" t="s">
         <v>608</v>
-      </c>
-      <c r="D277" s="52" t="s">
-        <v>609</v>
       </c>
       <c r="E277" s="52">
         <v>105</v>
@@ -10886,16 +10889,16 @@
     </row>
     <row r="278" spans="1:9">
       <c r="A278" s="9" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B278" s="27" t="s">
-        <v>902</v>
+        <v>897</v>
       </c>
       <c r="C278" s="27" t="s">
-        <v>903</v>
+        <v>898</v>
       </c>
       <c r="D278" s="27" t="s">
-        <v>904</v>
+        <v>899</v>
       </c>
       <c r="E278" s="27">
         <v>159</v>
@@ -10913,13 +10916,13 @@
     </row>
     <row r="279" spans="1:9">
       <c r="A279" s="9" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B279" s="10" t="s">
-        <v>905</v>
+        <v>900</v>
       </c>
       <c r="C279" s="49" t="s">
-        <v>906</v>
+        <v>901</v>
       </c>
       <c r="D279" s="10" t="s">
         <v>144</v>
@@ -10940,16 +10943,16 @@
     </row>
     <row r="280" spans="1:9">
       <c r="A280" s="9" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B280" s="10" t="s">
-        <v>907</v>
+        <v>902</v>
       </c>
       <c r="C280" s="49" t="s">
-        <v>908</v>
+        <v>903</v>
       </c>
       <c r="D280" s="10" t="s">
-        <v>909</v>
+        <v>904</v>
       </c>
       <c r="E280" s="10"/>
       <c r="F280" s="9">
@@ -10965,13 +10968,13 @@
     </row>
     <row r="281" spans="1:9">
       <c r="A281" s="9" t="s">
+        <v>612</v>
+      </c>
+      <c r="B281" s="10" t="s">
         <v>613</v>
       </c>
-      <c r="B281" s="10" t="s">
+      <c r="C281" s="49" t="s">
         <v>614</v>
-      </c>
-      <c r="C281" s="49" t="s">
-        <v>615</v>
       </c>
       <c r="D281" s="10" t="s">
         <v>144</v>
@@ -10986,19 +10989,19 @@
         <v>222</v>
       </c>
       <c r="H281" s="10">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="I281" s="60"/>
     </row>
     <row r="282" spans="1:9">
       <c r="A282" s="9" t="s">
+        <v>615</v>
+      </c>
+      <c r="B282" s="10" t="s">
+        <v>905</v>
+      </c>
+      <c r="C282" s="49" t="s">
         <v>616</v>
-      </c>
-      <c r="B282" s="10" t="s">
-        <v>910</v>
-      </c>
-      <c r="C282" s="49" t="s">
-        <v>617</v>
       </c>
       <c r="D282" s="10" t="s">
         <v>39</v>
@@ -11019,13 +11022,13 @@
     </row>
     <row r="283" spans="1:9">
       <c r="A283" s="9" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B283" s="10" t="s">
-        <v>911</v>
+        <v>906</v>
       </c>
       <c r="C283" s="49" t="s">
-        <v>912</v>
+        <v>907</v>
       </c>
       <c r="D283" s="10" t="s">
         <v>39</v>
@@ -11046,16 +11049,16 @@
     </row>
     <row r="284" spans="1:9">
       <c r="A284" s="9" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B284" s="27" t="s">
-        <v>913</v>
+        <v>908</v>
       </c>
       <c r="C284" s="36" t="s">
-        <v>914</v>
+        <v>909</v>
       </c>
       <c r="D284" s="36" t="s">
-        <v>915</v>
+        <v>910</v>
       </c>
       <c r="E284" s="36">
         <v>80</v>
@@ -11073,16 +11076,16 @@
     </row>
     <row r="285" spans="1:9">
       <c r="A285" s="9" t="s">
+        <v>619</v>
+      </c>
+      <c r="B285" s="10" t="s">
         <v>620</v>
       </c>
-      <c r="B285" s="10" t="s">
+      <c r="C285" s="49" t="s">
         <v>621</v>
       </c>
-      <c r="C285" s="49" t="s">
-        <v>622</v>
-      </c>
       <c r="D285" s="36" t="s">
-        <v>915</v>
+        <v>910</v>
       </c>
       <c r="E285" s="10">
         <v>73</v>
@@ -11100,16 +11103,16 @@
     </row>
     <row r="286" spans="1:9">
       <c r="A286" s="9" t="s">
+        <v>622</v>
+      </c>
+      <c r="B286" s="52" t="s">
+        <v>911</v>
+      </c>
+      <c r="C286" s="52" t="s">
+        <v>912</v>
+      </c>
+      <c r="D286" s="52" t="s">
         <v>623</v>
-      </c>
-      <c r="B286" s="52" t="s">
-        <v>916</v>
-      </c>
-      <c r="C286" s="52" t="s">
-        <v>917</v>
-      </c>
-      <c r="D286" s="52" t="s">
-        <v>624</v>
       </c>
       <c r="E286" s="52">
         <v>85</v>
@@ -11127,16 +11130,16 @@
     </row>
     <row r="287" spans="1:9">
       <c r="A287" s="9" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B287" s="52" t="s">
-        <v>918</v>
+        <v>913</v>
       </c>
       <c r="C287" s="52" t="s">
-        <v>919</v>
+        <v>914</v>
       </c>
       <c r="D287" s="52" t="s">
-        <v>920</v>
+        <v>915</v>
       </c>
       <c r="E287" s="52">
         <v>88</v>
@@ -11154,13 +11157,13 @@
     </row>
     <row r="288" spans="1:9">
       <c r="A288" s="9" t="s">
+        <v>625</v>
+      </c>
+      <c r="B288" s="27" t="s">
+        <v>916</v>
+      </c>
+      <c r="C288" s="27" t="s">
         <v>626</v>
-      </c>
-      <c r="B288" s="27" t="s">
-        <v>921</v>
-      </c>
-      <c r="C288" s="27" t="s">
-        <v>627</v>
       </c>
       <c r="D288" s="50" t="s">
         <v>4</v>
@@ -11181,16 +11184,16 @@
     </row>
     <row r="289" spans="1:9">
       <c r="A289" s="9" t="s">
+        <v>627</v>
+      </c>
+      <c r="B289" s="10" t="s">
         <v>628</v>
       </c>
-      <c r="B289" s="10" t="s">
+      <c r="C289" s="10" t="s">
         <v>629</v>
       </c>
-      <c r="C289" s="10" t="s">
+      <c r="D289" s="49" t="s">
         <v>630</v>
-      </c>
-      <c r="D289" s="49" t="s">
-        <v>631</v>
       </c>
       <c r="E289" s="10">
         <v>135</v>
@@ -11205,18 +11208,18 @@
         <v>3.9</v>
       </c>
       <c r="I289" s="11" t="s">
-        <v>922</v>
+        <v>917</v>
       </c>
     </row>
     <row r="290" spans="1:9">
       <c r="A290" s="9" t="s">
+        <v>631</v>
+      </c>
+      <c r="B290" s="24" t="s">
         <v>632</v>
       </c>
-      <c r="B290" s="24" t="s">
+      <c r="C290" s="24" t="s">
         <v>633</v>
-      </c>
-      <c r="C290" s="24" t="s">
-        <v>634</v>
       </c>
       <c r="D290" s="63" t="s">
         <v>39</v>
@@ -11237,16 +11240,16 @@
     </row>
     <row r="291" spans="1:9">
       <c r="A291" s="9" t="s">
+        <v>634</v>
+      </c>
+      <c r="B291" s="64" t="s">
+        <v>918</v>
+      </c>
+      <c r="C291" s="64" t="s">
+        <v>919</v>
+      </c>
+      <c r="D291" s="64" t="s">
         <v>635</v>
-      </c>
-      <c r="B291" s="64" t="s">
-        <v>923</v>
-      </c>
-      <c r="C291" s="64" t="s">
-        <v>924</v>
-      </c>
-      <c r="D291" s="64" t="s">
-        <v>636</v>
       </c>
       <c r="E291" s="64">
         <v>88</v>
@@ -11264,16 +11267,16 @@
     </row>
     <row r="292" spans="1:9">
       <c r="A292" s="9" t="s">
+        <v>636</v>
+      </c>
+      <c r="B292" s="64" t="s">
+        <v>920</v>
+      </c>
+      <c r="C292" s="64" t="s">
         <v>637</v>
       </c>
-      <c r="B292" s="64" t="s">
-        <v>925</v>
-      </c>
-      <c r="C292" s="64" t="s">
+      <c r="D292" s="64" t="s">
         <v>638</v>
-      </c>
-      <c r="D292" s="64" t="s">
-        <v>639</v>
       </c>
       <c r="E292" s="64">
         <v>80</v>
@@ -11291,13 +11294,13 @@
     </row>
     <row r="293" spans="1:9">
       <c r="A293" s="9" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B293" s="65" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="C293" s="64" t="s">
-        <v>927</v>
+        <v>922</v>
       </c>
       <c r="D293" s="64" t="s">
         <v>39</v>
@@ -11318,16 +11321,16 @@
     </row>
     <row r="294" spans="1:9">
       <c r="A294" s="9" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B294" s="18" t="s">
-        <v>928</v>
+        <v>923</v>
       </c>
       <c r="C294" s="18" t="s">
-        <v>929</v>
+        <v>799</v>
       </c>
       <c r="D294" s="18" t="s">
-        <v>930</v>
+        <v>924</v>
       </c>
       <c r="E294" s="18">
         <v>150</v>
@@ -11345,16 +11348,16 @@
     </row>
     <row r="295" spans="1:9">
       <c r="A295" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="B295" s="10" t="s">
+        <v>925</v>
+      </c>
+      <c r="C295" s="10" t="s">
         <v>642</v>
       </c>
-      <c r="B295" s="10" t="s">
-        <v>931</v>
-      </c>
-      <c r="C295" s="10" t="s">
+      <c r="D295" s="10" t="s">
         <v>643</v>
-      </c>
-      <c r="D295" s="10" t="s">
-        <v>644</v>
       </c>
       <c r="E295" s="10"/>
       <c r="F295" s="9"/>
@@ -11368,16 +11371,16 @@
     </row>
     <row r="296" spans="1:9">
       <c r="A296" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="B296" s="35" t="s">
         <v>645</v>
       </c>
-      <c r="B296" s="35" t="s">
+      <c r="C296" s="35" t="s">
         <v>646</v>
       </c>
-      <c r="C296" s="35" t="s">
+      <c r="D296" s="35" t="s">
         <v>647</v>
-      </c>
-      <c r="D296" s="35" t="s">
-        <v>648</v>
       </c>
       <c r="E296" s="35"/>
       <c r="F296" s="36">
@@ -11393,16 +11396,16 @@
     </row>
     <row r="297" spans="1:9">
       <c r="A297" s="9" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B297" s="18" t="s">
-        <v>932</v>
+        <v>926</v>
       </c>
       <c r="C297" s="18" t="s">
-        <v>933</v>
+        <v>927</v>
       </c>
       <c r="D297" s="33" t="s">
-        <v>934</v>
+        <v>928</v>
       </c>
       <c r="E297" s="18">
         <v>125</v>
@@ -11420,16 +11423,16 @@
     </row>
     <row r="298" spans="1:9">
       <c r="A298" s="9" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B298" s="18" t="s">
-        <v>935</v>
+        <v>929</v>
       </c>
       <c r="C298" s="18" t="s">
-        <v>936</v>
+        <v>930</v>
       </c>
       <c r="D298" s="33" t="s">
-        <v>937</v>
+        <v>931</v>
       </c>
       <c r="E298" s="18">
         <v>190</v>
@@ -11444,21 +11447,21 @@
         <v>5.9</v>
       </c>
       <c r="I298" s="11" t="s">
-        <v>938</v>
+        <v>932</v>
       </c>
     </row>
     <row r="299" spans="1:9">
       <c r="A299" s="9" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B299" s="51" t="s">
-        <v>939</v>
+        <v>933</v>
       </c>
       <c r="C299" s="51" t="s">
-        <v>940</v>
+        <v>934</v>
       </c>
       <c r="D299" s="51" t="s">
-        <v>941</v>
+        <v>935</v>
       </c>
       <c r="E299" s="51">
         <v>124</v>
@@ -11470,15 +11473,15 @@
         <v>218</v>
       </c>
       <c r="H299" s="51">
-        <v>4.5999999999999996</v>
+        <v>4.8</v>
       </c>
       <c r="I299" s="55" t="s">
-        <v>942</v>
+        <v>936</v>
       </c>
     </row>
     <row r="300" spans="1:9">
       <c r="A300" s="9" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B300" s="36"/>
       <c r="C300" s="36"/>
@@ -11491,7 +11494,7 @@
     </row>
     <row r="301" spans="1:9">
       <c r="A301" s="9" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B301" s="36"/>
       <c r="C301" s="36"/>
@@ -11504,16 +11507,16 @@
     </row>
     <row r="302" spans="1:9">
       <c r="A302" s="9" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B302" s="11" t="s">
-        <v>943</v>
+        <v>937</v>
       </c>
       <c r="C302" s="11" t="s">
-        <v>944</v>
+        <v>938</v>
       </c>
       <c r="D302" s="11" t="s">
-        <v>945</v>
+        <v>939</v>
       </c>
       <c r="E302" s="11">
         <v>150</v>
@@ -11531,16 +11534,16 @@
     </row>
     <row r="303" spans="1:9">
       <c r="A303" s="9" t="s">
+        <v>654</v>
+      </c>
+      <c r="B303" s="10" t="s">
         <v>655</v>
       </c>
-      <c r="B303" s="10" t="s">
+      <c r="C303" s="10" t="s">
         <v>656</v>
       </c>
-      <c r="C303" s="10" t="s">
-        <v>657</v>
-      </c>
       <c r="D303" s="10" t="s">
-        <v>945</v>
+        <v>939</v>
       </c>
       <c r="E303" s="11">
         <v>140</v>
@@ -11558,16 +11561,16 @@
     </row>
     <row r="304" spans="1:9">
       <c r="A304" s="9" t="s">
+        <v>657</v>
+      </c>
+      <c r="B304" s="64" t="s">
         <v>658</v>
       </c>
-      <c r="B304" s="64" t="s">
+      <c r="C304" s="64" t="s">
+        <v>940</v>
+      </c>
+      <c r="D304" s="64" t="s">
         <v>659</v>
-      </c>
-      <c r="C304" s="64" t="s">
-        <v>946</v>
-      </c>
-      <c r="D304" s="64" t="s">
-        <v>660</v>
       </c>
       <c r="E304" s="64">
         <v>90</v>
@@ -11579,24 +11582,24 @@
         <v>218</v>
       </c>
       <c r="H304" s="64">
-        <v>4.5</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="I304" s="37" t="s">
-        <v>947</v>
+        <v>941</v>
       </c>
     </row>
     <row r="305" spans="1:9">
       <c r="A305" s="9" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B305" s="36" t="s">
-        <v>948</v>
+        <v>942</v>
       </c>
       <c r="C305" s="36" t="s">
-        <v>949</v>
+        <v>943</v>
       </c>
       <c r="D305" s="18" t="s">
-        <v>950</v>
+        <v>944</v>
       </c>
       <c r="E305" s="36">
         <v>215</v>
@@ -11608,13 +11611,13 @@
         <v>225</v>
       </c>
       <c r="H305" s="61">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="I305" s="61"/>
     </row>
     <row r="306" spans="1:9">
       <c r="A306" s="9" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B306" s="36"/>
       <c r="C306" s="36"/>
@@ -11627,7 +11630,7 @@
     </row>
     <row r="307" spans="1:9">
       <c r="A307" s="9" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B307" s="36"/>
       <c r="C307" s="36"/>
@@ -11640,7 +11643,7 @@
     </row>
     <row r="308" spans="1:9">
       <c r="A308" s="9" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B308" s="36"/>
       <c r="C308" s="36"/>
@@ -11653,7 +11656,7 @@
     </row>
     <row r="309" spans="1:9">
       <c r="A309" s="9" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B309" s="36"/>
       <c r="C309" s="36"/>
@@ -11666,7 +11669,7 @@
     </row>
     <row r="310" spans="1:9">
       <c r="A310" s="9" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B310" s="36"/>
       <c r="C310" s="36"/>
@@ -11679,16 +11682,16 @@
     </row>
     <row r="311" spans="1:9">
       <c r="A311" s="9" t="s">
+        <v>666</v>
+      </c>
+      <c r="B311" s="35" t="s">
         <v>667</v>
       </c>
-      <c r="B311" s="35" t="s">
+      <c r="C311" s="35" t="s">
+        <v>945</v>
+      </c>
+      <c r="D311" s="35" t="s">
         <v>668</v>
-      </c>
-      <c r="C311" s="35" t="s">
-        <v>951</v>
-      </c>
-      <c r="D311" s="35" t="s">
-        <v>669</v>
       </c>
       <c r="E311" s="35">
         <v>85</v>
@@ -11706,16 +11709,16 @@
     </row>
     <row r="312" spans="1:9">
       <c r="A312" s="9" t="s">
+        <v>669</v>
+      </c>
+      <c r="B312" s="10" t="s">
         <v>670</v>
       </c>
-      <c r="B312" s="10" t="s">
+      <c r="C312" s="10" t="s">
         <v>671</v>
       </c>
-      <c r="C312" s="10" t="s">
+      <c r="D312" s="10" t="s">
         <v>672</v>
-      </c>
-      <c r="D312" s="10" t="s">
-        <v>673</v>
       </c>
       <c r="E312" s="10">
         <v>73</v>
@@ -11733,7 +11736,7 @@
     </row>
     <row r="313" spans="1:9">
       <c r="A313" s="9" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B313" s="36"/>
       <c r="C313" s="36"/>
@@ -11746,7 +11749,7 @@
     </row>
     <row r="314" spans="1:9">
       <c r="A314" s="9" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B314" s="36"/>
       <c r="C314" s="36"/>
@@ -11759,16 +11762,16 @@
     </row>
     <row r="315" spans="1:9">
       <c r="A315" s="9" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B315" s="36" t="s">
-        <v>952</v>
+        <v>946</v>
       </c>
       <c r="C315" s="36" t="s">
-        <v>953</v>
+        <v>851</v>
       </c>
       <c r="D315" s="11" t="s">
-        <v>954</v>
+        <v>947</v>
       </c>
       <c r="E315" s="36">
         <v>116</v>
@@ -11783,21 +11786,21 @@
         <v>5</v>
       </c>
       <c r="I315" s="61" t="s">
-        <v>955</v>
+        <v>948</v>
       </c>
     </row>
     <row r="316" spans="1:9">
       <c r="A316" s="9" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B316" s="36" t="s">
-        <v>956</v>
+        <v>949</v>
       </c>
       <c r="C316" s="36" t="s">
-        <v>957</v>
+        <v>950</v>
       </c>
       <c r="D316" s="11" t="s">
-        <v>958</v>
+        <v>951</v>
       </c>
       <c r="E316" s="36">
         <v>160</v>
@@ -11812,21 +11815,21 @@
         <v>5.2</v>
       </c>
       <c r="I316" s="61" t="s">
-        <v>959</v>
+        <v>952</v>
       </c>
     </row>
     <row r="317" spans="1:9">
       <c r="A317" s="9" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B317" s="11" t="s">
-        <v>960</v>
+        <v>953</v>
       </c>
       <c r="C317" s="11" t="s">
-        <v>961</v>
+        <v>954</v>
       </c>
       <c r="D317" s="11" t="s">
-        <v>962</v>
+        <v>955</v>
       </c>
       <c r="E317" s="11">
         <v>110</v>
@@ -11841,21 +11844,21 @@
         <v>3.6</v>
       </c>
       <c r="I317" s="11" t="s">
-        <v>963</v>
+        <v>956</v>
       </c>
     </row>
     <row r="318" spans="1:9">
       <c r="A318" s="9" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B318" s="11" t="s">
-        <v>960</v>
+        <v>953</v>
       </c>
       <c r="C318" s="11" t="s">
-        <v>964</v>
+        <v>957</v>
       </c>
       <c r="D318" s="11" t="s">
-        <v>962</v>
+        <v>955</v>
       </c>
       <c r="E318" s="11">
         <v>110</v>
@@ -11873,45 +11876,45 @@
     </row>
     <row r="319" spans="1:9">
       <c r="A319" s="9" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B319" s="18" t="s">
-        <v>965</v>
+        <v>958</v>
       </c>
       <c r="C319" s="18" t="s">
-        <v>966</v>
+        <v>930</v>
       </c>
       <c r="D319" s="18" t="s">
-        <v>967</v>
+        <v>959</v>
       </c>
       <c r="E319" s="18">
-        <v>205</v>
+        <v>185</v>
       </c>
       <c r="F319" s="31">
         <v>270</v>
       </c>
       <c r="G319" s="32">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="H319" s="18">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="I319" s="11" t="s">
-        <v>968</v>
+        <v>960</v>
       </c>
     </row>
     <row r="320" spans="1:9">
       <c r="A320" s="9" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B320" s="18" t="s">
-        <v>969</v>
+        <v>961</v>
       </c>
       <c r="C320" s="18" t="s">
-        <v>970</v>
+        <v>962</v>
       </c>
       <c r="D320" s="18" t="s">
-        <v>971</v>
+        <v>963</v>
       </c>
       <c r="E320" s="18">
         <v>182</v>
@@ -11926,21 +11929,21 @@
         <v>6</v>
       </c>
       <c r="I320" s="11" t="s">
-        <v>938</v>
+        <v>932</v>
       </c>
     </row>
     <row r="321" spans="1:9">
       <c r="A321" s="9" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B321" s="18" t="s">
-        <v>972</v>
+        <v>964</v>
       </c>
       <c r="C321" s="18" t="s">
-        <v>973</v>
+        <v>965</v>
       </c>
       <c r="D321" s="18" t="s">
-        <v>974</v>
+        <v>966</v>
       </c>
       <c r="E321" s="18">
         <v>138</v>
@@ -11955,21 +11958,21 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="I321" s="11" t="s">
-        <v>975</v>
+        <v>967</v>
       </c>
     </row>
     <row r="322" spans="1:9">
       <c r="A322" s="9" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B322" s="18" t="s">
-        <v>976</v>
+        <v>968</v>
       </c>
       <c r="C322" s="18" t="s">
-        <v>977</v>
+        <v>969</v>
       </c>
       <c r="D322" s="18" t="s">
-        <v>967</v>
+        <v>959</v>
       </c>
       <c r="E322" s="18">
         <v>225</v>
@@ -11984,50 +11987,50 @@
         <v>6.2</v>
       </c>
       <c r="I322" s="11" t="s">
-        <v>978</v>
+        <v>970</v>
       </c>
     </row>
     <row r="323" spans="1:9">
       <c r="A323" s="9" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B323" s="18" t="s">
-        <v>979</v>
+        <v>971</v>
       </c>
       <c r="C323" s="18" t="s">
-        <v>980</v>
+        <v>972</v>
       </c>
       <c r="D323" s="18" t="s">
-        <v>974</v>
+        <v>966</v>
       </c>
       <c r="E323" s="18">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="F323" s="31">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="G323" s="32">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="H323" s="18">
         <v>4.5999999999999996</v>
       </c>
       <c r="I323" s="11" t="s">
-        <v>981</v>
+        <v>973</v>
       </c>
     </row>
     <row r="324" spans="1:9">
       <c r="A324" s="9" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B324" s="18" t="s">
-        <v>982</v>
+        <v>974</v>
       </c>
       <c r="C324" s="18" t="s">
-        <v>983</v>
+        <v>975</v>
       </c>
       <c r="D324" s="18" t="s">
-        <v>967</v>
+        <v>959</v>
       </c>
       <c r="E324" s="18">
         <v>220</v>
@@ -12039,15 +12042,15 @@
         <v>218</v>
       </c>
       <c r="H324" s="18">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="I324" s="11" t="s">
-        <v>978</v>
+        <v>970</v>
       </c>
     </row>
     <row r="325" spans="1:9">
       <c r="A325" s="9" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B325" s="36"/>
       <c r="C325" s="36"/>
@@ -12060,20 +12063,34 @@
     </row>
     <row r="326" spans="1:9">
       <c r="A326" s="9" t="s">
-        <v>702</v>
-      </c>
-      <c r="B326" s="36"/>
-      <c r="C326" s="36"/>
-      <c r="D326" s="36"/>
-      <c r="E326" s="36"/>
+        <v>700</v>
+      </c>
+      <c r="B326" s="36" t="s">
+        <v>976</v>
+      </c>
+      <c r="C326" s="36" t="s">
+        <v>977</v>
+      </c>
+      <c r="D326" s="36" t="s">
+        <v>978</v>
+      </c>
+      <c r="E326" s="36">
+        <v>145</v>
+      </c>
       <c r="F326" s="36"/>
-      <c r="G326" s="36"/>
-      <c r="H326" s="61"/>
-      <c r="I326" s="61"/>
+      <c r="G326" s="36">
+        <v>220</v>
+      </c>
+      <c r="H326" s="61">
+        <v>5.5</v>
+      </c>
+      <c r="I326" s="61" t="s">
+        <v>979</v>
+      </c>
     </row>
     <row r="327" spans="1:9">
       <c r="A327" s="9" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="B327" s="36"/>
       <c r="C327" s="36"/>
@@ -12086,7 +12103,7 @@
     </row>
     <row r="328" spans="1:9">
       <c r="A328" s="9" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="B328" s="36"/>
       <c r="C328" s="36"/>
@@ -12099,7 +12116,7 @@
     </row>
     <row r="329" spans="1:9">
       <c r="A329" s="9" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="B329" s="36"/>
       <c r="C329" s="36"/>
@@ -12112,7 +12129,7 @@
     </row>
     <row r="330" spans="1:9">
       <c r="A330" s="9" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="B330" s="36"/>
       <c r="C330" s="36"/>
@@ -12125,7 +12142,7 @@
     </row>
     <row r="331" spans="1:9">
       <c r="A331" s="9" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="B331" s="36"/>
       <c r="C331" s="36"/>
@@ -12138,7 +12155,7 @@
     </row>
     <row r="332" spans="1:9">
       <c r="A332" s="9" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="B332" s="36"/>
       <c r="C332" s="36"/>
@@ -12151,7 +12168,7 @@
     </row>
     <row r="333" spans="1:9">
       <c r="A333" s="9" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="B333" s="36"/>
       <c r="C333" s="36"/>
@@ -12164,7 +12181,7 @@
     </row>
     <row r="334" spans="1:9">
       <c r="A334" s="9" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="B334" s="36"/>
       <c r="C334" s="36"/>
@@ -12177,7 +12194,7 @@
     </row>
     <row r="335" spans="1:9">
       <c r="A335" s="9" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="B335" s="36"/>
       <c r="C335" s="36"/>
@@ -12190,7 +12207,7 @@
     </row>
     <row r="336" spans="1:9">
       <c r="A336" s="9" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="B336" s="36"/>
       <c r="C336" s="36"/>
@@ -12203,7 +12220,7 @@
     </row>
     <row r="337" spans="1:9">
       <c r="A337" s="9" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="B337" s="36"/>
       <c r="C337" s="36"/>
@@ -12216,7 +12233,7 @@
     </row>
     <row r="338" spans="1:9">
       <c r="A338" s="9" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="B338" s="36"/>
       <c r="C338" s="36"/>
@@ -12229,7 +12246,7 @@
     </row>
     <row r="339" spans="1:9">
       <c r="A339" s="9" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="B339" s="36"/>
       <c r="C339" s="36"/>
@@ -12242,7 +12259,7 @@
     </row>
     <row r="340" spans="1:9">
       <c r="A340" s="9" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="B340" s="36"/>
       <c r="C340" s="36"/>
@@ -12255,7 +12272,7 @@
     </row>
     <row r="341" spans="1:9">
       <c r="A341" s="9" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="B341" s="36"/>
       <c r="C341" s="36"/>
@@ -12268,7 +12285,7 @@
     </row>
     <row r="342" spans="1:9">
       <c r="A342" s="9" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="B342" s="36"/>
       <c r="C342" s="36"/>
@@ -12281,7 +12298,7 @@
     </row>
     <row r="343" spans="1:9">
       <c r="A343" s="9" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="B343" s="36"/>
       <c r="C343" s="36"/>
@@ -12294,7 +12311,7 @@
     </row>
     <row r="344" spans="1:9">
       <c r="A344" s="9" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="B344" s="36"/>
       <c r="C344" s="36"/>
@@ -12307,7 +12324,7 @@
     </row>
     <row r="345" spans="1:9">
       <c r="A345" s="9" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="B345" s="36"/>
       <c r="C345" s="36"/>
@@ -12320,7 +12337,7 @@
     </row>
     <row r="346" spans="1:9">
       <c r="A346" s="9" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="B346" s="36"/>
       <c r="C346" s="36"/>
@@ -12333,7 +12350,7 @@
     </row>
     <row r="347" spans="1:9">
       <c r="A347" s="9" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="B347" s="36"/>
       <c r="C347" s="36"/>
@@ -12346,7 +12363,7 @@
     </row>
     <row r="348" spans="1:9">
       <c r="A348" s="9" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="B348" s="36"/>
       <c r="C348" s="36"/>
@@ -12359,7 +12376,7 @@
     </row>
     <row r="349" spans="1:9">
       <c r="A349" s="9" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="B349" s="36"/>
       <c r="C349" s="36"/>
@@ -12372,7 +12389,7 @@
     </row>
     <row r="350" spans="1:9">
       <c r="A350" s="9" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="B350" s="36"/>
       <c r="C350" s="36"/>
@@ -12385,7 +12402,7 @@
     </row>
     <row r="351" spans="1:9">
       <c r="A351" s="9" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="B351" s="36"/>
       <c r="C351" s="36"/>
@@ -12398,7 +12415,7 @@
     </row>
     <row r="352" spans="1:9">
       <c r="A352" s="9" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="B352" s="36"/>
       <c r="C352" s="36"/>
@@ -12411,7 +12428,7 @@
     </row>
     <row r="353" spans="1:9">
       <c r="A353" s="9" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="B353" s="36"/>
       <c r="C353" s="36"/>
@@ -12424,7 +12441,7 @@
     </row>
     <row r="354" spans="1:9">
       <c r="A354" s="9" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="B354" s="36"/>
       <c r="C354" s="36"/>
@@ -12437,7 +12454,7 @@
     </row>
     <row r="355" spans="1:9">
       <c r="A355" s="9" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="B355" s="36"/>
       <c r="C355" s="36"/>
@@ -12450,7 +12467,7 @@
     </row>
     <row r="356" spans="1:9">
       <c r="A356" s="9" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="B356" s="36"/>
       <c r="C356" s="36"/>
@@ -12463,7 +12480,7 @@
     </row>
     <row r="357" spans="1:9">
       <c r="A357" s="9" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="B357" s="36"/>
       <c r="C357" s="36"/>
@@ -12476,7 +12493,7 @@
     </row>
     <row r="358" spans="1:9">
       <c r="A358" s="9" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="B358" s="36"/>
       <c r="C358" s="36"/>
@@ -12489,7 +12506,7 @@
     </row>
     <row r="359" spans="1:9">
       <c r="A359" s="9" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="B359" s="36"/>
       <c r="C359" s="36"/>
@@ -12502,7 +12519,7 @@
     </row>
     <row r="360" spans="1:9">
       <c r="A360" s="9" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="B360" s="36"/>
       <c r="C360" s="36"/>
@@ -12515,7 +12532,7 @@
     </row>
     <row r="361" spans="1:9">
       <c r="A361" s="9" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="B361" s="36"/>
       <c r="C361" s="36"/>
@@ -12528,7 +12545,7 @@
     </row>
     <row r="362" spans="1:9">
       <c r="A362" s="9" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="B362" s="36"/>
       <c r="C362" s="36"/>
@@ -12541,7 +12558,7 @@
     </row>
     <row r="363" spans="1:9">
       <c r="A363" s="9" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="B363" s="36"/>
       <c r="C363" s="36"/>
@@ -12554,7 +12571,7 @@
     </row>
     <row r="364" spans="1:9">
       <c r="A364" s="9" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="B364" s="36"/>
       <c r="C364" s="36"/>
@@ -12567,7 +12584,7 @@
     </row>
     <row r="365" spans="1:9">
       <c r="A365" s="9" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="B365" s="36"/>
       <c r="C365" s="36"/>
@@ -12580,7 +12597,7 @@
     </row>
     <row r="366" spans="1:9">
       <c r="A366" s="9" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="B366" s="36"/>
       <c r="C366" s="36"/>
@@ -12593,7 +12610,7 @@
     </row>
     <row r="367" spans="1:9">
       <c r="A367" s="9" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="B367" s="36"/>
       <c r="C367" s="36"/>
@@ -12606,7 +12623,7 @@
     </row>
     <row r="368" spans="1:9">
       <c r="A368" s="9" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="B368" s="36"/>
       <c r="C368" s="36"/>
@@ -12619,7 +12636,7 @@
     </row>
     <row r="369" spans="1:9">
       <c r="A369" s="9" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="B369" s="36"/>
       <c r="C369" s="36"/>
@@ -12632,7 +12649,7 @@
     </row>
     <row r="370" spans="1:9">
       <c r="A370" s="9" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="B370" s="36"/>
       <c r="C370" s="36"/>
@@ -12645,7 +12662,7 @@
     </row>
     <row r="371" spans="1:9">
       <c r="A371" s="9" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="B371" s="36"/>
       <c r="C371" s="36"/>
@@ -12658,7 +12675,7 @@
     </row>
     <row r="372" spans="1:9">
       <c r="A372" s="9" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="B372" s="36"/>
       <c r="C372" s="36"/>
@@ -12671,7 +12688,7 @@
     </row>
     <row r="373" spans="1:9">
       <c r="A373" s="9" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="B373" s="36"/>
       <c r="C373" s="36"/>
@@ -12684,7 +12701,7 @@
     </row>
     <row r="374" spans="1:9">
       <c r="A374" s="9" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="B374" s="36"/>
       <c r="C374" s="36"/>
@@ -12697,7 +12714,7 @@
     </row>
     <row r="375" spans="1:9">
       <c r="A375" s="9" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="B375" s="36"/>
       <c r="C375" s="36"/>
@@ -12710,7 +12727,7 @@
     </row>
     <row r="376" spans="1:9">
       <c r="A376" s="9" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="B376" s="36"/>
       <c r="C376" s="36"/>
@@ -12723,7 +12740,7 @@
     </row>
     <row r="377" spans="1:9">
       <c r="A377" s="9" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="B377" s="36"/>
       <c r="C377" s="36"/>
@@ -12736,7 +12753,7 @@
     </row>
     <row r="378" spans="1:9">
       <c r="A378" s="9" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="B378" s="36"/>
       <c r="C378" s="36"/>
@@ -12749,7 +12766,7 @@
     </row>
     <row r="379" spans="1:9">
       <c r="A379" s="9" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="B379" s="36"/>
       <c r="C379" s="36"/>
@@ -12762,7 +12779,7 @@
     </row>
     <row r="380" spans="1:9">
       <c r="A380" s="9" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="B380" s="36"/>
       <c r="C380" s="36"/>
@@ -12775,7 +12792,7 @@
     </row>
     <row r="381" spans="1:9">
       <c r="A381" s="9" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="B381" s="36"/>
       <c r="C381" s="36"/>
@@ -12788,7 +12805,7 @@
     </row>
     <row r="382" spans="1:9">
       <c r="A382" s="9" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="B382" s="36"/>
       <c r="C382" s="36"/>
@@ -12801,7 +12818,7 @@
     </row>
     <row r="383" spans="1:9">
       <c r="A383" s="9" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="B383" s="36"/>
       <c r="C383" s="36"/>
@@ -12814,7 +12831,7 @@
     </row>
     <row r="384" spans="1:9">
       <c r="A384" s="9" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="B384" s="36"/>
       <c r="C384" s="36"/>
@@ -12827,7 +12844,7 @@
     </row>
     <row r="385" spans="1:9">
       <c r="A385" s="9" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="B385" s="36"/>
       <c r="C385" s="36"/>
@@ -12840,7 +12857,7 @@
     </row>
     <row r="386" spans="1:9">
       <c r="A386" s="9" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="B386" s="36"/>
       <c r="C386" s="36"/>
@@ -12853,7 +12870,7 @@
     </row>
     <row r="387" spans="1:9">
       <c r="A387" s="9" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="B387" s="36"/>
       <c r="C387" s="36"/>
@@ -12866,7 +12883,7 @@
     </row>
     <row r="388" spans="1:9">
       <c r="A388" s="9" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="B388" s="36"/>
       <c r="C388" s="36"/>
@@ -12879,7 +12896,7 @@
     </row>
     <row r="389" spans="1:9">
       <c r="A389" s="9" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="B389" s="36"/>
       <c r="C389" s="36"/>
@@ -12892,7 +12909,7 @@
     </row>
     <row r="390" spans="1:9">
       <c r="A390" s="9" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="B390" s="36"/>
       <c r="C390" s="36"/>
@@ -12905,7 +12922,7 @@
     </row>
     <row r="391" spans="1:9">
       <c r="A391" s="9" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="B391" s="36"/>
       <c r="C391" s="36"/>
@@ -12918,7 +12935,7 @@
     </row>
     <row r="392" spans="1:9">
       <c r="A392" s="9" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="B392" s="36"/>
       <c r="C392" s="36"/>
@@ -12931,7 +12948,7 @@
     </row>
     <row r="393" spans="1:9">
       <c r="A393" s="9" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="B393" s="36"/>
       <c r="C393" s="36"/>

--- a/产品规格.xlsx
+++ b/产品规格.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4507"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\2种产品规格\18962500118标签加二维码\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="0" yWindow="90" windowWidth="19200" windowHeight="11640"/>
   </bookViews>
@@ -11,12 +16,12 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="125725"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1301" uniqueCount="981">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1308" uniqueCount="993">
   <si>
     <t>17.5*3*27</t>
   </si>
@@ -364,9 +369,6 @@
   </si>
   <si>
     <t>XC047</t>
-  </si>
-  <si>
-    <t>消光珍珠点50*50*150</t>
   </si>
   <si>
     <t>22*3+40</t>
@@ -2335,19 +2337,495 @@
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
+    <t>22*3*38</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>14*2*25</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>17*3*28</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>25梭T400无捻牛津</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>26梭T400无捻牛津</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>17*2*26</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">50S*50S弹力 酷丝棉平纹  </t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>17*2*30</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>50S*50S</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">40S*40S弹力 酷丝棉平纹  </t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*40S</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">40S*75T 酷丝棉平纹  </t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*75D 酷丝棉2/1</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">40S*75D 酷丝棉2/2 </t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">40S*150 酷丝棉28S平纹  </t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">40S*150 酷丝棉24S平纹  </t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>50S*75D 酷丝棉绮兵</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">40S*75 酷丝棉3/3斜  </t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>13.5*4*35</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">50S*75D 酷丝棉2/1 </t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>17.5*3*35</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">40S*75 酷丝棉3/2斜  </t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>17.5*3*34</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">40S*150 酷丝棉5/1斜  </t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>100*150T8 4/2斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>17*4*215*40</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>75*150T400 消3/3斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>17*4*36</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>75*75T400消 3/3斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>18*4*46</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>75*75 消光2/2 斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>75*75-T800消光骑士斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>17*4*38</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>19*5*45</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>19*3*39</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>X字格</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>16*4*46</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>T400横条2*1</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>16*4+28</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>238克</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>T400横条1*4</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>17*4+38</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>白坯200米克</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>T400横条1*1</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>16*4*30</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>100*75*150</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*75闪电斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*75</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*300 3/2变化斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>13.5*4*28</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*150*2T400</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>米克385</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>100D半光*35S-3/3斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>120D扁平0.5格</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>120*35S</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>米克370</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>17*4*45</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>100D消光多乐3/3斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>米克300</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>120D扁平1/2斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>米克350</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>120D扁平T800变化斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>120*150T800</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>米克380</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>20*2*31</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">40S*75 酷丝棉3/1斜 </t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*150 酷丝棉3/1斜 31</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>17*3*30</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*75D 酷丝棉2/2 30</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">40S*75D 骑兵斜 30 </t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*300 酷丝棉3/2斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>13.5*4*27</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*300酷丝绵珍珠点</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>80S*75双线格酷丝绵</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>75 T800半光0.5格</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>75*75*210</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>22*2*40</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>50*50</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>半光大猫眼</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>100半低*150半T800</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>50D低弹*50T800 平纹</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>23*2*40</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>22*3*57</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>75D经纬T8平纹</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">50DT8*50DT8 骑兵斜  </t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>50DT8*50DT8</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>T8五面埋伏</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>14*4*38</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>50D*50D*100D T800</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>T800双链条</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>米克265</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>20*2*26</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>17.5*4*38</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>空变T8平纹</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*75T8酷丝棉3/1.超钛棉</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*75T800</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>14*4*27</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>白坯370克</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>100D消光75DT800 3/3斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>15.5*4*48</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>100*75T8</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>100D*40S+150D T8</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>白坯188克</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">斜纹毛巾底 </t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>13.5*4*51</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>100D*35S+150DT8</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>天丝棉</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>20*3*32</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>80S*三合一</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>21*3*31</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>270-钛金棉</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*35S*2</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>16*4*44</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>210-钛金棉</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>加厚钛金棉</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>15.5*4*30</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>230-钛金棉</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>白坯300克</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>16*4*31</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>张：18962500118  盛泽温州商区13幢1号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>75*75*150</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>22*3*38</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
     <t>22*3*39</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>14*2*25</t>
+    <t>消半光珍珠点50*50*150</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
@@ -2355,66 +2833,18 @@
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>17*3*28</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
     <t>17*3*44</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>25梭T400无捻牛津</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
     <t>27梭T400无捻牛津</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>26梭T400无捻牛津</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>17*2*26</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">50S*50S弹力 酷丝棉平纹  </t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>17*2*30</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>50S*50S</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">40S*40S弹力 酷丝棉平纹  </t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
     <t>18*2*27</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>40S*40S</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">40S*75T 酷丝棉平纹  </t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*75D 酷丝棉2/1</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">40S*75D 酷丝棉2/2 </t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">40S*150 酷丝棉26S平纹  </t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
@@ -2427,14 +2857,6 @@
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">40S*150 酷丝棉28S平纹  </t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">40S*150 酷丝棉24S平纹  </t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">40S*150 酷丝棉3/3斜  </t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
@@ -2443,71 +2865,23 @@
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>50S*75D 酷丝棉绮兵</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">40S*75 酷丝棉3/3斜  </t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>13.5*4*35</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
     <t>40S*75T400</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">50S*75D 酷丝棉2/1 </t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
     <t>XC186</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>17.5*3*35</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">40S*75 酷丝棉3/2斜  </t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>17.5*3*34</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
     <t>40S*75DT400</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">40S*150 酷丝棉5/1斜  </t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>100*150T8 4/2斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>17*4*215*40</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
     <t>100D*150T800</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>75*150T400 消3/3斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>17*4*36</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>75*75T400消 3/3斜</t>
+    <t xml:space="preserve">40S*150D 酷丝棉2/2 </t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
@@ -2515,14 +2889,6 @@
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>18*4*46</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>75*75 消光2/2 斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
     <t>18*4*43</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
@@ -2531,86 +2897,14 @@
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>75*75-T800消光骑士斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>17*4*38</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
     <t>75消*75T800</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>19*5*45</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>19*3*39</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>X字格</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>16*4*46</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>T400横条2*1</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>16*4+28</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>238克</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>T400横条1*4</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>17*4+38</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>75*75*150</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>白坯200米克</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>T400横条1*1</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>16*4*30</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>100*75*150</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*75闪电斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
     <t>18*3*38</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>40S*75</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
     <t>40S*150酷丝绵 小钻石斜</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
@@ -2619,26 +2913,6 @@
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>40S*300 3/2变化斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>13.5*4*28</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*150*2T400</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>米克385</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>100D半光*35S-3/3斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
     <t>16*4*40</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
@@ -2655,27 +2929,11 @@
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>120D扁平0.5格</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
     <t>17*4*44</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>120*35S</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>米克370</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>120D扁平3/3斜-45</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>16*4*45</t>
+    <t>120D扁平3/3斜-44</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
@@ -2683,55 +2941,83 @@
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>17*4*45</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
     <t>米克375</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>100D消光多乐3/3斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
     <t>15*4*43</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>米克300</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>120D扁平1/2斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
     <t>17*4*34</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>米克350</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>120D扁平T800变化斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
     <t>17*4*29</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
+    <t>米克380</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>120D扁平牛津</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
     <t>120*150T800</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>米克380</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>120D扁平牛津</t>
+    <t>13.5*4*34</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*75T400</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*150 酷丝棉3/2斜 39</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*75D 酷丝棉2/1 30</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*75D 酷丝棉2/2 38</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">40S*75D 骑兵斜 38 </t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">40S*75T 酷丝棉平纹 33S </t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>17.5*3*25</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*150*300T400</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>米克368</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*75D酷丝绵变化斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>17.5*3*36</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*150T400+300T400</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
@@ -2739,146 +3025,22 @@
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">40S*75 酷丝棉3/1斜 </t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>13.5*4*34</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*150 酷丝棉3/1斜 31</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*150 酷丝棉3/2斜 39</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*75D 酷丝棉2/1 30</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>17*3*30</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*75D 酷丝棉2/2 30</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*75D 酷丝棉2/2 38</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">40S*75D 骑兵斜 30 </t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">40S*75D 骑兵斜 38 </t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*300 酷丝棉3/2斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>13.5*4*27</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">40S*75T 酷丝棉平纹 33S </t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*300酷丝绵珍珠点</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>17.5*3*25</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*150*300T400</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>米克368</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*75D酷丝绵变化斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>17.5*3*36</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*150T400+300T400</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>80S*75双线格酷丝绵</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>75 T800半光0.5格</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>75*75*210</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
     <t>50D经纬 T8 0.5格</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>22*2*40</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>50*50</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>半光大猫眼</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
     <t>16*4*43</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>100半低*150半T800</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>50D低弹*50T800 平纹</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>23*2*40</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
     <t>30D T8 平纹</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>22*3*57</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
     <t>30*30</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>75D经纬T8平纹</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
     <t>75经纬T8 2/2斜</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
@@ -2887,26 +3049,10 @@
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">50DT8*50DT8 骑兵斜  </t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
     <t>21*3*53</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>50DT8*50DT8</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>T8五面埋伏</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>14*4*38</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
     <t>50D*100D经纬T800珍珠点</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
@@ -2915,26 +3061,10 @@
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>50D*50D*100D T800</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>T800双链条</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>米克265</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
     <t>经消光低弹 双纬T800</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>20*2*26</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
     <t>75D半光T800双纬平纹</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
@@ -2943,10 +3073,6 @@
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>17.5*4*38</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">40S*150T800酷丝棉3/2斜  </t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
@@ -2955,47 +3081,15 @@
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>空变T8平纹</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*75T8酷丝棉3/1.超钛棉</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
     <t>17.5*3*44</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>40S*75T800</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
     <t>40S*300加厚超钛棉</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>14*4*27</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*300T800</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>白坯370克</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>100D消光75DT800 3/3斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>15.5*4*48</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>100*75T8</t>
+    <t>40S*150*2-T800</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
@@ -3011,26 +3105,10 @@
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>100D*40S+150D T8</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
     <t>21*3*45</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>白坯188克</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">斜纹毛巾底 </t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>13.5*4*51</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
     <t>40S*150T8*300低弹</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
@@ -3043,6 +3121,10 @@
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
+    <t>17*4*44</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
     <t>75D*50S+10DT8</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
@@ -3056,10 +3138,6 @@
   </si>
   <si>
     <t>15*4*44</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>100D*35S+150DT8</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
@@ -3085,30 +3163,10 @@
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>20*3*32</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>80S*三合一</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
     <t>白坯195克</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>21*3*31</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>270-钛金棉</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*35S*2</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
     <t>白坯368克</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
@@ -3117,18 +3175,10 @@
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>16*4*44</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
     <t>40S*35S</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>210-钛金棉</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
     <t>17*3*27</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
@@ -3141,27 +3191,15 @@
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>加厚钛金棉</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>15.5*4*30</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
     <t>白坯390克</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>230-钛金棉</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
     <t>17*3*31</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>白坯300克</t>
+    <t>40S*30S</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
@@ -3169,7 +3207,15 @@
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>16*4*31</t>
+    <t>270单股钛金棉</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>14*4*27</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*18S</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
@@ -3203,15 +3249,23 @@
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>张：18962500118  盛泽温州商区13幢1号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>40*300平纹</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>18*2*24</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*300D</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="11">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3748,11 +3802,19 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -3794,7 +3856,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -3826,9 +3888,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -3860,6 +3923,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -4035,10 +4099,10 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:M393"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="9" width="9" style="4"/>
     <col min="10" max="10" width="27" customWidth="1"/>
@@ -4046,56 +4110,56 @@
     <col min="12" max="12" width="24.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>689</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>692</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>693</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>694</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>695</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>696</v>
       </c>
-      <c r="I1" s="3" t="s">
-        <v>697</v>
-      </c>
       <c r="J1" s="5" t="s">
+        <v>686</v>
+      </c>
+      <c r="K1" s="5" t="s">
         <v>687</v>
       </c>
-      <c r="K1" s="5" t="s">
-        <v>688</v>
-      </c>
       <c r="L1" s="5" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A2" s="9" t="s">
+        <v>767</v>
+      </c>
+      <c r="B2" s="10" t="s">
         <v>768</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>769</v>
       </c>
       <c r="C2" s="10" t="s">
         <v>0</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>770</v>
+        <v>889</v>
       </c>
       <c r="E2" s="10">
         <v>79</v>
@@ -4109,16 +4173,16 @@
       </c>
       <c r="I2" s="11"/>
       <c r="J2" s="7" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="L2" s="8" t="s">
-        <v>980</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A3" s="9" t="s">
         <v>1</v>
       </c>
@@ -4146,7 +4210,7 @@
       <c r="L3" s="6"/>
       <c r="M3" s="6"/>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A4" s="9" t="s">
         <v>5</v>
       </c>
@@ -4174,7 +4238,7 @@
       <c r="L4" s="6"/>
       <c r="M4" s="6"/>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A5" s="9" t="s">
         <v>8</v>
       </c>
@@ -4199,7 +4263,7 @@
       </c>
       <c r="I5" s="11"/>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A6" s="9" t="s">
         <v>10</v>
       </c>
@@ -4224,7 +4288,7 @@
       </c>
       <c r="I6" s="11"/>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A7" s="9" t="s">
         <v>12</v>
       </c>
@@ -4249,7 +4313,7 @@
       </c>
       <c r="I7" s="11"/>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A8" s="9" t="s">
         <v>14</v>
       </c>
@@ -4274,7 +4338,7 @@
       </c>
       <c r="I8" s="11"/>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A9" s="9" t="s">
         <v>18</v>
       </c>
@@ -4299,7 +4363,7 @@
       </c>
       <c r="I9" s="11"/>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A10" s="9" t="s">
         <v>20</v>
       </c>
@@ -4324,7 +4388,7 @@
       </c>
       <c r="I10" s="11"/>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A11" s="9" t="s">
         <v>22</v>
       </c>
@@ -4349,7 +4413,7 @@
       </c>
       <c r="I11" s="11"/>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A12" s="9" t="s">
         <v>24</v>
       </c>
@@ -4374,7 +4438,7 @@
       </c>
       <c r="I12" s="11"/>
     </row>
-    <row r="13" spans="1:13">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A13" s="9" t="s">
         <v>26</v>
       </c>
@@ -4399,7 +4463,7 @@
       </c>
       <c r="I13" s="11"/>
     </row>
-    <row r="14" spans="1:13">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A14" s="9" t="s">
         <v>28</v>
       </c>
@@ -4424,7 +4488,7 @@
       </c>
       <c r="I14" s="11"/>
     </row>
-    <row r="15" spans="1:13">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A15" s="9" t="s">
         <v>30</v>
       </c>
@@ -4449,7 +4513,7 @@
       </c>
       <c r="I15" s="11"/>
     </row>
-    <row r="16" spans="1:13">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A16" s="9" t="s">
         <v>33</v>
       </c>
@@ -4474,7 +4538,7 @@
       </c>
       <c r="I16" s="11"/>
     </row>
-    <row r="17" spans="1:9">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A17" s="9" t="s">
         <v>35</v>
       </c>
@@ -4499,7 +4563,7 @@
       </c>
       <c r="I17" s="11"/>
     </row>
-    <row r="18" spans="1:9">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A18" s="9" t="s">
         <v>37</v>
       </c>
@@ -4524,7 +4588,7 @@
       </c>
       <c r="I18" s="11"/>
     </row>
-    <row r="19" spans="1:9">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A19" s="9" t="s">
         <v>40</v>
       </c>
@@ -4549,7 +4613,7 @@
       </c>
       <c r="I19" s="11"/>
     </row>
-    <row r="20" spans="1:9">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A20" s="9" t="s">
         <v>43</v>
       </c>
@@ -4574,7 +4638,7 @@
       </c>
       <c r="I20" s="11"/>
     </row>
-    <row r="21" spans="1:9">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A21" s="9" t="s">
         <v>47</v>
       </c>
@@ -4599,7 +4663,7 @@
       </c>
       <c r="I21" s="11"/>
     </row>
-    <row r="22" spans="1:9">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A22" s="9" t="s">
         <v>49</v>
       </c>
@@ -4624,7 +4688,7 @@
       </c>
       <c r="I22" s="11"/>
     </row>
-    <row r="23" spans="1:9">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A23" s="9" t="s">
         <v>51</v>
       </c>
@@ -4649,7 +4713,7 @@
       </c>
       <c r="I23" s="11"/>
     </row>
-    <row r="24" spans="1:9">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A24" s="9" t="s">
         <v>54</v>
       </c>
@@ -4674,7 +4738,7 @@
       </c>
       <c r="I24" s="11"/>
     </row>
-    <row r="25" spans="1:9">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A25" s="9" t="s">
         <v>56</v>
       </c>
@@ -4699,7 +4763,7 @@
       </c>
       <c r="I25" s="11"/>
     </row>
-    <row r="26" spans="1:9">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A26" s="9" t="s">
         <v>58</v>
       </c>
@@ -4724,7 +4788,7 @@
       </c>
       <c r="I26" s="11"/>
     </row>
-    <row r="27" spans="1:9">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A27" s="9" t="s">
         <v>61</v>
       </c>
@@ -4749,7 +4813,7 @@
       </c>
       <c r="I27" s="11"/>
     </row>
-    <row r="28" spans="1:9">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A28" s="9" t="s">
         <v>64</v>
       </c>
@@ -4774,7 +4838,7 @@
       </c>
       <c r="I28" s="11"/>
     </row>
-    <row r="29" spans="1:9">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A29" s="9" t="s">
         <v>67</v>
       </c>
@@ -4782,7 +4846,7 @@
         <v>68</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="D29" s="10" t="s">
         <v>46</v>
@@ -4799,7 +4863,7 @@
       </c>
       <c r="I29" s="11"/>
     </row>
-    <row r="30" spans="1:9">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A30" s="9" t="s">
         <v>69</v>
       </c>
@@ -4807,7 +4871,7 @@
         <v>70</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>772</v>
+        <v>890</v>
       </c>
       <c r="D30" s="10" t="s">
         <v>46</v>
@@ -4824,7 +4888,7 @@
       </c>
       <c r="I30" s="11"/>
     </row>
-    <row r="31" spans="1:9">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A31" s="9" t="s">
         <v>71</v>
       </c>
@@ -4849,7 +4913,7 @@
       </c>
       <c r="I31" s="11"/>
     </row>
-    <row r="32" spans="1:9">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A32" s="9" t="s">
         <v>74</v>
       </c>
@@ -4874,7 +4938,7 @@
       </c>
       <c r="I32" s="11"/>
     </row>
-    <row r="33" spans="1:9">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A33" s="9" t="s">
         <v>76</v>
       </c>
@@ -4899,7 +4963,7 @@
       </c>
       <c r="I33" s="11"/>
     </row>
-    <row r="34" spans="1:9">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A34" s="9" t="s">
         <v>78</v>
       </c>
@@ -4924,7 +4988,7 @@
       </c>
       <c r="I34" s="11"/>
     </row>
-    <row r="35" spans="1:9">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A35" s="9" t="s">
         <v>81</v>
       </c>
@@ -4949,7 +5013,7 @@
       </c>
       <c r="I35" s="11"/>
     </row>
-    <row r="36" spans="1:9">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A36" s="9" t="s">
         <v>83</v>
       </c>
@@ -4974,7 +5038,7 @@
       </c>
       <c r="I36" s="11"/>
     </row>
-    <row r="37" spans="1:9">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A37" s="9" t="s">
         <v>86</v>
       </c>
@@ -4999,7 +5063,7 @@
       </c>
       <c r="I37" s="11"/>
     </row>
-    <row r="38" spans="1:9">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A38" s="9" t="s">
         <v>89</v>
       </c>
@@ -5024,7 +5088,7 @@
       </c>
       <c r="I38" s="11"/>
     </row>
-    <row r="39" spans="1:9">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A39" s="9" t="s">
         <v>92</v>
       </c>
@@ -5049,7 +5113,7 @@
       </c>
       <c r="I39" s="11"/>
     </row>
-    <row r="40" spans="1:9">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A40" s="9" t="s">
         <v>94</v>
       </c>
@@ -5074,7 +5138,7 @@
       </c>
       <c r="I40" s="11"/>
     </row>
-    <row r="41" spans="1:9">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A41" s="9" t="s">
         <v>96</v>
       </c>
@@ -5099,7 +5163,7 @@
       </c>
       <c r="I41" s="11"/>
     </row>
-    <row r="42" spans="1:9">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A42" s="9" t="s">
         <v>99</v>
       </c>
@@ -5124,7 +5188,7 @@
       </c>
       <c r="I42" s="11"/>
     </row>
-    <row r="43" spans="1:9">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A43" s="9" t="s">
         <v>101</v>
       </c>
@@ -5149,7 +5213,7 @@
       </c>
       <c r="I43" s="11"/>
     </row>
-    <row r="44" spans="1:9">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A44" s="9" t="s">
         <v>104</v>
       </c>
@@ -5174,7 +5238,7 @@
       </c>
       <c r="I44" s="11"/>
     </row>
-    <row r="45" spans="1:9">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A45" s="9" t="s">
         <v>108</v>
       </c>
@@ -5199,7 +5263,7 @@
       </c>
       <c r="I45" s="11"/>
     </row>
-    <row r="46" spans="1:9">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A46" s="9" t="s">
         <v>111</v>
       </c>
@@ -5224,7 +5288,7 @@
       </c>
       <c r="I46" s="11"/>
     </row>
-    <row r="47" spans="1:9">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A47" s="9" t="s">
         <v>113</v>
       </c>
@@ -5249,15 +5313,15 @@
       </c>
       <c r="I47" s="11"/>
     </row>
-    <row r="48" spans="1:9">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A48" s="9" t="s">
         <v>115</v>
       </c>
       <c r="B48" s="14" t="s">
+        <v>891</v>
+      </c>
+      <c r="C48" s="14" t="s">
         <v>116</v>
-      </c>
-      <c r="C48" s="14" t="s">
-        <v>117</v>
       </c>
       <c r="D48" s="14" t="s">
         <v>103</v>
@@ -5274,12 +5338,12 @@
       </c>
       <c r="I48" s="11"/>
     </row>
-    <row r="49" spans="1:9">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A49" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="B49" s="15" t="s">
         <v>118</v>
-      </c>
-      <c r="B49" s="15" t="s">
-        <v>119</v>
       </c>
       <c r="C49" s="15" t="s">
         <v>32</v>
@@ -5299,18 +5363,18 @@
       </c>
       <c r="I49" s="11"/>
     </row>
-    <row r="50" spans="1:9">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A50" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="B50" s="15" t="s">
         <v>120</v>
-      </c>
-      <c r="B50" s="15" t="s">
-        <v>121</v>
       </c>
       <c r="C50" s="15" t="s">
         <v>32</v>
       </c>
       <c r="D50" s="15" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E50" s="15">
         <v>92</v>
@@ -5324,18 +5388,18 @@
       </c>
       <c r="I50" s="11"/>
     </row>
-    <row r="51" spans="1:9">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A51" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="B51" s="15" t="s">
         <v>123</v>
-      </c>
-      <c r="B51" s="15" t="s">
-        <v>124</v>
       </c>
       <c r="C51" s="15" t="s">
         <v>32</v>
       </c>
       <c r="D51" s="15" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E51" s="15">
         <v>92</v>
@@ -5349,12 +5413,12 @@
       </c>
       <c r="I51" s="11"/>
     </row>
-    <row r="52" spans="1:9">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A52" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="B52" s="15" t="s">
         <v>125</v>
-      </c>
-      <c r="B52" s="15" t="s">
-        <v>126</v>
       </c>
       <c r="C52" s="15" t="s">
         <v>32</v>
@@ -5374,12 +5438,12 @@
       </c>
       <c r="I52" s="11"/>
     </row>
-    <row r="53" spans="1:9">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A53" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="B53" s="15" t="s">
         <v>127</v>
-      </c>
-      <c r="B53" s="15" t="s">
-        <v>128</v>
       </c>
       <c r="C53" s="15" t="s">
         <v>32</v>
@@ -5399,15 +5463,15 @@
       </c>
       <c r="I53" s="11"/>
     </row>
-    <row r="54" spans="1:9">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A54" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="B54" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="B54" s="13" t="s">
+      <c r="C54" s="13" t="s">
         <v>130</v>
-      </c>
-      <c r="C54" s="13" t="s">
-        <v>131</v>
       </c>
       <c r="D54" s="13" t="s">
         <v>4</v>
@@ -5424,18 +5488,18 @@
       </c>
       <c r="I54" s="11"/>
     </row>
-    <row r="55" spans="1:9">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A55" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="B55" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="B55" s="13" t="s">
+      <c r="C55" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="C55" s="13" t="s">
+      <c r="D55" s="13" t="s">
         <v>134</v>
-      </c>
-      <c r="D55" s="13" t="s">
-        <v>135</v>
       </c>
       <c r="E55" s="13">
         <v>90</v>
@@ -5451,18 +5515,18 @@
       </c>
       <c r="I55" s="11"/>
     </row>
-    <row r="56" spans="1:9">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A56" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="B56" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="B56" s="13" t="s">
-        <v>137</v>
-      </c>
       <c r="C56" s="13" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="D56" s="13" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E56" s="13">
         <v>90</v>
@@ -5476,15 +5540,15 @@
       </c>
       <c r="I56" s="11"/>
     </row>
-    <row r="57" spans="1:9">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A57" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="B57" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="B57" s="13" t="s">
+      <c r="C57" s="13" t="s">
         <v>139</v>
-      </c>
-      <c r="C57" s="13" t="s">
-        <v>140</v>
       </c>
       <c r="D57" s="16" t="s">
         <v>39</v>
@@ -5503,18 +5567,18 @@
       </c>
       <c r="I57" s="11"/>
     </row>
-    <row r="58" spans="1:9">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A58" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="B58" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="B58" s="13" t="s">
+      <c r="C58" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="C58" s="13" t="s">
+      <c r="D58" s="13" t="s">
         <v>143</v>
-      </c>
-      <c r="D58" s="13" t="s">
-        <v>144</v>
       </c>
       <c r="E58" s="13">
         <v>49</v>
@@ -5528,18 +5592,18 @@
       </c>
       <c r="I58" s="11"/>
     </row>
-    <row r="59" spans="1:9">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A59" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="B59" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="B59" s="10" t="s">
+      <c r="C59" s="10" t="s">
         <v>146</v>
       </c>
-      <c r="C59" s="10" t="s">
+      <c r="D59" s="10" t="s">
         <v>147</v>
-      </c>
-      <c r="D59" s="10" t="s">
-        <v>148</v>
       </c>
       <c r="E59" s="10">
         <v>100</v>
@@ -5553,18 +5617,18 @@
       </c>
       <c r="I59" s="11"/>
     </row>
-    <row r="60" spans="1:9">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A60" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="B60" s="10" t="s">
         <v>149</v>
-      </c>
-      <c r="B60" s="10" t="s">
-        <v>150</v>
       </c>
       <c r="C60" s="10" t="s">
         <v>88</v>
       </c>
       <c r="D60" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E60" s="10">
         <v>100</v>
@@ -5578,18 +5642,18 @@
       </c>
       <c r="I60" s="11"/>
     </row>
-    <row r="61" spans="1:9">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A61" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="B61" s="18" t="s">
         <v>151</v>
       </c>
-      <c r="B61" s="18" t="s">
+      <c r="C61" s="18" t="s">
         <v>152</v>
       </c>
-      <c r="C61" s="18" t="s">
-        <v>153</v>
-      </c>
       <c r="D61" s="18" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E61" s="18">
         <v>95</v>
@@ -5603,18 +5667,18 @@
       </c>
       <c r="I61" s="11"/>
     </row>
-    <row r="62" spans="1:9">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A62" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="B62" s="18" t="s">
         <v>154</v>
       </c>
-      <c r="B62" s="18" t="s">
+      <c r="C62" s="18" t="s">
         <v>155</v>
       </c>
-      <c r="C62" s="18" t="s">
-        <v>156</v>
-      </c>
       <c r="D62" s="18" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E62" s="18">
         <v>108</v>
@@ -5628,18 +5692,18 @@
       </c>
       <c r="I62" s="11"/>
     </row>
-    <row r="63" spans="1:9">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A63" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="B63" s="18" t="s">
         <v>157</v>
-      </c>
-      <c r="B63" s="18" t="s">
-        <v>158</v>
       </c>
       <c r="C63" s="18" t="s">
         <v>0</v>
       </c>
       <c r="D63" s="18" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E63" s="18">
         <v>91</v>
@@ -5653,18 +5717,18 @@
       </c>
       <c r="I63" s="11"/>
     </row>
-    <row r="64" spans="1:9">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A64" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="B64" s="18" t="s">
         <v>159</v>
       </c>
-      <c r="B64" s="18" t="s">
+      <c r="C64" s="18" t="s">
         <v>160</v>
       </c>
-      <c r="C64" s="18" t="s">
+      <c r="D64" s="18" t="s">
         <v>161</v>
-      </c>
-      <c r="D64" s="18" t="s">
-        <v>162</v>
       </c>
       <c r="E64" s="18">
         <v>98</v>
@@ -5678,18 +5742,18 @@
       </c>
       <c r="I64" s="11"/>
     </row>
-    <row r="65" spans="1:9">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A65" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="B65" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="B65" s="18" t="s">
+      <c r="C65" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="C65" s="18" t="s">
-        <v>165</v>
-      </c>
       <c r="D65" s="18" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E65" s="18">
         <v>103</v>
@@ -5703,18 +5767,18 @@
       </c>
       <c r="I65" s="11"/>
     </row>
-    <row r="66" spans="1:9">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A66" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="B66" s="18" t="s">
         <v>166</v>
-      </c>
-      <c r="B66" s="18" t="s">
-        <v>167</v>
       </c>
       <c r="C66" s="18" t="s">
         <v>42</v>
       </c>
       <c r="D66" s="18" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E66" s="18">
         <v>108</v>
@@ -5728,18 +5792,18 @@
       </c>
       <c r="I66" s="11"/>
     </row>
-    <row r="67" spans="1:9">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A67" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="B67" s="19" t="s">
         <v>168</v>
       </c>
-      <c r="B67" s="19" t="s">
+      <c r="C67" s="19" t="s">
         <v>169</v>
       </c>
-      <c r="C67" s="19" t="s">
+      <c r="D67" s="19" t="s">
         <v>170</v>
-      </c>
-      <c r="D67" s="19" t="s">
-        <v>171</v>
       </c>
       <c r="E67" s="19">
         <v>105</v>
@@ -5753,15 +5817,15 @@
       </c>
       <c r="I67" s="11"/>
     </row>
-    <row r="68" spans="1:9">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A68" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="B68" s="10" t="s">
         <v>172</v>
       </c>
-      <c r="B68" s="10" t="s">
+      <c r="C68" s="10" t="s">
         <v>173</v>
-      </c>
-      <c r="C68" s="10" t="s">
-        <v>174</v>
       </c>
       <c r="D68" s="10" t="s">
         <v>39</v>
@@ -5778,12 +5842,12 @@
       </c>
       <c r="I68" s="11"/>
     </row>
-    <row r="69" spans="1:9">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A69" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="B69" s="10" t="s">
         <v>175</v>
-      </c>
-      <c r="B69" s="10" t="s">
-        <v>176</v>
       </c>
       <c r="C69" s="10" t="s">
         <v>7</v>
@@ -5803,12 +5867,12 @@
       </c>
       <c r="I69" s="11"/>
     </row>
-    <row r="70" spans="1:9">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A70" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="B70" s="10" t="s">
         <v>177</v>
-      </c>
-      <c r="B70" s="10" t="s">
-        <v>178</v>
       </c>
       <c r="C70" s="10" t="s">
         <v>7</v>
@@ -5828,12 +5892,12 @@
       </c>
       <c r="I70" s="11"/>
     </row>
-    <row r="71" spans="1:9">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A71" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="B71" s="10" t="s">
         <v>179</v>
-      </c>
-      <c r="B71" s="10" t="s">
-        <v>180</v>
       </c>
       <c r="C71" s="10" t="s">
         <v>7</v>
@@ -5853,15 +5917,15 @@
       </c>
       <c r="I71" s="11"/>
     </row>
-    <row r="72" spans="1:9">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A72" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="B72" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="B72" s="10" t="s">
-        <v>182</v>
-      </c>
       <c r="C72" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D72" s="10" t="s">
         <v>39</v>
@@ -5878,12 +5942,12 @@
       </c>
       <c r="I72" s="11"/>
     </row>
-    <row r="73" spans="1:9">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A73" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="B73" s="10" t="s">
         <v>183</v>
-      </c>
-      <c r="B73" s="10" t="s">
-        <v>184</v>
       </c>
       <c r="C73" s="10" t="s">
         <v>7</v>
@@ -5903,15 +5967,15 @@
       </c>
       <c r="I73" s="11"/>
     </row>
-    <row r="74" spans="1:9">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A74" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="B74" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="B74" s="10" t="s">
+      <c r="C74" s="10" t="s">
         <v>186</v>
-      </c>
-      <c r="C74" s="10" t="s">
-        <v>187</v>
       </c>
       <c r="D74" s="10" t="s">
         <v>39</v>
@@ -5928,15 +5992,15 @@
       </c>
       <c r="I74" s="11"/>
     </row>
-    <row r="75" spans="1:9">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A75" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="B75" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="B75" s="10" t="s">
-        <v>189</v>
-      </c>
       <c r="C75" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D75" s="10" t="s">
         <v>39</v>
@@ -5953,15 +6017,15 @@
       </c>
       <c r="I75" s="11"/>
     </row>
-    <row r="76" spans="1:9">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A76" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="B76" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="B76" s="10" t="s">
-        <v>191</v>
-      </c>
       <c r="C76" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D76" s="10" t="s">
         <v>39</v>
@@ -5978,18 +6042,18 @@
       </c>
       <c r="I76" s="11"/>
     </row>
-    <row r="77" spans="1:9">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A77" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="B77" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="B77" s="10" t="s">
-        <v>193</v>
-      </c>
       <c r="C77" s="10" t="s">
-        <v>774</v>
+        <v>892</v>
       </c>
       <c r="D77" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E77" s="10">
         <v>60</v>
@@ -6003,18 +6067,18 @@
       </c>
       <c r="I77" s="11"/>
     </row>
-    <row r="78" spans="1:9">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A78" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="B78" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="B78" s="10" t="s">
+      <c r="C78" s="10" t="s">
         <v>195</v>
       </c>
-      <c r="C78" s="10" t="s">
-        <v>196</v>
-      </c>
       <c r="D78" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E78" s="10">
         <v>63</v>
@@ -6028,18 +6092,18 @@
       </c>
       <c r="I78" s="11"/>
     </row>
-    <row r="79" spans="1:9">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A79" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="B79" s="11" t="s">
         <v>197</v>
       </c>
-      <c r="B79" s="11" t="s">
+      <c r="C79" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="C79" s="11" t="s">
-        <v>199</v>
-      </c>
       <c r="D79" s="11" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E79" s="10">
         <v>64</v>
@@ -6053,18 +6117,18 @@
       </c>
       <c r="I79" s="11"/>
     </row>
-    <row r="80" spans="1:9">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A80" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="B80" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="B80" s="10" t="s">
+      <c r="C80" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="C80" s="10" t="s">
-        <v>202</v>
-      </c>
       <c r="D80" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E80" s="10">
         <v>65</v>
@@ -6078,18 +6142,18 @@
       </c>
       <c r="I80" s="11"/>
     </row>
-    <row r="81" spans="1:9">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A81" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="B81" s="10" t="s">
         <v>203</v>
-      </c>
-      <c r="B81" s="10" t="s">
-        <v>204</v>
       </c>
       <c r="C81" s="10" t="s">
         <v>73</v>
       </c>
       <c r="D81" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E81" s="10">
         <v>60</v>
@@ -6103,18 +6167,18 @@
       </c>
       <c r="I81" s="11"/>
     </row>
-    <row r="82" spans="1:9">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A82" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="B82" s="10" t="s">
         <v>205</v>
       </c>
-      <c r="B82" s="10" t="s">
+      <c r="C82" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="C82" s="10" t="s">
-        <v>207</v>
-      </c>
       <c r="D82" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E82" s="10">
         <v>68</v>
@@ -6128,15 +6192,15 @@
       </c>
       <c r="I82" s="11"/>
     </row>
-    <row r="83" spans="1:9">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A83" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="B83" s="10" t="s">
         <v>208</v>
       </c>
-      <c r="B83" s="10" t="s">
-        <v>209</v>
-      </c>
       <c r="C83" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D83" s="10" t="s">
         <v>39</v>
@@ -6153,18 +6217,18 @@
       </c>
       <c r="I83" s="11"/>
     </row>
-    <row r="84" spans="1:9">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A84" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="B84" s="21" t="s">
         <v>210</v>
       </c>
-      <c r="B84" s="21" t="s">
-        <v>211</v>
-      </c>
       <c r="C84" s="21" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D84" s="21" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E84" s="21">
         <v>64</v>
@@ -6178,18 +6242,18 @@
       </c>
       <c r="I84" s="11"/>
     </row>
-    <row r="85" spans="1:9">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A85" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="B85" s="21" t="s">
         <v>212</v>
       </c>
-      <c r="B85" s="21" t="s">
-        <v>213</v>
-      </c>
       <c r="C85" s="21" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D85" s="21" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E85" s="21">
         <v>64</v>
@@ -6203,18 +6267,18 @@
       </c>
       <c r="I85" s="11"/>
     </row>
-    <row r="86" spans="1:9">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A86" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="B86" s="10" t="s">
         <v>214</v>
       </c>
-      <c r="B86" s="10" t="s">
-        <v>215</v>
-      </c>
       <c r="C86" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D86" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E86" s="10">
         <v>65</v>
@@ -6228,18 +6292,18 @@
       </c>
       <c r="I86" s="11"/>
     </row>
-    <row r="87" spans="1:9">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A87" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="B87" s="10" t="s">
         <v>216</v>
       </c>
-      <c r="B87" s="10" t="s">
-        <v>217</v>
-      </c>
       <c r="C87" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D87" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E87" s="10">
         <v>65</v>
@@ -6253,18 +6317,18 @@
       </c>
       <c r="I87" s="11"/>
     </row>
-    <row r="88" spans="1:9">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A88" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="B88" s="10" t="s">
         <v>218</v>
       </c>
-      <c r="B88" s="10" t="s">
-        <v>219</v>
-      </c>
       <c r="C88" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D88" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E88" s="10">
         <v>65</v>
@@ -6278,18 +6342,18 @@
       </c>
       <c r="I88" s="11"/>
     </row>
-    <row r="89" spans="1:9">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A89" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="B89" s="10" t="s">
         <v>220</v>
       </c>
-      <c r="B89" s="10" t="s">
+      <c r="C89" s="10" t="s">
         <v>221</v>
       </c>
-      <c r="C89" s="10" t="s">
-        <v>222</v>
-      </c>
       <c r="D89" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E89" s="10">
         <v>68</v>
@@ -6303,18 +6367,18 @@
       </c>
       <c r="I89" s="11"/>
     </row>
-    <row r="90" spans="1:9">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A90" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="B90" s="10" t="s">
         <v>223</v>
       </c>
-      <c r="B90" s="10" t="s">
+      <c r="C90" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="D90" s="10" t="s">
         <v>224</v>
-      </c>
-      <c r="C90" s="10" t="s">
-        <v>222</v>
-      </c>
-      <c r="D90" s="10" t="s">
-        <v>225</v>
       </c>
       <c r="E90" s="10">
         <v>78</v>
@@ -6328,18 +6392,18 @@
       </c>
       <c r="I90" s="11"/>
     </row>
-    <row r="91" spans="1:9">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A91" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="B91" s="10" t="s">
         <v>226</v>
       </c>
-      <c r="B91" s="10" t="s">
+      <c r="C91" s="10" t="s">
         <v>227</v>
       </c>
-      <c r="C91" s="10" t="s">
-        <v>228</v>
-      </c>
       <c r="D91" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E91" s="10">
         <v>82</v>
@@ -6353,15 +6417,15 @@
       </c>
       <c r="I91" s="11"/>
     </row>
-    <row r="92" spans="1:9">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A92" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="B92" s="11" t="s">
         <v>229</v>
       </c>
-      <c r="B92" s="11" t="s">
-        <v>230</v>
-      </c>
       <c r="C92" s="11" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D92" s="11" t="s">
         <v>39</v>
@@ -6378,15 +6442,15 @@
       </c>
       <c r="I92" s="11"/>
     </row>
-    <row r="93" spans="1:9">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A93" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="B93" s="10" t="s">
         <v>231</v>
       </c>
-      <c r="B93" s="10" t="s">
+      <c r="C93" s="10" t="s">
         <v>232</v>
-      </c>
-      <c r="C93" s="10" t="s">
-        <v>233</v>
       </c>
       <c r="D93" s="10" t="s">
         <v>39</v>
@@ -6403,15 +6467,15 @@
       </c>
       <c r="I93" s="11"/>
     </row>
-    <row r="94" spans="1:9">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A94" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="B94" s="10" t="s">
         <v>234</v>
       </c>
-      <c r="B94" s="10" t="s">
-        <v>235</v>
-      </c>
       <c r="C94" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D94" s="10" t="s">
         <v>39</v>
@@ -6428,15 +6492,15 @@
       </c>
       <c r="I94" s="11"/>
     </row>
-    <row r="95" spans="1:9">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A95" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="B95" s="10" t="s">
         <v>236</v>
       </c>
-      <c r="B95" s="10" t="s">
+      <c r="C95" s="10" t="s">
         <v>237</v>
-      </c>
-      <c r="C95" s="10" t="s">
-        <v>238</v>
       </c>
       <c r="D95" s="10" t="s">
         <v>39</v>
@@ -6453,15 +6517,15 @@
       </c>
       <c r="I95" s="11"/>
     </row>
-    <row r="96" spans="1:9">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A96" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="B96" s="10" t="s">
         <v>239</v>
       </c>
-      <c r="B96" s="10" t="s">
-        <v>240</v>
-      </c>
       <c r="C96" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D96" s="10" t="s">
         <v>39</v>
@@ -6478,18 +6542,18 @@
       </c>
       <c r="I96" s="11"/>
     </row>
-    <row r="97" spans="1:9">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A97" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="B97" s="10" t="s">
         <v>241</v>
       </c>
-      <c r="B97" s="10" t="s">
-        <v>242</v>
-      </c>
       <c r="C97" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D97" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E97" s="10">
         <v>94</v>
@@ -6503,12 +6567,12 @@
       </c>
       <c r="I97" s="11"/>
     </row>
-    <row r="98" spans="1:9">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A98" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="B98" s="10" t="s">
         <v>243</v>
-      </c>
-      <c r="B98" s="10" t="s">
-        <v>244</v>
       </c>
       <c r="C98" s="10" t="s">
         <v>7</v>
@@ -6528,18 +6592,18 @@
       </c>
       <c r="I98" s="11"/>
     </row>
-    <row r="99" spans="1:9">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A99" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="B99" s="11" t="s">
         <v>245</v>
       </c>
-      <c r="B99" s="11" t="s">
-        <v>246</v>
-      </c>
       <c r="C99" s="11" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D99" s="11" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E99" s="10">
         <v>68</v>
@@ -6553,18 +6617,18 @@
       </c>
       <c r="I99" s="11"/>
     </row>
-    <row r="100" spans="1:9">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A100" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="B100" s="11" t="s">
         <v>247</v>
-      </c>
-      <c r="B100" s="11" t="s">
-        <v>248</v>
       </c>
       <c r="C100" s="10" t="s">
         <v>73</v>
       </c>
       <c r="D100" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E100" s="10">
         <v>63</v>
@@ -6578,18 +6642,18 @@
       </c>
       <c r="I100" s="11"/>
     </row>
-    <row r="101" spans="1:9">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A101" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="B101" s="10" t="s">
         <v>249</v>
       </c>
-      <c r="B101" s="10" t="s">
+      <c r="C101" s="10" t="s">
         <v>250</v>
       </c>
-      <c r="C101" s="10" t="s">
-        <v>251</v>
-      </c>
       <c r="D101" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E101" s="10">
         <v>65</v>
@@ -6603,18 +6667,18 @@
       </c>
       <c r="I101" s="11"/>
     </row>
-    <row r="102" spans="1:9">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A102" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="B102" s="22" t="s">
         <v>252</v>
       </c>
-      <c r="B102" s="22" t="s">
+      <c r="C102" s="22" t="s">
         <v>253</v>
       </c>
-      <c r="C102" s="22" t="s">
+      <c r="D102" s="22" t="s">
         <v>254</v>
-      </c>
-      <c r="D102" s="22" t="s">
-        <v>255</v>
       </c>
       <c r="E102" s="22">
         <v>148</v>
@@ -6628,18 +6692,18 @@
       </c>
       <c r="I102" s="11"/>
     </row>
-    <row r="103" spans="1:9">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A103" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="B103" s="22" t="s">
         <v>256</v>
       </c>
-      <c r="B103" s="22" t="s">
+      <c r="C103" s="22" t="s">
         <v>257</v>
       </c>
-      <c r="C103" s="22" t="s">
+      <c r="D103" s="22" t="s">
         <v>258</v>
-      </c>
-      <c r="D103" s="22" t="s">
-        <v>259</v>
       </c>
       <c r="E103" s="22">
         <v>113</v>
@@ -6653,18 +6717,18 @@
       </c>
       <c r="I103" s="11"/>
     </row>
-    <row r="104" spans="1:9">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A104" s="9" t="s">
+        <v>259</v>
+      </c>
+      <c r="B104" s="22" t="s">
         <v>260</v>
       </c>
-      <c r="B104" s="22" t="s">
+      <c r="C104" s="22" t="s">
         <v>261</v>
       </c>
-      <c r="C104" s="22" t="s">
+      <c r="D104" s="22" t="s">
         <v>262</v>
-      </c>
-      <c r="D104" s="22" t="s">
-        <v>263</v>
       </c>
       <c r="E104" s="22">
         <v>125</v>
@@ -6678,18 +6742,18 @@
       </c>
       <c r="I104" s="11"/>
     </row>
-    <row r="105" spans="1:9">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A105" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="B105" s="22" t="s">
         <v>264</v>
       </c>
-      <c r="B105" s="22" t="s">
+      <c r="C105" s="22" t="s">
         <v>265</v>
       </c>
-      <c r="C105" s="22" t="s">
-        <v>266</v>
-      </c>
       <c r="D105" s="22" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E105" s="22">
         <v>118</v>
@@ -6703,18 +6767,18 @@
       </c>
       <c r="I105" s="11"/>
     </row>
-    <row r="106" spans="1:9">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A106" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="B106" s="22" t="s">
         <v>267</v>
       </c>
-      <c r="B106" s="22" t="s">
+      <c r="C106" s="22" t="s">
+        <v>253</v>
+      </c>
+      <c r="D106" s="22" t="s">
         <v>268</v>
-      </c>
-      <c r="C106" s="22" t="s">
-        <v>254</v>
-      </c>
-      <c r="D106" s="22" t="s">
-        <v>269</v>
       </c>
       <c r="E106" s="22">
         <v>140</v>
@@ -6728,15 +6792,15 @@
       </c>
       <c r="I106" s="11"/>
     </row>
-    <row r="107" spans="1:9">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A107" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="B107" s="10" t="s">
         <v>270</v>
       </c>
-      <c r="B107" s="10" t="s">
+      <c r="C107" s="10" t="s">
         <v>271</v>
-      </c>
-      <c r="C107" s="10" t="s">
-        <v>272</v>
       </c>
       <c r="D107" s="10" t="s">
         <v>4</v>
@@ -6753,18 +6817,18 @@
       </c>
       <c r="I107" s="11"/>
     </row>
-    <row r="108" spans="1:9">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A108" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="B108" s="10" t="s">
         <v>273</v>
-      </c>
-      <c r="B108" s="10" t="s">
-        <v>274</v>
       </c>
       <c r="C108" s="10" t="s">
         <v>53</v>
       </c>
       <c r="D108" s="10" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E108" s="10">
         <v>70</v>
@@ -6778,12 +6842,12 @@
       </c>
       <c r="I108" s="11"/>
     </row>
-    <row r="109" spans="1:9">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A109" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="B109" s="10" t="s">
         <v>276</v>
-      </c>
-      <c r="B109" s="10" t="s">
-        <v>277</v>
       </c>
       <c r="C109" s="10" t="s">
         <v>88</v>
@@ -6803,18 +6867,18 @@
       </c>
       <c r="I109" s="11"/>
     </row>
-    <row r="110" spans="1:9">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A110" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="B110" s="10" t="s">
         <v>278</v>
       </c>
-      <c r="B110" s="10" t="s">
-        <v>279</v>
-      </c>
       <c r="C110" s="10" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D110" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E110" s="10">
         <v>88</v>
@@ -6828,18 +6892,18 @@
       </c>
       <c r="I110" s="11"/>
     </row>
-    <row r="111" spans="1:9">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A111" s="9" t="s">
+        <v>279</v>
+      </c>
+      <c r="B111" s="10" t="s">
         <v>280</v>
       </c>
-      <c r="B111" s="10" t="s">
-        <v>281</v>
-      </c>
       <c r="C111" s="10" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D111" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E111" s="10">
         <v>60</v>
@@ -6853,18 +6917,18 @@
       </c>
       <c r="I111" s="11"/>
     </row>
-    <row r="112" spans="1:9">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A112" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="B112" s="10" t="s">
         <v>282</v>
-      </c>
-      <c r="B112" s="10" t="s">
-        <v>283</v>
       </c>
       <c r="C112" s="10" t="s">
         <v>88</v>
       </c>
       <c r="D112" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E112" s="11">
         <v>93</v>
@@ -6878,12 +6942,12 @@
       </c>
       <c r="I112" s="11"/>
     </row>
-    <row r="113" spans="1:9">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A113" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="B113" s="11" t="s">
         <v>284</v>
-      </c>
-      <c r="B113" s="11" t="s">
-        <v>285</v>
       </c>
       <c r="C113" s="11" t="s">
         <v>7</v>
@@ -6903,18 +6967,18 @@
       </c>
       <c r="I113" s="11"/>
     </row>
-    <row r="114" spans="1:9">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A114" s="9" t="s">
+        <v>285</v>
+      </c>
+      <c r="B114" s="11" t="s">
         <v>286</v>
-      </c>
-      <c r="B114" s="11" t="s">
-        <v>287</v>
       </c>
       <c r="C114" s="11" t="s">
         <v>7</v>
       </c>
       <c r="D114" s="11" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E114" s="10">
         <v>100</v>
@@ -6928,15 +6992,15 @@
       </c>
       <c r="I114" s="11"/>
     </row>
-    <row r="115" spans="1:9">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A115" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="B115" s="10" t="s">
         <v>288</v>
       </c>
-      <c r="B115" s="10" t="s">
+      <c r="C115" s="10" t="s">
         <v>289</v>
-      </c>
-      <c r="C115" s="10" t="s">
-        <v>290</v>
       </c>
       <c r="D115" s="10" t="s">
         <v>39</v>
@@ -6953,18 +7017,18 @@
       </c>
       <c r="I115" s="11"/>
     </row>
-    <row r="116" spans="1:9">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A116" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="B116" s="10" t="s">
         <v>291</v>
       </c>
-      <c r="B116" s="10" t="s">
+      <c r="C116" s="10" t="s">
         <v>292</v>
       </c>
-      <c r="C116" s="10" t="s">
-        <v>293</v>
-      </c>
       <c r="D116" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E116" s="10">
         <v>61</v>
@@ -6978,12 +7042,12 @@
       </c>
       <c r="I116" s="11"/>
     </row>
-    <row r="117" spans="1:9">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A117" s="9" t="s">
+        <v>293</v>
+      </c>
+      <c r="B117" s="10" t="s">
         <v>294</v>
-      </c>
-      <c r="B117" s="10" t="s">
-        <v>295</v>
       </c>
       <c r="C117" s="10" t="s">
         <v>7</v>
@@ -7003,18 +7067,18 @@
       </c>
       <c r="I117" s="11"/>
     </row>
-    <row r="118" spans="1:9">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A118" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="B118" s="10" t="s">
         <v>296</v>
       </c>
-      <c r="B118" s="10" t="s">
+      <c r="C118" s="10" t="s">
         <v>297</v>
       </c>
-      <c r="C118" s="10" t="s">
-        <v>298</v>
-      </c>
       <c r="D118" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E118" s="10">
         <v>76</v>
@@ -7028,18 +7092,18 @@
       </c>
       <c r="I118" s="11"/>
     </row>
-    <row r="119" spans="1:9">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A119" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="B119" s="10" t="s">
         <v>299</v>
       </c>
-      <c r="B119" s="10" t="s">
-        <v>300</v>
-      </c>
       <c r="C119" s="10" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D119" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E119" s="10">
         <v>76</v>
@@ -7053,18 +7117,18 @@
       </c>
       <c r="I119" s="11"/>
     </row>
-    <row r="120" spans="1:9">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A120" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="B120" s="10" t="s">
         <v>301</v>
-      </c>
-      <c r="B120" s="10" t="s">
-        <v>302</v>
       </c>
       <c r="C120" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D120" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E120" s="10">
         <v>92</v>
@@ -7078,15 +7142,15 @@
       </c>
       <c r="I120" s="11"/>
     </row>
-    <row r="121" spans="1:9">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A121" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="B121" s="10" t="s">
         <v>303</v>
       </c>
-      <c r="B121" s="10" t="s">
-        <v>304</v>
-      </c>
       <c r="C121" s="10" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D121" s="10" t="s">
         <v>39</v>
@@ -7103,18 +7167,18 @@
       </c>
       <c r="I121" s="11"/>
     </row>
-    <row r="122" spans="1:9">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A122" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="B122" s="10" t="s">
         <v>305</v>
-      </c>
-      <c r="B122" s="10" t="s">
-        <v>306</v>
       </c>
       <c r="C122" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D122" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E122" s="10">
         <v>92</v>
@@ -7128,18 +7192,18 @@
       </c>
       <c r="I122" s="11"/>
     </row>
-    <row r="123" spans="1:9">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A123" s="9" t="s">
+        <v>306</v>
+      </c>
+      <c r="B123" s="23" t="s">
         <v>307</v>
       </c>
-      <c r="B123" s="23" t="s">
+      <c r="C123" s="23" t="s">
         <v>308</v>
       </c>
-      <c r="C123" s="23" t="s">
+      <c r="D123" s="23" t="s">
         <v>309</v>
-      </c>
-      <c r="D123" s="23" t="s">
-        <v>310</v>
       </c>
       <c r="E123" s="10">
         <v>68</v>
@@ -7153,18 +7217,18 @@
       </c>
       <c r="I123" s="11"/>
     </row>
-    <row r="124" spans="1:9">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A124" s="9" t="s">
+        <v>310</v>
+      </c>
+      <c r="B124" s="10" t="s">
         <v>311</v>
       </c>
-      <c r="B124" s="10" t="s">
+      <c r="C124" s="10" t="s">
         <v>312</v>
       </c>
-      <c r="C124" s="10" t="s">
+      <c r="D124" s="10" t="s">
         <v>313</v>
-      </c>
-      <c r="D124" s="10" t="s">
-        <v>314</v>
       </c>
       <c r="E124" s="10">
         <v>105</v>
@@ -7178,18 +7242,18 @@
       </c>
       <c r="I124" s="11"/>
     </row>
-    <row r="125" spans="1:9">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A125" s="9" t="s">
+        <v>314</v>
+      </c>
+      <c r="B125" s="10" t="s">
         <v>315</v>
-      </c>
-      <c r="B125" s="10" t="s">
-        <v>316</v>
       </c>
       <c r="C125" s="10" t="s">
         <v>32</v>
       </c>
       <c r="D125" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E125" s="10">
         <v>92</v>
@@ -7203,12 +7267,12 @@
       </c>
       <c r="I125" s="11"/>
     </row>
-    <row r="126" spans="1:9">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A126" s="9" t="s">
+        <v>316</v>
+      </c>
+      <c r="B126" s="10" t="s">
         <v>317</v>
-      </c>
-      <c r="B126" s="10" t="s">
-        <v>318</v>
       </c>
       <c r="C126" s="10" t="s">
         <v>3</v>
@@ -7228,18 +7292,18 @@
       </c>
       <c r="I126" s="11"/>
     </row>
-    <row r="127" spans="1:9">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A127" s="9" t="s">
+        <v>318</v>
+      </c>
+      <c r="B127" s="10" t="s">
         <v>319</v>
       </c>
-      <c r="B127" s="10" t="s">
+      <c r="C127" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="C127" s="10" t="s">
+      <c r="D127" s="10" t="s">
         <v>321</v>
-      </c>
-      <c r="D127" s="10" t="s">
-        <v>322</v>
       </c>
       <c r="E127" s="10">
         <v>86</v>
@@ -7253,15 +7317,15 @@
       </c>
       <c r="I127" s="11"/>
     </row>
-    <row r="128" spans="1:9">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A128" s="9" t="s">
+        <v>322</v>
+      </c>
+      <c r="B128" s="10" t="s">
         <v>323</v>
       </c>
-      <c r="B128" s="10" t="s">
-        <v>324</v>
-      </c>
       <c r="C128" s="10" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D128" s="10" t="s">
         <v>4</v>
@@ -7278,12 +7342,12 @@
       </c>
       <c r="I128" s="11"/>
     </row>
-    <row r="129" spans="1:9">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A129" s="9" t="s">
+        <v>324</v>
+      </c>
+      <c r="B129" s="10" t="s">
         <v>325</v>
-      </c>
-      <c r="B129" s="10" t="s">
-        <v>326</v>
       </c>
       <c r="C129" s="10" t="s">
         <v>32</v>
@@ -7303,12 +7367,12 @@
       </c>
       <c r="I129" s="11"/>
     </row>
-    <row r="130" spans="1:9">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A130" s="9" t="s">
+        <v>326</v>
+      </c>
+      <c r="B130" s="24" t="s">
         <v>327</v>
-      </c>
-      <c r="B130" s="24" t="s">
-        <v>328</v>
       </c>
       <c r="C130" s="24" t="s">
         <v>32</v>
@@ -7328,18 +7392,18 @@
       </c>
       <c r="I130" s="11"/>
     </row>
-    <row r="131" spans="1:9">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A131" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="B131" s="24" t="s">
         <v>329</v>
       </c>
-      <c r="B131" s="24" t="s">
-        <v>330</v>
-      </c>
       <c r="C131" s="24" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="D131" s="24" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E131" s="24">
         <v>90</v>
@@ -7353,18 +7417,18 @@
       </c>
       <c r="I131" s="11"/>
     </row>
-    <row r="132" spans="1:9">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A132" s="9" t="s">
+        <v>330</v>
+      </c>
+      <c r="B132" s="24" t="s">
         <v>331</v>
       </c>
-      <c r="B132" s="24" t="s">
+      <c r="C132" s="24" t="s">
         <v>332</v>
       </c>
-      <c r="C132" s="24" t="s">
+      <c r="D132" s="24" t="s">
         <v>333</v>
-      </c>
-      <c r="D132" s="24" t="s">
-        <v>334</v>
       </c>
       <c r="E132" s="24">
         <v>120</v>
@@ -7378,18 +7442,18 @@
       </c>
       <c r="I132" s="11"/>
     </row>
-    <row r="133" spans="1:9">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A133" s="9" t="s">
+        <v>334</v>
+      </c>
+      <c r="B133" s="24" t="s">
         <v>335</v>
-      </c>
-      <c r="B133" s="24" t="s">
-        <v>336</v>
       </c>
       <c r="C133" s="24" t="s">
         <v>7</v>
       </c>
       <c r="D133" s="24" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E133" s="24">
         <v>98</v>
@@ -7403,18 +7467,18 @@
       </c>
       <c r="I133" s="11"/>
     </row>
-    <row r="134" spans="1:9">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A134" s="9" t="s">
+        <v>337</v>
+      </c>
+      <c r="B134" s="25" t="s">
         <v>338</v>
-      </c>
-      <c r="B134" s="25" t="s">
-        <v>339</v>
       </c>
       <c r="C134" s="25" t="s">
         <v>32</v>
       </c>
       <c r="D134" s="25" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E134" s="25"/>
       <c r="F134" s="9"/>
@@ -7426,18 +7490,18 @@
       </c>
       <c r="I134" s="11"/>
     </row>
-    <row r="135" spans="1:9">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A135" s="9" t="s">
+        <v>340</v>
+      </c>
+      <c r="B135" s="26" t="s">
         <v>341</v>
-      </c>
-      <c r="B135" s="26" t="s">
-        <v>342</v>
       </c>
       <c r="C135" s="26" t="s">
         <v>85</v>
       </c>
       <c r="D135" s="26" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E135" s="26">
         <v>88</v>
@@ -7451,18 +7515,18 @@
       </c>
       <c r="I135" s="11"/>
     </row>
-    <row r="136" spans="1:9">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A136" s="9" t="s">
+        <v>342</v>
+      </c>
+      <c r="B136" s="26" t="s">
         <v>343</v>
-      </c>
-      <c r="B136" s="26" t="s">
-        <v>344</v>
       </c>
       <c r="C136" s="26" t="s">
         <v>85</v>
       </c>
       <c r="D136" s="26" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E136" s="26">
         <v>88</v>
@@ -7476,18 +7540,18 @@
       </c>
       <c r="I136" s="11"/>
     </row>
-    <row r="137" spans="1:9">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A137" s="9" t="s">
+        <v>344</v>
+      </c>
+      <c r="B137" s="26" t="s">
         <v>345</v>
       </c>
-      <c r="B137" s="26" t="s">
+      <c r="C137" s="26" t="s">
         <v>346</v>
       </c>
-      <c r="C137" s="26" t="s">
+      <c r="D137" s="26" t="s">
         <v>347</v>
-      </c>
-      <c r="D137" s="26" t="s">
-        <v>348</v>
       </c>
       <c r="E137" s="26">
         <v>103</v>
@@ -7501,18 +7565,18 @@
       </c>
       <c r="I137" s="11"/>
     </row>
-    <row r="138" spans="1:9">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A138" s="9" t="s">
+        <v>348</v>
+      </c>
+      <c r="B138" s="26" t="s">
         <v>349</v>
       </c>
-      <c r="B138" s="26" t="s">
+      <c r="C138" s="26" t="s">
         <v>350</v>
       </c>
-      <c r="C138" s="26" t="s">
-        <v>351</v>
-      </c>
       <c r="D138" s="26" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E138" s="26">
         <v>102</v>
@@ -7526,18 +7590,18 @@
       </c>
       <c r="I138" s="11"/>
     </row>
-    <row r="139" spans="1:9">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A139" s="9" t="s">
+        <v>351</v>
+      </c>
+      <c r="B139" s="26" t="s">
         <v>352</v>
       </c>
-      <c r="B139" s="26" t="s">
+      <c r="C139" s="26" t="s">
         <v>353</v>
       </c>
-      <c r="C139" s="26" t="s">
-        <v>354</v>
-      </c>
       <c r="D139" s="26" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E139" s="26">
         <v>110</v>
@@ -7551,18 +7615,18 @@
       </c>
       <c r="I139" s="11"/>
     </row>
-    <row r="140" spans="1:9">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A140" s="9" t="s">
+        <v>354</v>
+      </c>
+      <c r="B140" s="26" t="s">
         <v>355</v>
       </c>
-      <c r="B140" s="26" t="s">
+      <c r="C140" s="26" t="s">
         <v>356</v>
       </c>
-      <c r="C140" s="26" t="s">
-        <v>357</v>
-      </c>
       <c r="D140" s="26" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E140" s="26">
         <v>113</v>
@@ -7576,18 +7640,18 @@
       </c>
       <c r="I140" s="11"/>
     </row>
-    <row r="141" spans="1:9">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A141" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="B141" s="26" t="s">
         <v>358</v>
       </c>
-      <c r="B141" s="26" t="s">
-        <v>359</v>
-      </c>
       <c r="C141" s="26" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D141" s="26" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E141" s="26">
         <v>95</v>
@@ -7601,12 +7665,12 @@
       </c>
       <c r="I141" s="11"/>
     </row>
-    <row r="142" spans="1:9">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A142" s="9" t="s">
+        <v>359</v>
+      </c>
+      <c r="B142" s="11" t="s">
         <v>360</v>
-      </c>
-      <c r="B142" s="11" t="s">
-        <v>361</v>
       </c>
       <c r="C142" s="11" t="s">
         <v>7</v>
@@ -7626,18 +7690,18 @@
       </c>
       <c r="I142" s="11"/>
     </row>
-    <row r="143" spans="1:9">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A143" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="B143" s="10" t="s">
         <v>362</v>
-      </c>
-      <c r="B143" s="10" t="s">
-        <v>363</v>
       </c>
       <c r="C143" s="10" t="s">
         <v>73</v>
       </c>
       <c r="D143" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E143" s="10">
         <v>57</v>
@@ -7651,18 +7715,18 @@
       </c>
       <c r="I143" s="11"/>
     </row>
-    <row r="144" spans="1:9">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A144" s="9" t="s">
+        <v>363</v>
+      </c>
+      <c r="B144" s="10" t="s">
         <v>364</v>
-      </c>
-      <c r="B144" s="10" t="s">
-        <v>365</v>
       </c>
       <c r="C144" s="10" t="s">
         <v>73</v>
       </c>
       <c r="D144" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E144" s="10">
         <v>62</v>
@@ -7676,18 +7740,18 @@
       </c>
       <c r="I144" s="11"/>
     </row>
-    <row r="145" spans="1:9">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A145" s="9" t="s">
+        <v>365</v>
+      </c>
+      <c r="B145" s="10" t="s">
         <v>366</v>
-      </c>
-      <c r="B145" s="10" t="s">
-        <v>367</v>
       </c>
       <c r="C145" s="10" t="s">
         <v>73</v>
       </c>
       <c r="D145" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E145" s="10">
         <v>62</v>
@@ -7701,18 +7765,18 @@
       </c>
       <c r="I145" s="11"/>
     </row>
-    <row r="146" spans="1:9">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A146" s="9" t="s">
+        <v>367</v>
+      </c>
+      <c r="B146" s="10" t="s">
         <v>368</v>
-      </c>
-      <c r="B146" s="10" t="s">
-        <v>369</v>
       </c>
       <c r="C146" s="10" t="s">
         <v>73</v>
       </c>
       <c r="D146" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E146" s="10">
         <v>62</v>
@@ -7726,18 +7790,18 @@
       </c>
       <c r="I146" s="11"/>
     </row>
-    <row r="147" spans="1:9">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A147" s="9" t="s">
+        <v>369</v>
+      </c>
+      <c r="B147" s="10" t="s">
         <v>370</v>
-      </c>
-      <c r="B147" s="10" t="s">
-        <v>371</v>
       </c>
       <c r="C147" s="10" t="s">
         <v>73</v>
       </c>
       <c r="D147" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E147" s="10">
         <v>62</v>
@@ -7751,12 +7815,12 @@
       </c>
       <c r="I147" s="11"/>
     </row>
-    <row r="148" spans="1:9">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A148" s="9" t="s">
+        <v>371</v>
+      </c>
+      <c r="B148" s="11" t="s">
         <v>372</v>
-      </c>
-      <c r="B148" s="11" t="s">
-        <v>373</v>
       </c>
       <c r="C148" s="11" t="s">
         <v>7</v>
@@ -7776,15 +7840,15 @@
       </c>
       <c r="I148" s="11"/>
     </row>
-    <row r="149" spans="1:9">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A149" s="9" t="s">
+        <v>373</v>
+      </c>
+      <c r="B149" s="10" t="s">
         <v>374</v>
       </c>
-      <c r="B149" s="10" t="s">
+      <c r="C149" s="10" t="s">
         <v>375</v>
-      </c>
-      <c r="C149" s="10" t="s">
-        <v>376</v>
       </c>
       <c r="D149" s="10" t="s">
         <v>17</v>
@@ -7801,18 +7865,18 @@
       </c>
       <c r="I149" s="11"/>
     </row>
-    <row r="150" spans="1:9">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A150" s="9" t="s">
+        <v>376</v>
+      </c>
+      <c r="B150" s="10" t="s">
         <v>377</v>
       </c>
-      <c r="B150" s="10" t="s">
+      <c r="C150" s="10" t="s">
         <v>378</v>
       </c>
-      <c r="C150" s="10" t="s">
+      <c r="D150" s="10" t="s">
         <v>379</v>
-      </c>
-      <c r="D150" s="10" t="s">
-        <v>380</v>
       </c>
       <c r="E150" s="10">
         <v>97</v>
@@ -7826,12 +7890,12 @@
       </c>
       <c r="I150" s="11"/>
     </row>
-    <row r="151" spans="1:9">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A151" s="9" t="s">
+        <v>380</v>
+      </c>
+      <c r="B151" s="11" t="s">
         <v>381</v>
-      </c>
-      <c r="B151" s="11" t="s">
-        <v>382</v>
       </c>
       <c r="C151" s="11" t="s">
         <v>7</v>
@@ -7851,18 +7915,18 @@
       </c>
       <c r="I151" s="11"/>
     </row>
-    <row r="152" spans="1:9">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A152" s="9" t="s">
+        <v>382</v>
+      </c>
+      <c r="B152" s="13" t="s">
         <v>383</v>
       </c>
-      <c r="B152" s="13" t="s">
+      <c r="C152" s="13" t="s">
         <v>384</v>
       </c>
-      <c r="C152" s="13" t="s">
+      <c r="D152" s="13" t="s">
         <v>385</v>
-      </c>
-      <c r="D152" s="13" t="s">
-        <v>386</v>
       </c>
       <c r="E152" s="13">
         <v>90</v>
@@ -7874,22 +7938,22 @@
         <v>208</v>
       </c>
       <c r="H152" s="13">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="I152" s="11"/>
     </row>
-    <row r="153" spans="1:9">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A153" s="9" t="s">
+        <v>386</v>
+      </c>
+      <c r="B153" s="13" t="s">
         <v>387</v>
       </c>
-      <c r="B153" s="13" t="s">
+      <c r="C153" s="13" t="s">
         <v>388</v>
       </c>
-      <c r="C153" s="13" t="s">
-        <v>389</v>
-      </c>
       <c r="D153" s="13" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E153" s="13">
         <v>100</v>
@@ -7901,22 +7965,22 @@
         <v>216</v>
       </c>
       <c r="H153" s="13">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="I153" s="11"/>
     </row>
-    <row r="154" spans="1:9">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A154" s="9" t="s">
+        <v>389</v>
+      </c>
+      <c r="B154" s="10" t="s">
         <v>390</v>
       </c>
-      <c r="B154" s="10" t="s">
+      <c r="C154" s="10" t="s">
         <v>391</v>
       </c>
-      <c r="C154" s="10" t="s">
+      <c r="D154" s="10" t="s">
         <v>392</v>
-      </c>
-      <c r="D154" s="10" t="s">
-        <v>393</v>
       </c>
       <c r="E154" s="10">
         <v>96</v>
@@ -7928,22 +7992,22 @@
         <v>208</v>
       </c>
       <c r="H154" s="10">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="I154" s="11"/>
     </row>
-    <row r="155" spans="1:9">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A155" s="9" t="s">
+        <v>393</v>
+      </c>
+      <c r="B155" s="10" t="s">
         <v>394</v>
       </c>
-      <c r="B155" s="10" t="s">
-        <v>395</v>
-      </c>
       <c r="C155" s="10" t="s">
+        <v>391</v>
+      </c>
+      <c r="D155" s="10" t="s">
         <v>392</v>
-      </c>
-      <c r="D155" s="10" t="s">
-        <v>393</v>
       </c>
       <c r="E155" s="10">
         <v>95</v>
@@ -7959,18 +8023,18 @@
       </c>
       <c r="I155" s="11"/>
     </row>
-    <row r="156" spans="1:9">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A156" s="9" t="s">
+        <v>395</v>
+      </c>
+      <c r="B156" s="10" t="s">
         <v>396</v>
       </c>
-      <c r="B156" s="10" t="s">
+      <c r="C156" s="10" t="s">
         <v>397</v>
       </c>
-      <c r="C156" s="10" t="s">
-        <v>398</v>
-      </c>
       <c r="D156" s="10" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="E156" s="10">
         <v>107</v>
@@ -7982,22 +8046,22 @@
         <v>215</v>
       </c>
       <c r="H156" s="10">
-        <v>4.5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="I156" s="11"/>
     </row>
-    <row r="157" spans="1:9">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A157" s="9" t="s">
+        <v>398</v>
+      </c>
+      <c r="B157" s="13" t="s">
         <v>399</v>
       </c>
-      <c r="B157" s="13" t="s">
+      <c r="C157" s="13" t="s">
         <v>400</v>
       </c>
-      <c r="C157" s="13" t="s">
-        <v>401</v>
-      </c>
       <c r="D157" s="13" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E157" s="13">
         <v>92</v>
@@ -8013,18 +8077,18 @@
       </c>
       <c r="I157" s="11"/>
     </row>
-    <row r="158" spans="1:9">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A158" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="B158" s="27" t="s">
         <v>402</v>
       </c>
-      <c r="B158" s="27" t="s">
-        <v>403</v>
-      </c>
       <c r="C158" s="27" t="s">
-        <v>776</v>
+        <v>893</v>
       </c>
       <c r="D158" s="27" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="E158" s="27">
         <v>94</v>
@@ -8040,18 +8104,18 @@
       </c>
       <c r="I158" s="11"/>
     </row>
-    <row r="159" spans="1:9">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A159" s="9" t="s">
+        <v>403</v>
+      </c>
+      <c r="B159" s="10" t="s">
         <v>404</v>
       </c>
-      <c r="B159" s="10" t="s">
+      <c r="C159" s="10" t="s">
         <v>405</v>
       </c>
-      <c r="C159" s="10" t="s">
-        <v>406</v>
-      </c>
       <c r="D159" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E159" s="10">
         <v>120</v>
@@ -8065,18 +8129,18 @@
       </c>
       <c r="I159" s="11"/>
     </row>
-    <row r="160" spans="1:9">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A160" s="9" t="s">
+        <v>406</v>
+      </c>
+      <c r="B160" s="10" t="s">
         <v>407</v>
       </c>
-      <c r="B160" s="10" t="s">
+      <c r="C160" s="10" t="s">
         <v>408</v>
       </c>
-      <c r="C160" s="10" t="s">
+      <c r="D160" s="10" t="s">
         <v>409</v>
-      </c>
-      <c r="D160" s="10" t="s">
-        <v>410</v>
       </c>
       <c r="E160" s="10">
         <v>85</v>
@@ -8090,18 +8154,18 @@
       </c>
       <c r="I160" s="11"/>
     </row>
-    <row r="161" spans="1:9">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A161" s="9" t="s">
+        <v>410</v>
+      </c>
+      <c r="B161" s="22" t="s">
+        <v>772</v>
+      </c>
+      <c r="C161" s="22" t="s">
         <v>411</v>
       </c>
-      <c r="B161" s="22" t="s">
-        <v>777</v>
-      </c>
-      <c r="C161" s="22" t="s">
+      <c r="D161" s="22" t="s">
         <v>412</v>
-      </c>
-      <c r="D161" s="22" t="s">
-        <v>413</v>
       </c>
       <c r="E161" s="22">
         <v>104</v>
@@ -8117,18 +8181,18 @@
       </c>
       <c r="I161" s="11"/>
     </row>
-    <row r="162" spans="1:9">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A162" s="9" t="s">
+        <v>413</v>
+      </c>
+      <c r="B162" s="22" t="s">
         <v>414</v>
       </c>
-      <c r="B162" s="22" t="s">
+      <c r="C162" s="22" t="s">
         <v>415</v>
       </c>
-      <c r="C162" s="22" t="s">
-        <v>416</v>
-      </c>
       <c r="D162" s="22" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E162" s="22">
         <v>117</v>
@@ -8144,18 +8208,18 @@
       </c>
       <c r="I162" s="11"/>
     </row>
-    <row r="163" spans="1:9">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A163" s="9" t="s">
+        <v>416</v>
+      </c>
+      <c r="B163" s="22" t="s">
         <v>417</v>
       </c>
-      <c r="B163" s="22" t="s">
+      <c r="C163" s="22" t="s">
         <v>418</v>
       </c>
-      <c r="C163" s="22" t="s">
-        <v>419</v>
-      </c>
       <c r="D163" s="22" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E163" s="22">
         <v>117</v>
@@ -8171,18 +8235,18 @@
       </c>
       <c r="I163" s="11"/>
     </row>
-    <row r="164" spans="1:9">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A164" s="9" t="s">
+        <v>419</v>
+      </c>
+      <c r="B164" s="22" t="s">
+        <v>894</v>
+      </c>
+      <c r="C164" s="22" t="s">
         <v>420</v>
       </c>
-      <c r="B164" s="22" t="s">
-        <v>778</v>
-      </c>
-      <c r="C164" s="22" t="s">
-        <v>421</v>
-      </c>
       <c r="D164" s="22" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E164" s="22">
         <v>110</v>
@@ -8194,22 +8258,22 @@
         <v>208</v>
       </c>
       <c r="H164" s="22">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="I164" s="11"/>
     </row>
-    <row r="165" spans="1:9">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A165" s="9" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B165" s="22" t="s">
-        <v>779</v>
+        <v>773</v>
       </c>
       <c r="C165" s="22" t="s">
-        <v>780</v>
+        <v>774</v>
       </c>
       <c r="D165" s="22" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E165" s="22">
         <v>108</v>
@@ -8225,9 +8289,9 @@
       </c>
       <c r="I165" s="11"/>
     </row>
-    <row r="166" spans="1:9">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A166" s="9" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B166" s="30"/>
       <c r="C166" s="30"/>
@@ -8238,18 +8302,18 @@
       <c r="H166" s="30"/>
       <c r="I166" s="11"/>
     </row>
-    <row r="167" spans="1:9">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A167" s="9" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B167" s="18" t="s">
-        <v>781</v>
+        <v>775</v>
       </c>
       <c r="C167" s="18" t="s">
-        <v>782</v>
+        <v>776</v>
       </c>
       <c r="D167" s="18" t="s">
-        <v>783</v>
+        <v>777</v>
       </c>
       <c r="E167" s="18">
         <v>80</v>
@@ -8265,18 +8329,18 @@
       </c>
       <c r="I167" s="11"/>
     </row>
-    <row r="168" spans="1:9">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A168" s="9" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B168" s="18" t="s">
-        <v>784</v>
+        <v>778</v>
       </c>
       <c r="C168" s="18" t="s">
-        <v>785</v>
+        <v>895</v>
       </c>
       <c r="D168" s="18" t="s">
-        <v>786</v>
+        <v>779</v>
       </c>
       <c r="E168" s="18">
         <v>110</v>
@@ -8292,18 +8356,18 @@
       </c>
       <c r="I168" s="11"/>
     </row>
-    <row r="169" spans="1:9">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A169" s="31" t="s">
+        <v>425</v>
+      </c>
+      <c r="B169" s="18" t="s">
+        <v>780</v>
+      </c>
+      <c r="C169" s="18" t="s">
         <v>426</v>
       </c>
-      <c r="B169" s="18" t="s">
-        <v>787</v>
-      </c>
-      <c r="C169" s="18" t="s">
+      <c r="D169" s="18" t="s">
         <v>427</v>
-      </c>
-      <c r="D169" s="18" t="s">
-        <v>428</v>
       </c>
       <c r="E169" s="18">
         <v>83</v>
@@ -8315,22 +8379,22 @@
         <v>208</v>
       </c>
       <c r="H169" s="18">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="I169" s="32"/>
     </row>
-    <row r="170" spans="1:9">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A170" s="31" t="s">
+        <v>428</v>
+      </c>
+      <c r="B170" s="18" t="s">
+        <v>781</v>
+      </c>
+      <c r="C170" s="18" t="s">
         <v>429</v>
       </c>
-      <c r="B170" s="18" t="s">
-        <v>788</v>
-      </c>
-      <c r="C170" s="18" t="s">
-        <v>430</v>
-      </c>
       <c r="D170" s="18" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E170" s="32">
         <v>110</v>
@@ -8346,18 +8410,18 @@
       </c>
       <c r="I170" s="32"/>
     </row>
-    <row r="171" spans="1:9">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A171" s="31" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B171" s="18" t="s">
-        <v>789</v>
+        <v>782</v>
       </c>
       <c r="C171" s="18" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D171" s="18" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E171" s="32">
         <v>112</v>
@@ -8373,18 +8437,18 @@
       </c>
       <c r="I171" s="32"/>
     </row>
-    <row r="172" spans="1:9">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A172" s="31" t="s">
+        <v>431</v>
+      </c>
+      <c r="B172" s="18" t="s">
         <v>432</v>
       </c>
-      <c r="B172" s="18" t="s">
-        <v>433</v>
-      </c>
       <c r="C172" s="18" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D172" s="18" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E172" s="18">
         <v>112</v>
@@ -8400,18 +8464,18 @@
       </c>
       <c r="I172" s="32"/>
     </row>
-    <row r="173" spans="1:9">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A173" s="31" t="s">
+        <v>433</v>
+      </c>
+      <c r="B173" s="18" t="s">
+        <v>896</v>
+      </c>
+      <c r="C173" s="18" t="s">
         <v>434</v>
       </c>
-      <c r="B173" s="18" t="s">
-        <v>790</v>
-      </c>
-      <c r="C173" s="18" t="s">
+      <c r="D173" s="18" t="s">
         <v>435</v>
-      </c>
-      <c r="D173" s="18" t="s">
-        <v>436</v>
       </c>
       <c r="E173" s="18">
         <v>102</v>
@@ -8427,24 +8491,24 @@
       </c>
       <c r="I173" s="32"/>
     </row>
-    <row r="174" spans="1:9">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A174" s="31" t="s">
+        <v>436</v>
+      </c>
+      <c r="B174" s="18" t="s">
+        <v>897</v>
+      </c>
+      <c r="C174" s="18" t="s">
         <v>437</v>
       </c>
-      <c r="B174" s="18" t="s">
-        <v>791</v>
-      </c>
-      <c r="C174" s="18" t="s">
-        <v>438</v>
-      </c>
       <c r="D174" s="18" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E174" s="32">
         <v>130</v>
       </c>
       <c r="F174" s="31">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G174" s="32">
         <v>215</v>
@@ -8454,18 +8518,18 @@
       </c>
       <c r="I174" s="32"/>
     </row>
-    <row r="175" spans="1:9">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A175" s="31" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B175" s="18" t="s">
-        <v>792</v>
+        <v>898</v>
       </c>
       <c r="C175" s="18" t="s">
         <v>32</v>
       </c>
       <c r="D175" s="18" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E175" s="32">
         <v>135</v>
@@ -8481,18 +8545,18 @@
       </c>
       <c r="I175" s="32"/>
     </row>
-    <row r="176" spans="1:9">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A176" s="31" t="s">
+        <v>439</v>
+      </c>
+      <c r="B176" s="18" t="s">
         <v>440</v>
-      </c>
-      <c r="B176" s="18" t="s">
-        <v>441</v>
       </c>
       <c r="C176" s="18" t="s">
         <v>32</v>
       </c>
       <c r="D176" s="18" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E176" s="18">
         <v>135</v>
@@ -8508,18 +8572,18 @@
       </c>
       <c r="I176" s="32"/>
     </row>
-    <row r="177" spans="1:9">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A177" s="31" t="s">
+        <v>441</v>
+      </c>
+      <c r="B177" s="18" t="s">
         <v>442</v>
       </c>
-      <c r="B177" s="18" t="s">
+      <c r="C177" s="18" t="s">
         <v>443</v>
       </c>
-      <c r="C177" s="18" t="s">
-        <v>444</v>
-      </c>
       <c r="D177" s="18" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E177" s="18">
         <v>150</v>
@@ -8531,22 +8595,22 @@
         <v>215</v>
       </c>
       <c r="H177" s="18">
-        <v>4.5999999999999996</v>
+        <v>4.7</v>
       </c>
       <c r="I177" s="32"/>
     </row>
-    <row r="178" spans="1:9">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A178" s="31" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B178" s="18" t="s">
-        <v>793</v>
+        <v>783</v>
       </c>
       <c r="C178" s="18" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D178" s="18" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E178" s="18">
         <v>106</v>
@@ -8562,18 +8626,18 @@
       </c>
       <c r="I178" s="32"/>
     </row>
-    <row r="179" spans="1:9">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A179" s="31" t="s">
+        <v>445</v>
+      </c>
+      <c r="B179" s="18" t="s">
         <v>446</v>
       </c>
-      <c r="B179" s="18" t="s">
+      <c r="C179" s="18" t="s">
         <v>447</v>
       </c>
-      <c r="C179" s="18" t="s">
-        <v>448</v>
-      </c>
       <c r="D179" s="33" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E179" s="18">
         <v>110</v>
@@ -8589,18 +8653,18 @@
       </c>
       <c r="I179" s="32"/>
     </row>
-    <row r="180" spans="1:9">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A180" s="31" t="s">
+        <v>448</v>
+      </c>
+      <c r="B180" s="18" t="s">
+        <v>784</v>
+      </c>
+      <c r="C180" s="18" t="s">
         <v>449</v>
       </c>
-      <c r="B180" s="18" t="s">
-        <v>794</v>
-      </c>
-      <c r="C180" s="18" t="s">
-        <v>450</v>
-      </c>
       <c r="D180" s="18" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E180" s="18">
         <v>96</v>
@@ -8616,18 +8680,18 @@
       </c>
       <c r="I180" s="32"/>
     </row>
-    <row r="181" spans="1:9">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A181" s="9" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B181" s="18" t="s">
-        <v>795</v>
+        <v>899</v>
       </c>
       <c r="C181" s="18" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D181" s="18" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E181" s="18">
         <v>150</v>
@@ -8639,22 +8703,22 @@
         <v>215</v>
       </c>
       <c r="H181" s="18">
-        <v>4.5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="I181" s="11"/>
     </row>
-    <row r="182" spans="1:9">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A182" s="9" t="s">
+        <v>451</v>
+      </c>
+      <c r="B182" s="34" t="s">
+        <v>900</v>
+      </c>
+      <c r="C182" s="34" t="s">
+        <v>308</v>
+      </c>
+      <c r="D182" s="34" t="s">
         <v>452</v>
-      </c>
-      <c r="B182" s="34" t="s">
-        <v>796</v>
-      </c>
-      <c r="C182" s="34" t="s">
-        <v>309</v>
-      </c>
-      <c r="D182" s="34" t="s">
-        <v>453</v>
       </c>
       <c r="E182" s="34">
         <v>108</v>
@@ -8670,18 +8734,18 @@
       </c>
       <c r="I182" s="11"/>
     </row>
-    <row r="183" spans="1:9">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A183" s="9" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B183" s="34" t="s">
-        <v>797</v>
+        <v>785</v>
       </c>
       <c r="C183" s="34" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D183" s="34" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E183" s="34">
         <v>108</v>
@@ -8697,18 +8761,18 @@
       </c>
       <c r="I183" s="11"/>
     </row>
-    <row r="184" spans="1:9">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A184" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="B184" s="35" t="s">
         <v>455</v>
       </c>
-      <c r="B184" s="35" t="s">
+      <c r="C184" s="35" t="s">
         <v>456</v>
       </c>
-      <c r="C184" s="35" t="s">
+      <c r="D184" s="35" t="s">
         <v>457</v>
-      </c>
-      <c r="D184" s="35" t="s">
-        <v>458</v>
       </c>
       <c r="E184" s="35">
         <v>150</v>
@@ -8724,18 +8788,18 @@
       </c>
       <c r="I184" s="38"/>
     </row>
-    <row r="185" spans="1:9">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A185" s="9" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B185" s="18" t="s">
-        <v>798</v>
+        <v>786</v>
       </c>
       <c r="C185" s="18" t="s">
-        <v>799</v>
+        <v>787</v>
       </c>
       <c r="D185" s="18" t="s">
-        <v>800</v>
+        <v>901</v>
       </c>
       <c r="E185" s="18">
         <v>112</v>
@@ -8751,18 +8815,18 @@
       </c>
       <c r="I185" s="11"/>
     </row>
-    <row r="186" spans="1:9">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A186" s="9" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B186" s="34" t="s">
-        <v>801</v>
+        <v>788</v>
       </c>
       <c r="C186" s="34" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D186" s="34" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E186" s="34">
         <v>108</v>
@@ -8778,18 +8842,18 @@
       </c>
       <c r="I186" s="11"/>
     </row>
-    <row r="187" spans="1:9">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A187" s="9" t="s">
-        <v>802</v>
+        <v>902</v>
       </c>
       <c r="B187" s="18" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C187" s="18" t="s">
-        <v>803</v>
+        <v>789</v>
       </c>
       <c r="D187" s="18" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E187" s="18">
         <v>150</v>
@@ -8801,22 +8865,22 @@
         <v>215</v>
       </c>
       <c r="H187" s="18">
-        <v>4.4000000000000004</v>
+        <v>4.5</v>
       </c>
       <c r="I187" s="11"/>
     </row>
-    <row r="188" spans="1:9">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A188" s="9" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B188" s="18" t="s">
-        <v>804</v>
+        <v>790</v>
       </c>
       <c r="C188" s="18" t="s">
-        <v>805</v>
+        <v>791</v>
       </c>
       <c r="D188" s="18" t="s">
-        <v>806</v>
+        <v>903</v>
       </c>
       <c r="E188" s="18">
         <v>110</v>
@@ -8832,18 +8896,18 @@
       </c>
       <c r="I188" s="11"/>
     </row>
-    <row r="189" spans="1:9">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A189" s="9" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B189" s="18" t="s">
-        <v>807</v>
+        <v>792</v>
       </c>
       <c r="C189" s="18" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D189" s="18" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E189" s="18">
         <v>150</v>
@@ -8855,22 +8919,22 @@
         <v>215</v>
       </c>
       <c r="H189" s="18">
-        <v>4.4000000000000004</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="I189" s="11"/>
     </row>
-    <row r="190" spans="1:9">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A190" s="9" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B190" s="10" t="s">
-        <v>808</v>
+        <v>793</v>
       </c>
       <c r="C190" s="10" t="s">
-        <v>809</v>
+        <v>794</v>
       </c>
       <c r="D190" s="10" t="s">
-        <v>810</v>
+        <v>904</v>
       </c>
       <c r="E190" s="11">
         <v>152</v>
@@ -8886,18 +8950,18 @@
       </c>
       <c r="I190" s="11"/>
     </row>
-    <row r="191" spans="1:9">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A191" s="9" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B191" s="18" t="s">
-        <v>792</v>
+        <v>905</v>
       </c>
       <c r="C191" s="18" t="s">
-        <v>803</v>
+        <v>789</v>
       </c>
       <c r="D191" s="18" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E191" s="32">
         <v>150</v>
@@ -8913,9 +8977,9 @@
       </c>
       <c r="I191" s="11"/>
     </row>
-    <row r="192" spans="1:9">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A192" s="9" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B192" s="27"/>
       <c r="C192" s="27"/>
@@ -8926,9 +8990,9 @@
       <c r="H192" s="27"/>
       <c r="I192" s="11"/>
     </row>
-    <row r="193" spans="1:9">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A193" s="9" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B193" s="27"/>
       <c r="C193" s="27"/>
@@ -8939,18 +9003,18 @@
       <c r="H193" s="39"/>
       <c r="I193" s="37"/>
     </row>
-    <row r="194" spans="1:9">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A194" s="9" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B194" s="41" t="s">
-        <v>811</v>
+        <v>795</v>
       </c>
       <c r="C194" s="42" t="s">
-        <v>812</v>
+        <v>796</v>
       </c>
       <c r="D194" s="43" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E194" s="41">
         <v>138</v>
@@ -8966,15 +9030,15 @@
       </c>
       <c r="I194" s="37"/>
     </row>
-    <row r="195" spans="1:9">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A195" s="9" t="s">
+        <v>467</v>
+      </c>
+      <c r="B195" s="41" t="s">
+        <v>797</v>
+      </c>
+      <c r="C195" s="42" t="s">
         <v>468</v>
-      </c>
-      <c r="B195" s="41" t="s">
-        <v>813</v>
-      </c>
-      <c r="C195" s="42" t="s">
-        <v>469</v>
       </c>
       <c r="D195" s="43" t="s">
         <v>39</v>
@@ -8993,18 +9057,18 @@
       </c>
       <c r="I195" s="37"/>
     </row>
-    <row r="196" spans="1:9">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A196" s="9" t="s">
+        <v>469</v>
+      </c>
+      <c r="B196" s="45" t="s">
+        <v>906</v>
+      </c>
+      <c r="C196" s="45" t="s">
+        <v>798</v>
+      </c>
+      <c r="D196" s="45" t="s">
         <v>470</v>
-      </c>
-      <c r="B196" s="45" t="s">
-        <v>814</v>
-      </c>
-      <c r="C196" s="45" t="s">
-        <v>815</v>
-      </c>
-      <c r="D196" s="45" t="s">
-        <v>471</v>
       </c>
       <c r="E196" s="45">
         <v>105</v>
@@ -9020,18 +9084,18 @@
       </c>
       <c r="I196" s="11"/>
     </row>
-    <row r="197" spans="1:9">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A197" s="9" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B197" s="45" t="s">
-        <v>816</v>
+        <v>799</v>
       </c>
       <c r="C197" s="45" t="s">
-        <v>817</v>
+        <v>907</v>
       </c>
       <c r="D197" s="45" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E197" s="45">
         <v>100</v>
@@ -9047,18 +9111,18 @@
       </c>
       <c r="I197" s="37"/>
     </row>
-    <row r="198" spans="1:9">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A198" s="9" t="s">
+        <v>472</v>
+      </c>
+      <c r="B198" s="45" t="s">
+        <v>908</v>
+      </c>
+      <c r="C198" s="45" t="s">
         <v>473</v>
       </c>
-      <c r="B198" s="45" t="s">
-        <v>818</v>
-      </c>
-      <c r="C198" s="45" t="s">
+      <c r="D198" s="45" t="s">
         <v>474</v>
-      </c>
-      <c r="D198" s="45" t="s">
-        <v>475</v>
       </c>
       <c r="E198" s="45">
         <v>129</v>
@@ -9074,18 +9138,18 @@
       </c>
       <c r="I198" s="37"/>
     </row>
-    <row r="199" spans="1:9">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A199" s="9" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B199" s="45" t="s">
-        <v>819</v>
+        <v>800</v>
       </c>
       <c r="C199" s="45" t="s">
-        <v>820</v>
+        <v>801</v>
       </c>
       <c r="D199" s="45" t="s">
-        <v>821</v>
+        <v>909</v>
       </c>
       <c r="E199" s="45">
         <v>95</v>
@@ -9101,9 +9165,9 @@
       </c>
       <c r="I199" s="37"/>
     </row>
-    <row r="200" spans="1:9">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A200" s="9" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B200" s="30"/>
       <c r="C200" s="30"/>
@@ -9114,9 +9178,9 @@
       <c r="H200" s="30"/>
       <c r="I200" s="37"/>
     </row>
-    <row r="201" spans="1:9">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A201" s="9" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B201" s="10"/>
       <c r="C201" s="10"/>
@@ -9127,9 +9191,9 @@
       <c r="H201" s="10"/>
       <c r="I201" s="37"/>
     </row>
-    <row r="202" spans="1:9">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A202" s="9" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B202" s="10"/>
       <c r="C202" s="10"/>
@@ -9140,9 +9204,9 @@
       <c r="H202" s="10"/>
       <c r="I202" s="37"/>
     </row>
-    <row r="203" spans="1:9">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A203" s="9" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B203" s="10"/>
       <c r="C203" s="10"/>
@@ -9153,18 +9217,18 @@
       <c r="H203" s="10"/>
       <c r="I203" s="37"/>
     </row>
-    <row r="204" spans="1:9">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A204" s="9" t="s">
+        <v>480</v>
+      </c>
+      <c r="B204" s="24" t="s">
         <v>481</v>
       </c>
-      <c r="B204" s="24" t="s">
+      <c r="C204" s="24" t="s">
         <v>482</v>
       </c>
-      <c r="C204" s="24" t="s">
+      <c r="D204" s="24" t="s">
         <v>483</v>
-      </c>
-      <c r="D204" s="24" t="s">
-        <v>484</v>
       </c>
       <c r="E204" s="24"/>
       <c r="F204" s="47">
@@ -9178,18 +9242,18 @@
       </c>
       <c r="I204" s="37"/>
     </row>
-    <row r="205" spans="1:9">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A205" s="9" t="s">
+        <v>484</v>
+      </c>
+      <c r="B205" s="24" t="s">
         <v>485</v>
       </c>
-      <c r="B205" s="24" t="s">
+      <c r="C205" s="24" t="s">
         <v>486</v>
       </c>
-      <c r="C205" s="24" t="s">
+      <c r="D205" s="48" t="s">
         <v>487</v>
-      </c>
-      <c r="D205" s="48" t="s">
-        <v>488</v>
       </c>
       <c r="E205" s="24">
         <v>47</v>
@@ -9205,18 +9269,18 @@
       </c>
       <c r="I205" s="11"/>
     </row>
-    <row r="206" spans="1:9">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A206" s="9" t="s">
+        <v>488</v>
+      </c>
+      <c r="B206" s="24" t="s">
         <v>489</v>
       </c>
-      <c r="B206" s="24" t="s">
+      <c r="C206" s="24" t="s">
         <v>490</v>
       </c>
-      <c r="C206" s="24" t="s">
-        <v>491</v>
-      </c>
       <c r="D206" s="48" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E206" s="24">
         <v>47</v>
@@ -9232,18 +9296,18 @@
       </c>
       <c r="I206" s="11"/>
     </row>
-    <row r="207" spans="1:9">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A207" s="9" t="s">
+        <v>491</v>
+      </c>
+      <c r="B207" s="27" t="s">
         <v>492</v>
-      </c>
-      <c r="B207" s="27" t="s">
-        <v>493</v>
       </c>
       <c r="C207" s="10" t="s">
         <v>53</v>
       </c>
       <c r="D207" s="11" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E207" s="10"/>
       <c r="F207" s="36"/>
@@ -9255,15 +9319,15 @@
       </c>
       <c r="I207" s="37"/>
     </row>
-    <row r="208" spans="1:9">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A208" s="9" t="s">
+        <v>493</v>
+      </c>
+      <c r="B208" s="27" t="s">
         <v>494</v>
       </c>
-      <c r="B208" s="27" t="s">
-        <v>495</v>
-      </c>
       <c r="C208" s="10" t="s">
-        <v>822</v>
+        <v>802</v>
       </c>
       <c r="D208" s="10" t="s">
         <v>39</v>
@@ -9282,18 +9346,18 @@
       </c>
       <c r="I208" s="11"/>
     </row>
-    <row r="209" spans="1:9">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A209" s="9" t="s">
+        <v>495</v>
+      </c>
+      <c r="B209" s="10" t="s">
         <v>496</v>
       </c>
-      <c r="B209" s="10" t="s">
-        <v>497</v>
-      </c>
       <c r="C209" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D209" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E209" s="10"/>
       <c r="F209" s="36"/>
@@ -9305,9 +9369,9 @@
       </c>
       <c r="I209" s="37"/>
     </row>
-    <row r="210" spans="1:9">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A210" s="9" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B210" s="10"/>
       <c r="C210" s="10"/>
@@ -9318,15 +9382,15 @@
       <c r="H210" s="10"/>
       <c r="I210" s="37"/>
     </row>
-    <row r="211" spans="1:9">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A211" s="9" t="s">
+        <v>498</v>
+      </c>
+      <c r="B211" s="10" t="s">
         <v>499</v>
       </c>
-      <c r="B211" s="10" t="s">
-        <v>500</v>
-      </c>
       <c r="C211" s="10" t="s">
-        <v>823</v>
+        <v>803</v>
       </c>
       <c r="D211" s="10" t="s">
         <v>39</v>
@@ -9343,18 +9407,18 @@
       </c>
       <c r="I211" s="37"/>
     </row>
-    <row r="212" spans="1:9">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A212" s="9" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B212" s="35" t="s">
-        <v>824</v>
+        <v>804</v>
       </c>
       <c r="C212" s="35" t="s">
-        <v>825</v>
+        <v>805</v>
       </c>
       <c r="D212" s="35" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E212" s="35">
         <v>62</v>
@@ -9368,18 +9432,18 @@
       </c>
       <c r="I212" s="37"/>
     </row>
-    <row r="213" spans="1:9">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A213" s="9" t="s">
+        <v>501</v>
+      </c>
+      <c r="B213" s="10" t="s">
         <v>502</v>
       </c>
-      <c r="B213" s="10" t="s">
+      <c r="C213" s="10" t="s">
         <v>503</v>
       </c>
-      <c r="C213" s="10" t="s">
-        <v>504</v>
-      </c>
       <c r="D213" s="10" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E213" s="10">
         <v>52</v>
@@ -9395,18 +9459,18 @@
       </c>
       <c r="I213" s="37"/>
     </row>
-    <row r="214" spans="1:9">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A214" s="9" t="s">
+        <v>504</v>
+      </c>
+      <c r="B214" s="10" t="s">
         <v>505</v>
       </c>
-      <c r="B214" s="10" t="s">
-        <v>506</v>
-      </c>
       <c r="C214" s="35" t="s">
-        <v>825</v>
+        <v>805</v>
       </c>
       <c r="D214" s="35" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E214" s="10">
         <v>65</v>
@@ -9420,9 +9484,9 @@
       </c>
       <c r="I214" s="37"/>
     </row>
-    <row r="215" spans="1:9">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A215" s="9" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B215" s="30"/>
       <c r="C215" s="30"/>
@@ -9433,18 +9497,18 @@
       <c r="H215" s="30"/>
       <c r="I215" s="37"/>
     </row>
-    <row r="216" spans="1:9">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A216" s="9" t="s">
+        <v>507</v>
+      </c>
+      <c r="B216" s="10" t="s">
         <v>508</v>
       </c>
-      <c r="B216" s="10" t="s">
+      <c r="C216" s="10" t="s">
         <v>509</v>
       </c>
-      <c r="C216" s="10" t="s">
+      <c r="D216" s="10" t="s">
         <v>510</v>
-      </c>
-      <c r="D216" s="10" t="s">
-        <v>511</v>
       </c>
       <c r="E216" s="10">
         <v>69</v>
@@ -9458,9 +9522,9 @@
       </c>
       <c r="I216" s="37"/>
     </row>
-    <row r="217" spans="1:9">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A217" s="9" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B217" s="30"/>
       <c r="C217" s="30"/>
@@ -9471,9 +9535,9 @@
       <c r="H217" s="30"/>
       <c r="I217" s="11"/>
     </row>
-    <row r="218" spans="1:9">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A218" s="9" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B218" s="10"/>
       <c r="C218" s="10"/>
@@ -9484,18 +9548,18 @@
       <c r="H218" s="10"/>
       <c r="I218" s="37"/>
     </row>
-    <row r="219" spans="1:9">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A219" s="9" t="s">
+        <v>513</v>
+      </c>
+      <c r="B219" s="35" t="s">
         <v>514</v>
       </c>
-      <c r="B219" s="35" t="s">
+      <c r="C219" s="35" t="s">
         <v>515</v>
       </c>
-      <c r="C219" s="35" t="s">
+      <c r="D219" s="35" t="s">
         <v>516</v>
-      </c>
-      <c r="D219" s="35" t="s">
-        <v>517</v>
       </c>
       <c r="E219" s="35">
         <v>90</v>
@@ -9511,18 +9575,18 @@
       </c>
       <c r="I219" s="37"/>
     </row>
-    <row r="220" spans="1:9">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A220" s="9" t="s">
+        <v>517</v>
+      </c>
+      <c r="B220" s="10" t="s">
+        <v>806</v>
+      </c>
+      <c r="C220" s="10" t="s">
+        <v>807</v>
+      </c>
+      <c r="D220" s="49" t="s">
         <v>518</v>
-      </c>
-      <c r="B220" s="10" t="s">
-        <v>826</v>
-      </c>
-      <c r="C220" s="10" t="s">
-        <v>827</v>
-      </c>
-      <c r="D220" s="49" t="s">
-        <v>519</v>
       </c>
       <c r="E220" s="10">
         <v>120</v>
@@ -9537,21 +9601,21 @@
         <v>3.4</v>
       </c>
       <c r="I220" s="11" t="s">
-        <v>828</v>
-      </c>
-    </row>
-    <row r="221" spans="1:9">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="221" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A221" s="9" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B221" s="10" t="s">
-        <v>829</v>
+        <v>809</v>
       </c>
       <c r="C221" s="10" t="s">
-        <v>830</v>
+        <v>810</v>
       </c>
       <c r="D221" s="49" t="s">
-        <v>831</v>
+        <v>889</v>
       </c>
       <c r="E221" s="10">
         <v>100</v>
@@ -9566,21 +9630,21 @@
         <v>3.3</v>
       </c>
       <c r="I221" s="37" t="s">
-        <v>832</v>
-      </c>
-    </row>
-    <row r="222" spans="1:9">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="222" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A222" s="9" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B222" s="10" t="s">
-        <v>833</v>
+        <v>812</v>
       </c>
       <c r="C222" s="10" t="s">
-        <v>834</v>
+        <v>813</v>
       </c>
       <c r="D222" s="49" t="s">
-        <v>835</v>
+        <v>814</v>
       </c>
       <c r="E222" s="10">
         <v>115</v>
@@ -9596,15 +9660,15 @@
       </c>
       <c r="I222" s="37"/>
     </row>
-    <row r="223" spans="1:9">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A223" s="9" t="s">
+        <v>521</v>
+      </c>
+      <c r="B223" s="35" t="s">
         <v>522</v>
       </c>
-      <c r="B223" s="35" t="s">
+      <c r="C223" s="35" t="s">
         <v>523</v>
-      </c>
-      <c r="C223" s="35" t="s">
-        <v>524</v>
       </c>
       <c r="D223" s="50" t="s">
         <v>4</v>
@@ -9623,18 +9687,18 @@
       </c>
       <c r="I223" s="37"/>
     </row>
-    <row r="224" spans="1:9">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A224" s="9" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B224" s="35" t="s">
-        <v>836</v>
+        <v>815</v>
       </c>
       <c r="C224" s="35" t="s">
-        <v>837</v>
+        <v>910</v>
       </c>
       <c r="D224" s="35" t="s">
-        <v>838</v>
+        <v>816</v>
       </c>
       <c r="E224" s="35">
         <v>120</v>
@@ -9650,18 +9714,18 @@
       </c>
       <c r="I224" s="37"/>
     </row>
-    <row r="225" spans="1:9">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A225" s="9" t="s">
+        <v>525</v>
+      </c>
+      <c r="B225" s="27" t="s">
         <v>526</v>
       </c>
-      <c r="B225" s="27" t="s">
+      <c r="C225" s="35" t="s">
         <v>527</v>
       </c>
-      <c r="C225" s="35" t="s">
-        <v>528</v>
-      </c>
       <c r="D225" s="35" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E225" s="35">
         <v>135</v>
@@ -9677,18 +9741,18 @@
       </c>
       <c r="I225" s="11"/>
     </row>
-    <row r="226" spans="1:9">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A226" s="9" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B226" s="35" t="s">
-        <v>839</v>
+        <v>911</v>
       </c>
       <c r="C226" s="35" t="s">
-        <v>803</v>
+        <v>789</v>
       </c>
       <c r="D226" s="35" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E226" s="35">
         <v>145</v>
@@ -9700,22 +9764,22 @@
         <v>215</v>
       </c>
       <c r="H226" s="35">
-        <v>4.5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="I226" s="37"/>
     </row>
-    <row r="227" spans="1:9">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A227" s="9" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B227" s="35" t="s">
-        <v>840</v>
+        <v>912</v>
       </c>
       <c r="C227" s="35" t="s">
-        <v>803</v>
+        <v>789</v>
       </c>
       <c r="D227" s="35" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E227" s="35">
         <v>145</v>
@@ -9727,22 +9791,22 @@
         <v>215</v>
       </c>
       <c r="H227" s="35">
-        <v>4.5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="I227" s="37"/>
     </row>
-    <row r="228" spans="1:9">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A228" s="9" t="s">
+        <v>530</v>
+      </c>
+      <c r="B228" s="35" t="s">
         <v>531</v>
       </c>
-      <c r="B228" s="35" t="s">
-        <v>532</v>
-      </c>
       <c r="C228" s="35" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D228" s="35" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E228" s="35">
         <v>150</v>
@@ -9758,18 +9822,18 @@
       </c>
       <c r="I228" s="11"/>
     </row>
-    <row r="229" spans="1:9">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A229" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="B229" s="35" t="s">
         <v>533</v>
       </c>
-      <c r="B229" s="35" t="s">
-        <v>534</v>
-      </c>
       <c r="C229" s="35" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D229" s="35" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E229" s="35">
         <v>150</v>
@@ -9781,22 +9845,22 @@
         <v>215</v>
       </c>
       <c r="H229" s="35">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I229" s="11"/>
     </row>
-    <row r="230" spans="1:9">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A230" s="9" t="s">
+        <v>534</v>
+      </c>
+      <c r="B230" s="51" t="s">
         <v>535</v>
       </c>
-      <c r="B230" s="51" t="s">
-        <v>536</v>
-      </c>
       <c r="C230" s="51" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="D230" s="51" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E230" s="51">
         <v>145</v>
@@ -9808,13 +9872,13 @@
         <v>215</v>
       </c>
       <c r="H230" s="51">
-        <v>4.8</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="I230" s="11"/>
     </row>
-    <row r="231" spans="1:9">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A231" s="9" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B231" s="18"/>
       <c r="C231" s="18"/>
@@ -9825,9 +9889,9 @@
       <c r="H231" s="18"/>
       <c r="I231" s="11"/>
     </row>
-    <row r="232" spans="1:9">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A232" s="9" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B232" s="35"/>
       <c r="C232" s="35"/>
@@ -9838,41 +9902,45 @@
       <c r="H232" s="35"/>
       <c r="I232" s="37"/>
     </row>
-    <row r="233" spans="1:9">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A233" s="9" t="s">
+        <v>538</v>
+      </c>
+      <c r="B233" s="35" t="s">
         <v>539</v>
       </c>
-      <c r="B233" s="35" t="s">
+      <c r="C233" s="35" t="s">
         <v>540</v>
       </c>
-      <c r="C233" s="35" t="s">
+      <c r="D233" s="35" t="s">
         <v>541</v>
       </c>
-      <c r="D233" s="35" t="s">
-        <v>542</v>
-      </c>
-      <c r="E233" s="35"/>
-      <c r="F233" s="36"/>
+      <c r="E233" s="35">
+        <v>185</v>
+      </c>
+      <c r="F233" s="36">
+        <v>270</v>
+      </c>
       <c r="G233" s="37">
         <v>215</v>
       </c>
       <c r="H233" s="35">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="I233" s="37"/>
     </row>
-    <row r="234" spans="1:9">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A234" s="9" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B234" s="52" t="s">
-        <v>841</v>
+        <v>817</v>
       </c>
       <c r="C234" s="52" t="s">
-        <v>842</v>
+        <v>818</v>
       </c>
       <c r="D234" s="50" t="s">
-        <v>843</v>
+        <v>819</v>
       </c>
       <c r="E234" s="52">
         <v>190</v>
@@ -9887,21 +9955,21 @@
         <v>5.8</v>
       </c>
       <c r="I234" s="54" t="s">
-        <v>844</v>
-      </c>
-    </row>
-    <row r="235" spans="1:9">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="235" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A235" s="9" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B235" s="51" t="s">
-        <v>845</v>
+        <v>821</v>
       </c>
       <c r="C235" s="51" t="s">
-        <v>846</v>
+        <v>913</v>
       </c>
       <c r="D235" s="51" t="s">
-        <v>847</v>
+        <v>914</v>
       </c>
       <c r="E235" s="51">
         <v>155</v>
@@ -9913,15 +9981,15 @@
         <v>215</v>
       </c>
       <c r="H235" s="51">
-        <v>4.5999999999999996</v>
+        <v>4.7</v>
       </c>
       <c r="I235" s="55" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="236" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A236" s="9" t="s">
         <v>545</v>
-      </c>
-    </row>
-    <row r="236" spans="1:9">
-      <c r="A236" s="9" t="s">
-        <v>546</v>
       </c>
       <c r="B236" s="51"/>
       <c r="C236" s="51"/>
@@ -9932,18 +10000,18 @@
       <c r="H236" s="51"/>
       <c r="I236" s="54"/>
     </row>
-    <row r="237" spans="1:9">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A237" s="9" t="s">
+        <v>546</v>
+      </c>
+      <c r="B237" s="51" t="s">
+        <v>915</v>
+      </c>
+      <c r="C237" s="51" t="s">
         <v>547</v>
       </c>
-      <c r="B237" s="51" t="s">
-        <v>848</v>
-      </c>
-      <c r="C237" s="51" t="s">
-        <v>548</v>
-      </c>
       <c r="D237" s="51" t="s">
-        <v>849</v>
+        <v>916</v>
       </c>
       <c r="E237" s="51">
         <v>155</v>
@@ -9955,24 +10023,24 @@
         <v>218</v>
       </c>
       <c r="H237" s="51">
-        <v>4.9000000000000004</v>
+        <v>5</v>
       </c>
       <c r="I237" s="55" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="238" spans="1:9">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="238" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A238" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B238" s="51" t="s">
-        <v>850</v>
+        <v>822</v>
       </c>
       <c r="C238" s="51" t="s">
-        <v>851</v>
+        <v>917</v>
       </c>
       <c r="D238" s="51" t="s">
-        <v>852</v>
+        <v>823</v>
       </c>
       <c r="E238" s="52">
         <v>190</v>
@@ -9987,50 +10055,50 @@
         <v>5.7</v>
       </c>
       <c r="I238" s="54" t="s">
-        <v>853</v>
-      </c>
-    </row>
-    <row r="239" spans="1:9">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="239" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A239" s="9" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B239" s="51" t="s">
-        <v>854</v>
+        <v>918</v>
       </c>
       <c r="C239" s="51" t="s">
-        <v>855</v>
+        <v>881</v>
       </c>
       <c r="D239" s="51" t="s">
-        <v>852</v>
+        <v>823</v>
       </c>
       <c r="E239" s="52">
         <v>180</v>
       </c>
       <c r="F239" s="36">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="G239" s="55">
         <v>220</v>
       </c>
       <c r="H239" s="51">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="I239" s="54" t="s">
-        <v>853</v>
-      </c>
-    </row>
-    <row r="240" spans="1:9">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="240" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A240" s="9" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B240" s="51" t="s">
-        <v>856</v>
+        <v>919</v>
       </c>
       <c r="C240" s="51" t="s">
-        <v>857</v>
+        <v>825</v>
       </c>
       <c r="D240" s="51" t="s">
-        <v>852</v>
+        <v>823</v>
       </c>
       <c r="E240" s="52">
         <v>190</v>
@@ -10042,24 +10110,24 @@
         <v>225</v>
       </c>
       <c r="H240" s="35">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="I240" s="54" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="241" spans="1:9">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="241" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A241" s="9" t="s">
+        <v>551</v>
+      </c>
+      <c r="B241" s="51" t="s">
+        <v>826</v>
+      </c>
+      <c r="C241" s="51" t="s">
+        <v>921</v>
+      </c>
+      <c r="D241" s="11" t="s">
         <v>552</v>
-      </c>
-      <c r="B241" s="51" t="s">
-        <v>859</v>
-      </c>
-      <c r="C241" s="51" t="s">
-        <v>860</v>
-      </c>
-      <c r="D241" s="11" t="s">
-        <v>553</v>
       </c>
       <c r="E241" s="51">
         <v>150</v>
@@ -10074,21 +10142,21 @@
         <v>5.3</v>
       </c>
       <c r="I241" s="55" t="s">
-        <v>861</v>
-      </c>
-    </row>
-    <row r="242" spans="1:9">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="242" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A242" s="9" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B242" s="51" t="s">
-        <v>862</v>
+        <v>828</v>
       </c>
       <c r="C242" s="51" t="s">
-        <v>863</v>
+        <v>922</v>
       </c>
       <c r="D242" s="51" t="s">
-        <v>852</v>
+        <v>823</v>
       </c>
       <c r="E242" s="52">
         <v>160</v>
@@ -10100,24 +10168,24 @@
         <v>225</v>
       </c>
       <c r="H242" s="35">
-        <v>4.9000000000000004</v>
+        <v>5.4</v>
       </c>
       <c r="I242" s="54" t="s">
-        <v>864</v>
-      </c>
-    </row>
-    <row r="243" spans="1:9">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="243" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A243" s="9" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B243" s="51" t="s">
-        <v>865</v>
+        <v>830</v>
       </c>
       <c r="C243" s="51" t="s">
-        <v>866</v>
+        <v>923</v>
       </c>
       <c r="D243" s="51" t="s">
-        <v>867</v>
+        <v>831</v>
       </c>
       <c r="E243" s="52">
         <v>190</v>
@@ -10132,21 +10200,21 @@
         <v>5.6</v>
       </c>
       <c r="I243" s="54" t="s">
-        <v>868</v>
-      </c>
-    </row>
-    <row r="244" spans="1:9">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="244" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A244" s="9" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B244" s="51" t="s">
-        <v>869</v>
+        <v>925</v>
       </c>
       <c r="C244" s="51" t="s">
-        <v>870</v>
+        <v>833</v>
       </c>
       <c r="D244" s="51" t="s">
-        <v>867</v>
+        <v>926</v>
       </c>
       <c r="E244" s="51">
         <v>150</v>
@@ -10156,13 +10224,13 @@
         <v>220</v>
       </c>
       <c r="H244" s="35">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="I244" s="54"/>
     </row>
-    <row r="245" spans="1:9">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A245" s="9" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B245" s="38"/>
       <c r="C245" s="38"/>
@@ -10173,18 +10241,18 @@
       <c r="H245" s="38"/>
       <c r="I245" s="11"/>
     </row>
-    <row r="246" spans="1:9">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A246" s="9" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B246" s="18" t="s">
-        <v>871</v>
+        <v>834</v>
       </c>
       <c r="C246" s="18" t="s">
-        <v>872</v>
+        <v>927</v>
       </c>
       <c r="D246" s="33" t="s">
-        <v>800</v>
+        <v>928</v>
       </c>
       <c r="E246" s="18">
         <v>112</v>
@@ -10196,22 +10264,22 @@
         <v>215</v>
       </c>
       <c r="H246" s="18">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="I246" s="37"/>
     </row>
-    <row r="247" spans="1:9">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A247" s="31" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B247" s="18" t="s">
-        <v>873</v>
+        <v>835</v>
       </c>
       <c r="C247" s="18" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="D247" s="33" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E247" s="18">
         <v>135</v>
@@ -10227,18 +10295,18 @@
       </c>
       <c r="I247" s="56"/>
     </row>
-    <row r="248" spans="1:9">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A248" s="31" t="s">
+        <v>559</v>
+      </c>
+      <c r="B248" s="18" t="s">
+        <v>929</v>
+      </c>
+      <c r="C248" s="18" t="s">
         <v>560</v>
       </c>
-      <c r="B248" s="18" t="s">
-        <v>874</v>
-      </c>
-      <c r="C248" s="18" t="s">
-        <v>561</v>
-      </c>
       <c r="D248" s="18" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E248" s="18">
         <v>160</v>
@@ -10250,22 +10318,22 @@
         <v>215</v>
       </c>
       <c r="H248" s="18">
-        <v>4.9000000000000004</v>
+        <v>5</v>
       </c>
       <c r="I248" s="57"/>
     </row>
-    <row r="249" spans="1:9">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A249" s="31" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B249" s="18" t="s">
-        <v>875</v>
+        <v>930</v>
       </c>
       <c r="C249" s="18" t="s">
-        <v>876</v>
+        <v>836</v>
       </c>
       <c r="D249" s="18" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E249" s="32">
         <v>105</v>
@@ -10281,18 +10349,18 @@
       </c>
       <c r="I249" s="57"/>
     </row>
-    <row r="250" spans="1:9">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A250" s="31" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B250" s="18" t="s">
-        <v>877</v>
+        <v>837</v>
       </c>
       <c r="C250" s="18" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D250" s="18" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E250" s="32">
         <v>108</v>
@@ -10308,18 +10376,18 @@
       </c>
       <c r="I250" s="32"/>
     </row>
-    <row r="251" spans="1:9">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A251" s="31" t="s">
+        <v>563</v>
+      </c>
+      <c r="B251" s="18" t="s">
+        <v>931</v>
+      </c>
+      <c r="C251" s="18" t="s">
         <v>564</v>
       </c>
-      <c r="B251" s="18" t="s">
-        <v>878</v>
-      </c>
-      <c r="C251" s="18" t="s">
-        <v>565</v>
-      </c>
       <c r="D251" s="18" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E251" s="18">
         <v>116</v>
@@ -10331,22 +10399,22 @@
         <v>215</v>
       </c>
       <c r="H251" s="18">
-        <v>4.0999999999999996</v>
+        <v>4.2</v>
       </c>
       <c r="I251" s="32"/>
     </row>
-    <row r="252" spans="1:9">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A252" s="31" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B252" s="18" t="s">
-        <v>879</v>
+        <v>838</v>
       </c>
       <c r="C252" s="18" t="s">
-        <v>876</v>
+        <v>836</v>
       </c>
       <c r="D252" s="18" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E252" s="18">
         <v>105</v>
@@ -10362,18 +10430,18 @@
       </c>
       <c r="I252" s="32"/>
     </row>
-    <row r="253" spans="1:9">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A253" s="31" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B253" s="18" t="s">
-        <v>880</v>
+        <v>932</v>
       </c>
       <c r="C253" s="18" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="D253" s="18" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E253" s="18">
         <v>116</v>
@@ -10389,18 +10457,18 @@
       </c>
       <c r="I253" s="32"/>
     </row>
-    <row r="254" spans="1:9">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A254" s="31" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B254" s="18" t="s">
-        <v>881</v>
+        <v>839</v>
       </c>
       <c r="C254" s="18" t="s">
-        <v>882</v>
+        <v>840</v>
       </c>
       <c r="D254" s="18" t="s">
-        <v>843</v>
+        <v>819</v>
       </c>
       <c r="E254" s="18">
         <v>190</v>
@@ -10412,24 +10480,24 @@
         <v>215</v>
       </c>
       <c r="H254" s="18">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I254" s="54" t="s">
-        <v>868</v>
-      </c>
-    </row>
-    <row r="255" spans="1:9">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="255" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A255" s="31" t="s">
+        <v>568</v>
+      </c>
+      <c r="B255" s="18" t="s">
+        <v>933</v>
+      </c>
+      <c r="C255" s="18" t="s">
         <v>569</v>
       </c>
-      <c r="B255" s="18" t="s">
-        <v>883</v>
-      </c>
-      <c r="C255" s="18" t="s">
-        <v>570</v>
-      </c>
       <c r="D255" s="18" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E255" s="59">
         <v>88</v>
@@ -10441,22 +10509,22 @@
         <v>208</v>
       </c>
       <c r="H255" s="59">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="I255" s="54"/>
     </row>
-    <row r="256" spans="1:9">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A256" s="9" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B256" s="52" t="s">
-        <v>884</v>
+        <v>841</v>
       </c>
       <c r="C256" s="18" t="s">
-        <v>885</v>
+        <v>934</v>
       </c>
       <c r="D256" s="50" t="s">
-        <v>886</v>
+        <v>935</v>
       </c>
       <c r="E256" s="52">
         <v>190</v>
@@ -10468,24 +10536,24 @@
         <v>215</v>
       </c>
       <c r="H256" s="60">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I256" s="54" t="s">
-        <v>887</v>
-      </c>
-    </row>
-    <row r="257" spans="1:9">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="257" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A257" s="9" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B257" s="36" t="s">
-        <v>888</v>
+        <v>937</v>
       </c>
       <c r="C257" s="36" t="s">
-        <v>889</v>
+        <v>938</v>
       </c>
       <c r="D257" s="36" t="s">
-        <v>800</v>
+        <v>901</v>
       </c>
       <c r="E257" s="36">
         <v>118</v>
@@ -10497,22 +10565,22 @@
         <v>215</v>
       </c>
       <c r="H257" s="60">
-        <v>4.7</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="I257" s="60"/>
     </row>
-    <row r="258" spans="1:9">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A258" s="9" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B258" s="18" t="s">
-        <v>877</v>
+        <v>837</v>
       </c>
       <c r="C258" s="18" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D258" s="18" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E258" s="32">
         <v>108</v>
@@ -10528,9 +10596,9 @@
       </c>
       <c r="I258" s="60"/>
     </row>
-    <row r="259" spans="1:9">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A259" s="9" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B259" s="36"/>
       <c r="C259" s="36"/>
@@ -10541,9 +10609,9 @@
       <c r="H259" s="60"/>
       <c r="I259" s="60"/>
     </row>
-    <row r="260" spans="1:9">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A260" s="9" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B260" s="36"/>
       <c r="C260" s="36"/>
@@ -10554,18 +10622,18 @@
       <c r="H260" s="60"/>
       <c r="I260" s="60"/>
     </row>
-    <row r="261" spans="1:9">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A261" s="9" t="s">
+        <v>575</v>
+      </c>
+      <c r="B261" s="10" t="s">
         <v>576</v>
       </c>
-      <c r="B261" s="10" t="s">
+      <c r="C261" s="10" t="s">
         <v>577</v>
       </c>
-      <c r="C261" s="10" t="s">
-        <v>578</v>
-      </c>
       <c r="D261" s="49" t="s">
-        <v>890</v>
+        <v>939</v>
       </c>
       <c r="E261" s="10">
         <v>108</v>
@@ -10577,22 +10645,22 @@
         <v>210</v>
       </c>
       <c r="H261" s="10">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="I261" s="60"/>
     </row>
-    <row r="262" spans="1:9">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A262" s="9" t="s">
+        <v>578</v>
+      </c>
+      <c r="B262" s="10" t="s">
+        <v>842</v>
+      </c>
+      <c r="C262" s="10" t="s">
         <v>579</v>
       </c>
-      <c r="B262" s="10" t="s">
-        <v>891</v>
-      </c>
-      <c r="C262" s="10" t="s">
+      <c r="D262" s="49" t="s">
         <v>580</v>
-      </c>
-      <c r="D262" s="49" t="s">
-        <v>581</v>
       </c>
       <c r="E262" s="10">
         <v>87</v>
@@ -10608,18 +10676,18 @@
       </c>
       <c r="I262" s="60"/>
     </row>
-    <row r="263" spans="1:9">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A263" s="9" t="s">
+        <v>581</v>
+      </c>
+      <c r="B263" s="27" t="s">
         <v>582</v>
       </c>
-      <c r="B263" s="27" t="s">
+      <c r="C263" s="27" t="s">
         <v>583</v>
       </c>
-      <c r="C263" s="27" t="s">
+      <c r="D263" s="27" t="s">
         <v>584</v>
-      </c>
-      <c r="D263" s="27" t="s">
-        <v>585</v>
       </c>
       <c r="E263" s="27">
         <v>115</v>
@@ -10635,18 +10703,18 @@
       </c>
       <c r="I263" s="60"/>
     </row>
-    <row r="264" spans="1:9">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A264" s="9" t="s">
+        <v>585</v>
+      </c>
+      <c r="B264" s="10" t="s">
         <v>586</v>
       </c>
-      <c r="B264" s="10" t="s">
+      <c r="C264" s="10" t="s">
         <v>587</v>
       </c>
-      <c r="C264" s="10" t="s">
+      <c r="D264" s="10" t="s">
         <v>588</v>
-      </c>
-      <c r="D264" s="10" t="s">
-        <v>589</v>
       </c>
       <c r="E264" s="10">
         <v>70</v>
@@ -10662,18 +10730,18 @@
       </c>
       <c r="I264" s="60"/>
     </row>
-    <row r="265" spans="1:9">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A265" s="9" t="s">
+        <v>589</v>
+      </c>
+      <c r="B265" s="35" t="s">
         <v>590</v>
       </c>
-      <c r="B265" s="35" t="s">
+      <c r="C265" s="35" t="s">
         <v>591</v>
       </c>
-      <c r="C265" s="35" t="s">
+      <c r="D265" s="35" t="s">
         <v>592</v>
-      </c>
-      <c r="D265" s="35" t="s">
-        <v>593</v>
       </c>
       <c r="E265" s="35">
         <v>102</v>
@@ -10689,18 +10757,18 @@
       </c>
       <c r="I265" s="60"/>
     </row>
-    <row r="266" spans="1:9">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A266" s="9" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B266" s="35" t="s">
-        <v>892</v>
+        <v>843</v>
       </c>
       <c r="C266" s="35" t="s">
-        <v>870</v>
+        <v>940</v>
       </c>
       <c r="D266" s="35" t="s">
-        <v>893</v>
+        <v>844</v>
       </c>
       <c r="E266" s="35">
         <v>78</v>
@@ -10712,22 +10780,22 @@
         <v>215</v>
       </c>
       <c r="H266" s="35">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="I266" s="60"/>
     </row>
-    <row r="267" spans="1:9">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A267" s="9" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B267" s="10" t="s">
-        <v>894</v>
+        <v>941</v>
       </c>
       <c r="C267" s="10" t="s">
-        <v>895</v>
+        <v>845</v>
       </c>
       <c r="D267" s="49" t="s">
-        <v>896</v>
+        <v>846</v>
       </c>
       <c r="E267" s="10">
         <v>60</v>
@@ -10739,13 +10807,13 @@
         <v>220</v>
       </c>
       <c r="H267" s="10">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="I267" s="61"/>
     </row>
-    <row r="268" spans="1:9">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A268" s="9" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B268" s="36"/>
       <c r="C268" s="36"/>
@@ -10756,9 +10824,9 @@
       <c r="H268" s="60"/>
       <c r="I268" s="60"/>
     </row>
-    <row r="269" spans="1:9">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A269" s="9" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B269" s="36"/>
       <c r="C269" s="36"/>
@@ -10769,9 +10837,9 @@
       <c r="H269" s="60"/>
       <c r="I269" s="60"/>
     </row>
-    <row r="270" spans="1:9">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A270" s="9" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B270" s="36"/>
       <c r="C270" s="36"/>
@@ -10782,9 +10850,9 @@
       <c r="H270" s="60"/>
       <c r="I270" s="60"/>
     </row>
-    <row r="271" spans="1:9">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A271" s="9" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B271" s="36"/>
       <c r="C271" s="36"/>
@@ -10795,9 +10863,9 @@
       <c r="H271" s="60"/>
       <c r="I271" s="60"/>
     </row>
-    <row r="272" spans="1:9">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A272" s="9" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B272" s="36"/>
       <c r="C272" s="36"/>
@@ -10808,9 +10876,9 @@
       <c r="H272" s="60"/>
       <c r="I272" s="60"/>
     </row>
-    <row r="273" spans="1:9">
+    <row r="273" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A273" s="9" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B273" s="36"/>
       <c r="C273" s="36"/>
@@ -10821,9 +10889,9 @@
       <c r="H273" s="60"/>
       <c r="I273" s="60"/>
     </row>
-    <row r="274" spans="1:9">
+    <row r="274" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A274" s="9" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B274" s="36"/>
       <c r="C274" s="36"/>
@@ -10834,9 +10902,9 @@
       <c r="H274" s="60"/>
       <c r="I274" s="60"/>
     </row>
-    <row r="275" spans="1:9">
+    <row r="275" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A275" s="9" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B275" s="36"/>
       <c r="C275" s="36"/>
@@ -10847,9 +10915,9 @@
       <c r="H275" s="60"/>
       <c r="I275" s="60"/>
     </row>
-    <row r="276" spans="1:9">
+    <row r="276" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A276" s="9" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B276" s="36"/>
       <c r="C276" s="36"/>
@@ -10860,18 +10928,18 @@
       <c r="H276" s="60"/>
       <c r="I276" s="60"/>
     </row>
-    <row r="277" spans="1:9">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A277" s="9" t="s">
+        <v>604</v>
+      </c>
+      <c r="B277" s="52" t="s">
         <v>605</v>
       </c>
-      <c r="B277" s="52" t="s">
+      <c r="C277" s="52" t="s">
         <v>606</v>
       </c>
-      <c r="C277" s="52" t="s">
+      <c r="D277" s="52" t="s">
         <v>607</v>
-      </c>
-      <c r="D277" s="52" t="s">
-        <v>608</v>
       </c>
       <c r="E277" s="52">
         <v>105</v>
@@ -10887,18 +10955,18 @@
       </c>
       <c r="I277" s="60"/>
     </row>
-    <row r="278" spans="1:9">
+    <row r="278" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A278" s="9" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B278" s="27" t="s">
-        <v>897</v>
+        <v>847</v>
       </c>
       <c r="C278" s="27" t="s">
-        <v>898</v>
+        <v>942</v>
       </c>
       <c r="D278" s="27" t="s">
-        <v>899</v>
+        <v>848</v>
       </c>
       <c r="E278" s="27">
         <v>159</v>
@@ -10914,18 +10982,18 @@
       </c>
       <c r="I278" s="60"/>
     </row>
-    <row r="279" spans="1:9">
+    <row r="279" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A279" s="9" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B279" s="10" t="s">
-        <v>900</v>
+        <v>849</v>
       </c>
       <c r="C279" s="49" t="s">
-        <v>901</v>
+        <v>850</v>
       </c>
       <c r="D279" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E279" s="10">
         <v>50</v>
@@ -10941,18 +11009,18 @@
       </c>
       <c r="I279" s="60"/>
     </row>
-    <row r="280" spans="1:9">
+    <row r="280" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A280" s="9" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B280" s="10" t="s">
-        <v>902</v>
+        <v>943</v>
       </c>
       <c r="C280" s="49" t="s">
-        <v>903</v>
+        <v>851</v>
       </c>
       <c r="D280" s="10" t="s">
-        <v>904</v>
+        <v>944</v>
       </c>
       <c r="E280" s="10"/>
       <c r="F280" s="9">
@@ -10966,18 +11034,18 @@
       </c>
       <c r="I280" s="60"/>
     </row>
-    <row r="281" spans="1:9">
+    <row r="281" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A281" s="9" t="s">
+        <v>611</v>
+      </c>
+      <c r="B281" s="10" t="s">
         <v>612</v>
       </c>
-      <c r="B281" s="10" t="s">
+      <c r="C281" s="49" t="s">
         <v>613</v>
       </c>
-      <c r="C281" s="49" t="s">
-        <v>614</v>
-      </c>
       <c r="D281" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E281" s="10">
         <v>55</v>
@@ -10993,15 +11061,15 @@
       </c>
       <c r="I281" s="60"/>
     </row>
-    <row r="282" spans="1:9">
+    <row r="282" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A282" s="9" t="s">
+        <v>614</v>
+      </c>
+      <c r="B282" s="10" t="s">
+        <v>852</v>
+      </c>
+      <c r="C282" s="49" t="s">
         <v>615</v>
-      </c>
-      <c r="B282" s="10" t="s">
-        <v>905</v>
-      </c>
-      <c r="C282" s="49" t="s">
-        <v>616</v>
       </c>
       <c r="D282" s="10" t="s">
         <v>39</v>
@@ -11020,15 +11088,15 @@
       </c>
       <c r="I282" s="60"/>
     </row>
-    <row r="283" spans="1:9">
+    <row r="283" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A283" s="9" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B283" s="10" t="s">
-        <v>906</v>
+        <v>945</v>
       </c>
       <c r="C283" s="49" t="s">
-        <v>907</v>
+        <v>946</v>
       </c>
       <c r="D283" s="10" t="s">
         <v>39</v>
@@ -11047,18 +11115,18 @@
       </c>
       <c r="I283" s="60"/>
     </row>
-    <row r="284" spans="1:9">
+    <row r="284" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A284" s="9" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B284" s="27" t="s">
-        <v>908</v>
+        <v>853</v>
       </c>
       <c r="C284" s="36" t="s">
-        <v>909</v>
+        <v>947</v>
       </c>
       <c r="D284" s="36" t="s">
-        <v>910</v>
+        <v>854</v>
       </c>
       <c r="E284" s="36">
         <v>80</v>
@@ -11070,22 +11138,22 @@
         <v>208</v>
       </c>
       <c r="H284" s="60">
-        <v>4.5999999999999996</v>
+        <v>4.5</v>
       </c>
       <c r="I284" s="60"/>
     </row>
-    <row r="285" spans="1:9">
+    <row r="285" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A285" s="9" t="s">
+        <v>618</v>
+      </c>
+      <c r="B285" s="10" t="s">
         <v>619</v>
       </c>
-      <c r="B285" s="10" t="s">
+      <c r="C285" s="49" t="s">
         <v>620</v>
       </c>
-      <c r="C285" s="49" t="s">
-        <v>621</v>
-      </c>
       <c r="D285" s="36" t="s">
-        <v>910</v>
+        <v>854</v>
       </c>
       <c r="E285" s="10">
         <v>73</v>
@@ -11101,18 +11169,18 @@
       </c>
       <c r="I285" s="60"/>
     </row>
-    <row r="286" spans="1:9">
+    <row r="286" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A286" s="9" t="s">
+        <v>621</v>
+      </c>
+      <c r="B286" s="52" t="s">
+        <v>855</v>
+      </c>
+      <c r="C286" s="52" t="s">
+        <v>856</v>
+      </c>
+      <c r="D286" s="52" t="s">
         <v>622</v>
-      </c>
-      <c r="B286" s="52" t="s">
-        <v>911</v>
-      </c>
-      <c r="C286" s="52" t="s">
-        <v>912</v>
-      </c>
-      <c r="D286" s="52" t="s">
-        <v>623</v>
       </c>
       <c r="E286" s="52">
         <v>85</v>
@@ -11128,18 +11196,18 @@
       </c>
       <c r="I286" s="60"/>
     </row>
-    <row r="287" spans="1:9">
+    <row r="287" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A287" s="9" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B287" s="52" t="s">
-        <v>913</v>
+        <v>948</v>
       </c>
       <c r="C287" s="52" t="s">
-        <v>914</v>
+        <v>949</v>
       </c>
       <c r="D287" s="52" t="s">
-        <v>915</v>
+        <v>857</v>
       </c>
       <c r="E287" s="52">
         <v>88</v>
@@ -11155,15 +11223,15 @@
       </c>
       <c r="I287" s="61"/>
     </row>
-    <row r="288" spans="1:9">
+    <row r="288" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A288" s="9" t="s">
+        <v>624</v>
+      </c>
+      <c r="B288" s="27" t="s">
+        <v>858</v>
+      </c>
+      <c r="C288" s="27" t="s">
         <v>625</v>
-      </c>
-      <c r="B288" s="27" t="s">
-        <v>916</v>
-      </c>
-      <c r="C288" s="27" t="s">
-        <v>626</v>
       </c>
       <c r="D288" s="50" t="s">
         <v>4</v>
@@ -11182,18 +11250,18 @@
       </c>
       <c r="I288" s="61"/>
     </row>
-    <row r="289" spans="1:9">
+    <row r="289" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A289" s="9" t="s">
+        <v>626</v>
+      </c>
+      <c r="B289" s="10" t="s">
         <v>627</v>
       </c>
-      <c r="B289" s="10" t="s">
+      <c r="C289" s="10" t="s">
         <v>628</v>
       </c>
-      <c r="C289" s="10" t="s">
+      <c r="D289" s="49" t="s">
         <v>629</v>
-      </c>
-      <c r="D289" s="49" t="s">
-        <v>630</v>
       </c>
       <c r="E289" s="10">
         <v>135</v>
@@ -11205,21 +11273,21 @@
         <v>215</v>
       </c>
       <c r="H289" s="10">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I289" s="11" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="290" spans="1:9">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="290" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A290" s="9" t="s">
+        <v>630</v>
+      </c>
+      <c r="B290" s="24" t="s">
         <v>631</v>
       </c>
-      <c r="B290" s="24" t="s">
+      <c r="C290" s="24" t="s">
         <v>632</v>
-      </c>
-      <c r="C290" s="24" t="s">
-        <v>633</v>
       </c>
       <c r="D290" s="63" t="s">
         <v>39</v>
@@ -11238,18 +11306,18 @@
       </c>
       <c r="I290" s="61"/>
     </row>
-    <row r="291" spans="1:9">
+    <row r="291" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A291" s="9" t="s">
+        <v>633</v>
+      </c>
+      <c r="B291" s="64" t="s">
+        <v>950</v>
+      </c>
+      <c r="C291" s="64" t="s">
+        <v>860</v>
+      </c>
+      <c r="D291" s="64" t="s">
         <v>634</v>
-      </c>
-      <c r="B291" s="64" t="s">
-        <v>918</v>
-      </c>
-      <c r="C291" s="64" t="s">
-        <v>919</v>
-      </c>
-      <c r="D291" s="64" t="s">
-        <v>635</v>
       </c>
       <c r="E291" s="64">
         <v>88</v>
@@ -11265,18 +11333,18 @@
       </c>
       <c r="I291" s="61"/>
     </row>
-    <row r="292" spans="1:9">
+    <row r="292" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A292" s="9" t="s">
+        <v>635</v>
+      </c>
+      <c r="B292" s="64" t="s">
+        <v>951</v>
+      </c>
+      <c r="C292" s="64" t="s">
         <v>636</v>
       </c>
-      <c r="B292" s="64" t="s">
-        <v>920</v>
-      </c>
-      <c r="C292" s="64" t="s">
+      <c r="D292" s="64" t="s">
         <v>637</v>
-      </c>
-      <c r="D292" s="64" t="s">
-        <v>638</v>
       </c>
       <c r="E292" s="64">
         <v>80</v>
@@ -11292,15 +11360,15 @@
       </c>
       <c r="I292" s="61"/>
     </row>
-    <row r="293" spans="1:9">
+    <row r="293" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A293" s="9" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B293" s="65" t="s">
-        <v>921</v>
+        <v>952</v>
       </c>
       <c r="C293" s="64" t="s">
-        <v>922</v>
+        <v>861</v>
       </c>
       <c r="D293" s="64" t="s">
         <v>39</v>
@@ -11319,18 +11387,18 @@
       </c>
       <c r="I293" s="61"/>
     </row>
-    <row r="294" spans="1:9">
+    <row r="294" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A294" s="9" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B294" s="18" t="s">
-        <v>923</v>
+        <v>953</v>
       </c>
       <c r="C294" s="18" t="s">
-        <v>799</v>
+        <v>787</v>
       </c>
       <c r="D294" s="18" t="s">
-        <v>924</v>
+        <v>954</v>
       </c>
       <c r="E294" s="18">
         <v>150</v>
@@ -11346,18 +11414,18 @@
       </c>
       <c r="I294" s="61"/>
     </row>
-    <row r="295" spans="1:9">
+    <row r="295" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A295" s="9" t="s">
+        <v>640</v>
+      </c>
+      <c r="B295" s="10" t="s">
+        <v>862</v>
+      </c>
+      <c r="C295" s="10" t="s">
         <v>641</v>
       </c>
-      <c r="B295" s="10" t="s">
-        <v>925</v>
-      </c>
-      <c r="C295" s="10" t="s">
+      <c r="D295" s="10" t="s">
         <v>642</v>
-      </c>
-      <c r="D295" s="10" t="s">
-        <v>643</v>
       </c>
       <c r="E295" s="10"/>
       <c r="F295" s="9"/>
@@ -11369,18 +11437,18 @@
       </c>
       <c r="I295" s="61"/>
     </row>
-    <row r="296" spans="1:9">
+    <row r="296" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A296" s="9" t="s">
+        <v>643</v>
+      </c>
+      <c r="B296" s="35" t="s">
         <v>644</v>
       </c>
-      <c r="B296" s="35" t="s">
+      <c r="C296" s="35" t="s">
         <v>645</v>
       </c>
-      <c r="C296" s="35" t="s">
+      <c r="D296" s="35" t="s">
         <v>646</v>
-      </c>
-      <c r="D296" s="35" t="s">
-        <v>647</v>
       </c>
       <c r="E296" s="35"/>
       <c r="F296" s="36">
@@ -11394,18 +11462,18 @@
       </c>
       <c r="I296" s="61"/>
     </row>
-    <row r="297" spans="1:9">
+    <row r="297" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A297" s="9" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B297" s="18" t="s">
-        <v>926</v>
+        <v>863</v>
       </c>
       <c r="C297" s="18" t="s">
-        <v>927</v>
+        <v>955</v>
       </c>
       <c r="D297" s="33" t="s">
-        <v>928</v>
+        <v>864</v>
       </c>
       <c r="E297" s="18">
         <v>125</v>
@@ -11417,22 +11485,22 @@
         <v>215</v>
       </c>
       <c r="H297" s="18">
-        <v>4.5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="I297" s="54"/>
     </row>
-    <row r="298" spans="1:9">
+    <row r="298" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A298" s="9" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B298" s="18" t="s">
-        <v>929</v>
+        <v>956</v>
       </c>
       <c r="C298" s="18" t="s">
-        <v>930</v>
+        <v>865</v>
       </c>
       <c r="D298" s="33" t="s">
-        <v>931</v>
+        <v>957</v>
       </c>
       <c r="E298" s="18">
         <v>190</v>
@@ -11444,24 +11512,24 @@
         <v>225</v>
       </c>
       <c r="H298" s="18">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="I298" s="11" t="s">
-        <v>932</v>
-      </c>
-    </row>
-    <row r="299" spans="1:9">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="299" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A299" s="9" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B299" s="51" t="s">
-        <v>933</v>
+        <v>867</v>
       </c>
       <c r="C299" s="51" t="s">
-        <v>934</v>
+        <v>868</v>
       </c>
       <c r="D299" s="51" t="s">
-        <v>935</v>
+        <v>869</v>
       </c>
       <c r="E299" s="51">
         <v>124</v>
@@ -11473,15 +11541,15 @@
         <v>218</v>
       </c>
       <c r="H299" s="51">
-        <v>4.8</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="I299" s="55" t="s">
-        <v>936</v>
-      </c>
-    </row>
-    <row r="300" spans="1:9">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="300" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A300" s="9" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B300" s="36"/>
       <c r="C300" s="36"/>
@@ -11492,9 +11560,9 @@
       <c r="H300" s="61"/>
       <c r="I300" s="61"/>
     </row>
-    <row r="301" spans="1:9">
+    <row r="301" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A301" s="9" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B301" s="36"/>
       <c r="C301" s="36"/>
@@ -11505,18 +11573,18 @@
       <c r="H301" s="61"/>
       <c r="I301" s="61"/>
     </row>
-    <row r="302" spans="1:9">
+    <row r="302" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A302" s="9" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B302" s="11" t="s">
-        <v>937</v>
+        <v>959</v>
       </c>
       <c r="C302" s="11" t="s">
-        <v>938</v>
+        <v>960</v>
       </c>
       <c r="D302" s="11" t="s">
-        <v>939</v>
+        <v>870</v>
       </c>
       <c r="E302" s="11">
         <v>150</v>
@@ -11528,22 +11596,22 @@
         <v>215</v>
       </c>
       <c r="H302" s="11">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="I302" s="61"/>
     </row>
-    <row r="303" spans="1:9">
+    <row r="303" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A303" s="9" t="s">
+        <v>653</v>
+      </c>
+      <c r="B303" s="10" t="s">
         <v>654</v>
       </c>
-      <c r="B303" s="10" t="s">
+      <c r="C303" s="10" t="s">
         <v>655</v>
       </c>
-      <c r="C303" s="10" t="s">
-        <v>656</v>
-      </c>
       <c r="D303" s="10" t="s">
-        <v>939</v>
+        <v>870</v>
       </c>
       <c r="E303" s="11">
         <v>140</v>
@@ -11555,22 +11623,22 @@
         <v>215</v>
       </c>
       <c r="H303" s="10">
-        <v>4.0999999999999996</v>
+        <v>4.2</v>
       </c>
       <c r="I303" s="61"/>
     </row>
-    <row r="304" spans="1:9">
+    <row r="304" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A304" s="9" t="s">
+        <v>656</v>
+      </c>
+      <c r="B304" s="64" t="s">
         <v>657</v>
       </c>
-      <c r="B304" s="64" t="s">
+      <c r="C304" s="64" t="s">
+        <v>961</v>
+      </c>
+      <c r="D304" s="64" t="s">
         <v>658</v>
-      </c>
-      <c r="C304" s="64" t="s">
-        <v>940</v>
-      </c>
-      <c r="D304" s="64" t="s">
-        <v>659</v>
       </c>
       <c r="E304" s="64">
         <v>90</v>
@@ -11582,24 +11650,24 @@
         <v>218</v>
       </c>
       <c r="H304" s="64">
-        <v>4.4000000000000004</v>
+        <v>4.5</v>
       </c>
       <c r="I304" s="37" t="s">
-        <v>941</v>
-      </c>
-    </row>
-    <row r="305" spans="1:9">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="305" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A305" s="9" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B305" s="36" t="s">
-        <v>942</v>
+        <v>872</v>
       </c>
       <c r="C305" s="36" t="s">
-        <v>943</v>
+        <v>873</v>
       </c>
       <c r="D305" s="18" t="s">
-        <v>944</v>
+        <v>962</v>
       </c>
       <c r="E305" s="36">
         <v>215</v>
@@ -11615,9 +11683,9 @@
       </c>
       <c r="I305" s="61"/>
     </row>
-    <row r="306" spans="1:9">
+    <row r="306" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A306" s="9" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B306" s="36"/>
       <c r="C306" s="36"/>
@@ -11628,9 +11696,9 @@
       <c r="H306" s="61"/>
       <c r="I306" s="61"/>
     </row>
-    <row r="307" spans="1:9">
+    <row r="307" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A307" s="9" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B307" s="36"/>
       <c r="C307" s="36"/>
@@ -11641,9 +11709,9 @@
       <c r="H307" s="61"/>
       <c r="I307" s="61"/>
     </row>
-    <row r="308" spans="1:9">
+    <row r="308" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A308" s="9" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B308" s="36"/>
       <c r="C308" s="36"/>
@@ -11654,9 +11722,9 @@
       <c r="H308" s="61"/>
       <c r="I308" s="61"/>
     </row>
-    <row r="309" spans="1:9">
+    <row r="309" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A309" s="9" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B309" s="36"/>
       <c r="C309" s="36"/>
@@ -11667,9 +11735,9 @@
       <c r="H309" s="61"/>
       <c r="I309" s="61"/>
     </row>
-    <row r="310" spans="1:9">
+    <row r="310" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A310" s="9" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B310" s="36"/>
       <c r="C310" s="36"/>
@@ -11680,18 +11748,18 @@
       <c r="H310" s="61"/>
       <c r="I310" s="61"/>
     </row>
-    <row r="311" spans="1:9">
+    <row r="311" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A311" s="9" t="s">
+        <v>665</v>
+      </c>
+      <c r="B311" s="35" t="s">
         <v>666</v>
       </c>
-      <c r="B311" s="35" t="s">
+      <c r="C311" s="35" t="s">
+        <v>963</v>
+      </c>
+      <c r="D311" s="35" t="s">
         <v>667</v>
-      </c>
-      <c r="C311" s="35" t="s">
-        <v>945</v>
-      </c>
-      <c r="D311" s="35" t="s">
-        <v>668</v>
       </c>
       <c r="E311" s="35">
         <v>85</v>
@@ -11707,18 +11775,18 @@
       </c>
       <c r="I311" s="61"/>
     </row>
-    <row r="312" spans="1:9">
+    <row r="312" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A312" s="9" t="s">
+        <v>668</v>
+      </c>
+      <c r="B312" s="10" t="s">
         <v>669</v>
       </c>
-      <c r="B312" s="10" t="s">
+      <c r="C312" s="10" t="s">
         <v>670</v>
       </c>
-      <c r="C312" s="10" t="s">
+      <c r="D312" s="10" t="s">
         <v>671</v>
-      </c>
-      <c r="D312" s="10" t="s">
-        <v>672</v>
       </c>
       <c r="E312" s="10">
         <v>73</v>
@@ -11734,9 +11802,9 @@
       </c>
       <c r="I312" s="61"/>
     </row>
-    <row r="313" spans="1:9">
+    <row r="313" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A313" s="9" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B313" s="36"/>
       <c r="C313" s="36"/>
@@ -11747,9 +11815,9 @@
       <c r="H313" s="61"/>
       <c r="I313" s="61"/>
     </row>
-    <row r="314" spans="1:9">
+    <row r="314" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A314" s="9" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B314" s="36"/>
       <c r="C314" s="36"/>
@@ -11760,18 +11828,18 @@
       <c r="H314" s="61"/>
       <c r="I314" s="61"/>
     </row>
-    <row r="315" spans="1:9">
+    <row r="315" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A315" s="9" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B315" s="36" t="s">
-        <v>946</v>
+        <v>964</v>
       </c>
       <c r="C315" s="36" t="s">
-        <v>851</v>
+        <v>965</v>
       </c>
       <c r="D315" s="11" t="s">
-        <v>947</v>
+        <v>966</v>
       </c>
       <c r="E315" s="36">
         <v>116</v>
@@ -11786,21 +11854,21 @@
         <v>5</v>
       </c>
       <c r="I315" s="61" t="s">
-        <v>948</v>
-      </c>
-    </row>
-    <row r="316" spans="1:9">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="316" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A316" s="9" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B316" s="36" t="s">
-        <v>949</v>
+        <v>968</v>
       </c>
       <c r="C316" s="36" t="s">
-        <v>950</v>
+        <v>969</v>
       </c>
       <c r="D316" s="11" t="s">
-        <v>951</v>
+        <v>874</v>
       </c>
       <c r="E316" s="36">
         <v>160</v>
@@ -11815,21 +11883,21 @@
         <v>5.2</v>
       </c>
       <c r="I316" s="61" t="s">
-        <v>952</v>
-      </c>
-    </row>
-    <row r="317" spans="1:9">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="317" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A317" s="9" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B317" s="11" t="s">
-        <v>953</v>
+        <v>971</v>
       </c>
       <c r="C317" s="11" t="s">
-        <v>954</v>
+        <v>876</v>
       </c>
       <c r="D317" s="11" t="s">
-        <v>955</v>
+        <v>877</v>
       </c>
       <c r="E317" s="11">
         <v>110</v>
@@ -11844,21 +11912,21 @@
         <v>3.6</v>
       </c>
       <c r="I317" s="11" t="s">
-        <v>956</v>
-      </c>
-    </row>
-    <row r="318" spans="1:9">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="318" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A318" s="9" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B318" s="11" t="s">
-        <v>953</v>
+        <v>875</v>
       </c>
       <c r="C318" s="11" t="s">
-        <v>957</v>
+        <v>878</v>
       </c>
       <c r="D318" s="11" t="s">
-        <v>955</v>
+        <v>877</v>
       </c>
       <c r="E318" s="11">
         <v>110</v>
@@ -11874,18 +11942,18 @@
       </c>
       <c r="I318" s="11"/>
     </row>
-    <row r="319" spans="1:9">
+    <row r="319" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A319" s="9" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B319" s="18" t="s">
-        <v>958</v>
+        <v>879</v>
       </c>
       <c r="C319" s="18" t="s">
-        <v>930</v>
+        <v>865</v>
       </c>
       <c r="D319" s="18" t="s">
-        <v>959</v>
+        <v>880</v>
       </c>
       <c r="E319" s="18">
         <v>185</v>
@@ -11897,24 +11965,24 @@
         <v>225</v>
       </c>
       <c r="H319" s="18">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I319" s="11" t="s">
-        <v>960</v>
-      </c>
-    </row>
-    <row r="320" spans="1:9">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="320" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A320" s="9" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B320" s="18" t="s">
-        <v>961</v>
+        <v>974</v>
       </c>
       <c r="C320" s="18" t="s">
-        <v>962</v>
+        <v>881</v>
       </c>
       <c r="D320" s="18" t="s">
-        <v>963</v>
+        <v>975</v>
       </c>
       <c r="E320" s="18">
         <v>182</v>
@@ -11926,24 +11994,24 @@
         <v>220</v>
       </c>
       <c r="H320" s="18">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="I320" s="11" t="s">
-        <v>932</v>
-      </c>
-    </row>
-    <row r="321" spans="1:9">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="321" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A321" s="9" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B321" s="18" t="s">
-        <v>964</v>
+        <v>882</v>
       </c>
       <c r="C321" s="18" t="s">
-        <v>965</v>
+        <v>976</v>
       </c>
       <c r="D321" s="18" t="s">
-        <v>966</v>
+        <v>977</v>
       </c>
       <c r="E321" s="18">
         <v>138</v>
@@ -11955,24 +12023,24 @@
         <v>220</v>
       </c>
       <c r="H321" s="18">
-        <v>4.4000000000000004</v>
+        <v>4.5</v>
       </c>
       <c r="I321" s="11" t="s">
-        <v>967</v>
-      </c>
-    </row>
-    <row r="322" spans="1:9">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="322" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A322" s="9" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B322" s="18" t="s">
-        <v>968</v>
+        <v>883</v>
       </c>
       <c r="C322" s="18" t="s">
-        <v>969</v>
+        <v>884</v>
       </c>
       <c r="D322" s="18" t="s">
-        <v>959</v>
+        <v>880</v>
       </c>
       <c r="E322" s="18">
         <v>225</v>
@@ -11987,21 +12055,21 @@
         <v>6.2</v>
       </c>
       <c r="I322" s="11" t="s">
-        <v>970</v>
-      </c>
-    </row>
-    <row r="323" spans="1:9">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="323" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A323" s="9" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B323" s="18" t="s">
-        <v>971</v>
+        <v>885</v>
       </c>
       <c r="C323" s="18" t="s">
-        <v>972</v>
+        <v>980</v>
       </c>
       <c r="D323" s="18" t="s">
-        <v>966</v>
+        <v>981</v>
       </c>
       <c r="E323" s="18">
         <v>150</v>
@@ -12013,24 +12081,24 @@
         <v>220</v>
       </c>
       <c r="H323" s="18">
-        <v>4.5999999999999996</v>
+        <v>4.7</v>
       </c>
       <c r="I323" s="11" t="s">
-        <v>973</v>
-      </c>
-    </row>
-    <row r="324" spans="1:9">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="324" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A324" s="9" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B324" s="18" t="s">
-        <v>974</v>
+        <v>982</v>
       </c>
       <c r="C324" s="18" t="s">
-        <v>975</v>
+        <v>887</v>
       </c>
       <c r="D324" s="18" t="s">
-        <v>959</v>
+        <v>880</v>
       </c>
       <c r="E324" s="18">
         <v>220</v>
@@ -12042,37 +12110,53 @@
         <v>218</v>
       </c>
       <c r="H324" s="18">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="I324" s="11" t="s">
-        <v>970</v>
-      </c>
-    </row>
-    <row r="325" spans="1:9">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="325" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A325" s="9" t="s">
-        <v>685</v>
-      </c>
-      <c r="B325" s="36"/>
-      <c r="C325" s="36"/>
-      <c r="D325" s="36"/>
-      <c r="E325" s="36"/>
-      <c r="F325" s="36"/>
-      <c r="G325" s="36"/>
-      <c r="H325" s="61"/>
-      <c r="I325" s="61"/>
-    </row>
-    <row r="326" spans="1:9">
+        <v>684</v>
+      </c>
+      <c r="B325" s="18" t="s">
+        <v>983</v>
+      </c>
+      <c r="C325" s="18" t="s">
+        <v>984</v>
+      </c>
+      <c r="D325" s="18" t="s">
+        <v>985</v>
+      </c>
+      <c r="E325" s="18">
+        <v>185</v>
+      </c>
+      <c r="F325" s="31">
+        <v>270</v>
+      </c>
+      <c r="G325" s="32">
+        <v>225</v>
+      </c>
+      <c r="H325" s="18">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="I325" s="11" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="326" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A326" s="9" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B326" s="36" t="s">
-        <v>976</v>
+        <v>986</v>
       </c>
       <c r="C326" s="36" t="s">
-        <v>977</v>
+        <v>987</v>
       </c>
       <c r="D326" s="36" t="s">
-        <v>978</v>
+        <v>988</v>
       </c>
       <c r="E326" s="36">
         <v>145</v>
@@ -12082,28 +12166,42 @@
         <v>220</v>
       </c>
       <c r="H326" s="61">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="I326" s="61" t="s">
-        <v>979</v>
-      </c>
-    </row>
-    <row r="327" spans="1:9">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="327" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A327" s="9" t="s">
+        <v>700</v>
+      </c>
+      <c r="B327" s="36" t="s">
+        <v>990</v>
+      </c>
+      <c r="C327" s="36" t="s">
+        <v>991</v>
+      </c>
+      <c r="D327" s="36" t="s">
+        <v>992</v>
+      </c>
+      <c r="E327" s="36">
+        <v>150</v>
+      </c>
+      <c r="F327" s="36">
+        <v>225</v>
+      </c>
+      <c r="G327" s="36">
+        <v>208</v>
+      </c>
+      <c r="H327" s="61">
+        <v>5</v>
+      </c>
+      <c r="I327" s="61"/>
+    </row>
+    <row r="328" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A328" s="9" t="s">
         <v>701</v>
-      </c>
-      <c r="B327" s="36"/>
-      <c r="C327" s="36"/>
-      <c r="D327" s="36"/>
-      <c r="E327" s="36"/>
-      <c r="F327" s="36"/>
-      <c r="G327" s="36"/>
-      <c r="H327" s="61"/>
-      <c r="I327" s="61"/>
-    </row>
-    <row r="328" spans="1:9">
-      <c r="A328" s="9" t="s">
-        <v>702</v>
       </c>
       <c r="B328" s="36"/>
       <c r="C328" s="36"/>
@@ -12114,9 +12212,9 @@
       <c r="H328" s="61"/>
       <c r="I328" s="61"/>
     </row>
-    <row r="329" spans="1:9">
+    <row r="329" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A329" s="9" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B329" s="36"/>
       <c r="C329" s="36"/>
@@ -12127,9 +12225,9 @@
       <c r="H329" s="61"/>
       <c r="I329" s="61"/>
     </row>
-    <row r="330" spans="1:9">
+    <row r="330" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A330" s="9" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B330" s="36"/>
       <c r="C330" s="36"/>
@@ -12140,9 +12238,9 @@
       <c r="H330" s="61"/>
       <c r="I330" s="61"/>
     </row>
-    <row r="331" spans="1:9">
+    <row r="331" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A331" s="9" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B331" s="36"/>
       <c r="C331" s="36"/>
@@ -12153,9 +12251,9 @@
       <c r="H331" s="61"/>
       <c r="I331" s="61"/>
     </row>
-    <row r="332" spans="1:9">
+    <row r="332" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A332" s="9" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B332" s="36"/>
       <c r="C332" s="36"/>
@@ -12166,9 +12264,9 @@
       <c r="H332" s="61"/>
       <c r="I332" s="61"/>
     </row>
-    <row r="333" spans="1:9">
+    <row r="333" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A333" s="9" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B333" s="36"/>
       <c r="C333" s="36"/>
@@ -12179,9 +12277,9 @@
       <c r="H333" s="61"/>
       <c r="I333" s="61"/>
     </row>
-    <row r="334" spans="1:9">
+    <row r="334" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A334" s="9" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B334" s="36"/>
       <c r="C334" s="36"/>
@@ -12192,9 +12290,9 @@
       <c r="H334" s="61"/>
       <c r="I334" s="61"/>
     </row>
-    <row r="335" spans="1:9">
+    <row r="335" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A335" s="9" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B335" s="36"/>
       <c r="C335" s="36"/>
@@ -12205,9 +12303,9 @@
       <c r="H335" s="61"/>
       <c r="I335" s="61"/>
     </row>
-    <row r="336" spans="1:9">
+    <row r="336" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A336" s="9" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B336" s="36"/>
       <c r="C336" s="36"/>
@@ -12218,9 +12316,9 @@
       <c r="H336" s="61"/>
       <c r="I336" s="61"/>
     </row>
-    <row r="337" spans="1:9">
+    <row r="337" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A337" s="9" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B337" s="36"/>
       <c r="C337" s="36"/>
@@ -12231,9 +12329,9 @@
       <c r="H337" s="61"/>
       <c r="I337" s="61"/>
     </row>
-    <row r="338" spans="1:9">
+    <row r="338" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A338" s="9" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B338" s="36"/>
       <c r="C338" s="36"/>
@@ -12244,9 +12342,9 @@
       <c r="H338" s="61"/>
       <c r="I338" s="61"/>
     </row>
-    <row r="339" spans="1:9">
+    <row r="339" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A339" s="9" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B339" s="36"/>
       <c r="C339" s="36"/>
@@ -12257,9 +12355,9 @@
       <c r="H339" s="61"/>
       <c r="I339" s="61"/>
     </row>
-    <row r="340" spans="1:9">
+    <row r="340" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A340" s="9" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B340" s="36"/>
       <c r="C340" s="36"/>
@@ -12270,9 +12368,9 @@
       <c r="H340" s="61"/>
       <c r="I340" s="61"/>
     </row>
-    <row r="341" spans="1:9">
+    <row r="341" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A341" s="9" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B341" s="36"/>
       <c r="C341" s="36"/>
@@ -12283,9 +12381,9 @@
       <c r="H341" s="61"/>
       <c r="I341" s="61"/>
     </row>
-    <row r="342" spans="1:9">
+    <row r="342" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A342" s="9" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B342" s="36"/>
       <c r="C342" s="36"/>
@@ -12296,9 +12394,9 @@
       <c r="H342" s="61"/>
       <c r="I342" s="61"/>
     </row>
-    <row r="343" spans="1:9">
+    <row r="343" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A343" s="9" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B343" s="36"/>
       <c r="C343" s="36"/>
@@ -12309,9 +12407,9 @@
       <c r="H343" s="61"/>
       <c r="I343" s="61"/>
     </row>
-    <row r="344" spans="1:9">
+    <row r="344" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A344" s="9" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B344" s="36"/>
       <c r="C344" s="36"/>
@@ -12322,9 +12420,9 @@
       <c r="H344" s="61"/>
       <c r="I344" s="61"/>
     </row>
-    <row r="345" spans="1:9">
+    <row r="345" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A345" s="9" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B345" s="36"/>
       <c r="C345" s="36"/>
@@ -12335,9 +12433,9 @@
       <c r="H345" s="61"/>
       <c r="I345" s="61"/>
     </row>
-    <row r="346" spans="1:9">
+    <row r="346" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A346" s="9" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B346" s="36"/>
       <c r="C346" s="36"/>
@@ -12348,9 +12446,9 @@
       <c r="H346" s="61"/>
       <c r="I346" s="61"/>
     </row>
-    <row r="347" spans="1:9">
+    <row r="347" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A347" s="9" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B347" s="36"/>
       <c r="C347" s="36"/>
@@ -12361,9 +12459,9 @@
       <c r="H347" s="61"/>
       <c r="I347" s="61"/>
     </row>
-    <row r="348" spans="1:9">
+    <row r="348" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A348" s="9" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B348" s="36"/>
       <c r="C348" s="36"/>
@@ -12374,9 +12472,9 @@
       <c r="H348" s="61"/>
       <c r="I348" s="61"/>
     </row>
-    <row r="349" spans="1:9">
+    <row r="349" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A349" s="9" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B349" s="36"/>
       <c r="C349" s="36"/>
@@ -12387,9 +12485,9 @@
       <c r="H349" s="61"/>
       <c r="I349" s="61"/>
     </row>
-    <row r="350" spans="1:9">
+    <row r="350" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A350" s="9" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B350" s="36"/>
       <c r="C350" s="36"/>
@@ -12400,9 +12498,9 @@
       <c r="H350" s="61"/>
       <c r="I350" s="61"/>
     </row>
-    <row r="351" spans="1:9">
+    <row r="351" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A351" s="9" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B351" s="36"/>
       <c r="C351" s="36"/>
@@ -12413,9 +12511,9 @@
       <c r="H351" s="61"/>
       <c r="I351" s="61"/>
     </row>
-    <row r="352" spans="1:9">
+    <row r="352" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A352" s="9" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B352" s="36"/>
       <c r="C352" s="36"/>
@@ -12426,9 +12524,9 @@
       <c r="H352" s="61"/>
       <c r="I352" s="61"/>
     </row>
-    <row r="353" spans="1:9">
+    <row r="353" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A353" s="9" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B353" s="36"/>
       <c r="C353" s="36"/>
@@ -12439,9 +12537,9 @@
       <c r="H353" s="61"/>
       <c r="I353" s="61"/>
     </row>
-    <row r="354" spans="1:9">
+    <row r="354" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A354" s="9" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B354" s="36"/>
       <c r="C354" s="36"/>
@@ -12452,9 +12550,9 @@
       <c r="H354" s="61"/>
       <c r="I354" s="61"/>
     </row>
-    <row r="355" spans="1:9">
+    <row r="355" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A355" s="9" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B355" s="36"/>
       <c r="C355" s="36"/>
@@ -12465,9 +12563,9 @@
       <c r="H355" s="61"/>
       <c r="I355" s="61"/>
     </row>
-    <row r="356" spans="1:9">
+    <row r="356" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A356" s="9" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B356" s="36"/>
       <c r="C356" s="36"/>
@@ -12478,9 +12576,9 @@
       <c r="H356" s="61"/>
       <c r="I356" s="61"/>
     </row>
-    <row r="357" spans="1:9">
+    <row r="357" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A357" s="9" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B357" s="36"/>
       <c r="C357" s="36"/>
@@ -12491,9 +12589,9 @@
       <c r="H357" s="61"/>
       <c r="I357" s="61"/>
     </row>
-    <row r="358" spans="1:9">
+    <row r="358" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A358" s="9" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B358" s="36"/>
       <c r="C358" s="36"/>
@@ -12504,9 +12602,9 @@
       <c r="H358" s="61"/>
       <c r="I358" s="61"/>
     </row>
-    <row r="359" spans="1:9">
+    <row r="359" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A359" s="9" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B359" s="36"/>
       <c r="C359" s="36"/>
@@ -12517,9 +12615,9 @@
       <c r="H359" s="61"/>
       <c r="I359" s="61"/>
     </row>
-    <row r="360" spans="1:9">
+    <row r="360" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A360" s="9" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B360" s="36"/>
       <c r="C360" s="36"/>
@@ -12530,9 +12628,9 @@
       <c r="H360" s="61"/>
       <c r="I360" s="61"/>
     </row>
-    <row r="361" spans="1:9">
+    <row r="361" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A361" s="9" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B361" s="36"/>
       <c r="C361" s="36"/>
@@ -12543,9 +12641,9 @@
       <c r="H361" s="61"/>
       <c r="I361" s="61"/>
     </row>
-    <row r="362" spans="1:9">
+    <row r="362" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A362" s="9" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B362" s="36"/>
       <c r="C362" s="36"/>
@@ -12556,9 +12654,9 @@
       <c r="H362" s="61"/>
       <c r="I362" s="61"/>
     </row>
-    <row r="363" spans="1:9">
+    <row r="363" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A363" s="9" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B363" s="36"/>
       <c r="C363" s="36"/>
@@ -12569,9 +12667,9 @@
       <c r="H363" s="61"/>
       <c r="I363" s="61"/>
     </row>
-    <row r="364" spans="1:9">
+    <row r="364" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A364" s="9" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="B364" s="36"/>
       <c r="C364" s="36"/>
@@ -12582,9 +12680,9 @@
       <c r="H364" s="61"/>
       <c r="I364" s="61"/>
     </row>
-    <row r="365" spans="1:9">
+    <row r="365" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A365" s="9" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="B365" s="36"/>
       <c r="C365" s="36"/>
@@ -12595,9 +12693,9 @@
       <c r="H365" s="61"/>
       <c r="I365" s="61"/>
     </row>
-    <row r="366" spans="1:9">
+    <row r="366" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A366" s="9" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="B366" s="36"/>
       <c r="C366" s="36"/>
@@ -12608,9 +12706,9 @@
       <c r="H366" s="61"/>
       <c r="I366" s="61"/>
     </row>
-    <row r="367" spans="1:9">
+    <row r="367" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A367" s="9" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B367" s="36"/>
       <c r="C367" s="36"/>
@@ -12621,9 +12719,9 @@
       <c r="H367" s="61"/>
       <c r="I367" s="61"/>
     </row>
-    <row r="368" spans="1:9">
+    <row r="368" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A368" s="9" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="B368" s="36"/>
       <c r="C368" s="36"/>
@@ -12634,9 +12732,9 @@
       <c r="H368" s="61"/>
       <c r="I368" s="61"/>
     </row>
-    <row r="369" spans="1:9">
+    <row r="369" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A369" s="9" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="B369" s="36"/>
       <c r="C369" s="36"/>
@@ -12647,9 +12745,9 @@
       <c r="H369" s="61"/>
       <c r="I369" s="61"/>
     </row>
-    <row r="370" spans="1:9">
+    <row r="370" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A370" s="9" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="B370" s="36"/>
       <c r="C370" s="36"/>
@@ -12660,9 +12758,9 @@
       <c r="H370" s="61"/>
       <c r="I370" s="61"/>
     </row>
-    <row r="371" spans="1:9">
+    <row r="371" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A371" s="9" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="B371" s="36"/>
       <c r="C371" s="36"/>
@@ -12673,9 +12771,9 @@
       <c r="H371" s="61"/>
       <c r="I371" s="61"/>
     </row>
-    <row r="372" spans="1:9">
+    <row r="372" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A372" s="9" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="B372" s="36"/>
       <c r="C372" s="36"/>
@@ -12686,9 +12784,9 @@
       <c r="H372" s="61"/>
       <c r="I372" s="61"/>
     </row>
-    <row r="373" spans="1:9">
+    <row r="373" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A373" s="9" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B373" s="36"/>
       <c r="C373" s="36"/>
@@ -12699,9 +12797,9 @@
       <c r="H373" s="61"/>
       <c r="I373" s="61"/>
     </row>
-    <row r="374" spans="1:9">
+    <row r="374" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A374" s="9" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B374" s="36"/>
       <c r="C374" s="36"/>
@@ -12712,9 +12810,9 @@
       <c r="H374" s="61"/>
       <c r="I374" s="61"/>
     </row>
-    <row r="375" spans="1:9">
+    <row r="375" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A375" s="9" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B375" s="36"/>
       <c r="C375" s="36"/>
@@ -12725,9 +12823,9 @@
       <c r="H375" s="61"/>
       <c r="I375" s="61"/>
     </row>
-    <row r="376" spans="1:9">
+    <row r="376" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A376" s="9" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="B376" s="36"/>
       <c r="C376" s="36"/>
@@ -12738,9 +12836,9 @@
       <c r="H376" s="61"/>
       <c r="I376" s="61"/>
     </row>
-    <row r="377" spans="1:9">
+    <row r="377" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A377" s="9" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B377" s="36"/>
       <c r="C377" s="36"/>
@@ -12751,9 +12849,9 @@
       <c r="H377" s="61"/>
       <c r="I377" s="61"/>
     </row>
-    <row r="378" spans="1:9">
+    <row r="378" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A378" s="9" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B378" s="36"/>
       <c r="C378" s="36"/>
@@ -12764,9 +12862,9 @@
       <c r="H378" s="61"/>
       <c r="I378" s="61"/>
     </row>
-    <row r="379" spans="1:9">
+    <row r="379" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A379" s="9" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B379" s="36"/>
       <c r="C379" s="36"/>
@@ -12777,9 +12875,9 @@
       <c r="H379" s="61"/>
       <c r="I379" s="61"/>
     </row>
-    <row r="380" spans="1:9">
+    <row r="380" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A380" s="9" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B380" s="36"/>
       <c r="C380" s="36"/>
@@ -12790,9 +12888,9 @@
       <c r="H380" s="61"/>
       <c r="I380" s="61"/>
     </row>
-    <row r="381" spans="1:9">
+    <row r="381" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A381" s="9" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B381" s="36"/>
       <c r="C381" s="36"/>
@@ -12803,9 +12901,9 @@
       <c r="H381" s="61"/>
       <c r="I381" s="61"/>
     </row>
-    <row r="382" spans="1:9">
+    <row r="382" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A382" s="9" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B382" s="36"/>
       <c r="C382" s="36"/>
@@ -12816,9 +12914,9 @@
       <c r="H382" s="61"/>
       <c r="I382" s="61"/>
     </row>
-    <row r="383" spans="1:9">
+    <row r="383" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A383" s="9" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B383" s="36"/>
       <c r="C383" s="36"/>
@@ -12829,9 +12927,9 @@
       <c r="H383" s="61"/>
       <c r="I383" s="61"/>
     </row>
-    <row r="384" spans="1:9">
+    <row r="384" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A384" s="9" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B384" s="36"/>
       <c r="C384" s="36"/>
@@ -12842,9 +12940,9 @@
       <c r="H384" s="61"/>
       <c r="I384" s="61"/>
     </row>
-    <row r="385" spans="1:9">
+    <row r="385" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A385" s="9" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="B385" s="36"/>
       <c r="C385" s="36"/>
@@ -12855,9 +12953,9 @@
       <c r="H385" s="61"/>
       <c r="I385" s="61"/>
     </row>
-    <row r="386" spans="1:9">
+    <row r="386" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A386" s="9" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="B386" s="36"/>
       <c r="C386" s="36"/>
@@ -12868,9 +12966,9 @@
       <c r="H386" s="61"/>
       <c r="I386" s="61"/>
     </row>
-    <row r="387" spans="1:9">
+    <row r="387" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A387" s="9" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B387" s="36"/>
       <c r="C387" s="36"/>
@@ -12881,9 +12979,9 @@
       <c r="H387" s="61"/>
       <c r="I387" s="61"/>
     </row>
-    <row r="388" spans="1:9">
+    <row r="388" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A388" s="9" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="B388" s="36"/>
       <c r="C388" s="36"/>
@@ -12894,9 +12992,9 @@
       <c r="H388" s="61"/>
       <c r="I388" s="61"/>
     </row>
-    <row r="389" spans="1:9">
+    <row r="389" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A389" s="9" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B389" s="36"/>
       <c r="C389" s="36"/>
@@ -12907,9 +13005,9 @@
       <c r="H389" s="61"/>
       <c r="I389" s="61"/>
     </row>
-    <row r="390" spans="1:9">
+    <row r="390" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A390" s="9" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="B390" s="36"/>
       <c r="C390" s="36"/>
@@ -12920,9 +13018,9 @@
       <c r="H390" s="61"/>
       <c r="I390" s="61"/>
     </row>
-    <row r="391" spans="1:9">
+    <row r="391" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A391" s="9" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B391" s="36"/>
       <c r="C391" s="36"/>
@@ -12933,9 +13031,9 @@
       <c r="H391" s="61"/>
       <c r="I391" s="61"/>
     </row>
-    <row r="392" spans="1:9">
+    <row r="392" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A392" s="9" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="B392" s="36"/>
       <c r="C392" s="36"/>
@@ -12946,9 +13044,9 @@
       <c r="H392" s="61"/>
       <c r="I392" s="61"/>
     </row>
-    <row r="393" spans="1:9">
+    <row r="393" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A393" s="9" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="B393" s="36"/>
       <c r="C393" s="36"/>
@@ -12967,10 +13065,10 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12979,10 +13077,10 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
